--- a/fivem_case_analyzer/圣安地列斯州_案件罪名分析器.xlsx
+++ b/fivem_case_analyzer/圣安地列斯州_案件罪名分析器.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,6 +53,11 @@
       <i val="1"/>
       <color rgb="00595959"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -129,12 +134,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -170,6 +175,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -557,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -567,7 +575,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>圣安地列斯州 · 案件罪名分析器 — 使用说明</t>
+          <t>圣安地列斯州 · 案件罪名分析器 — 使用说明（原创制作：袁尘）</t>
         </is>
       </c>
     </row>
@@ -722,6 +730,18 @@
       <c r="B24" s="3" t="inlineStr">
         <is>
           <t>本工具仅为辅助参考，最终定罪与量刑以服务器法官 / 司法部裁量为准。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>原创制作</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>袁尘</t>
         </is>
       </c>
     </row>
@@ -739,7 +759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -928,8 +948,15 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>原创制作：袁尘</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
@@ -938,6 +965,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1029,3173 +1057,3173 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>二·人身</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>威胁罪</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="18" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D2" s="15" t="n">
+      <c r="D2" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="E2" s="15" t="n">
+      <c r="E2" s="16" t="n">
         <v>8000</v>
       </c>
-      <c r="F2" s="15" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>口头/书面/网络威胁他人或其亲友</t>
         </is>
       </c>
-      <c r="G2" s="15">
+      <c r="G2" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B2)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H2" s="15">
+      <c r="H2" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B2)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I2" s="15">
+      <c r="I2" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B2)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J2" s="15">
+      <c r="J2" s="16">
         <f>IF($G2=1,$B2,"")</f>
         <v/>
       </c>
-      <c r="K2" s="15">
+      <c r="K2" s="16">
         <f>IF($H2=1,$B2,"")</f>
         <v/>
       </c>
-      <c r="L2" s="15">
+      <c r="L2" s="16">
         <f>IF($I2=1,$B2,"")</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>二·人身</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>持有危险武器人身攻击罪</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D3" s="15" t="n">
+      <c r="D3" s="16" t="n">
         <v>48</v>
       </c>
-      <c r="E3" s="15" t="n">
+      <c r="E3" s="16" t="n">
         <v>20000</v>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>用武器/工具威胁或伤害他人</t>
         </is>
       </c>
-      <c r="G3" s="15">
+      <c r="G3" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B3)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H3" s="15">
+      <c r="H3" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B3)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I3" s="15">
+      <c r="I3" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B3)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J3" s="15">
+      <c r="J3" s="16">
         <f>IF($G3=1,IF($J2="",$B3,$J2&amp;"、"&amp;$B3),$J2)</f>
         <v/>
       </c>
-      <c r="K3" s="15">
+      <c r="K3" s="16">
         <f>IF($H3=1,IF($K2="",$B3,$K2&amp;"、"&amp;$B3),$K2)</f>
         <v/>
       </c>
-      <c r="L3" s="15">
+      <c r="L3" s="16">
         <f>IF($I3=1,IF($L2="",$B3,$L2&amp;"、"&amp;$B3),$L2)</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>二·人身</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>一级谋杀罪</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="16" t="n">
         <v>60</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="16" t="n">
         <v>30000</v>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>预谋故意杀人 / 重罪过程中杀人</t>
         </is>
       </c>
-      <c r="G4" s="15">
+      <c r="G4" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B4)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B4)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I4" s="15">
+      <c r="I4" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B4)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J4" s="15">
+      <c r="J4" s="16">
         <f>IF($G4=1,IF($J3="",$B4,$J3&amp;"、"&amp;$B4),$J3)</f>
         <v/>
       </c>
-      <c r="K4" s="15">
+      <c r="K4" s="16">
         <f>IF($H4=1,IF($K3="",$B4,$K3&amp;"、"&amp;$B4),$K3)</f>
         <v/>
       </c>
-      <c r="L4" s="15">
+      <c r="L4" s="16">
         <f>IF($I4=1,IF($L3="",$B4,$L3&amp;"、"&amp;$B4),$L3)</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>二·人身</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>二级谋杀罪</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="16" t="n">
         <v>60</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="16" t="n">
         <v>20000</v>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>非预谋的故意杀人 (3至5年)</t>
         </is>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B5)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B5)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B5)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J5" s="15">
+      <c r="J5" s="16">
         <f>IF($G5=1,IF($J4="",$B5,$J4&amp;"、"&amp;$B5),$J4)</f>
         <v/>
       </c>
-      <c r="K5" s="15">
+      <c r="K5" s="16">
         <f>IF($H5=1,IF($K4="",$B5,$K4&amp;"、"&amp;$B5),$K4)</f>
         <v/>
       </c>
-      <c r="L5" s="15">
+      <c r="L5" s="16">
         <f>IF($I5=1,IF($L4="",$B5,$L4&amp;"、"&amp;$B5),$L4)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>二·人身</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>三级谋杀罪</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="16" t="n">
         <v>60</v>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="E6" s="16" t="n">
         <v>15000</v>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>无意致死/鲁莽过失致死 (3至5年, 不含正当防卫)</t>
         </is>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B6)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B6)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B6)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J6" s="15">
+      <c r="J6" s="16">
         <f>IF($G6=1,IF($J5="",$B6,$J5&amp;"、"&amp;$B6),$J5)</f>
         <v/>
       </c>
-      <c r="K6" s="15">
+      <c r="K6" s="16">
         <f>IF($H6=1,IF($K5="",$B6,$K5&amp;"、"&amp;$B6),$K5)</f>
         <v/>
       </c>
-      <c r="L6" s="15">
+      <c r="L6" s="16">
         <f>IF($I6=1,IF($L5="",$B6,$L5&amp;"、"&amp;$B6),$L5)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>二·人身</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>非法拘禁罪</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="16" t="n">
         <v>36</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="16" t="n">
         <v>15000</v>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>违背意愿约束/扣押/拘禁他人</t>
         </is>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B7)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B7)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B7)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J7" s="15">
+      <c r="J7" s="16">
         <f>IF($G7=1,IF($J6="",$B7,$J6&amp;"、"&amp;$B7),$J6)</f>
         <v/>
       </c>
-      <c r="K7" s="15">
+      <c r="K7" s="16">
         <f>IF($H7=1,IF($K6="",$B7,$K6&amp;"、"&amp;$B7),$K6)</f>
         <v/>
       </c>
-      <c r="L7" s="15">
+      <c r="L7" s="16">
         <f>IF($I7=1,IF($L6="",$B7,$L6&amp;"、"&amp;$B7),$L6)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>二·人身</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>故意袭击罪</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="16" t="n">
         <v>36</v>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="E8" s="16" t="n">
         <v>15000</v>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>蓄意暴力致他人身体受伤</t>
         </is>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B8)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B8)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I8" s="15">
+      <c r="I8" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B8)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J8" s="15">
+      <c r="J8" s="16">
         <f>IF($G8=1,IF($J7="",$B8,$J7&amp;"、"&amp;$B8),$J7)</f>
         <v/>
       </c>
-      <c r="K8" s="15">
+      <c r="K8" s="16">
         <f>IF($H8=1,IF($K7="",$B8,$K7&amp;"、"&amp;$B8),$K7)</f>
         <v/>
       </c>
-      <c r="L8" s="15">
+      <c r="L8" s="16">
         <f>IF($I8=1,IF($L7="",$B8,$L7&amp;"、"&amp;$B8),$L7)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>二·人身</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>绑架罪</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="16" t="n">
         <v>60</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E9" s="16" t="n">
         <v>25000</v>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>侵占/羁押/控制他人意图恐吓</t>
         </is>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B9)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B9)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I9" s="15">
+      <c r="I9" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B9)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J9" s="15">
+      <c r="J9" s="16">
         <f>IF($G9=1,IF($J8="",$B9,$J8&amp;"、"&amp;$B9),$J8)</f>
         <v/>
       </c>
-      <c r="K9" s="15">
+      <c r="K9" s="16">
         <f>IF($H9=1,IF($K8="",$B9,$K8&amp;"、"&amp;$B9),$K8)</f>
         <v/>
       </c>
-      <c r="L9" s="15">
+      <c r="L9" s="16">
         <f>IF($I9=1,IF($L8="",$B9,$L8&amp;"、"&amp;$B9),$L8)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>二·人身</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>亵渎尸体罪</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="E10" s="15" t="n">
+      <c r="E10" s="16" t="n">
         <v>20000</v>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>毁损/处置尸体掩盖犯罪</t>
         </is>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B10)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H10" s="15">
+      <c r="H10" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B10)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I10" s="15">
+      <c r="I10" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B10)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J10" s="15">
+      <c r="J10" s="16">
         <f>IF($G10=1,IF($J9="",$B10,$J9&amp;"、"&amp;$B10),$J9)</f>
         <v/>
       </c>
-      <c r="K10" s="15">
+      <c r="K10" s="16">
         <f>IF($H10=1,IF($K9="",$B10,$K9&amp;"、"&amp;$B10),$K9)</f>
         <v/>
       </c>
-      <c r="L10" s="15">
+      <c r="L10" s="16">
         <f>IF($I10=1,IF($L9="",$B10,$L9&amp;"、"&amp;$B10),$L9)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>二·人身</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>诈骗罪</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="16" t="n">
         <v>60</v>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E11" s="16" t="n">
         <v>5000</v>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>以欺诈欺瞒获取他人财物 (1-5年)</t>
         </is>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B11)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B11)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I11" s="15">
+      <c r="I11" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B11)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J11" s="15">
+      <c r="J11" s="16">
         <f>IF($G11=1,IF($J10="",$B11,$J10&amp;"、"&amp;$B11),$J10)</f>
         <v/>
       </c>
-      <c r="K11" s="15">
+      <c r="K11" s="16">
         <f>IF($H11=1,IF($K10="",$B11,$K10&amp;"、"&amp;$B11),$K10)</f>
         <v/>
       </c>
-      <c r="L11" s="15">
+      <c r="L11" s="16">
         <f>IF($I11=1,IF($L10="",$B11,$L10&amp;"、"&amp;$B11),$L10)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>三·财产</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>非法入侵罪</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="E12" s="15" t="n">
+      <c r="E12" s="16" t="n">
         <v>8000</v>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>被要求离开后仍拒绝离开</t>
         </is>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B12)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H12" s="15">
+      <c r="H12" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B12)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I12" s="15">
+      <c r="I12" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B12)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J12" s="15">
+      <c r="J12" s="16">
         <f>IF($G12=1,IF($J11="",$B12,$J11&amp;"、"&amp;$B12),$J11)</f>
         <v/>
       </c>
-      <c r="K12" s="15">
+      <c r="K12" s="16">
         <f>IF($H12=1,IF($K11="",$B12,$K11&amp;"、"&amp;$B12),$K11)</f>
         <v/>
       </c>
-      <c r="L12" s="15">
+      <c r="L12" s="16">
         <f>IF($I12=1,IF($L11="",$B12,$L11&amp;"、"&amp;$B12),$L11)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>三·财产</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>非法入侵禁区罪</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="16" t="n">
         <v>36</v>
       </c>
-      <c r="E13" s="15" t="n">
+      <c r="E13" s="16" t="n">
         <v>10000</v>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>未经授权进入警局/机场/军事基地等限制区</t>
         </is>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B13)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H13" s="15">
+      <c r="H13" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B13)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I13" s="15">
+      <c r="I13" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B13)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J13" s="15">
+      <c r="J13" s="16">
         <f>IF($G13=1,IF($J12="",$B13,$J12&amp;"、"&amp;$B13),$J12)</f>
         <v/>
       </c>
-      <c r="K13" s="15">
+      <c r="K13" s="16">
         <f>IF($H13=1,IF($K12="",$B13,$K12&amp;"、"&amp;$B13),$K12)</f>
         <v/>
       </c>
-      <c r="L13" s="15">
+      <c r="L13" s="16">
         <f>IF($I13=1,IF($L12="",$B13,$L12&amp;"、"&amp;$B13),$L12)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>三·财产</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>入室盗窃罪</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="D14" s="16" t="n">
         <v>36</v>
       </c>
-      <c r="E14" s="15" t="n">
+      <c r="E14" s="16" t="n">
         <v>25000</v>
       </c>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>擅入住宅/办公室/仓库盗窃, 另需赔偿</t>
         </is>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B14)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H14" s="15">
+      <c r="H14" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B14)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I14" s="15">
+      <c r="I14" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B14)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J14" s="15">
+      <c r="J14" s="16">
         <f>IF($G14=1,IF($J13="",$B14,$J13&amp;"、"&amp;$B14),$J13)</f>
         <v/>
       </c>
-      <c r="K14" s="15">
+      <c r="K14" s="16">
         <f>IF($H14=1,IF($K13="",$B14,$K13&amp;"、"&amp;$B14),$K13)</f>
         <v/>
       </c>
-      <c r="L14" s="15">
+      <c r="L14" s="16">
         <f>IF($I14=1,IF($L13="",$B14,$L13&amp;"、"&amp;$B14),$L13)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>三·财产</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>抢劫罪</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D15" s="15" t="n">
+      <c r="D15" s="16" t="n">
         <v>60</v>
       </c>
-      <c r="E15" s="15" t="n">
+      <c r="E15" s="16" t="n">
         <v>20000</v>
       </c>
-      <c r="F15" s="15" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>以武力/威胁强夺他人财产, 另需赔偿</t>
         </is>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B15)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H15" s="15">
+      <c r="H15" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B15)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I15" s="15">
+      <c r="I15" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B15)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J15" s="15">
+      <c r="J15" s="16">
         <f>IF($G15=1,IF($J14="",$B15,$J14&amp;"、"&amp;$B15),$J14)</f>
         <v/>
       </c>
-      <c r="K15" s="15">
+      <c r="K15" s="16">
         <f>IF($H15=1,IF($K14="",$B15,$K14&amp;"、"&amp;$B15),$K14)</f>
         <v/>
       </c>
-      <c r="L15" s="15">
+      <c r="L15" s="16">
         <f>IF($I15=1,IF($L14="",$B15,$L14&amp;"、"&amp;$B15),$L14)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>三·财产</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>盗窃罪</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D16" s="15" t="n">
+      <c r="D16" s="16" t="n">
         <v>48</v>
       </c>
-      <c r="E16" s="15" t="n">
+      <c r="E16" s="16" t="n">
         <v>20000</v>
       </c>
-      <c r="F16" s="15" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>盗窃/占用他人财物, 另需赔偿</t>
         </is>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B16)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H16" s="15">
+      <c r="H16" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B16)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I16" s="15">
+      <c r="I16" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B16)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J16" s="15">
+      <c r="J16" s="16">
         <f>IF($G16=1,IF($J15="",$B16,$J15&amp;"、"&amp;$B16),$J15)</f>
         <v/>
       </c>
-      <c r="K16" s="15">
+      <c r="K16" s="16">
         <f>IF($H16=1,IF($K15="",$B16,$K15&amp;"、"&amp;$B16),$K15)</f>
         <v/>
       </c>
-      <c r="L16" s="15">
+      <c r="L16" s="16">
         <f>IF($I16=1,IF($L15="",$B16,$L15&amp;"、"&amp;$B16),$L15)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>三·财产</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>盗窃车辆罪</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D17" s="15" t="n">
+      <c r="D17" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="E17" s="15" t="n">
+      <c r="E17" s="16" t="n">
         <v>5000</v>
       </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>默认未造成严重后果(轻罪1年$5000); 严重后果=重罪4年$15000, 均赔偿</t>
         </is>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B17)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H17" s="15">
+      <c r="H17" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B17)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I17" s="15">
+      <c r="I17" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B17)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J17" s="15">
+      <c r="J17" s="16">
         <f>IF($G17=1,IF($J16="",$B17,$J16&amp;"、"&amp;$B17),$J16)</f>
         <v/>
       </c>
-      <c r="K17" s="15">
+      <c r="K17" s="16">
         <f>IF($H17=1,IF($K16="",$B17,$K16&amp;"、"&amp;$B17),$K16)</f>
         <v/>
       </c>
-      <c r="L17" s="15">
+      <c r="L17" s="16">
         <f>IF($I17=1,IF($L16="",$B17,$L16&amp;"、"&amp;$B17),$L16)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>三·财产</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>收受赃物罪</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D18" s="15" t="n">
+      <c r="D18" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="E18" s="15" t="n">
+      <c r="E18" s="16" t="n">
         <v>10000</v>
       </c>
-      <c r="F18" s="15" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>默认赃值&lt;$5000(轻罪2年$10000); ≥$5000=重罪4年$20000</t>
         </is>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B18)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H18" s="15">
+      <c r="H18" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B18)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I18" s="15">
+      <c r="I18" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B18)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J18" s="15">
+      <c r="J18" s="16">
         <f>IF($G18=1,IF($J17="",$B18,$J17&amp;"、"&amp;$B18),$J17)</f>
         <v/>
       </c>
-      <c r="K18" s="15">
+      <c r="K18" s="16">
         <f>IF($H18=1,IF($K17="",$B18,$K17&amp;"、"&amp;$B18),$K17)</f>
         <v/>
       </c>
-      <c r="L18" s="15">
+      <c r="L18" s="16">
         <f>IF($I18=1,IF($L17="",$B18,$L17&amp;"、"&amp;$B18),$L17)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>三·财产</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>敲诈勒索罪</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D19" s="15" t="n">
+      <c r="D19" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="E19" s="15" t="n">
+      <c r="E19" s="16" t="n">
         <v>20000</v>
       </c>
-      <c r="F19" s="15" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>以威胁/恐吓/滥权强迫他人交付财物</t>
         </is>
       </c>
-      <c r="G19" s="15">
+      <c r="G19" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B19)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H19" s="15">
+      <c r="H19" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B19)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I19" s="15">
+      <c r="I19" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B19)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J19" s="15">
+      <c r="J19" s="16">
         <f>IF($G19=1,IF($J18="",$B19,$J18&amp;"、"&amp;$B19),$J18)</f>
         <v/>
       </c>
-      <c r="K19" s="15">
+      <c r="K19" s="16">
         <f>IF($H19=1,IF($K18="",$B19,$K18&amp;"、"&amp;$B19),$K18)</f>
         <v/>
       </c>
-      <c r="L19" s="15">
+      <c r="L19" s="16">
         <f>IF($I19=1,IF($L18="",$B19,$L18&amp;"、"&amp;$B19),$L18)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>三·财产</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>蓄意破坏罪</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C20" s="18" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D20" s="15" t="n">
+      <c r="D20" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="E20" s="15" t="n">
+      <c r="E20" s="16" t="n">
         <v>25000</v>
       </c>
-      <c r="F20" s="15" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>蓄意破坏他人财产/车辆, 另需赔偿</t>
         </is>
       </c>
-      <c r="G20" s="15">
+      <c r="G20" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B20)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H20" s="15">
+      <c r="H20" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B20)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I20" s="15">
+      <c r="I20" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B20)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J20" s="15">
+      <c r="J20" s="16">
         <f>IF($G20=1,IF($J19="",$B20,$J19&amp;"、"&amp;$B20),$J19)</f>
         <v/>
       </c>
-      <c r="K20" s="15">
+      <c r="K20" s="16">
         <f>IF($H20=1,IF($K19="",$B20,$K19&amp;"、"&amp;$B20),$K19)</f>
         <v/>
       </c>
-      <c r="L20" s="15">
+      <c r="L20" s="16">
         <f>IF($I20=1,IF($L19="",$B20,$L19&amp;"、"&amp;$B20),$L19)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>三·财产</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>挪用公款公物罪</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D21" s="15" t="n">
+      <c r="D21" s="16" t="n">
         <v>48</v>
       </c>
-      <c r="E21" s="15" t="n">
+      <c r="E21" s="16" t="n">
         <v>80000</v>
       </c>
-      <c r="F21" s="15" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>擅自挪用受托管理的财物, 另需赔偿</t>
         </is>
       </c>
-      <c r="G21" s="15">
+      <c r="G21" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B21)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H21" s="15">
+      <c r="H21" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B21)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I21" s="15">
+      <c r="I21" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B21)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J21" s="15">
+      <c r="J21" s="16">
         <f>IF($G21=1,IF($J20="",$B21,$J20&amp;"、"&amp;$B21),$J20)</f>
         <v/>
       </c>
-      <c r="K21" s="15">
+      <c r="K21" s="16">
         <f>IF($H21=1,IF($K20="",$B21,$K20&amp;"、"&amp;$B21),$K20)</f>
         <v/>
       </c>
-      <c r="L21" s="15">
+      <c r="L21" s="16">
         <f>IF($I21=1,IF($L20="",$B21,$L20&amp;"、"&amp;$B21),$L20)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>三·财产</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>持有失窃物品罪</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C22" s="18" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D22" s="15" t="n">
+      <c r="D22" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="E22" s="15" t="n">
+      <c r="E22" s="16" t="n">
         <v>2000</v>
       </c>
-      <c r="F22" s="15" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>非法占有他人遗失/失窃财物 (1-2年), 另需赔偿</t>
         </is>
       </c>
-      <c r="G22" s="15">
+      <c r="G22" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B22)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H22" s="15">
+      <c r="H22" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B22)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I22" s="15">
+      <c r="I22" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B22)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J22" s="15">
+      <c r="J22" s="16">
         <f>IF($G22=1,IF($J21="",$B22,$J21&amp;"、"&amp;$B22),$J21)</f>
         <v/>
       </c>
-      <c r="K22" s="15">
+      <c r="K22" s="16">
         <f>IF($H22=1,IF($K21="",$B22,$K21&amp;"、"&amp;$B22),$K21)</f>
         <v/>
       </c>
-      <c r="L22" s="15">
+      <c r="L22" s="16">
         <f>IF($I22=1,IF($L21="",$B22,$L21&amp;"、"&amp;$B22),$L21)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>四·公德</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>在公共场合从事淫秽行为罪</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C23" s="18" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D23" s="15" t="n">
+      <c r="D23" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="E23" s="15" t="n">
+      <c r="E23" s="16" t="n">
         <v>10000</v>
       </c>
-      <c r="F23" s="15" t="inlineStr">
+      <c r="F23" s="16" t="inlineStr">
         <is>
           <t>公开场所性行为/猥亵/招嫖 (1-2年)</t>
         </is>
       </c>
-      <c r="G23" s="15">
+      <c r="G23" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B23)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H23" s="15">
+      <c r="H23" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B23)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I23" s="15">
+      <c r="I23" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B23)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J23" s="15">
+      <c r="J23" s="16">
         <f>IF($G23=1,IF($J22="",$B23,$J22&amp;"、"&amp;$B23),$J22)</f>
         <v/>
       </c>
-      <c r="K23" s="15">
+      <c r="K23" s="16">
         <f>IF($H23=1,IF($K22="",$B23,$K22&amp;"、"&amp;$B23),$K22)</f>
         <v/>
       </c>
-      <c r="L23" s="15">
+      <c r="L23" s="16">
         <f>IF($I23=1,IF($L22="",$B23,$L22&amp;"、"&amp;$B23),$L22)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>四·公德</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>组织卖淫罪</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D24" s="15" t="n">
+      <c r="D24" s="16" t="n">
         <v>36</v>
       </c>
-      <c r="E24" s="15" t="n">
+      <c r="E24" s="16" t="n">
         <v>15000</v>
       </c>
-      <c r="F24" s="15" t="inlineStr">
+      <c r="F24" s="16" t="inlineStr">
         <is>
           <t>支持/介绍/强迫他人卖淫牟利</t>
         </is>
       </c>
-      <c r="G24" s="15">
+      <c r="G24" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B24)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H24" s="15">
+      <c r="H24" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B24)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I24" s="15">
+      <c r="I24" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B24)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J24" s="15">
+      <c r="J24" s="16">
         <f>IF($G24=1,IF($J23="",$B24,$J23&amp;"、"&amp;$B24),$J23)</f>
         <v/>
       </c>
-      <c r="K24" s="15">
+      <c r="K24" s="16">
         <f>IF($H24=1,IF($K23="",$B24,$K23&amp;"、"&amp;$B24),$K23)</f>
         <v/>
       </c>
-      <c r="L24" s="15">
+      <c r="L24" s="16">
         <f>IF($I24=1,IF($L23="",$B24,$L23&amp;"、"&amp;$B24),$L23)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>四·公德</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>卖淫罪</t>
         </is>
       </c>
-      <c r="C25" s="17" t="inlineStr">
+      <c r="C25" s="18" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D25" s="15" t="n">
+      <c r="D25" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="E25" s="15" t="n">
+      <c r="E25" s="16" t="n">
         <v>15000</v>
       </c>
-      <c r="F25" s="15" t="inlineStr">
+      <c r="F25" s="16" t="inlineStr">
         <is>
           <t>以性服务换取财物</t>
         </is>
       </c>
-      <c r="G25" s="15">
+      <c r="G25" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B25)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H25" s="15">
+      <c r="H25" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B25)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I25" s="15">
+      <c r="I25" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B25)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J25" s="15">
+      <c r="J25" s="16">
         <f>IF($G25=1,IF($J24="",$B25,$J24&amp;"、"&amp;$B25),$J24)</f>
         <v/>
       </c>
-      <c r="K25" s="15">
+      <c r="K25" s="16">
         <f>IF($H25=1,IF($K24="",$B25,$K24&amp;"、"&amp;$B25),$K24)</f>
         <v/>
       </c>
-      <c r="L25" s="15">
+      <c r="L25" s="16">
         <f>IF($I25=1,IF($L24="",$B25,$L24&amp;"、"&amp;$B25),$L24)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>四·公德</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>强奸罪</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C26" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D26" s="15" t="n">
+      <c r="D26" s="16" t="n">
         <v>60</v>
       </c>
-      <c r="E26" s="15" t="n">
+      <c r="E26" s="16" t="n">
         <v>30000</v>
       </c>
-      <c r="F26" s="15" t="inlineStr">
+      <c r="F26" s="16" t="inlineStr">
         <is>
           <t>违背意愿强迫性行为 / 与未满18岁者发生关系</t>
         </is>
       </c>
-      <c r="G26" s="15">
+      <c r="G26" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B26)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H26" s="15">
+      <c r="H26" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B26)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I26" s="15">
+      <c r="I26" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B26)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J26" s="15">
+      <c r="J26" s="16">
         <f>IF($G26=1,IF($J25="",$B26,$J25&amp;"、"&amp;$B26),$J25)</f>
         <v/>
       </c>
-      <c r="K26" s="15">
+      <c r="K26" s="16">
         <f>IF($H26=1,IF($K25="",$B26,$K25&amp;"、"&amp;$B26),$K25)</f>
         <v/>
       </c>
-      <c r="L26" s="15">
+      <c r="L26" s="16">
         <f>IF($I26=1,IF($L25="",$B26,$L25&amp;"、"&amp;$B26),$L25)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>四·公德</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>传播淫秽色情罪</t>
         </is>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C27" s="18" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D27" s="15" t="n">
+      <c r="D27" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="E27" s="15" t="n">
+      <c r="E27" s="16" t="n">
         <v>8000</v>
       </c>
-      <c r="F27" s="15" t="inlineStr">
+      <c r="F27" s="16" t="inlineStr">
         <is>
           <t>制作/传播/贩卖淫秽色情内容</t>
         </is>
       </c>
-      <c r="G27" s="15">
+      <c r="G27" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B27)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H27" s="15">
+      <c r="H27" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B27)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I27" s="15">
+      <c r="I27" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B27)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J27" s="15">
+      <c r="J27" s="16">
         <f>IF($G27=1,IF($J26="",$B27,$J26&amp;"、"&amp;$B27),$J26)</f>
         <v/>
       </c>
-      <c r="K27" s="15">
+      <c r="K27" s="16">
         <f>IF($H27=1,IF($K26="",$B27,$K26&amp;"、"&amp;$B27),$K26)</f>
         <v/>
       </c>
-      <c r="L27" s="15">
+      <c r="L27" s="16">
         <f>IF($I27=1,IF($L26="",$B27,$L26&amp;"、"&amp;$B27),$L26)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>四·公德</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>歧视罪</t>
         </is>
       </c>
-      <c r="C28" s="17" t="inlineStr">
+      <c r="C28" s="18" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D28" s="15" t="n">
+      <c r="D28" s="16" t="n">
         <v>36</v>
       </c>
-      <c r="E28" s="15" t="n">
+      <c r="E28" s="16" t="n">
         <v>30000</v>
       </c>
-      <c r="F28" s="15" t="inlineStr">
+      <c r="F28" s="16" t="inlineStr">
         <is>
           <t>因受保护特征贬低/辱骂/歧视他人</t>
         </is>
       </c>
-      <c r="G28" s="15">
+      <c r="G28" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B28)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H28" s="15">
+      <c r="H28" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B28)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I28" s="15">
+      <c r="I28" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B28)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J28" s="15">
+      <c r="J28" s="16">
         <f>IF($G28=1,IF($J27="",$B28,$J27&amp;"、"&amp;$B28),$J27)</f>
         <v/>
       </c>
-      <c r="K28" s="15">
+      <c r="K28" s="16">
         <f>IF($H28=1,IF($K27="",$B28,$K27&amp;"、"&amp;$B28),$K27)</f>
         <v/>
       </c>
-      <c r="L28" s="15">
+      <c r="L28" s="16">
         <f>IF($I28=1,IF($L27="",$B28,$L27&amp;"、"&amp;$B28),$L27)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>四·公德</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>诽谤罪</t>
         </is>
       </c>
-      <c r="C29" s="17" t="inlineStr">
+      <c r="C29" s="18" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D29" s="15" t="n">
+      <c r="D29" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="E29" s="15" t="n">
+      <c r="E29" s="16" t="n">
         <v>15000</v>
       </c>
-      <c r="F29" s="15" t="inlineStr">
+      <c r="F29" s="16" t="inlineStr">
         <is>
           <t>捏造/传播虚假信息损害名誉</t>
         </is>
       </c>
-      <c r="G29" s="15">
+      <c r="G29" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B29)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H29" s="15">
+      <c r="H29" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B29)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I29" s="15">
+      <c r="I29" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B29)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J29" s="15">
+      <c r="J29" s="16">
         <f>IF($G29=1,IF($J28="",$B29,$J28&amp;"、"&amp;$B29),$J28)</f>
         <v/>
       </c>
-      <c r="K29" s="15">
+      <c r="K29" s="16">
         <f>IF($H29=1,IF($K28="",$B29,$K28&amp;"、"&amp;$B29),$K28)</f>
         <v/>
       </c>
-      <c r="L29" s="15">
+      <c r="L29" s="16">
         <f>IF($I29=1,IF($L28="",$B29,$L28&amp;"、"&amp;$B29),$L28)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>行贿罪</t>
         </is>
       </c>
-      <c r="C30" s="18" t="inlineStr">
+      <c r="C30" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D30" s="15" t="n">
+      <c r="D30" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="E30" s="15" t="n">
+      <c r="E30" s="16" t="n">
         <v>20000</v>
       </c>
-      <c r="F30" s="15" t="inlineStr">
+      <c r="F30" s="16" t="inlineStr">
         <is>
           <t>向政府雇员提供财物/利益以影响其职责</t>
         </is>
       </c>
-      <c r="G30" s="15">
+      <c r="G30" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B30)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H30" s="15">
+      <c r="H30" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B30)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I30" s="15">
+      <c r="I30" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B30)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J30" s="15">
+      <c r="J30" s="16">
         <f>IF($G30=1,IF($J29="",$B30,$J29&amp;"、"&amp;$B30),$J29)</f>
         <v/>
       </c>
-      <c r="K30" s="15">
+      <c r="K30" s="16">
         <f>IF($H30=1,IF($K29="",$B30,$K29&amp;"、"&amp;$B30),$K29)</f>
         <v/>
       </c>
-      <c r="L30" s="15">
+      <c r="L30" s="16">
         <f>IF($I30=1,IF($L29="",$B30,$L29&amp;"、"&amp;$B30),$L29)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>妨碍司法罪</t>
         </is>
       </c>
-      <c r="C31" s="18" t="inlineStr">
+      <c r="C31" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D31" s="15" t="n">
+      <c r="D31" s="16" t="n">
         <v>36</v>
       </c>
-      <c r="E31" s="15" t="n">
+      <c r="E31" s="16" t="n">
         <v>15000</v>
       </c>
-      <c r="F31" s="15" t="inlineStr">
+      <c r="F31" s="16" t="inlineStr">
         <is>
           <t>阻碍法律文书签署/分发/执行</t>
         </is>
       </c>
-      <c r="G31" s="15">
+      <c r="G31" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B31)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H31" s="15">
+      <c r="H31" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B31)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I31" s="15">
+      <c r="I31" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B31)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J31" s="15">
+      <c r="J31" s="16">
         <f>IF($G31=1,IF($J30="",$B31,$J30&amp;"、"&amp;$B31),$J30)</f>
         <v/>
       </c>
-      <c r="K31" s="15">
+      <c r="K31" s="16">
         <f>IF($H31=1,IF($K30="",$B31,$K30&amp;"、"&amp;$B31),$K30)</f>
         <v/>
       </c>
-      <c r="L31" s="15">
+      <c r="L31" s="16">
         <f>IF($I31=1,IF($L30="",$B31,$L30&amp;"、"&amp;$B31),$L30)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>拒绝听从执法人员命令与检查罪</t>
         </is>
       </c>
-      <c r="C32" s="17" t="inlineStr">
+      <c r="C32" s="18" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D32" s="15" t="n">
+      <c r="D32" s="16" t="n">
         <v>36</v>
       </c>
-      <c r="E32" s="15" t="n">
+      <c r="E32" s="16" t="n">
         <v>15000</v>
       </c>
-      <c r="F32" s="15" t="inlineStr">
+      <c r="F32" s="16" t="inlineStr">
         <is>
           <t>拒绝执法人员合法命令/检查</t>
         </is>
       </c>
-      <c r="G32" s="15">
+      <c r="G32" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B32)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H32" s="15">
+      <c r="H32" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B32)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I32" s="15">
+      <c r="I32" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B32)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J32" s="15">
+      <c r="J32" s="16">
         <f>IF($G32=1,IF($J31="",$B32,$J31&amp;"、"&amp;$B32),$J31)</f>
         <v/>
       </c>
-      <c r="K32" s="15">
+      <c r="K32" s="16">
         <f>IF($H32=1,IF($K31="",$B32,$K31&amp;"、"&amp;$B32),$K31)</f>
         <v/>
       </c>
-      <c r="L32" s="15">
+      <c r="L32" s="16">
         <f>IF($I32=1,IF($L31="",$B32,$L31&amp;"、"&amp;$B32),$L31)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B33" s="17" t="inlineStr">
         <is>
           <t>拒绝提供身份罪</t>
         </is>
       </c>
-      <c r="C33" s="17" t="inlineStr">
+      <c r="C33" s="18" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D33" s="15" t="n">
+      <c r="D33" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="E33" s="15" t="n">
+      <c r="E33" s="16" t="n">
         <v>10000</v>
       </c>
-      <c r="F33" s="15" t="inlineStr">
+      <c r="F33" s="16" t="inlineStr">
         <is>
           <t>被扣留/逮捕后拒绝提供身份信息</t>
         </is>
       </c>
-      <c r="G33" s="15">
+      <c r="G33" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B33)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H33" s="15">
+      <c r="H33" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B33)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I33" s="15">
+      <c r="I33" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B33)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J33" s="15">
+      <c r="J33" s="16">
         <f>IF($G33=1,IF($J32="",$B33,$J32&amp;"、"&amp;$B33),$J32)</f>
         <v/>
       </c>
-      <c r="K33" s="15">
+      <c r="K33" s="16">
         <f>IF($H33=1,IF($K32="",$B33,$K32&amp;"、"&amp;$B33),$K32)</f>
         <v/>
       </c>
-      <c r="L33" s="15">
+      <c r="L33" s="16">
         <f>IF($I33=1,IF($L32="",$B33,$L32&amp;"、"&amp;$B33),$L32)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B34" s="17" t="inlineStr">
         <is>
           <t>破坏证据罪</t>
         </is>
       </c>
-      <c r="C34" s="17" t="inlineStr">
+      <c r="C34" s="18" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D34" s="15" t="n">
+      <c r="D34" s="16" t="n">
         <v>36</v>
       </c>
-      <c r="E34" s="15" t="n">
+      <c r="E34" s="16" t="n">
         <v>20000</v>
       </c>
-      <c r="F34" s="15" t="inlineStr">
+      <c r="F34" s="16" t="inlineStr">
         <is>
           <t>隐瞒/销毁/篡改/伪造证据</t>
         </is>
       </c>
-      <c r="G34" s="15">
+      <c r="G34" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B34)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H34" s="15">
+      <c r="H34" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B34)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I34" s="15">
+      <c r="I34" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B34)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J34" s="15">
+      <c r="J34" s="16">
         <f>IF($G34=1,IF($J33="",$B34,$J33&amp;"、"&amp;$B34),$J33)</f>
         <v/>
       </c>
-      <c r="K34" s="15">
+      <c r="K34" s="16">
         <f>IF($H34=1,IF($K33="",$B34,$K33&amp;"、"&amp;$B34),$K33)</f>
         <v/>
       </c>
-      <c r="L34" s="15">
+      <c r="L34" s="16">
         <f>IF($I34=1,IF($L33="",$B34,$L33&amp;"、"&amp;$B34),$L33)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B35" s="17" t="inlineStr">
         <is>
           <t>冒充政府雇员罪</t>
         </is>
       </c>
-      <c r="C35" s="18" t="inlineStr">
+      <c r="C35" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D35" s="15" t="n">
+      <c r="D35" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="E35" s="15" t="n">
+      <c r="E35" s="16" t="n">
         <v>15000</v>
       </c>
-      <c r="F35" s="15" t="inlineStr">
+      <c r="F35" s="16" t="inlineStr">
         <is>
           <t>假冒政府雇员身份(穿制服/佩戴徽章等)</t>
         </is>
       </c>
-      <c r="G35" s="15">
+      <c r="G35" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B35)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H35" s="15">
+      <c r="H35" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B35)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I35" s="15">
+      <c r="I35" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B35)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J35" s="15">
+      <c r="J35" s="16">
         <f>IF($G35=1,IF($J34="",$B35,$J34&amp;"、"&amp;$B35),$J34)</f>
         <v/>
       </c>
-      <c r="K35" s="15">
+      <c r="K35" s="16">
         <f>IF($H35=1,IF($K34="",$B35,$K34&amp;"、"&amp;$B35),$K34)</f>
         <v/>
       </c>
-      <c r="L35" s="15">
+      <c r="L35" s="16">
         <f>IF($I35=1,IF($L34="",$B35,$L34&amp;"、"&amp;$B35),$L34)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B36" s="17" t="inlineStr">
         <is>
           <t>虚假逮捕罪</t>
         </is>
       </c>
-      <c r="C36" s="18" t="inlineStr">
+      <c r="C36" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D36" s="15" t="n">
+      <c r="D36" s="16" t="n">
         <v>48</v>
       </c>
-      <c r="E36" s="15" t="n">
+      <c r="E36" s="16" t="n">
         <v>20000</v>
       </c>
-      <c r="F36" s="15" t="inlineStr">
+      <c r="F36" s="16" t="inlineStr">
         <is>
           <t>无法律依据以执法名义扣留/逮捕/没收(仅主管可起诉)</t>
         </is>
       </c>
-      <c r="G36" s="15">
+      <c r="G36" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B36)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H36" s="15">
+      <c r="H36" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B36)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I36" s="15">
+      <c r="I36" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B36)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J36" s="15">
+      <c r="J36" s="16">
         <f>IF($G36=1,IF($J35="",$B36,$J35&amp;"、"&amp;$B36),$J35)</f>
         <v/>
       </c>
-      <c r="K36" s="15">
+      <c r="K36" s="16">
         <f>IF($H36=1,IF($K35="",$B36,$K35&amp;"、"&amp;$B36),$K35)</f>
         <v/>
       </c>
-      <c r="L36" s="15">
+      <c r="L36" s="16">
         <f>IF($I36=1,IF($L35="",$B36,$L35&amp;"、"&amp;$B36),$L35)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B37" s="17" t="inlineStr">
         <is>
           <t>伪证罪</t>
         </is>
       </c>
-      <c r="C37" s="18" t="inlineStr">
+      <c r="C37" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D37" s="15" t="n">
+      <c r="D37" s="16" t="n">
         <v>48</v>
       </c>
-      <c r="E37" s="15" t="n">
+      <c r="E37" s="16" t="n">
         <v>25000</v>
       </c>
-      <c r="F37" s="15" t="inlineStr">
+      <c r="F37" s="16" t="inlineStr">
         <is>
           <t>司法程序中提供虚假证言/信息</t>
         </is>
       </c>
-      <c r="G37" s="15">
+      <c r="G37" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B37)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H37" s="15">
+      <c r="H37" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B37)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I37" s="15">
+      <c r="I37" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B37)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J37" s="15">
+      <c r="J37" s="16">
         <f>IF($G37=1,IF($J36="",$B37,$J36&amp;"、"&amp;$B37),$J36)</f>
         <v/>
       </c>
-      <c r="K37" s="15">
+      <c r="K37" s="16">
         <f>IF($H37=1,IF($K36="",$B37,$K36&amp;"、"&amp;$B37),$K36)</f>
         <v/>
       </c>
-      <c r="L37" s="15">
+      <c r="L37" s="16">
         <f>IF($I37=1,IF($L36="",$B37,$L36&amp;"、"&amp;$B37),$L36)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B38" s="17" t="inlineStr">
         <is>
           <t>冒充律师罪</t>
         </is>
       </c>
-      <c r="C38" s="17" t="inlineStr">
+      <c r="C38" s="18" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D38" s="15" t="n">
+      <c r="D38" s="16" t="n">
         <v>36</v>
       </c>
-      <c r="E38" s="15" t="n">
+      <c r="E38" s="16" t="n">
         <v>15000</v>
       </c>
-      <c r="F38" s="15" t="inlineStr">
+      <c r="F38" s="16" t="inlineStr">
         <is>
           <t>未经认证从事律师业务/假扮律师</t>
         </is>
       </c>
-      <c r="G38" s="15">
+      <c r="G38" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B38)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H38" s="15">
+      <c r="H38" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B38)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I38" s="15">
+      <c r="I38" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B38)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J38" s="15">
+      <c r="J38" s="16">
         <f>IF($G38=1,IF($J37="",$B38,$J37&amp;"、"&amp;$B38),$J37)</f>
         <v/>
       </c>
-      <c r="K38" s="15">
+      <c r="K38" s="16">
         <f>IF($H38=1,IF($K37="",$B38,$K37&amp;"、"&amp;$B38),$K37)</f>
         <v/>
       </c>
-      <c r="L38" s="15">
+      <c r="L38" s="16">
         <f>IF($I38=1,IF($L37="",$B38,$L37&amp;"、"&amp;$B38),$L37)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="B39" s="17" t="inlineStr">
         <is>
           <t>妨碍政府雇员执行公务罪</t>
         </is>
       </c>
-      <c r="C39" s="18" t="inlineStr">
+      <c r="C39" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D39" s="15" t="n">
+      <c r="D39" s="16" t="n">
         <v>36</v>
       </c>
-      <c r="E39" s="15" t="n">
+      <c r="E39" s="16" t="n">
         <v>15000</v>
       </c>
-      <c r="F39" s="15" t="inlineStr">
+      <c r="F39" s="16" t="inlineStr">
         <is>
           <t>抵抗/延误/阻碍执法/消防/急救/司法人员执行职责</t>
         </is>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B39)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H39" s="15">
+      <c r="H39" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B39)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I39" s="15">
+      <c r="I39" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B39)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="16">
         <f>IF($G39=1,IF($J38="",$B39,$J38&amp;"、"&amp;$B39),$J38)</f>
         <v/>
       </c>
-      <c r="K39" s="15">
+      <c r="K39" s="16">
         <f>IF($H39=1,IF($K38="",$B39,$K38&amp;"、"&amp;$B39),$K38)</f>
         <v/>
       </c>
-      <c r="L39" s="15">
+      <c r="L39" s="16">
         <f>IF($I39=1,IF($L38="",$B39,$L38&amp;"、"&amp;$B39),$L38)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="B40" s="17" t="inlineStr">
         <is>
           <t>拒捕罪</t>
         </is>
       </c>
-      <c r="C40" s="18" t="inlineStr">
+      <c r="C40" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D40" s="15" t="n">
+      <c r="D40" s="16" t="n">
         <v>36</v>
       </c>
-      <c r="E40" s="15" t="n">
+      <c r="E40" s="16" t="n">
         <v>15000</v>
       </c>
-      <c r="F40" s="15" t="inlineStr">
+      <c r="F40" s="16" t="inlineStr">
         <is>
           <t>逮捕时以任何方式拒绝/抗拒/逃避逮捕</t>
         </is>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B40)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H40" s="15">
+      <c r="H40" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B40)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I40" s="15">
+      <c r="I40" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B40)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="16">
         <f>IF($G40=1,IF($J39="",$B40,$J39&amp;"、"&amp;$B40),$J39)</f>
         <v/>
       </c>
-      <c r="K40" s="15">
+      <c r="K40" s="16">
         <f>IF($H40=1,IF($K39="",$B40,$K39&amp;"、"&amp;$B40),$K39)</f>
         <v/>
       </c>
-      <c r="L40" s="15">
+      <c r="L40" s="16">
         <f>IF($I40=1,IF($L39="",$B40,$L39&amp;"、"&amp;$B40),$L39)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B41" s="17" t="inlineStr">
         <is>
           <t>逃避羁押罪</t>
         </is>
       </c>
-      <c r="C41" s="18" t="inlineStr">
+      <c r="C41" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D41" s="15" t="n">
+      <c r="D41" s="16" t="n">
         <v>36</v>
       </c>
-      <c r="E41" s="15" t="n">
+      <c r="E41" s="16" t="n">
         <v>10000</v>
       </c>
-      <c r="F41" s="15" t="inlineStr">
+      <c r="F41" s="16" t="inlineStr">
         <is>
           <t>被合法扣留/逮捕后逃脱监护</t>
         </is>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B41)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H41" s="15">
+      <c r="H41" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B41)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B41)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="16">
         <f>IF($G41=1,IF($J40="",$B41,$J40&amp;"、"&amp;$B41),$J40)</f>
         <v/>
       </c>
-      <c r="K41" s="15">
+      <c r="K41" s="16">
         <f>IF($H41=1,IF($K40="",$B41,$K40&amp;"、"&amp;$B41),$K40)</f>
         <v/>
       </c>
-      <c r="L41" s="15">
+      <c r="L41" s="16">
         <f>IF($I41=1,IF($L40="",$B41,$L40&amp;"、"&amp;$B41),$L40)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B42" s="16" t="inlineStr">
+      <c r="B42" s="17" t="inlineStr">
         <is>
           <t>藐视法庭罪</t>
         </is>
       </c>
-      <c r="C42" s="18" t="inlineStr">
+      <c r="C42" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D42" s="15" t="n">
+      <c r="D42" s="16" t="n">
         <v>48</v>
       </c>
-      <c r="E42" s="15" t="n">
+      <c r="E42" s="16" t="n">
         <v>25000</v>
       </c>
-      <c r="F42" s="15" t="inlineStr">
+      <c r="F42" s="16" t="inlineStr">
         <is>
           <t>扰乱法庭秩序/无视法庭命令(须法官当庭宣布)</t>
         </is>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B42)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H42" s="15">
+      <c r="H42" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B42)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B42)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="16">
         <f>IF($G42=1,IF($J41="",$B42,$J41&amp;"、"&amp;$B42),$J41)</f>
         <v/>
       </c>
-      <c r="K42" s="15">
+      <c r="K42" s="16">
         <f>IF($H42=1,IF($K41="",$B42,$K41&amp;"、"&amp;$B42),$K41)</f>
         <v/>
       </c>
-      <c r="L42" s="15">
+      <c r="L42" s="16">
         <f>IF($I42=1,IF($L41="",$B42,$L41&amp;"、"&amp;$B42),$L41)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B43" s="16" t="inlineStr">
+      <c r="B43" s="17" t="inlineStr">
         <is>
           <t>恶意占用公共资源罪</t>
         </is>
       </c>
-      <c r="C43" s="17" t="inlineStr">
+      <c r="C43" s="18" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D43" s="15" t="n">
+      <c r="D43" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="E43" s="15" t="n">
+      <c r="E43" s="16" t="n">
         <v>5000</v>
       </c>
-      <c r="F43" s="15" t="inlineStr">
+      <c r="F43" s="16" t="inlineStr">
         <is>
           <t>非紧急/恶意占用政府紧急热线</t>
         </is>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B43)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H43" s="15">
+      <c r="H43" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B43)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B43)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="16">
         <f>IF($G43=1,IF($J42="",$B43,$J42&amp;"、"&amp;$B43),$J42)</f>
         <v/>
       </c>
-      <c r="K43" s="15">
+      <c r="K43" s="16">
         <f>IF($H43=1,IF($K42="",$B43,$K42&amp;"、"&amp;$B43),$K42)</f>
         <v/>
       </c>
-      <c r="L43" s="15">
+      <c r="L43" s="16">
         <f>IF($I43=1,IF($L42="",$B43,$L42&amp;"、"&amp;$B43),$L42)</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B44" s="16" t="inlineStr">
+      <c r="B44" s="17" t="inlineStr">
         <is>
           <t>未经许可进入封闭紧急区域罪</t>
         </is>
       </c>
-      <c r="C44" s="17" t="inlineStr">
+      <c r="C44" s="18" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D44" s="15" t="n">
+      <c r="D44" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="E44" s="15" t="n">
+      <c r="E44" s="16" t="n">
         <v>15000</v>
       </c>
-      <c r="F44" s="15" t="inlineStr">
+      <c r="F44" s="16" t="inlineStr">
         <is>
           <t>未经授权进入被警戒线封闭的紧急区域</t>
         </is>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B44)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H44" s="15">
+      <c r="H44" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B44)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B44)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="16">
         <f>IF($G44=1,IF($J43="",$B44,$J43&amp;"、"&amp;$B44),$J43)</f>
         <v/>
       </c>
-      <c r="K44" s="15">
+      <c r="K44" s="16">
         <f>IF($H44=1,IF($K43="",$B44,$K43&amp;"、"&amp;$B44),$K43)</f>
         <v/>
       </c>
-      <c r="L44" s="15">
+      <c r="L44" s="16">
         <f>IF($I44=1,IF($L43="",$B44,$L43&amp;"、"&amp;$B44),$L43)</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B45" s="16" t="inlineStr">
+      <c r="B45" s="17" t="inlineStr">
         <is>
           <t>袭警罪</t>
         </is>
       </c>
-      <c r="C45" s="18" t="inlineStr">
+      <c r="C45" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D45" s="15" t="n">
+      <c r="D45" s="16" t="n">
         <v>48</v>
       </c>
-      <c r="E45" s="15" t="n">
+      <c r="E45" s="16" t="n">
         <v>25000</v>
       </c>
-      <c r="F45" s="15" t="inlineStr">
+      <c r="F45" s="16" t="inlineStr">
         <is>
           <t>袭击/伤害警务人员/警车/警犬</t>
         </is>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B45)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H45" s="15">
+      <c r="H45" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B45)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I45" s="15">
+      <c r="I45" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B45)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="16">
         <f>IF($G45=1,IF($J44="",$B45,$J44&amp;"、"&amp;$B45),$J44)</f>
         <v/>
       </c>
-      <c r="K45" s="15">
+      <c r="K45" s="16">
         <f>IF($H45=1,IF($K44="",$B45,$K44&amp;"、"&amp;$B45),$K44)</f>
         <v/>
       </c>
-      <c r="L45" s="15">
+      <c r="L45" s="16">
         <f>IF($I45=1,IF($L44="",$B45,$L44&amp;"、"&amp;$B45),$L44)</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>六·秩序</t>
         </is>
       </c>
-      <c r="B46" s="16" t="inlineStr">
+      <c r="B46" s="17" t="inlineStr">
         <is>
           <t>扰乱治安罪</t>
         </is>
       </c>
-      <c r="C46" s="17" t="inlineStr">
+      <c r="C46" s="18" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D46" s="15" t="n">
+      <c r="D46" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="E46" s="15" t="n">
+      <c r="E46" s="16" t="n">
         <v>5000</v>
       </c>
-      <c r="F46" s="15" t="inlineStr">
+      <c r="F46" s="16" t="inlineStr">
         <is>
           <t>公共场所挑衅/扰乱/冒犯性言语</t>
         </is>
       </c>
-      <c r="G46" s="15">
+      <c r="G46" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B46)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H46" s="15">
+      <c r="H46" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B46)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I46" s="15">
+      <c r="I46" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B46)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J46" s="15">
+      <c r="J46" s="16">
         <f>IF($G46=1,IF($J45="",$B46,$J45&amp;"、"&amp;$B46),$J45)</f>
         <v/>
       </c>
-      <c r="K46" s="15">
+      <c r="K46" s="16">
         <f>IF($H46=1,IF($K45="",$B46,$K45&amp;"、"&amp;$B46),$K45)</f>
         <v/>
       </c>
-      <c r="L46" s="15">
+      <c r="L46" s="16">
         <f>IF($I46=1,IF($L45="",$B46,$L45&amp;"、"&amp;$B46),$L45)</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>六·秩序</t>
         </is>
       </c>
-      <c r="B47" s="16" t="inlineStr">
+      <c r="B47" s="17" t="inlineStr">
         <is>
           <t>非法集会罪</t>
         </is>
       </c>
-      <c r="C47" s="17" t="inlineStr">
+      <c r="C47" s="18" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D47" s="15" t="n">
+      <c r="D47" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="E47" s="15" t="n">
+      <c r="E47" s="16" t="n">
         <v>20000</v>
       </c>
-      <c r="F47" s="15" t="inlineStr">
+      <c r="F47" s="16" t="inlineStr">
         <is>
           <t>两人以上聚集引发骚乱/非法行动</t>
         </is>
       </c>
-      <c r="G47" s="15">
+      <c r="G47" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B47)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H47" s="15">
+      <c r="H47" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B47)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I47" s="15">
+      <c r="I47" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B47)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J47" s="15">
+      <c r="J47" s="16">
         <f>IF($G47=1,IF($J46="",$B47,$J46&amp;"、"&amp;$B47),$J46)</f>
         <v/>
       </c>
-      <c r="K47" s="15">
+      <c r="K47" s="16">
         <f>IF($H47=1,IF($K46="",$B47,$K46&amp;"、"&amp;$B47),$K46)</f>
         <v/>
       </c>
-      <c r="L47" s="15">
+      <c r="L47" s="16">
         <f>IF($I47=1,IF($L46="",$B47,$L46&amp;"、"&amp;$B47),$L46)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>六·秩序</t>
         </is>
       </c>
-      <c r="B48" s="16" t="inlineStr">
+      <c r="B48" s="17" t="inlineStr">
         <is>
           <t>煽动暴乱罪</t>
         </is>
       </c>
-      <c r="C48" s="18" t="inlineStr">
+      <c r="C48" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D48" s="15" t="n">
+      <c r="D48" s="16" t="n">
         <v>48</v>
       </c>
-      <c r="E48" s="15" t="n">
+      <c r="E48" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F48" s="15" t="inlineStr">
+      <c r="F48" s="16" t="inlineStr">
         <is>
           <t>意图引起暴乱/鼓励他人暴力破坏(仅监禁)</t>
         </is>
       </c>
-      <c r="G48" s="15">
+      <c r="G48" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B48)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H48" s="15">
+      <c r="H48" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B48)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I48" s="15">
+      <c r="I48" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B48)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J48" s="15">
+      <c r="J48" s="16">
         <f>IF($G48=1,IF($J47="",$B48,$J47&amp;"、"&amp;$B48),$J47)</f>
         <v/>
       </c>
-      <c r="K48" s="15">
+      <c r="K48" s="16">
         <f>IF($H48=1,IF($K47="",$B48,$K47&amp;"、"&amp;$B48),$K47)</f>
         <v/>
       </c>
-      <c r="L48" s="15">
+      <c r="L48" s="16">
         <f>IF($I48=1,IF($L47="",$B48,$L47&amp;"、"&amp;$B48),$L47)</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="A49" s="16" t="inlineStr">
         <is>
           <t>六·秩序</t>
         </is>
       </c>
-      <c r="B49" s="16" t="inlineStr">
+      <c r="B49" s="17" t="inlineStr">
         <is>
           <t>遮挡面部罪</t>
         </is>
       </c>
-      <c r="C49" s="17" t="inlineStr">
+      <c r="C49" s="18" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D49" s="15" t="n">
+      <c r="D49" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="E49" s="15" t="n">
+      <c r="E49" s="16" t="n">
         <v>5000</v>
       </c>
-      <c r="F49" s="15" t="inlineStr">
+      <c r="F49" s="16" t="inlineStr">
         <is>
           <t>遮面拒揭 / 犯罪过程中遮面(节庆等除外)</t>
         </is>
       </c>
-      <c r="G49" s="15">
+      <c r="G49" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B49)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H49" s="15">
+      <c r="H49" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B49)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I49" s="15">
+      <c r="I49" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B49)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J49" s="15">
+      <c r="J49" s="16">
         <f>IF($G49=1,IF($J48="",$B49,$J48&amp;"、"&amp;$B49),$J48)</f>
         <v/>
       </c>
-      <c r="K49" s="15">
+      <c r="K49" s="16">
         <f>IF($H49=1,IF($K48="",$B49,$K48&amp;"、"&amp;$B49),$K48)</f>
         <v/>
       </c>
-      <c r="L49" s="15">
+      <c r="L49" s="16">
         <f>IF($I49=1,IF($L48="",$B49,$L48&amp;"、"&amp;$B49),$L48)</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="15" t="inlineStr">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>七·热武器</t>
         </is>
       </c>
-      <c r="B50" s="16" t="inlineStr">
+      <c r="B50" s="17" t="inlineStr">
         <is>
           <t>非法持有热武器罪</t>
         </is>
       </c>
-      <c r="C50" s="18" t="inlineStr">
+      <c r="C50" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D50" s="15" t="n">
+      <c r="D50" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="E50" s="15" t="n">
+      <c r="E50" s="16" t="n">
         <v>15000</v>
       </c>
-      <c r="F50" s="15" t="inlineStr">
+      <c r="F50" s="16" t="inlineStr">
         <is>
           <t>无证/非法持有枪支/爆炸物(执法公务除外)</t>
         </is>
       </c>
-      <c r="G50" s="15">
+      <c r="G50" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B50)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H50" s="15">
+      <c r="H50" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B50)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I50" s="15">
+      <c r="I50" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B50)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J50" s="15">
+      <c r="J50" s="16">
         <f>IF($G50=1,IF($J49="",$B50,$J49&amp;"、"&amp;$B50),$J49)</f>
         <v/>
       </c>
-      <c r="K50" s="15">
+      <c r="K50" s="16">
         <f>IF($H50=1,IF($K49="",$B50,$K49&amp;"、"&amp;$B50),$K49)</f>
         <v/>
       </c>
-      <c r="L50" s="15">
+      <c r="L50" s="16">
         <f>IF($I50=1,IF($L49="",$B50,$L49&amp;"、"&amp;$B50),$L49)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="15" t="inlineStr">
+      <c r="A51" s="16" t="inlineStr">
         <is>
           <t>七·热武器</t>
         </is>
       </c>
-      <c r="B51" s="16" t="inlineStr">
+      <c r="B51" s="17" t="inlineStr">
         <is>
           <t>非法展示热武器罪</t>
         </is>
       </c>
-      <c r="C51" s="17" t="inlineStr">
+      <c r="C51" s="18" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D51" s="15" t="n">
+      <c r="D51" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="E51" s="15" t="n">
+      <c r="E51" s="16" t="n">
         <v>8000</v>
       </c>
-      <c r="F51" s="15" t="inlineStr">
+      <c r="F51" s="16" t="inlineStr">
         <is>
           <t>公共场所公开携带/挥舞展示武器</t>
         </is>
       </c>
-      <c r="G51" s="15">
+      <c r="G51" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B51)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H51" s="15">
+      <c r="H51" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B51)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I51" s="15">
+      <c r="I51" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B51)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J51" s="15">
+      <c r="J51" s="16">
         <f>IF($G51=1,IF($J50="",$B51,$J50&amp;"、"&amp;$B51),$J50)</f>
         <v/>
       </c>
-      <c r="K51" s="15">
+      <c r="K51" s="16">
         <f>IF($H51=1,IF($K50="",$B51,$K50&amp;"、"&amp;$B51),$K50)</f>
         <v/>
       </c>
-      <c r="L51" s="15">
+      <c r="L51" s="16">
         <f>IF($I51=1,IF($L50="",$B51,$L50&amp;"、"&amp;$B51),$L50)</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="15" t="inlineStr">
+      <c r="A52" s="16" t="inlineStr">
         <is>
           <t>七·热武器</t>
         </is>
       </c>
-      <c r="B52" s="16" t="inlineStr">
+      <c r="B52" s="17" t="inlineStr">
         <is>
           <t>非法使用热武器罪</t>
         </is>
       </c>
-      <c r="C52" s="18" t="inlineStr">
+      <c r="C52" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D52" s="15" t="n">
+      <c r="D52" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="E52" s="15" t="n">
+      <c r="E52" s="16" t="n">
         <v>15000</v>
       </c>
-      <c r="F52" s="15" t="inlineStr">
+      <c r="F52" s="16" t="inlineStr">
         <is>
           <t>鲁莽/蓄意/威胁公共安全方式开枪</t>
         </is>
       </c>
-      <c r="G52" s="15">
+      <c r="G52" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B52)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H52" s="15">
+      <c r="H52" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B52)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I52" s="15">
+      <c r="I52" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B52)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J52" s="15">
+      <c r="J52" s="16">
         <f>IF($G52=1,IF($J51="",$B52,$J51&amp;"、"&amp;$B52),$J51)</f>
         <v/>
       </c>
-      <c r="K52" s="15">
+      <c r="K52" s="16">
         <f>IF($H52=1,IF($K51="",$B52,$K51&amp;"、"&amp;$B52),$K51)</f>
         <v/>
       </c>
-      <c r="L52" s="15">
+      <c r="L52" s="16">
         <f>IF($I52=1,IF($L51="",$B52,$L51&amp;"、"&amp;$B52),$L51)</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="A53" s="16" t="inlineStr">
         <is>
           <t>七·热武器</t>
         </is>
       </c>
-      <c r="B53" s="16" t="inlineStr">
+      <c r="B53" s="17" t="inlineStr">
         <is>
           <t>非法贩卖武器罪</t>
         </is>
       </c>
-      <c r="C53" s="18" t="inlineStr">
+      <c r="C53" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D53" s="15" t="n">
+      <c r="D53" s="16" t="n">
         <v>48</v>
       </c>
-      <c r="E53" s="15" t="n">
+      <c r="E53" s="16" t="n">
         <v>25000</v>
       </c>
-      <c r="F53" s="15" t="inlineStr">
+      <c r="F53" s="16" t="inlineStr">
         <is>
           <t>贩卖/转让/出售非法或未认证武器</t>
         </is>
       </c>
-      <c r="G53" s="15">
+      <c r="G53" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B53)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H53" s="15">
+      <c r="H53" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B53)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I53" s="15">
+      <c r="I53" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B53)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J53" s="15">
+      <c r="J53" s="16">
         <f>IF($G53=1,IF($J52="",$B53,$J52&amp;"、"&amp;$B53),$J52)</f>
         <v/>
       </c>
-      <c r="K53" s="15">
+      <c r="K53" s="16">
         <f>IF($H53=1,IF($K52="",$B53,$K52&amp;"、"&amp;$B53),$K52)</f>
         <v/>
       </c>
-      <c r="L53" s="15">
+      <c r="L53" s="16">
         <f>IF($I53=1,IF($L52="",$B53,$L52&amp;"、"&amp;$B53),$L52)</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="15" t="inlineStr">
+      <c r="A54" s="16" t="inlineStr">
         <is>
           <t>七·热武器</t>
         </is>
       </c>
-      <c r="B54" s="16" t="inlineStr">
+      <c r="B54" s="17" t="inlineStr">
         <is>
           <t>走私罪</t>
         </is>
       </c>
-      <c r="C54" s="18" t="inlineStr">
+      <c r="C54" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D54" s="15" t="n">
+      <c r="D54" s="16" t="n">
         <v>48</v>
       </c>
-      <c r="E54" s="15" t="n">
+      <c r="E54" s="16" t="n">
         <v>30000</v>
       </c>
-      <c r="F54" s="15" t="inlineStr">
+      <c r="F54" s="16" t="inlineStr">
         <is>
           <t>非法运输/转让武器爆炸物 / 参与军火走私</t>
         </is>
       </c>
-      <c r="G54" s="15">
+      <c r="G54" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B54)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H54" s="15">
+      <c r="H54" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B54)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I54" s="15">
+      <c r="I54" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B54)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J54" s="15">
+      <c r="J54" s="16">
         <f>IF($G54=1,IF($J53="",$B54,$J53&amp;"、"&amp;$B54),$J53)</f>
         <v/>
       </c>
-      <c r="K54" s="15">
+      <c r="K54" s="16">
         <f>IF($H54=1,IF($K53="",$B54,$K53&amp;"、"&amp;$B54),$K53)</f>
         <v/>
       </c>
-      <c r="L54" s="15">
+      <c r="L54" s="16">
         <f>IF($I54=1,IF($L53="",$B54,$L53&amp;"、"&amp;$B54),$L53)</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="15" t="inlineStr">
+      <c r="A55" s="16" t="inlineStr">
         <is>
           <t>十·公共安全</t>
         </is>
       </c>
-      <c r="B55" s="16" t="inlineStr">
+      <c r="B55" s="17" t="inlineStr">
         <is>
           <t>非法持有管制物品罪</t>
         </is>
       </c>
-      <c r="C55" s="18" t="inlineStr">
+      <c r="C55" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D55" s="15" t="n">
+      <c r="D55" s="16" t="n">
         <v>48</v>
       </c>
-      <c r="E55" s="15" t="n">
+      <c r="E55" s="16" t="n">
         <v>30000</v>
       </c>
-      <c r="F55" s="15" t="inlineStr">
+      <c r="F55" s="16" t="inlineStr">
         <is>
           <t>默认毒品/非法枪支(重罪4年$30000); 工具/8cm刀具=轻罪1年$15000</t>
         </is>
       </c>
-      <c r="G55" s="15">
+      <c r="G55" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B55)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H55" s="15">
+      <c r="H55" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B55)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I55" s="15">
+      <c r="I55" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B55)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J55" s="15">
+      <c r="J55" s="16">
         <f>IF($G55=1,IF($J54="",$B55,$J54&amp;"、"&amp;$B55),$J54)</f>
         <v/>
       </c>
-      <c r="K55" s="15">
+      <c r="K55" s="16">
         <f>IF($H55=1,IF($K54="",$B55,$K54&amp;"、"&amp;$B55),$K54)</f>
         <v/>
       </c>
-      <c r="L55" s="15">
+      <c r="L55" s="16">
         <f>IF($I55=1,IF($L54="",$B55,$L54&amp;"、"&amp;$B55),$L54)</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="15" t="inlineStr">
+      <c r="A56" s="16" t="inlineStr">
         <is>
           <t>十·公共安全</t>
         </is>
       </c>
-      <c r="B56" s="16" t="inlineStr">
+      <c r="B56" s="17" t="inlineStr">
         <is>
           <t>非法持有大量管制物品罪</t>
         </is>
       </c>
-      <c r="C56" s="18" t="inlineStr">
+      <c r="C56" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D56" s="15" t="n">
+      <c r="D56" s="16" t="n">
         <v>36</v>
       </c>
-      <c r="E56" s="15" t="n">
+      <c r="E56" s="16" t="n">
         <v>6000</v>
       </c>
-      <c r="F56" s="15" t="inlineStr">
+      <c r="F56" s="16" t="inlineStr">
         <is>
           <t>按量: 10-50个=3年$6000; 51-200=2-4年$10000; 201-500=4-6年$15000; 501-999=6-10年$30000(可超5年)</t>
         </is>
       </c>
-      <c r="G56" s="15">
+      <c r="G56" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B56)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H56" s="15">
+      <c r="H56" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B56)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I56" s="15">
+      <c r="I56" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B56)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J56" s="15">
+      <c r="J56" s="16">
         <f>IF($G56=1,IF($J55="",$B56,$J55&amp;"、"&amp;$B56),$J55)</f>
         <v/>
       </c>
-      <c r="K56" s="15">
+      <c r="K56" s="16">
         <f>IF($H56=1,IF($K55="",$B56,$K55&amp;"、"&amp;$B56),$K55)</f>
         <v/>
       </c>
-      <c r="L56" s="15">
+      <c r="L56" s="16">
         <f>IF($I56=1,IF($L55="",$B56,$L55&amp;"、"&amp;$B56),$L55)</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="15" t="inlineStr">
+      <c r="A57" s="16" t="inlineStr">
         <is>
           <t>十·公共安全</t>
         </is>
       </c>
-      <c r="B57" s="16" t="inlineStr">
+      <c r="B57" s="17" t="inlineStr">
         <is>
           <t>非法经营和分发管制物品罪</t>
         </is>
       </c>
-      <c r="C57" s="18" t="inlineStr">
+      <c r="C57" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D57" s="15" t="n">
+      <c r="D57" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="E57" s="15" t="n">
+      <c r="E57" s="16" t="n">
         <v>5000</v>
       </c>
-      <c r="F57" s="15" t="inlineStr">
+      <c r="F57" s="16" t="inlineStr">
         <is>
           <t>以出售/分发/储存为目的经营管制物品</t>
         </is>
       </c>
-      <c r="G57" s="15">
+      <c r="G57" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B57)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H57" s="15">
+      <c r="H57" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B57)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I57" s="15">
+      <c r="I57" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B57)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J57" s="15">
+      <c r="J57" s="16">
         <f>IF($G57=1,IF($J56="",$B57,$J56&amp;"、"&amp;$B57),$J56)</f>
         <v/>
       </c>
-      <c r="K57" s="15">
+      <c r="K57" s="16">
         <f>IF($H57=1,IF($K56="",$B57,$K56&amp;"、"&amp;$B57),$K56)</f>
         <v/>
       </c>
-      <c r="L57" s="15">
+      <c r="L57" s="16">
         <f>IF($I57=1,IF($L56="",$B57,$L56&amp;"、"&amp;$B57),$L56)</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="15" t="inlineStr">
+      <c r="A58" s="16" t="inlineStr">
         <is>
           <t>十·公共安全</t>
         </is>
       </c>
-      <c r="B58" s="16" t="inlineStr">
+      <c r="B58" s="17" t="inlineStr">
         <is>
           <t>非法制造管制物品罪</t>
         </is>
       </c>
-      <c r="C58" s="18" t="inlineStr">
+      <c r="C58" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D58" s="15" t="n">
+      <c r="D58" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="E58" s="15" t="n">
+      <c r="E58" s="16" t="n">
         <v>8000</v>
       </c>
-      <c r="F58" s="15" t="inlineStr">
+      <c r="F58" s="16" t="inlineStr">
         <is>
           <t>生产/制造处方药/大麻等管制物品</t>
         </is>
       </c>
-      <c r="G58" s="15">
+      <c r="G58" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B58)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H58" s="15">
+      <c r="H58" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B58)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I58" s="15">
+      <c r="I58" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B58)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J58" s="15">
+      <c r="J58" s="16">
         <f>IF($G58=1,IF($J57="",$B58,$J57&amp;"、"&amp;$B58),$J57)</f>
         <v/>
       </c>
-      <c r="K58" s="15">
+      <c r="K58" s="16">
         <f>IF($H58=1,IF($K57="",$B58,$K57&amp;"、"&amp;$B58),$K57)</f>
         <v/>
       </c>
-      <c r="L58" s="15">
+      <c r="L58" s="16">
         <f>IF($I58=1,IF($L57="",$B58,$L57&amp;"、"&amp;$B58),$L57)</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="15" t="inlineStr">
+      <c r="A59" s="16" t="inlineStr">
         <is>
           <t>十·公共安全</t>
         </is>
       </c>
-      <c r="B59" s="16" t="inlineStr">
+      <c r="B59" s="17" t="inlineStr">
         <is>
           <t>非法贩卖管制物品罪</t>
         </is>
       </c>
-      <c r="C59" s="18" t="inlineStr">
+      <c r="C59" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D59" s="15" t="n">
+      <c r="D59" s="16" t="n">
         <v>36</v>
       </c>
-      <c r="E59" s="15" t="n">
+      <c r="E59" s="16" t="n">
         <v>10000</v>
       </c>
-      <c r="F59" s="15" t="inlineStr">
+      <c r="F59" s="16" t="inlineStr">
         <is>
           <t>非法出售/赠送/运输管制物品给他人</t>
         </is>
       </c>
-      <c r="G59" s="15">
+      <c r="G59" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B59)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H59" s="15">
+      <c r="H59" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B59)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I59" s="15">
+      <c r="I59" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B59)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J59" s="15">
+      <c r="J59" s="16">
         <f>IF($G59=1,IF($J58="",$B59,$J58&amp;"、"&amp;$B59),$J58)</f>
         <v/>
       </c>
-      <c r="K59" s="15">
+      <c r="K59" s="16">
         <f>IF($H59=1,IF($K58="",$B59,$K58&amp;"、"&amp;$B59),$K58)</f>
         <v/>
       </c>
-      <c r="L59" s="15">
+      <c r="L59" s="16">
         <f>IF($I59=1,IF($L58="",$B59,$L58&amp;"、"&amp;$B59),$L58)</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="15" t="inlineStr">
+      <c r="A60" s="16" t="inlineStr">
         <is>
           <t>十一·其他</t>
         </is>
       </c>
-      <c r="B60" s="16" t="inlineStr">
+      <c r="B60" s="17" t="inlineStr">
         <is>
           <t>有组织犯罪</t>
         </is>
       </c>
-      <c r="C60" s="18" t="inlineStr">
+      <c r="C60" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D60" s="15" t="n">
+      <c r="D60" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="E60" s="15" t="n">
+      <c r="E60" s="16" t="n">
         <v>10000</v>
       </c>
-      <c r="F60" s="15" t="inlineStr">
+      <c r="F60" s="16" t="inlineStr">
         <is>
           <t>团体以牟利为目的实施违法犯罪(逮捕须先取逮捕令)</t>
         </is>
       </c>
-      <c r="G60" s="15">
+      <c r="G60" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B60)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H60" s="15">
+      <c r="H60" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B60)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I60" s="15">
+      <c r="I60" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B60)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J60" s="15">
+      <c r="J60" s="16">
         <f>IF($G60=1,IF($J59="",$B60,$J59&amp;"、"&amp;$B60),$J59)</f>
         <v/>
       </c>
-      <c r="K60" s="15">
+      <c r="K60" s="16">
         <f>IF($H60=1,IF($K59="",$B60,$K59&amp;"、"&amp;$B60),$K59)</f>
         <v/>
       </c>
-      <c r="L60" s="15">
+      <c r="L60" s="16">
         <f>IF($I60=1,IF($L59="",$B60,$L59&amp;"、"&amp;$B60),$L59)</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="15" t="inlineStr">
+      <c r="A61" s="16" t="inlineStr">
         <is>
           <t>十一·其他</t>
         </is>
       </c>
-      <c r="B61" s="16" t="inlineStr">
+      <c r="B61" s="17" t="inlineStr">
         <is>
           <t>洗钱罪</t>
         </is>
       </c>
-      <c r="C61" s="18" t="inlineStr">
+      <c r="C61" s="19" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D61" s="15" t="n">
+      <c r="D61" s="16" t="n">
         <v>48</v>
       </c>
-      <c r="E61" s="15" t="n">
+      <c r="E61" s="16" t="n">
         <v>30000</v>
       </c>
-      <c r="F61" s="15" t="inlineStr">
+      <c r="F61" s="16" t="inlineStr">
         <is>
           <t>持有/隐藏/转移违法所得 / 协助洗钱</t>
         </is>
       </c>
-      <c r="G61" s="15">
+      <c r="G61" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B61)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H61" s="15">
+      <c r="H61" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B61)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I61" s="15">
+      <c r="I61" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B61)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J61" s="15">
+      <c r="J61" s="16">
         <f>IF($G61=1,IF($J60="",$B61,$J60&amp;"、"&amp;$B61),$J60)</f>
         <v/>
       </c>
-      <c r="K61" s="15">
+      <c r="K61" s="16">
         <f>IF($H61=1,IF($K60="",$B61,$K60&amp;"、"&amp;$B61),$K60)</f>
         <v/>
       </c>
-      <c r="L61" s="15">
+      <c r="L61" s="16">
         <f>IF($I61=1,IF($L60="",$B61,$L60&amp;"、"&amp;$B61),$L60)</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="15" t="inlineStr">
+      <c r="A62" s="16" t="inlineStr">
         <is>
           <t>十一·其他</t>
         </is>
       </c>
-      <c r="B62" s="16" t="inlineStr">
+      <c r="B62" s="17" t="inlineStr">
         <is>
           <t>身份盗用罪</t>
         </is>
       </c>
-      <c r="C62" s="17" t="inlineStr">
+      <c r="C62" s="18" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D62" s="15" t="n">
+      <c r="D62" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="E62" s="15" t="n">
+      <c r="E62" s="16" t="n">
         <v>8000</v>
       </c>
-      <c r="F62" s="15" t="inlineStr">
+      <c r="F62" s="16" t="inlineStr">
         <is>
           <t>未经许可盗取/使用他人个人信息, 另需赔偿</t>
         </is>
       </c>
-      <c r="G62" s="15">
+      <c r="G62" s="16">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B62)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H62" s="15">
+      <c r="H62" s="16">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B62)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I62" s="15">
+      <c r="I62" s="16">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B62)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J62" s="15">
+      <c r="J62" s="16">
         <f>IF($G62=1,IF($J61="",$B62,$J61&amp;"、"&amp;$B62),$J61)</f>
         <v/>
       </c>
-      <c r="K62" s="15">
+      <c r="K62" s="16">
         <f>IF($H62=1,IF($K61="",$B62,$K61&amp;"、"&amp;$B62),$K61)</f>
         <v/>
       </c>
-      <c r="L62" s="15">
+      <c r="L62" s="16">
         <f>IF($I62=1,IF($L61="",$B62,$L61&amp;"、"&amp;$B62),$L61)</f>
         <v/>
       </c>

--- a/fivem_case_analyzer/圣安地列斯州_案件罪名分析器.xlsx
+++ b/fivem_case_analyzer/圣安地列斯州_案件罪名分析器.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,25 +38,50 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="16"/>
+      <sz val="18"/>
     </font>
     <font>
       <i val="1"/>
+      <color rgb="00F3E6BE"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00C00000"/>
+      <color rgb="0012243B"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="001B2A41"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001B2A41"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C0392B"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
     <font>
       <i val="1"/>
-      <color rgb="00595959"/>
+      <color rgb="006B7280"/>
       <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F3864"/>
+      <color rgb="0012243B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -70,7 +95,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -79,36 +104,66 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E5496"/>
+        <fgColor rgb="001F3A5F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00FBE3CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
+        <fgColor rgb="00F6D4CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
+        <fgColor rgb="00F4F6FA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="0012243B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00F3E6BE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002C4A7C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFDF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E6B5C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005E4B8B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF4FA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -118,65 +173,125 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00D5DCE6"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00D5DCE6"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00D5DCE6"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00D5DCE6"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="00C9A227"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="00C9A227"/>
+      </left>
+    </border>
+    <border>
+      <top style="medium">
+        <color rgb="00C9A227"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00C9A227"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -191,6 +306,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -199,7 +317,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00C6E0B4"/>
+          <fgColor rgb="00CDE8D5"/>
         </patternFill>
       </fill>
     </dxf>
@@ -759,213 +877,319 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="40" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>🦅 圣安地列斯州 · 案件罪名分析器</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>把每位当事人「做了什么」分别填到下面黄色框里（尽量用法典里的词，如：抢劫、袭警、拒捕、开枪、逃跑…），下方自动算出罪名与刑期。详细规则见「使用说明」页。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="46" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>👤 当事人甲
-行为/案情</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
+          <t>⚖   圣 安 地 列 斯 州 · 案 件 罪 名 分 析 器   🦅</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="n"/>
+      <c r="C1" s="5" t="n"/>
+      <c r="D1" s="5" t="n"/>
+      <c r="E1" s="5" t="n"/>
+      <c r="F1" s="5" t="n"/>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>STATE OF SAN ANDREAS · PENAL CODE CASE ANALYZER　|　依据《圣安地列斯州刑法典》自动算罪</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="7" t="n"/>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　① 案情输入　—　把每位当事人「做了什么」分别填进右侧白框（只算一人就只填甲）</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="n"/>
+      <c r="C3" s="9" t="n"/>
+      <c r="D3" s="9" t="n"/>
+      <c r="E3" s="9" t="n"/>
+      <c r="F3" s="9" t="n"/>
+    </row>
+    <row r="4" ht="50" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>👤
+当事人甲</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>嫌疑人持枪抢劫便利店，被警察拦截后拒捕并开枪，随后驾车逃跑撞坏路边车辆。</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>👤 当事人乙
-行为/案情</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr"/>
-    </row>
-    <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>👤 当事人丙
-行为/案情</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr"/>
-    </row>
-    <row r="8" ht="22" customHeight="1">
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="12" t="n"/>
+    </row>
+    <row r="5" ht="50" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>👤
+当事人乙</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="50" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>👤
+当事人丙</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+    </row>
+    <row r="7" ht="6" customHeight="1">
+      <c r="A7" s="15" t="n"/>
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="15" t="n"/>
+      <c r="E7" s="15" t="n"/>
+      <c r="F7" s="15" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>📋 分析结果（自动计算）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+          <t xml:space="preserve">　② 分析结果　—　自动匹配罪名 / 合计刑期 / 罚款 / 保释金（绿色＝命中）</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>当事人</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>命中罪名</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>罪名数</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>合计刑期(月)</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>合计罚款($)</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>建议保释金($)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>当事人甲</t>
         </is>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="18">
         <f>IF('罪名表'!$J$62="","（无 / 请补充案情）",'罪名表'!$J$62)</f>
         <v/>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="19">
         <f>SUM('罪名表'!$G$2:$G$62)</f>
         <v/>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="20">
         <f>MIN(60,SUMIF('罪名表'!$G$2:$G$62,1,'罪名表'!$D$2:$D$62))</f>
         <v/>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="21">
         <f>SUMIF('罪名表'!$G$2:$G$62,1,'罪名表'!$E$2:$E$62)</f>
         <v/>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="22">
         <f>ROUND(D10*E10/6,0)</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t>当事人乙</t>
         </is>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="24">
         <f>IF('罪名表'!$K$62="","（无 / 请补充案情）",'罪名表'!$K$62)</f>
         <v/>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="25">
         <f>SUM('罪名表'!$H$2:$H$62)</f>
         <v/>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="26">
         <f>MIN(60,SUMIF('罪名表'!$H$2:$H$62,1,'罪名表'!$D$2:$D$62))</f>
         <v/>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="27">
         <f>SUMIF('罪名表'!$H$2:$H$62,1,'罪名表'!$E$2:$E$62)</f>
         <v/>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="28">
         <f>ROUND(D11*E11/6,0)</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>当事人丙</t>
         </is>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="18">
         <f>IF('罪名表'!$L$62="","（无 / 请补充案情）",'罪名表'!$L$62)</f>
         <v/>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="19">
         <f>SUM('罪名表'!$I$2:$I$62)</f>
         <v/>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="20">
         <f>MIN(60,SUMIF('罪名表'!$I$2:$I$62,1,'罪名表'!$D$2:$D$62))</f>
         <v/>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="21">
         <f>SUMIF('罪名表'!$I$2:$I$62,1,'罪名表'!$E$2:$E$62)</f>
         <v/>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="22">
         <f>ROUND(D12*E12/6,0)</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="13">
-        <f>IF(MAX(D10,D11,D12)=0,"⚠ 暂未匹配到罪名：请在上方更详细地描述案情，并尽量使用法典中的关键词。","🔨 主要责任方：当事人"&amp;IF(D10=MAX(D10,D11,D12),"甲",IF(D11=MAX(D10,D11,D12),"乙","丙"))&amp;"（合计刑期最重，约 "&amp;MAX(D10,D11,D12)&amp;" 个月 / "&amp;ROUND(MAX(D10,D11,D12)/12,1)&amp;" 年）"&amp;"  —  仅供参考，正当防卫/堡垒原则/同类不并罚等请人工复核")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>提示：① 只想算一个人时，只填「当事人甲」即可。 ② 刑期已按法典封顶 5 年(60个月)。 ③ 保释金 = 刑期(月)×罚款÷6。 ④ 想加/改罪名或关键词，去「罪名表」「关键词表」两页编辑即可。</t>
-        </is>
-      </c>
+    <row r="13" ht="6" customHeight="1">
+      <c r="A13" s="15" t="n"/>
+      <c r="B13" s="15" t="n"/>
+      <c r="C13" s="15" t="n"/>
+      <c r="D13" s="15" t="n"/>
+      <c r="E13" s="15" t="n"/>
+      <c r="F13" s="15" t="n"/>
+    </row>
+    <row r="14" ht="38" customHeight="1">
+      <c r="A14" s="30">
+        <f>IF(MAX(D10,D11,D12)=0,"⚠ 暂未匹配到罪名：请更详细地描述案情，并尽量使用法典中的关键词。","🔨 主要责任方：当事人"&amp;IF(D10=MAX(D10,D11,D12),"甲",IF(D11=MAX(D10,D11,D12),"乙","丙"))&amp;"　|　合计刑期约 "&amp;MAX(D10,D11,D12)&amp;" 个月（"&amp;ROUND(MAX(D10,D11,D12)/12,1)&amp;" 年）"&amp;"　|　仅供参考，正当防卫 / 堡垒原则 / 同类不并罚等请人工复核")</f>
+        <v/>
+      </c>
+      <c r="B14" s="31" t="n"/>
+      <c r="C14" s="31" t="n"/>
+      <c r="D14" s="31" t="n"/>
+      <c r="E14" s="31" t="n"/>
+      <c r="F14" s="31" t="n"/>
+    </row>
+    <row r="15" ht="6" customHeight="1">
+      <c r="A15" s="15" t="n"/>
+      <c r="B15" s="15" t="n"/>
+      <c r="C15" s="15" t="n"/>
+      <c r="D15" s="15" t="n"/>
+      <c r="E15" s="15" t="n"/>
+      <c r="F15" s="15" t="n"/>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t>提示  ·  ① 只算一人 → 只填当事人甲　② 刑期已按法典封顶 5 年(60 个月)　③ 保释金 = 刑期(月) × 罚款 ÷ 6　④ 想加/改罪名或关键词 → 去「罪名表」「关键词表」两页</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="15" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="n"/>
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="15" t="n"/>
+      <c r="E17" s="15" t="n"/>
+      <c r="F17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>原创制作：袁尘</t>
-        </is>
-      </c>
+      <c r="A18" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">原创制作：袁尘　</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="15" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n"/>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="n"/>
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="15" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="13">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A6"/>
     <mergeCell ref="B6:F6"/>
+    <mergeCell ref="A4"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -995,3235 +1219,3235 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>章节</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>罪名</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>定性</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>最高刑期(月)</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>罚款($)</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="16" t="inlineStr">
         <is>
           <t>甲命中</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="16" t="inlineStr">
         <is>
           <t>乙命中</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="16" t="inlineStr">
         <is>
           <t>丙命中</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="16" t="inlineStr">
         <is>
           <t>甲累积</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="16" t="inlineStr">
         <is>
           <t>乙累积</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="16" t="inlineStr">
         <is>
           <t>丙累积</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="34" t="inlineStr">
         <is>
           <t>二·人身</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="35" t="inlineStr">
         <is>
           <t>威胁罪</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
+      <c r="C2" s="36" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="34" t="n">
         <v>8000</v>
       </c>
-      <c r="F2" s="16" t="inlineStr">
+      <c r="F2" s="34" t="inlineStr">
         <is>
           <t>口头/书面/网络威胁他人或其亲友</t>
         </is>
       </c>
-      <c r="G2" s="16">
+      <c r="G2" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B2)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H2" s="16">
+      <c r="H2" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B2)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B2)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J2" s="16">
+      <c r="J2" s="34">
         <f>IF($G2=1,$B2,"")</f>
         <v/>
       </c>
-      <c r="K2" s="16">
+      <c r="K2" s="34">
         <f>IF($H2=1,$B2,"")</f>
         <v/>
       </c>
-      <c r="L2" s="16">
+      <c r="L2" s="34">
         <f>IF($I2=1,$B2,"")</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>二·人身</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="35" t="inlineStr">
         <is>
           <t>持有危险武器人身攻击罪</t>
         </is>
       </c>
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="D3" s="34" t="n">
         <v>48</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="34" t="n">
         <v>20000</v>
       </c>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="F3" s="34" t="inlineStr">
         <is>
           <t>用武器/工具威胁或伤害他人</t>
         </is>
       </c>
-      <c r="G3" s="16">
+      <c r="G3" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B3)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H3" s="16">
+      <c r="H3" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B3)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B3)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="34">
         <f>IF($G3=1,IF($J2="",$B3,$J2&amp;"、"&amp;$B3),$J2)</f>
         <v/>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="34">
         <f>IF($H3=1,IF($K2="",$B3,$K2&amp;"、"&amp;$B3),$K2)</f>
         <v/>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="34">
         <f>IF($I3=1,IF($L2="",$B3,$L2&amp;"、"&amp;$B3),$L2)</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>二·人身</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>一级谋杀罪</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="D4" s="34" t="n">
         <v>60</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="34" t="n">
         <v>30000</v>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="34" t="inlineStr">
         <is>
           <t>预谋故意杀人 / 重罪过程中杀人</t>
         </is>
       </c>
-      <c r="G4" s="16">
+      <c r="G4" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B4)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H4" s="16">
+      <c r="H4" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B4)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B4)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="34">
         <f>IF($G4=1,IF($J3="",$B4,$J3&amp;"、"&amp;$B4),$J3)</f>
         <v/>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="34">
         <f>IF($H4=1,IF($K3="",$B4,$K3&amp;"、"&amp;$B4),$K3)</f>
         <v/>
       </c>
-      <c r="L4" s="16">
+      <c r="L4" s="34">
         <f>IF($I4=1,IF($L3="",$B4,$L3&amp;"、"&amp;$B4),$L3)</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>二·人身</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>二级谋杀罪</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="34" t="n">
         <v>60</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="34" t="n">
         <v>20000</v>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F5" s="34" t="inlineStr">
         <is>
           <t>非预谋的故意杀人 (3至5年)</t>
         </is>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B5)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B5)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B5)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="34">
         <f>IF($G5=1,IF($J4="",$B5,$J4&amp;"、"&amp;$B5),$J4)</f>
         <v/>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="34">
         <f>IF($H5=1,IF($K4="",$B5,$K4&amp;"、"&amp;$B5),$K4)</f>
         <v/>
       </c>
-      <c r="L5" s="16">
+      <c r="L5" s="34">
         <f>IF($I5=1,IF($L4="",$B5,$L4&amp;"、"&amp;$B5),$L4)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>二·人身</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>三级谋杀罪</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="34" t="n">
         <v>60</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="34" t="n">
         <v>15000</v>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F6" s="34" t="inlineStr">
         <is>
           <t>无意致死/鲁莽过失致死 (3至5年, 不含正当防卫)</t>
         </is>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B6)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B6)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B6)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="34">
         <f>IF($G6=1,IF($J5="",$B6,$J5&amp;"、"&amp;$B6),$J5)</f>
         <v/>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="34">
         <f>IF($H6=1,IF($K5="",$B6,$K5&amp;"、"&amp;$B6),$K5)</f>
         <v/>
       </c>
-      <c r="L6" s="16">
+      <c r="L6" s="34">
         <f>IF($I6=1,IF($L5="",$B6,$L5&amp;"、"&amp;$B6),$L5)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>二·人身</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>非法拘禁罪</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="34" t="n">
         <v>36</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="34" t="n">
         <v>15000</v>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="34" t="inlineStr">
         <is>
           <t>违背意愿约束/扣押/拘禁他人</t>
         </is>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B7)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B7)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B7)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="34">
         <f>IF($G7=1,IF($J6="",$B7,$J6&amp;"、"&amp;$B7),$J6)</f>
         <v/>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="34">
         <f>IF($H7=1,IF($K6="",$B7,$K6&amp;"、"&amp;$B7),$K6)</f>
         <v/>
       </c>
-      <c r="L7" s="16">
+      <c r="L7" s="34">
         <f>IF($I7=1,IF($L6="",$B7,$L6&amp;"、"&amp;$B7),$L6)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>二·人身</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>故意袭击罪</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="34" t="n">
         <v>36</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="34" t="n">
         <v>15000</v>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="34" t="inlineStr">
         <is>
           <t>蓄意暴力致他人身体受伤</t>
         </is>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B8)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B8)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B8)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="34">
         <f>IF($G8=1,IF($J7="",$B8,$J7&amp;"、"&amp;$B8),$J7)</f>
         <v/>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="34">
         <f>IF($H8=1,IF($K7="",$B8,$K7&amp;"、"&amp;$B8),$K7)</f>
         <v/>
       </c>
-      <c r="L8" s="16">
+      <c r="L8" s="34">
         <f>IF($I8=1,IF($L7="",$B8,$L7&amp;"、"&amp;$B8),$L7)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>二·人身</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>绑架罪</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="34" t="n">
         <v>60</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="34" t="n">
         <v>25000</v>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F9" s="34" t="inlineStr">
         <is>
           <t>侵占/羁押/控制他人意图恐吓</t>
         </is>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B9)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B9)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B9)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="34">
         <f>IF($G9=1,IF($J8="",$B9,$J8&amp;"、"&amp;$B9),$J8)</f>
         <v/>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="34">
         <f>IF($H9=1,IF($K8="",$B9,$K8&amp;"、"&amp;$B9),$K8)</f>
         <v/>
       </c>
-      <c r="L9" s="16">
+      <c r="L9" s="34">
         <f>IF($I9=1,IF($L8="",$B9,$L8&amp;"、"&amp;$B9),$L8)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>二·人身</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>亵渎尸体罪</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="34" t="n">
         <v>24</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="34" t="n">
         <v>20000</v>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="34" t="inlineStr">
         <is>
           <t>毁损/处置尸体掩盖犯罪</t>
         </is>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B10)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B10)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B10)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="34">
         <f>IF($G10=1,IF($J9="",$B10,$J9&amp;"、"&amp;$B10),$J9)</f>
         <v/>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="34">
         <f>IF($H10=1,IF($K9="",$B10,$K9&amp;"、"&amp;$B10),$K9)</f>
         <v/>
       </c>
-      <c r="L10" s="16">
+      <c r="L10" s="34">
         <f>IF($I10=1,IF($L9="",$B10,$L9&amp;"、"&amp;$B10),$L9)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>二·人身</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr">
         <is>
           <t>诈骗罪</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="34" t="n">
         <v>60</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="34" t="n">
         <v>5000</v>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="34" t="inlineStr">
         <is>
           <t>以欺诈欺瞒获取他人财物 (1-5年)</t>
         </is>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B11)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B11)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B11)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="34">
         <f>IF($G11=1,IF($J10="",$B11,$J10&amp;"、"&amp;$B11),$J10)</f>
         <v/>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="34">
         <f>IF($H11=1,IF($K10="",$B11,$K10&amp;"、"&amp;$B11),$K10)</f>
         <v/>
       </c>
-      <c r="L11" s="16">
+      <c r="L11" s="34">
         <f>IF($I11=1,IF($L10="",$B11,$L10&amp;"、"&amp;$B11),$L10)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>三·财产</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>非法入侵罪</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="36" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="34" t="n">
         <v>24</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="34" t="n">
         <v>8000</v>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F12" s="34" t="inlineStr">
         <is>
           <t>被要求离开后仍拒绝离开</t>
         </is>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B12)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B12)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B12)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="34">
         <f>IF($G12=1,IF($J11="",$B12,$J11&amp;"、"&amp;$B12),$J11)</f>
         <v/>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="34">
         <f>IF($H12=1,IF($K11="",$B12,$K11&amp;"、"&amp;$B12),$K11)</f>
         <v/>
       </c>
-      <c r="L12" s="16">
+      <c r="L12" s="34">
         <f>IF($I12=1,IF($L11="",$B12,$L11&amp;"、"&amp;$B12),$L11)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>三·财产</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>非法入侵禁区罪</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="36" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="34" t="n">
         <v>36</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="34" t="n">
         <v>10000</v>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F13" s="34" t="inlineStr">
         <is>
           <t>未经授权进入警局/机场/军事基地等限制区</t>
         </is>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B13)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B13)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B13)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="34">
         <f>IF($G13=1,IF($J12="",$B13,$J12&amp;"、"&amp;$B13),$J12)</f>
         <v/>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="34">
         <f>IF($H13=1,IF($K12="",$B13,$K12&amp;"、"&amp;$B13),$K12)</f>
         <v/>
       </c>
-      <c r="L13" s="16">
+      <c r="L13" s="34">
         <f>IF($I13=1,IF($L12="",$B13,$L12&amp;"、"&amp;$B13),$L12)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>三·财产</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>入室盗窃罪</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C14" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="34" t="n">
         <v>36</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="34" t="n">
         <v>25000</v>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F14" s="34" t="inlineStr">
         <is>
           <t>擅入住宅/办公室/仓库盗窃, 另需赔偿</t>
         </is>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B14)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B14)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B14)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="34">
         <f>IF($G14=1,IF($J13="",$B14,$J13&amp;"、"&amp;$B14),$J13)</f>
         <v/>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="34">
         <f>IF($H14=1,IF($K13="",$B14,$K13&amp;"、"&amp;$B14),$K13)</f>
         <v/>
       </c>
-      <c r="L14" s="16">
+      <c r="L14" s="34">
         <f>IF($I14=1,IF($L13="",$B14,$L13&amp;"、"&amp;$B14),$L13)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>三·财产</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>抢劫罪</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="C15" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="34" t="n">
         <v>60</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="34" t="n">
         <v>20000</v>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F15" s="34" t="inlineStr">
         <is>
           <t>以武力/威胁强夺他人财产, 另需赔偿</t>
         </is>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B15)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H15" s="16">
+      <c r="H15" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B15)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B15)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="34">
         <f>IF($G15=1,IF($J14="",$B15,$J14&amp;"、"&amp;$B15),$J14)</f>
         <v/>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="34">
         <f>IF($H15=1,IF($K14="",$B15,$K14&amp;"、"&amp;$B15),$K14)</f>
         <v/>
       </c>
-      <c r="L15" s="16">
+      <c r="L15" s="34">
         <f>IF($I15=1,IF($L14="",$B15,$L14&amp;"、"&amp;$B15),$L14)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>三·财产</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>盗窃罪</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="34" t="n">
         <v>48</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="34" t="n">
         <v>20000</v>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F16" s="34" t="inlineStr">
         <is>
           <t>盗窃/占用他人财物, 另需赔偿</t>
         </is>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B16)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B16)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B16)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="34">
         <f>IF($G16=1,IF($J15="",$B16,$J15&amp;"、"&amp;$B16),$J15)</f>
         <v/>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="34">
         <f>IF($H16=1,IF($K15="",$B16,$K15&amp;"、"&amp;$B16),$K15)</f>
         <v/>
       </c>
-      <c r="L16" s="16">
+      <c r="L16" s="34">
         <f>IF($I16=1,IF($L15="",$B16,$L15&amp;"、"&amp;$B16),$L15)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>三·财产</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="35" t="inlineStr">
         <is>
           <t>盗窃车辆罪</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="36" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="34" t="n">
         <v>5000</v>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F17" s="34" t="inlineStr">
         <is>
           <t>默认未造成严重后果(轻罪1年$5000); 严重后果=重罪4年$15000, 均赔偿</t>
         </is>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B17)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B17)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B17)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="34">
         <f>IF($G17=1,IF($J16="",$B17,$J16&amp;"、"&amp;$B17),$J16)</f>
         <v/>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="34">
         <f>IF($H17=1,IF($K16="",$B17,$K16&amp;"、"&amp;$B17),$K16)</f>
         <v/>
       </c>
-      <c r="L17" s="16">
+      <c r="L17" s="34">
         <f>IF($I17=1,IF($L16="",$B17,$L16&amp;"、"&amp;$B17),$L16)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>三·财产</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="35" t="inlineStr">
         <is>
           <t>收受赃物罪</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="36" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="34" t="n">
         <v>24</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="34" t="n">
         <v>10000</v>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F18" s="34" t="inlineStr">
         <is>
           <t>默认赃值&lt;$5000(轻罪2年$10000); ≥$5000=重罪4年$20000</t>
         </is>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B18)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B18)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B18)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="34">
         <f>IF($G18=1,IF($J17="",$B18,$J17&amp;"、"&amp;$B18),$J17)</f>
         <v/>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="34">
         <f>IF($H18=1,IF($K17="",$B18,$K17&amp;"、"&amp;$B18),$K17)</f>
         <v/>
       </c>
-      <c r="L18" s="16">
+      <c r="L18" s="34">
         <f>IF($I18=1,IF($L17="",$B18,$L17&amp;"、"&amp;$B18),$L17)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>三·财产</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="35" t="inlineStr">
         <is>
           <t>敲诈勒索罪</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr">
+      <c r="C19" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="34" t="n">
         <v>24</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="34" t="n">
         <v>20000</v>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F19" s="34" t="inlineStr">
         <is>
           <t>以威胁/恐吓/滥权强迫他人交付财物</t>
         </is>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B19)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H19" s="16">
+      <c r="H19" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B19)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B19)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="34">
         <f>IF($G19=1,IF($J18="",$B19,$J18&amp;"、"&amp;$B19),$J18)</f>
         <v/>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="34">
         <f>IF($H19=1,IF($K18="",$B19,$K18&amp;"、"&amp;$B19),$K18)</f>
         <v/>
       </c>
-      <c r="L19" s="16">
+      <c r="L19" s="34">
         <f>IF($I19=1,IF($L18="",$B19,$L18&amp;"、"&amp;$B19),$L18)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>三·财产</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>蓄意破坏罪</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="36" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="34" t="n">
         <v>24</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="34" t="n">
         <v>25000</v>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F20" s="34" t="inlineStr">
         <is>
           <t>蓄意破坏他人财产/车辆, 另需赔偿</t>
         </is>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B20)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H20" s="16">
+      <c r="H20" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B20)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B20)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="34">
         <f>IF($G20=1,IF($J19="",$B20,$J19&amp;"、"&amp;$B20),$J19)</f>
         <v/>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="34">
         <f>IF($H20=1,IF($K19="",$B20,$K19&amp;"、"&amp;$B20),$K19)</f>
         <v/>
       </c>
-      <c r="L20" s="16">
+      <c r="L20" s="34">
         <f>IF($I20=1,IF($L19="",$B20,$L19&amp;"、"&amp;$B20),$L19)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>三·财产</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>挪用公款公物罪</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="36" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="34" t="n">
         <v>48</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="34" t="n">
         <v>80000</v>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F21" s="34" t="inlineStr">
         <is>
           <t>擅自挪用受托管理的财物, 另需赔偿</t>
         </is>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B21)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H21" s="16">
+      <c r="H21" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B21)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B21)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="34">
         <f>IF($G21=1,IF($J20="",$B21,$J20&amp;"、"&amp;$B21),$J20)</f>
         <v/>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="34">
         <f>IF($H21=1,IF($K20="",$B21,$K20&amp;"、"&amp;$B21),$K20)</f>
         <v/>
       </c>
-      <c r="L21" s="16">
+      <c r="L21" s="34">
         <f>IF($I21=1,IF($L20="",$B21,$L20&amp;"、"&amp;$B21),$L20)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="34" t="inlineStr">
         <is>
           <t>三·财产</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="35" t="inlineStr">
         <is>
           <t>持有失窃物品罪</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="36" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="34" t="n">
         <v>24</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="34" t="n">
         <v>2000</v>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F22" s="34" t="inlineStr">
         <is>
           <t>非法占有他人遗失/失窃财物 (1-2年), 另需赔偿</t>
         </is>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B22)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H22" s="16">
+      <c r="H22" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B22)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B22)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="34">
         <f>IF($G22=1,IF($J21="",$B22,$J21&amp;"、"&amp;$B22),$J21)</f>
         <v/>
       </c>
-      <c r="K22" s="16">
+      <c r="K22" s="34">
         <f>IF($H22=1,IF($K21="",$B22,$K21&amp;"、"&amp;$B22),$K21)</f>
         <v/>
       </c>
-      <c r="L22" s="16">
+      <c r="L22" s="34">
         <f>IF($I22=1,IF($L21="",$B22,$L21&amp;"、"&amp;$B22),$L21)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="34" t="inlineStr">
         <is>
           <t>四·公德</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>在公共场合从事淫秽行为罪</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" s="36" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="D23" s="34" t="n">
         <v>24</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="E23" s="34" t="n">
         <v>10000</v>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F23" s="34" t="inlineStr">
         <is>
           <t>公开场所性行为/猥亵/招嫖 (1-2年)</t>
         </is>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B23)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H23" s="16">
+      <c r="H23" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B23)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B23)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J23" s="16">
+      <c r="J23" s="34">
         <f>IF($G23=1,IF($J22="",$B23,$J22&amp;"、"&amp;$B23),$J22)</f>
         <v/>
       </c>
-      <c r="K23" s="16">
+      <c r="K23" s="34">
         <f>IF($H23=1,IF($K22="",$B23,$K22&amp;"、"&amp;$B23),$K22)</f>
         <v/>
       </c>
-      <c r="L23" s="16">
+      <c r="L23" s="34">
         <f>IF($I23=1,IF($L22="",$B23,$L22&amp;"、"&amp;$B23),$L22)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="A24" s="34" t="inlineStr">
         <is>
           <t>四·公德</t>
         </is>
       </c>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="35" t="inlineStr">
         <is>
           <t>组织卖淫罪</t>
         </is>
       </c>
-      <c r="C24" s="19" t="inlineStr">
+      <c r="C24" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D24" s="16" t="n">
+      <c r="D24" s="34" t="n">
         <v>36</v>
       </c>
-      <c r="E24" s="16" t="n">
+      <c r="E24" s="34" t="n">
         <v>15000</v>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F24" s="34" t="inlineStr">
         <is>
           <t>支持/介绍/强迫他人卖淫牟利</t>
         </is>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B24)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B24)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B24)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J24" s="16">
+      <c r="J24" s="34">
         <f>IF($G24=1,IF($J23="",$B24,$J23&amp;"、"&amp;$B24),$J23)</f>
         <v/>
       </c>
-      <c r="K24" s="16">
+      <c r="K24" s="34">
         <f>IF($H24=1,IF($K23="",$B24,$K23&amp;"、"&amp;$B24),$K23)</f>
         <v/>
       </c>
-      <c r="L24" s="16">
+      <c r="L24" s="34">
         <f>IF($I24=1,IF($L23="",$B24,$L23&amp;"、"&amp;$B24),$L23)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="A25" s="34" t="inlineStr">
         <is>
           <t>四·公德</t>
         </is>
       </c>
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B25" s="35" t="inlineStr">
         <is>
           <t>卖淫罪</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C25" s="36" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D25" s="16" t="n">
+      <c r="D25" s="34" t="n">
         <v>24</v>
       </c>
-      <c r="E25" s="16" t="n">
+      <c r="E25" s="34" t="n">
         <v>15000</v>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F25" s="34" t="inlineStr">
         <is>
           <t>以性服务换取财物</t>
         </is>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B25)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H25" s="16">
+      <c r="H25" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B25)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B25)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J25" s="16">
+      <c r="J25" s="34">
         <f>IF($G25=1,IF($J24="",$B25,$J24&amp;"、"&amp;$B25),$J24)</f>
         <v/>
       </c>
-      <c r="K25" s="16">
+      <c r="K25" s="34">
         <f>IF($H25=1,IF($K24="",$B25,$K24&amp;"、"&amp;$B25),$K24)</f>
         <v/>
       </c>
-      <c r="L25" s="16">
+      <c r="L25" s="34">
         <f>IF($I25=1,IF($L24="",$B25,$L24&amp;"、"&amp;$B25),$L24)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="34" t="inlineStr">
         <is>
           <t>四·公德</t>
         </is>
       </c>
-      <c r="B26" s="17" t="inlineStr">
+      <c r="B26" s="35" t="inlineStr">
         <is>
           <t>强奸罪</t>
         </is>
       </c>
-      <c r="C26" s="19" t="inlineStr">
+      <c r="C26" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D26" s="16" t="n">
+      <c r="D26" s="34" t="n">
         <v>60</v>
       </c>
-      <c r="E26" s="16" t="n">
+      <c r="E26" s="34" t="n">
         <v>30000</v>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F26" s="34" t="inlineStr">
         <is>
           <t>违背意愿强迫性行为 / 与未满18岁者发生关系</t>
         </is>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B26)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H26" s="16">
+      <c r="H26" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B26)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B26)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J26" s="16">
+      <c r="J26" s="34">
         <f>IF($G26=1,IF($J25="",$B26,$J25&amp;"、"&amp;$B26),$J25)</f>
         <v/>
       </c>
-      <c r="K26" s="16">
+      <c r="K26" s="34">
         <f>IF($H26=1,IF($K25="",$B26,$K25&amp;"、"&amp;$B26),$K25)</f>
         <v/>
       </c>
-      <c r="L26" s="16">
+      <c r="L26" s="34">
         <f>IF($I26=1,IF($L25="",$B26,$L25&amp;"、"&amp;$B26),$L25)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="34" t="inlineStr">
         <is>
           <t>四·公德</t>
         </is>
       </c>
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B27" s="35" t="inlineStr">
         <is>
           <t>传播淫秽色情罪</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C27" s="36" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D27" s="16" t="n">
+      <c r="D27" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="E27" s="16" t="n">
+      <c r="E27" s="34" t="n">
         <v>8000</v>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="F27" s="34" t="inlineStr">
         <is>
           <t>制作/传播/贩卖淫秽色情内容</t>
         </is>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B27)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H27" s="16">
+      <c r="H27" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B27)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B27)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J27" s="16">
+      <c r="J27" s="34">
         <f>IF($G27=1,IF($J26="",$B27,$J26&amp;"、"&amp;$B27),$J26)</f>
         <v/>
       </c>
-      <c r="K27" s="16">
+      <c r="K27" s="34">
         <f>IF($H27=1,IF($K26="",$B27,$K26&amp;"、"&amp;$B27),$K26)</f>
         <v/>
       </c>
-      <c r="L27" s="16">
+      <c r="L27" s="34">
         <f>IF($I27=1,IF($L26="",$B27,$L26&amp;"、"&amp;$B27),$L26)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="A28" s="34" t="inlineStr">
         <is>
           <t>四·公德</t>
         </is>
       </c>
-      <c r="B28" s="17" t="inlineStr">
+      <c r="B28" s="35" t="inlineStr">
         <is>
           <t>歧视罪</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C28" s="36" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D28" s="16" t="n">
+      <c r="D28" s="34" t="n">
         <v>36</v>
       </c>
-      <c r="E28" s="16" t="n">
+      <c r="E28" s="34" t="n">
         <v>30000</v>
       </c>
-      <c r="F28" s="16" t="inlineStr">
+      <c r="F28" s="34" t="inlineStr">
         <is>
           <t>因受保护特征贬低/辱骂/歧视他人</t>
         </is>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B28)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H28" s="16">
+      <c r="H28" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B28)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B28)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J28" s="16">
+      <c r="J28" s="34">
         <f>IF($G28=1,IF($J27="",$B28,$J27&amp;"、"&amp;$B28),$J27)</f>
         <v/>
       </c>
-      <c r="K28" s="16">
+      <c r="K28" s="34">
         <f>IF($H28=1,IF($K27="",$B28,$K27&amp;"、"&amp;$B28),$K27)</f>
         <v/>
       </c>
-      <c r="L28" s="16">
+      <c r="L28" s="34">
         <f>IF($I28=1,IF($L27="",$B28,$L27&amp;"、"&amp;$B28),$L27)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="34" t="inlineStr">
         <is>
           <t>四·公德</t>
         </is>
       </c>
-      <c r="B29" s="17" t="inlineStr">
+      <c r="B29" s="35" t="inlineStr">
         <is>
           <t>诽谤罪</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C29" s="36" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D29" s="16" t="n">
+      <c r="D29" s="34" t="n">
         <v>24</v>
       </c>
-      <c r="E29" s="16" t="n">
+      <c r="E29" s="34" t="n">
         <v>15000</v>
       </c>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="F29" s="34" t="inlineStr">
         <is>
           <t>捏造/传播虚假信息损害名誉</t>
         </is>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B29)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H29" s="16">
+      <c r="H29" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B29)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B29)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J29" s="16">
+      <c r="J29" s="34">
         <f>IF($G29=1,IF($J28="",$B29,$J28&amp;"、"&amp;$B29),$J28)</f>
         <v/>
       </c>
-      <c r="K29" s="16">
+      <c r="K29" s="34">
         <f>IF($H29=1,IF($K28="",$B29,$K28&amp;"、"&amp;$B29),$K28)</f>
         <v/>
       </c>
-      <c r="L29" s="16">
+      <c r="L29" s="34">
         <f>IF($I29=1,IF($L28="",$B29,$L28&amp;"、"&amp;$B29),$L28)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="34" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B30" s="17" t="inlineStr">
+      <c r="B30" s="35" t="inlineStr">
         <is>
           <t>行贿罪</t>
         </is>
       </c>
-      <c r="C30" s="19" t="inlineStr">
+      <c r="C30" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D30" s="16" t="n">
+      <c r="D30" s="34" t="n">
         <v>24</v>
       </c>
-      <c r="E30" s="16" t="n">
+      <c r="E30" s="34" t="n">
         <v>20000</v>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F30" s="34" t="inlineStr">
         <is>
           <t>向政府雇员提供财物/利益以影响其职责</t>
         </is>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B30)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H30" s="16">
+      <c r="H30" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B30)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B30)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J30" s="16">
+      <c r="J30" s="34">
         <f>IF($G30=1,IF($J29="",$B30,$J29&amp;"、"&amp;$B30),$J29)</f>
         <v/>
       </c>
-      <c r="K30" s="16">
+      <c r="K30" s="34">
         <f>IF($H30=1,IF($K29="",$B30,$K29&amp;"、"&amp;$B30),$K29)</f>
         <v/>
       </c>
-      <c r="L30" s="16">
+      <c r="L30" s="34">
         <f>IF($I30=1,IF($L29="",$B30,$L29&amp;"、"&amp;$B30),$L29)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="34" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B31" s="17" t="inlineStr">
+      <c r="B31" s="35" t="inlineStr">
         <is>
           <t>妨碍司法罪</t>
         </is>
       </c>
-      <c r="C31" s="19" t="inlineStr">
+      <c r="C31" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D31" s="16" t="n">
+      <c r="D31" s="34" t="n">
         <v>36</v>
       </c>
-      <c r="E31" s="16" t="n">
+      <c r="E31" s="34" t="n">
         <v>15000</v>
       </c>
-      <c r="F31" s="16" t="inlineStr">
+      <c r="F31" s="34" t="inlineStr">
         <is>
           <t>阻碍法律文书签署/分发/执行</t>
         </is>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B31)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B31)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B31)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J31" s="16">
+      <c r="J31" s="34">
         <f>IF($G31=1,IF($J30="",$B31,$J30&amp;"、"&amp;$B31),$J30)</f>
         <v/>
       </c>
-      <c r="K31" s="16">
+      <c r="K31" s="34">
         <f>IF($H31=1,IF($K30="",$B31,$K30&amp;"、"&amp;$B31),$K30)</f>
         <v/>
       </c>
-      <c r="L31" s="16">
+      <c r="L31" s="34">
         <f>IF($I31=1,IF($L30="",$B31,$L30&amp;"、"&amp;$B31),$L30)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="34" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B32" s="17" t="inlineStr">
+      <c r="B32" s="35" t="inlineStr">
         <is>
           <t>拒绝听从执法人员命令与检查罪</t>
         </is>
       </c>
-      <c r="C32" s="18" t="inlineStr">
+      <c r="C32" s="36" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D32" s="16" t="n">
+      <c r="D32" s="34" t="n">
         <v>36</v>
       </c>
-      <c r="E32" s="16" t="n">
+      <c r="E32" s="34" t="n">
         <v>15000</v>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="F32" s="34" t="inlineStr">
         <is>
           <t>拒绝执法人员合法命令/检查</t>
         </is>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B32)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H32" s="16">
+      <c r="H32" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B32)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B32)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J32" s="16">
+      <c r="J32" s="34">
         <f>IF($G32=1,IF($J31="",$B32,$J31&amp;"、"&amp;$B32),$J31)</f>
         <v/>
       </c>
-      <c r="K32" s="16">
+      <c r="K32" s="34">
         <f>IF($H32=1,IF($K31="",$B32,$K31&amp;"、"&amp;$B32),$K31)</f>
         <v/>
       </c>
-      <c r="L32" s="16">
+      <c r="L32" s="34">
         <f>IF($I32=1,IF($L31="",$B32,$L31&amp;"、"&amp;$B32),$L31)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="34" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B33" s="17" t="inlineStr">
+      <c r="B33" s="35" t="inlineStr">
         <is>
           <t>拒绝提供身份罪</t>
         </is>
       </c>
-      <c r="C33" s="18" t="inlineStr">
+      <c r="C33" s="36" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D33" s="16" t="n">
+      <c r="D33" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="E33" s="16" t="n">
+      <c r="E33" s="34" t="n">
         <v>10000</v>
       </c>
-      <c r="F33" s="16" t="inlineStr">
+      <c r="F33" s="34" t="inlineStr">
         <is>
           <t>被扣留/逮捕后拒绝提供身份信息</t>
         </is>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B33)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H33" s="16">
+      <c r="H33" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B33)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I33" s="16">
+      <c r="I33" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B33)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J33" s="16">
+      <c r="J33" s="34">
         <f>IF($G33=1,IF($J32="",$B33,$J32&amp;"、"&amp;$B33),$J32)</f>
         <v/>
       </c>
-      <c r="K33" s="16">
+      <c r="K33" s="34">
         <f>IF($H33=1,IF($K32="",$B33,$K32&amp;"、"&amp;$B33),$K32)</f>
         <v/>
       </c>
-      <c r="L33" s="16">
+      <c r="L33" s="34">
         <f>IF($I33=1,IF($L32="",$B33,$L32&amp;"、"&amp;$B33),$L32)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="34" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B34" s="17" t="inlineStr">
+      <c r="B34" s="35" t="inlineStr">
         <is>
           <t>破坏证据罪</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="C34" s="36" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D34" s="16" t="n">
+      <c r="D34" s="34" t="n">
         <v>36</v>
       </c>
-      <c r="E34" s="16" t="n">
+      <c r="E34" s="34" t="n">
         <v>20000</v>
       </c>
-      <c r="F34" s="16" t="inlineStr">
+      <c r="F34" s="34" t="inlineStr">
         <is>
           <t>隐瞒/销毁/篡改/伪造证据</t>
         </is>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B34)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H34" s="16">
+      <c r="H34" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B34)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I34" s="16">
+      <c r="I34" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B34)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J34" s="16">
+      <c r="J34" s="34">
         <f>IF($G34=1,IF($J33="",$B34,$J33&amp;"、"&amp;$B34),$J33)</f>
         <v/>
       </c>
-      <c r="K34" s="16">
+      <c r="K34" s="34">
         <f>IF($H34=1,IF($K33="",$B34,$K33&amp;"、"&amp;$B34),$K33)</f>
         <v/>
       </c>
-      <c r="L34" s="16">
+      <c r="L34" s="34">
         <f>IF($I34=1,IF($L33="",$B34,$L33&amp;"、"&amp;$B34),$L33)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="34" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B35" s="17" t="inlineStr">
+      <c r="B35" s="35" t="inlineStr">
         <is>
           <t>冒充政府雇员罪</t>
         </is>
       </c>
-      <c r="C35" s="19" t="inlineStr">
+      <c r="C35" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D35" s="16" t="n">
+      <c r="D35" s="34" t="n">
         <v>24</v>
       </c>
-      <c r="E35" s="16" t="n">
+      <c r="E35" s="34" t="n">
         <v>15000</v>
       </c>
-      <c r="F35" s="16" t="inlineStr">
+      <c r="F35" s="34" t="inlineStr">
         <is>
           <t>假冒政府雇员身份(穿制服/佩戴徽章等)</t>
         </is>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B35)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H35" s="16">
+      <c r="H35" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B35)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I35" s="16">
+      <c r="I35" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B35)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J35" s="16">
+      <c r="J35" s="34">
         <f>IF($G35=1,IF($J34="",$B35,$J34&amp;"、"&amp;$B35),$J34)</f>
         <v/>
       </c>
-      <c r="K35" s="16">
+      <c r="K35" s="34">
         <f>IF($H35=1,IF($K34="",$B35,$K34&amp;"、"&amp;$B35),$K34)</f>
         <v/>
       </c>
-      <c r="L35" s="16">
+      <c r="L35" s="34">
         <f>IF($I35=1,IF($L34="",$B35,$L34&amp;"、"&amp;$B35),$L34)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="A36" s="34" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B36" s="17" t="inlineStr">
+      <c r="B36" s="35" t="inlineStr">
         <is>
           <t>虚假逮捕罪</t>
         </is>
       </c>
-      <c r="C36" s="19" t="inlineStr">
+      <c r="C36" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D36" s="16" t="n">
+      <c r="D36" s="34" t="n">
         <v>48</v>
       </c>
-      <c r="E36" s="16" t="n">
+      <c r="E36" s="34" t="n">
         <v>20000</v>
       </c>
-      <c r="F36" s="16" t="inlineStr">
+      <c r="F36" s="34" t="inlineStr">
         <is>
           <t>无法律依据以执法名义扣留/逮捕/没收(仅主管可起诉)</t>
         </is>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B36)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H36" s="16">
+      <c r="H36" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B36)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I36" s="16">
+      <c r="I36" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B36)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J36" s="16">
+      <c r="J36" s="34">
         <f>IF($G36=1,IF($J35="",$B36,$J35&amp;"、"&amp;$B36),$J35)</f>
         <v/>
       </c>
-      <c r="K36" s="16">
+      <c r="K36" s="34">
         <f>IF($H36=1,IF($K35="",$B36,$K35&amp;"、"&amp;$B36),$K35)</f>
         <v/>
       </c>
-      <c r="L36" s="16">
+      <c r="L36" s="34">
         <f>IF($I36=1,IF($L35="",$B36,$L35&amp;"、"&amp;$B36),$L35)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="inlineStr">
+      <c r="A37" s="34" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B37" s="17" t="inlineStr">
+      <c r="B37" s="35" t="inlineStr">
         <is>
           <t>伪证罪</t>
         </is>
       </c>
-      <c r="C37" s="19" t="inlineStr">
+      <c r="C37" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="D37" s="34" t="n">
         <v>48</v>
       </c>
-      <c r="E37" s="16" t="n">
+      <c r="E37" s="34" t="n">
         <v>25000</v>
       </c>
-      <c r="F37" s="16" t="inlineStr">
+      <c r="F37" s="34" t="inlineStr">
         <is>
           <t>司法程序中提供虚假证言/信息</t>
         </is>
       </c>
-      <c r="G37" s="16">
+      <c r="G37" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B37)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H37" s="16">
+      <c r="H37" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B37)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I37" s="16">
+      <c r="I37" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B37)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J37" s="16">
+      <c r="J37" s="34">
         <f>IF($G37=1,IF($J36="",$B37,$J36&amp;"、"&amp;$B37),$J36)</f>
         <v/>
       </c>
-      <c r="K37" s="16">
+      <c r="K37" s="34">
         <f>IF($H37=1,IF($K36="",$B37,$K36&amp;"、"&amp;$B37),$K36)</f>
         <v/>
       </c>
-      <c r="L37" s="16">
+      <c r="L37" s="34">
         <f>IF($I37=1,IF($L36="",$B37,$L36&amp;"、"&amp;$B37),$L36)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="A38" s="34" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B38" s="17" t="inlineStr">
+      <c r="B38" s="35" t="inlineStr">
         <is>
           <t>冒充律师罪</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C38" s="36" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D38" s="16" t="n">
+      <c r="D38" s="34" t="n">
         <v>36</v>
       </c>
-      <c r="E38" s="16" t="n">
+      <c r="E38" s="34" t="n">
         <v>15000</v>
       </c>
-      <c r="F38" s="16" t="inlineStr">
+      <c r="F38" s="34" t="inlineStr">
         <is>
           <t>未经认证从事律师业务/假扮律师</t>
         </is>
       </c>
-      <c r="G38" s="16">
+      <c r="G38" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B38)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H38" s="16">
+      <c r="H38" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B38)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I38" s="16">
+      <c r="I38" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B38)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J38" s="16">
+      <c r="J38" s="34">
         <f>IF($G38=1,IF($J37="",$B38,$J37&amp;"、"&amp;$B38),$J37)</f>
         <v/>
       </c>
-      <c r="K38" s="16">
+      <c r="K38" s="34">
         <f>IF($H38=1,IF($K37="",$B38,$K37&amp;"、"&amp;$B38),$K37)</f>
         <v/>
       </c>
-      <c r="L38" s="16">
+      <c r="L38" s="34">
         <f>IF($I38=1,IF($L37="",$B38,$L37&amp;"、"&amp;$B38),$L37)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="inlineStr">
+      <c r="A39" s="34" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B39" s="17" t="inlineStr">
+      <c r="B39" s="35" t="inlineStr">
         <is>
           <t>妨碍政府雇员执行公务罪</t>
         </is>
       </c>
-      <c r="C39" s="19" t="inlineStr">
+      <c r="C39" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D39" s="16" t="n">
+      <c r="D39" s="34" t="n">
         <v>36</v>
       </c>
-      <c r="E39" s="16" t="n">
+      <c r="E39" s="34" t="n">
         <v>15000</v>
       </c>
-      <c r="F39" s="16" t="inlineStr">
+      <c r="F39" s="34" t="inlineStr">
         <is>
           <t>抵抗/延误/阻碍执法/消防/急救/司法人员执行职责</t>
         </is>
       </c>
-      <c r="G39" s="16">
+      <c r="G39" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B39)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H39" s="16">
+      <c r="H39" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B39)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I39" s="16">
+      <c r="I39" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B39)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J39" s="16">
+      <c r="J39" s="34">
         <f>IF($G39=1,IF($J38="",$B39,$J38&amp;"、"&amp;$B39),$J38)</f>
         <v/>
       </c>
-      <c r="K39" s="16">
+      <c r="K39" s="34">
         <f>IF($H39=1,IF($K38="",$B39,$K38&amp;"、"&amp;$B39),$K38)</f>
         <v/>
       </c>
-      <c r="L39" s="16">
+      <c r="L39" s="34">
         <f>IF($I39=1,IF($L38="",$B39,$L38&amp;"、"&amp;$B39),$L38)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="inlineStr">
+      <c r="A40" s="34" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B40" s="17" t="inlineStr">
+      <c r="B40" s="35" t="inlineStr">
         <is>
           <t>拒捕罪</t>
         </is>
       </c>
-      <c r="C40" s="19" t="inlineStr">
+      <c r="C40" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D40" s="16" t="n">
+      <c r="D40" s="34" t="n">
         <v>36</v>
       </c>
-      <c r="E40" s="16" t="n">
+      <c r="E40" s="34" t="n">
         <v>15000</v>
       </c>
-      <c r="F40" s="16" t="inlineStr">
+      <c r="F40" s="34" t="inlineStr">
         <is>
           <t>逮捕时以任何方式拒绝/抗拒/逃避逮捕</t>
         </is>
       </c>
-      <c r="G40" s="16">
+      <c r="G40" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B40)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H40" s="16">
+      <c r="H40" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B40)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I40" s="16">
+      <c r="I40" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B40)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J40" s="16">
+      <c r="J40" s="34">
         <f>IF($G40=1,IF($J39="",$B40,$J39&amp;"、"&amp;$B40),$J39)</f>
         <v/>
       </c>
-      <c r="K40" s="16">
+      <c r="K40" s="34">
         <f>IF($H40=1,IF($K39="",$B40,$K39&amp;"、"&amp;$B40),$K39)</f>
         <v/>
       </c>
-      <c r="L40" s="16">
+      <c r="L40" s="34">
         <f>IF($I40=1,IF($L39="",$B40,$L39&amp;"、"&amp;$B40),$L39)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="inlineStr">
+      <c r="A41" s="34" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B41" s="17" t="inlineStr">
+      <c r="B41" s="35" t="inlineStr">
         <is>
           <t>逃避羁押罪</t>
         </is>
       </c>
-      <c r="C41" s="19" t="inlineStr">
+      <c r="C41" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D41" s="16" t="n">
+      <c r="D41" s="34" t="n">
         <v>36</v>
       </c>
-      <c r="E41" s="16" t="n">
+      <c r="E41" s="34" t="n">
         <v>10000</v>
       </c>
-      <c r="F41" s="16" t="inlineStr">
+      <c r="F41" s="34" t="inlineStr">
         <is>
           <t>被合法扣留/逮捕后逃脱监护</t>
         </is>
       </c>
-      <c r="G41" s="16">
+      <c r="G41" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B41)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H41" s="16">
+      <c r="H41" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B41)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I41" s="16">
+      <c r="I41" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B41)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J41" s="16">
+      <c r="J41" s="34">
         <f>IF($G41=1,IF($J40="",$B41,$J40&amp;"、"&amp;$B41),$J40)</f>
         <v/>
       </c>
-      <c r="K41" s="16">
+      <c r="K41" s="34">
         <f>IF($H41=1,IF($K40="",$B41,$K40&amp;"、"&amp;$B41),$K40)</f>
         <v/>
       </c>
-      <c r="L41" s="16">
+      <c r="L41" s="34">
         <f>IF($I41=1,IF($L40="",$B41,$L40&amp;"、"&amp;$B41),$L40)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="16" t="inlineStr">
+      <c r="A42" s="34" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B42" s="17" t="inlineStr">
+      <c r="B42" s="35" t="inlineStr">
         <is>
           <t>藐视法庭罪</t>
         </is>
       </c>
-      <c r="C42" s="19" t="inlineStr">
+      <c r="C42" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D42" s="16" t="n">
+      <c r="D42" s="34" t="n">
         <v>48</v>
       </c>
-      <c r="E42" s="16" t="n">
+      <c r="E42" s="34" t="n">
         <v>25000</v>
       </c>
-      <c r="F42" s="16" t="inlineStr">
+      <c r="F42" s="34" t="inlineStr">
         <is>
           <t>扰乱法庭秩序/无视法庭命令(须法官当庭宣布)</t>
         </is>
       </c>
-      <c r="G42" s="16">
+      <c r="G42" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B42)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H42" s="16">
+      <c r="H42" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B42)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I42" s="16">
+      <c r="I42" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B42)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J42" s="16">
+      <c r="J42" s="34">
         <f>IF($G42=1,IF($J41="",$B42,$J41&amp;"、"&amp;$B42),$J41)</f>
         <v/>
       </c>
-      <c r="K42" s="16">
+      <c r="K42" s="34">
         <f>IF($H42=1,IF($K41="",$B42,$K41&amp;"、"&amp;$B42),$K41)</f>
         <v/>
       </c>
-      <c r="L42" s="16">
+      <c r="L42" s="34">
         <f>IF($I42=1,IF($L41="",$B42,$L41&amp;"、"&amp;$B42),$L41)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="inlineStr">
+      <c r="A43" s="34" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B43" s="17" t="inlineStr">
+      <c r="B43" s="35" t="inlineStr">
         <is>
           <t>恶意占用公共资源罪</t>
         </is>
       </c>
-      <c r="C43" s="18" t="inlineStr">
+      <c r="C43" s="36" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D43" s="16" t="n">
+      <c r="D43" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="E43" s="16" t="n">
+      <c r="E43" s="34" t="n">
         <v>5000</v>
       </c>
-      <c r="F43" s="16" t="inlineStr">
+      <c r="F43" s="34" t="inlineStr">
         <is>
           <t>非紧急/恶意占用政府紧急热线</t>
         </is>
       </c>
-      <c r="G43" s="16">
+      <c r="G43" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B43)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H43" s="16">
+      <c r="H43" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B43)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I43" s="16">
+      <c r="I43" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B43)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J43" s="16">
+      <c r="J43" s="34">
         <f>IF($G43=1,IF($J42="",$B43,$J42&amp;"、"&amp;$B43),$J42)</f>
         <v/>
       </c>
-      <c r="K43" s="16">
+      <c r="K43" s="34">
         <f>IF($H43=1,IF($K42="",$B43,$K42&amp;"、"&amp;$B43),$K42)</f>
         <v/>
       </c>
-      <c r="L43" s="16">
+      <c r="L43" s="34">
         <f>IF($I43=1,IF($L42="",$B43,$L42&amp;"、"&amp;$B43),$L42)</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="16" t="inlineStr">
+      <c r="A44" s="34" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B44" s="17" t="inlineStr">
+      <c r="B44" s="35" t="inlineStr">
         <is>
           <t>未经许可进入封闭紧急区域罪</t>
         </is>
       </c>
-      <c r="C44" s="18" t="inlineStr">
+      <c r="C44" s="36" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D44" s="16" t="n">
+      <c r="D44" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="E44" s="16" t="n">
+      <c r="E44" s="34" t="n">
         <v>15000</v>
       </c>
-      <c r="F44" s="16" t="inlineStr">
+      <c r="F44" s="34" t="inlineStr">
         <is>
           <t>未经授权进入被警戒线封闭的紧急区域</t>
         </is>
       </c>
-      <c r="G44" s="16">
+      <c r="G44" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B44)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H44" s="16">
+      <c r="H44" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B44)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I44" s="16">
+      <c r="I44" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B44)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J44" s="16">
+      <c r="J44" s="34">
         <f>IF($G44=1,IF($J43="",$B44,$J43&amp;"、"&amp;$B44),$J43)</f>
         <v/>
       </c>
-      <c r="K44" s="16">
+      <c r="K44" s="34">
         <f>IF($H44=1,IF($K43="",$B44,$K43&amp;"、"&amp;$B44),$K43)</f>
         <v/>
       </c>
-      <c r="L44" s="16">
+      <c r="L44" s="34">
         <f>IF($I44=1,IF($L43="",$B44,$L43&amp;"、"&amp;$B44),$L43)</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="inlineStr">
+      <c r="A45" s="34" t="inlineStr">
         <is>
           <t>五·司法</t>
         </is>
       </c>
-      <c r="B45" s="17" t="inlineStr">
+      <c r="B45" s="35" t="inlineStr">
         <is>
           <t>袭警罪</t>
         </is>
       </c>
-      <c r="C45" s="19" t="inlineStr">
+      <c r="C45" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D45" s="16" t="n">
+      <c r="D45" s="34" t="n">
         <v>48</v>
       </c>
-      <c r="E45" s="16" t="n">
+      <c r="E45" s="34" t="n">
         <v>25000</v>
       </c>
-      <c r="F45" s="16" t="inlineStr">
+      <c r="F45" s="34" t="inlineStr">
         <is>
           <t>袭击/伤害警务人员/警车/警犬</t>
         </is>
       </c>
-      <c r="G45" s="16">
+      <c r="G45" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B45)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H45" s="16">
+      <c r="H45" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B45)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I45" s="16">
+      <c r="I45" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B45)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J45" s="16">
+      <c r="J45" s="34">
         <f>IF($G45=1,IF($J44="",$B45,$J44&amp;"、"&amp;$B45),$J44)</f>
         <v/>
       </c>
-      <c r="K45" s="16">
+      <c r="K45" s="34">
         <f>IF($H45=1,IF($K44="",$B45,$K44&amp;"、"&amp;$B45),$K44)</f>
         <v/>
       </c>
-      <c r="L45" s="16">
+      <c r="L45" s="34">
         <f>IF($I45=1,IF($L44="",$B45,$L44&amp;"、"&amp;$B45),$L44)</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="16" t="inlineStr">
+      <c r="A46" s="34" t="inlineStr">
         <is>
           <t>六·秩序</t>
         </is>
       </c>
-      <c r="B46" s="17" t="inlineStr">
+      <c r="B46" s="35" t="inlineStr">
         <is>
           <t>扰乱治安罪</t>
         </is>
       </c>
-      <c r="C46" s="18" t="inlineStr">
+      <c r="C46" s="36" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D46" s="16" t="n">
+      <c r="D46" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="E46" s="16" t="n">
+      <c r="E46" s="34" t="n">
         <v>5000</v>
       </c>
-      <c r="F46" s="16" t="inlineStr">
+      <c r="F46" s="34" t="inlineStr">
         <is>
           <t>公共场所挑衅/扰乱/冒犯性言语</t>
         </is>
       </c>
-      <c r="G46" s="16">
+      <c r="G46" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B46)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H46" s="16">
+      <c r="H46" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B46)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I46" s="16">
+      <c r="I46" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B46)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J46" s="16">
+      <c r="J46" s="34">
         <f>IF($G46=1,IF($J45="",$B46,$J45&amp;"、"&amp;$B46),$J45)</f>
         <v/>
       </c>
-      <c r="K46" s="16">
+      <c r="K46" s="34">
         <f>IF($H46=1,IF($K45="",$B46,$K45&amp;"、"&amp;$B46),$K45)</f>
         <v/>
       </c>
-      <c r="L46" s="16">
+      <c r="L46" s="34">
         <f>IF($I46=1,IF($L45="",$B46,$L45&amp;"、"&amp;$B46),$L45)</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="inlineStr">
+      <c r="A47" s="34" t="inlineStr">
         <is>
           <t>六·秩序</t>
         </is>
       </c>
-      <c r="B47" s="17" t="inlineStr">
+      <c r="B47" s="35" t="inlineStr">
         <is>
           <t>非法集会罪</t>
         </is>
       </c>
-      <c r="C47" s="18" t="inlineStr">
+      <c r="C47" s="36" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D47" s="16" t="n">
+      <c r="D47" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="E47" s="16" t="n">
+      <c r="E47" s="34" t="n">
         <v>20000</v>
       </c>
-      <c r="F47" s="16" t="inlineStr">
+      <c r="F47" s="34" t="inlineStr">
         <is>
           <t>两人以上聚集引发骚乱/非法行动</t>
         </is>
       </c>
-      <c r="G47" s="16">
+      <c r="G47" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B47)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H47" s="16">
+      <c r="H47" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B47)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I47" s="16">
+      <c r="I47" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B47)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J47" s="16">
+      <c r="J47" s="34">
         <f>IF($G47=1,IF($J46="",$B47,$J46&amp;"、"&amp;$B47),$J46)</f>
         <v/>
       </c>
-      <c r="K47" s="16">
+      <c r="K47" s="34">
         <f>IF($H47=1,IF($K46="",$B47,$K46&amp;"、"&amp;$B47),$K46)</f>
         <v/>
       </c>
-      <c r="L47" s="16">
+      <c r="L47" s="34">
         <f>IF($I47=1,IF($L46="",$B47,$L46&amp;"、"&amp;$B47),$L46)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="inlineStr">
+      <c r="A48" s="34" t="inlineStr">
         <is>
           <t>六·秩序</t>
         </is>
       </c>
-      <c r="B48" s="17" t="inlineStr">
+      <c r="B48" s="35" t="inlineStr">
         <is>
           <t>煽动暴乱罪</t>
         </is>
       </c>
-      <c r="C48" s="19" t="inlineStr">
+      <c r="C48" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D48" s="16" t="n">
+      <c r="D48" s="34" t="n">
         <v>48</v>
       </c>
-      <c r="E48" s="16" t="n">
+      <c r="E48" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="F48" s="16" t="inlineStr">
+      <c r="F48" s="34" t="inlineStr">
         <is>
           <t>意图引起暴乱/鼓励他人暴力破坏(仅监禁)</t>
         </is>
       </c>
-      <c r="G48" s="16">
+      <c r="G48" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B48)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H48" s="16">
+      <c r="H48" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B48)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I48" s="16">
+      <c r="I48" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B48)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J48" s="16">
+      <c r="J48" s="34">
         <f>IF($G48=1,IF($J47="",$B48,$J47&amp;"、"&amp;$B48),$J47)</f>
         <v/>
       </c>
-      <c r="K48" s="16">
+      <c r="K48" s="34">
         <f>IF($H48=1,IF($K47="",$B48,$K47&amp;"、"&amp;$B48),$K47)</f>
         <v/>
       </c>
-      <c r="L48" s="16">
+      <c r="L48" s="34">
         <f>IF($I48=1,IF($L47="",$B48,$L47&amp;"、"&amp;$B48),$L47)</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="16" t="inlineStr">
+      <c r="A49" s="34" t="inlineStr">
         <is>
           <t>六·秩序</t>
         </is>
       </c>
-      <c r="B49" s="17" t="inlineStr">
+      <c r="B49" s="35" t="inlineStr">
         <is>
           <t>遮挡面部罪</t>
         </is>
       </c>
-      <c r="C49" s="18" t="inlineStr">
+      <c r="C49" s="36" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D49" s="16" t="n">
+      <c r="D49" s="34" t="n">
         <v>24</v>
       </c>
-      <c r="E49" s="16" t="n">
+      <c r="E49" s="34" t="n">
         <v>5000</v>
       </c>
-      <c r="F49" s="16" t="inlineStr">
+      <c r="F49" s="34" t="inlineStr">
         <is>
           <t>遮面拒揭 / 犯罪过程中遮面(节庆等除外)</t>
         </is>
       </c>
-      <c r="G49" s="16">
+      <c r="G49" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B49)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H49" s="16">
+      <c r="H49" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B49)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I49" s="16">
+      <c r="I49" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B49)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J49" s="16">
+      <c r="J49" s="34">
         <f>IF($G49=1,IF($J48="",$B49,$J48&amp;"、"&amp;$B49),$J48)</f>
         <v/>
       </c>
-      <c r="K49" s="16">
+      <c r="K49" s="34">
         <f>IF($H49=1,IF($K48="",$B49,$K48&amp;"、"&amp;$B49),$K48)</f>
         <v/>
       </c>
-      <c r="L49" s="16">
+      <c r="L49" s="34">
         <f>IF($I49=1,IF($L48="",$B49,$L48&amp;"、"&amp;$B49),$L48)</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="16" t="inlineStr">
+      <c r="A50" s="34" t="inlineStr">
         <is>
           <t>七·热武器</t>
         </is>
       </c>
-      <c r="B50" s="17" t="inlineStr">
+      <c r="B50" s="35" t="inlineStr">
         <is>
           <t>非法持有热武器罪</t>
         </is>
       </c>
-      <c r="C50" s="19" t="inlineStr">
+      <c r="C50" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D50" s="16" t="n">
+      <c r="D50" s="34" t="n">
         <v>24</v>
       </c>
-      <c r="E50" s="16" t="n">
+      <c r="E50" s="34" t="n">
         <v>15000</v>
       </c>
-      <c r="F50" s="16" t="inlineStr">
+      <c r="F50" s="34" t="inlineStr">
         <is>
           <t>无证/非法持有枪支/爆炸物(执法公务除外)</t>
         </is>
       </c>
-      <c r="G50" s="16">
+      <c r="G50" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B50)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H50" s="16">
+      <c r="H50" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B50)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I50" s="16">
+      <c r="I50" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B50)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J50" s="16">
+      <c r="J50" s="34">
         <f>IF($G50=1,IF($J49="",$B50,$J49&amp;"、"&amp;$B50),$J49)</f>
         <v/>
       </c>
-      <c r="K50" s="16">
+      <c r="K50" s="34">
         <f>IF($H50=1,IF($K49="",$B50,$K49&amp;"、"&amp;$B50),$K49)</f>
         <v/>
       </c>
-      <c r="L50" s="16">
+      <c r="L50" s="34">
         <f>IF($I50=1,IF($L49="",$B50,$L49&amp;"、"&amp;$B50),$L49)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="16" t="inlineStr">
+      <c r="A51" s="34" t="inlineStr">
         <is>
           <t>七·热武器</t>
         </is>
       </c>
-      <c r="B51" s="17" t="inlineStr">
+      <c r="B51" s="35" t="inlineStr">
         <is>
           <t>非法展示热武器罪</t>
         </is>
       </c>
-      <c r="C51" s="18" t="inlineStr">
+      <c r="C51" s="36" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D51" s="16" t="n">
+      <c r="D51" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="E51" s="16" t="n">
+      <c r="E51" s="34" t="n">
         <v>8000</v>
       </c>
-      <c r="F51" s="16" t="inlineStr">
+      <c r="F51" s="34" t="inlineStr">
         <is>
           <t>公共场所公开携带/挥舞展示武器</t>
         </is>
       </c>
-      <c r="G51" s="16">
+      <c r="G51" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B51)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H51" s="16">
+      <c r="H51" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B51)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I51" s="16">
+      <c r="I51" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B51)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J51" s="16">
+      <c r="J51" s="34">
         <f>IF($G51=1,IF($J50="",$B51,$J50&amp;"、"&amp;$B51),$J50)</f>
         <v/>
       </c>
-      <c r="K51" s="16">
+      <c r="K51" s="34">
         <f>IF($H51=1,IF($K50="",$B51,$K50&amp;"、"&amp;$B51),$K50)</f>
         <v/>
       </c>
-      <c r="L51" s="16">
+      <c r="L51" s="34">
         <f>IF($I51=1,IF($L50="",$B51,$L50&amp;"、"&amp;$B51),$L50)</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="16" t="inlineStr">
+      <c r="A52" s="34" t="inlineStr">
         <is>
           <t>七·热武器</t>
         </is>
       </c>
-      <c r="B52" s="17" t="inlineStr">
+      <c r="B52" s="35" t="inlineStr">
         <is>
           <t>非法使用热武器罪</t>
         </is>
       </c>
-      <c r="C52" s="19" t="inlineStr">
+      <c r="C52" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D52" s="16" t="n">
+      <c r="D52" s="34" t="n">
         <v>24</v>
       </c>
-      <c r="E52" s="16" t="n">
+      <c r="E52" s="34" t="n">
         <v>15000</v>
       </c>
-      <c r="F52" s="16" t="inlineStr">
+      <c r="F52" s="34" t="inlineStr">
         <is>
           <t>鲁莽/蓄意/威胁公共安全方式开枪</t>
         </is>
       </c>
-      <c r="G52" s="16">
+      <c r="G52" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B52)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H52" s="16">
+      <c r="H52" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B52)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I52" s="16">
+      <c r="I52" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B52)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J52" s="16">
+      <c r="J52" s="34">
         <f>IF($G52=1,IF($J51="",$B52,$J51&amp;"、"&amp;$B52),$J51)</f>
         <v/>
       </c>
-      <c r="K52" s="16">
+      <c r="K52" s="34">
         <f>IF($H52=1,IF($K51="",$B52,$K51&amp;"、"&amp;$B52),$K51)</f>
         <v/>
       </c>
-      <c r="L52" s="16">
+      <c r="L52" s="34">
         <f>IF($I52=1,IF($L51="",$B52,$L51&amp;"、"&amp;$B52),$L51)</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="16" t="inlineStr">
+      <c r="A53" s="34" t="inlineStr">
         <is>
           <t>七·热武器</t>
         </is>
       </c>
-      <c r="B53" s="17" t="inlineStr">
+      <c r="B53" s="35" t="inlineStr">
         <is>
           <t>非法贩卖武器罪</t>
         </is>
       </c>
-      <c r="C53" s="19" t="inlineStr">
+      <c r="C53" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D53" s="16" t="n">
+      <c r="D53" s="34" t="n">
         <v>48</v>
       </c>
-      <c r="E53" s="16" t="n">
+      <c r="E53" s="34" t="n">
         <v>25000</v>
       </c>
-      <c r="F53" s="16" t="inlineStr">
+      <c r="F53" s="34" t="inlineStr">
         <is>
           <t>贩卖/转让/出售非法或未认证武器</t>
         </is>
       </c>
-      <c r="G53" s="16">
+      <c r="G53" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B53)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H53" s="16">
+      <c r="H53" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B53)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I53" s="16">
+      <c r="I53" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B53)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J53" s="16">
+      <c r="J53" s="34">
         <f>IF($G53=1,IF($J52="",$B53,$J52&amp;"、"&amp;$B53),$J52)</f>
         <v/>
       </c>
-      <c r="K53" s="16">
+      <c r="K53" s="34">
         <f>IF($H53=1,IF($K52="",$B53,$K52&amp;"、"&amp;$B53),$K52)</f>
         <v/>
       </c>
-      <c r="L53" s="16">
+      <c r="L53" s="34">
         <f>IF($I53=1,IF($L52="",$B53,$L52&amp;"、"&amp;$B53),$L52)</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="16" t="inlineStr">
+      <c r="A54" s="34" t="inlineStr">
         <is>
           <t>七·热武器</t>
         </is>
       </c>
-      <c r="B54" s="17" t="inlineStr">
+      <c r="B54" s="35" t="inlineStr">
         <is>
           <t>走私罪</t>
         </is>
       </c>
-      <c r="C54" s="19" t="inlineStr">
+      <c r="C54" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D54" s="16" t="n">
+      <c r="D54" s="34" t="n">
         <v>48</v>
       </c>
-      <c r="E54" s="16" t="n">
+      <c r="E54" s="34" t="n">
         <v>30000</v>
       </c>
-      <c r="F54" s="16" t="inlineStr">
+      <c r="F54" s="34" t="inlineStr">
         <is>
           <t>非法运输/转让武器爆炸物 / 参与军火走私</t>
         </is>
       </c>
-      <c r="G54" s="16">
+      <c r="G54" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B54)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H54" s="16">
+      <c r="H54" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B54)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I54" s="16">
+      <c r="I54" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B54)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J54" s="16">
+      <c r="J54" s="34">
         <f>IF($G54=1,IF($J53="",$B54,$J53&amp;"、"&amp;$B54),$J53)</f>
         <v/>
       </c>
-      <c r="K54" s="16">
+      <c r="K54" s="34">
         <f>IF($H54=1,IF($K53="",$B54,$K53&amp;"、"&amp;$B54),$K53)</f>
         <v/>
       </c>
-      <c r="L54" s="16">
+      <c r="L54" s="34">
         <f>IF($I54=1,IF($L53="",$B54,$L53&amp;"、"&amp;$B54),$L53)</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="16" t="inlineStr">
+      <c r="A55" s="34" t="inlineStr">
         <is>
           <t>十·公共安全</t>
         </is>
       </c>
-      <c r="B55" s="17" t="inlineStr">
+      <c r="B55" s="35" t="inlineStr">
         <is>
           <t>非法持有管制物品罪</t>
         </is>
       </c>
-      <c r="C55" s="19" t="inlineStr">
+      <c r="C55" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D55" s="16" t="n">
+      <c r="D55" s="34" t="n">
         <v>48</v>
       </c>
-      <c r="E55" s="16" t="n">
+      <c r="E55" s="34" t="n">
         <v>30000</v>
       </c>
-      <c r="F55" s="16" t="inlineStr">
+      <c r="F55" s="34" t="inlineStr">
         <is>
           <t>默认毒品/非法枪支(重罪4年$30000); 工具/8cm刀具=轻罪1年$15000</t>
         </is>
       </c>
-      <c r="G55" s="16">
+      <c r="G55" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B55)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H55" s="16">
+      <c r="H55" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B55)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I55" s="16">
+      <c r="I55" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B55)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J55" s="16">
+      <c r="J55" s="34">
         <f>IF($G55=1,IF($J54="",$B55,$J54&amp;"、"&amp;$B55),$J54)</f>
         <v/>
       </c>
-      <c r="K55" s="16">
+      <c r="K55" s="34">
         <f>IF($H55=1,IF($K54="",$B55,$K54&amp;"、"&amp;$B55),$K54)</f>
         <v/>
       </c>
-      <c r="L55" s="16">
+      <c r="L55" s="34">
         <f>IF($I55=1,IF($L54="",$B55,$L54&amp;"、"&amp;$B55),$L54)</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="16" t="inlineStr">
+      <c r="A56" s="34" t="inlineStr">
         <is>
           <t>十·公共安全</t>
         </is>
       </c>
-      <c r="B56" s="17" t="inlineStr">
+      <c r="B56" s="35" t="inlineStr">
         <is>
           <t>非法持有大量管制物品罪</t>
         </is>
       </c>
-      <c r="C56" s="19" t="inlineStr">
+      <c r="C56" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D56" s="16" t="n">
+      <c r="D56" s="34" t="n">
         <v>36</v>
       </c>
-      <c r="E56" s="16" t="n">
+      <c r="E56" s="34" t="n">
         <v>6000</v>
       </c>
-      <c r="F56" s="16" t="inlineStr">
+      <c r="F56" s="34" t="inlineStr">
         <is>
           <t>按量: 10-50个=3年$6000; 51-200=2-4年$10000; 201-500=4-6年$15000; 501-999=6-10年$30000(可超5年)</t>
         </is>
       </c>
-      <c r="G56" s="16">
+      <c r="G56" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B56)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H56" s="16">
+      <c r="H56" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B56)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I56" s="16">
+      <c r="I56" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B56)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J56" s="16">
+      <c r="J56" s="34">
         <f>IF($G56=1,IF($J55="",$B56,$J55&amp;"、"&amp;$B56),$J55)</f>
         <v/>
       </c>
-      <c r="K56" s="16">
+      <c r="K56" s="34">
         <f>IF($H56=1,IF($K55="",$B56,$K55&amp;"、"&amp;$B56),$K55)</f>
         <v/>
       </c>
-      <c r="L56" s="16">
+      <c r="L56" s="34">
         <f>IF($I56=1,IF($L55="",$B56,$L55&amp;"、"&amp;$B56),$L55)</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="16" t="inlineStr">
+      <c r="A57" s="34" t="inlineStr">
         <is>
           <t>十·公共安全</t>
         </is>
       </c>
-      <c r="B57" s="17" t="inlineStr">
+      <c r="B57" s="35" t="inlineStr">
         <is>
           <t>非法经营和分发管制物品罪</t>
         </is>
       </c>
-      <c r="C57" s="19" t="inlineStr">
+      <c r="C57" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D57" s="16" t="n">
+      <c r="D57" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="E57" s="16" t="n">
+      <c r="E57" s="34" t="n">
         <v>5000</v>
       </c>
-      <c r="F57" s="16" t="inlineStr">
+      <c r="F57" s="34" t="inlineStr">
         <is>
           <t>以出售/分发/储存为目的经营管制物品</t>
         </is>
       </c>
-      <c r="G57" s="16">
+      <c r="G57" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B57)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H57" s="16">
+      <c r="H57" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B57)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I57" s="16">
+      <c r="I57" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B57)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J57" s="16">
+      <c r="J57" s="34">
         <f>IF($G57=1,IF($J56="",$B57,$J56&amp;"、"&amp;$B57),$J56)</f>
         <v/>
       </c>
-      <c r="K57" s="16">
+      <c r="K57" s="34">
         <f>IF($H57=1,IF($K56="",$B57,$K56&amp;"、"&amp;$B57),$K56)</f>
         <v/>
       </c>
-      <c r="L57" s="16">
+      <c r="L57" s="34">
         <f>IF($I57=1,IF($L56="",$B57,$L56&amp;"、"&amp;$B57),$L56)</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="16" t="inlineStr">
+      <c r="A58" s="34" t="inlineStr">
         <is>
           <t>十·公共安全</t>
         </is>
       </c>
-      <c r="B58" s="17" t="inlineStr">
+      <c r="B58" s="35" t="inlineStr">
         <is>
           <t>非法制造管制物品罪</t>
         </is>
       </c>
-      <c r="C58" s="19" t="inlineStr">
+      <c r="C58" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D58" s="16" t="n">
+      <c r="D58" s="34" t="n">
         <v>24</v>
       </c>
-      <c r="E58" s="16" t="n">
+      <c r="E58" s="34" t="n">
         <v>8000</v>
       </c>
-      <c r="F58" s="16" t="inlineStr">
+      <c r="F58" s="34" t="inlineStr">
         <is>
           <t>生产/制造处方药/大麻等管制物品</t>
         </is>
       </c>
-      <c r="G58" s="16">
+      <c r="G58" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B58)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H58" s="16">
+      <c r="H58" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B58)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I58" s="16">
+      <c r="I58" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B58)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J58" s="16">
+      <c r="J58" s="34">
         <f>IF($G58=1,IF($J57="",$B58,$J57&amp;"、"&amp;$B58),$J57)</f>
         <v/>
       </c>
-      <c r="K58" s="16">
+      <c r="K58" s="34">
         <f>IF($H58=1,IF($K57="",$B58,$K57&amp;"、"&amp;$B58),$K57)</f>
         <v/>
       </c>
-      <c r="L58" s="16">
+      <c r="L58" s="34">
         <f>IF($I58=1,IF($L57="",$B58,$L57&amp;"、"&amp;$B58),$L57)</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="16" t="inlineStr">
+      <c r="A59" s="34" t="inlineStr">
         <is>
           <t>十·公共安全</t>
         </is>
       </c>
-      <c r="B59" s="17" t="inlineStr">
+      <c r="B59" s="35" t="inlineStr">
         <is>
           <t>非法贩卖管制物品罪</t>
         </is>
       </c>
-      <c r="C59" s="19" t="inlineStr">
+      <c r="C59" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D59" s="16" t="n">
+      <c r="D59" s="34" t="n">
         <v>36</v>
       </c>
-      <c r="E59" s="16" t="n">
+      <c r="E59" s="34" t="n">
         <v>10000</v>
       </c>
-      <c r="F59" s="16" t="inlineStr">
+      <c r="F59" s="34" t="inlineStr">
         <is>
           <t>非法出售/赠送/运输管制物品给他人</t>
         </is>
       </c>
-      <c r="G59" s="16">
+      <c r="G59" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B59)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H59" s="16">
+      <c r="H59" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B59)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I59" s="16">
+      <c r="I59" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B59)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J59" s="16">
+      <c r="J59" s="34">
         <f>IF($G59=1,IF($J58="",$B59,$J58&amp;"、"&amp;$B59),$J58)</f>
         <v/>
       </c>
-      <c r="K59" s="16">
+      <c r="K59" s="34">
         <f>IF($H59=1,IF($K58="",$B59,$K58&amp;"、"&amp;$B59),$K58)</f>
         <v/>
       </c>
-      <c r="L59" s="16">
+      <c r="L59" s="34">
         <f>IF($I59=1,IF($L58="",$B59,$L58&amp;"、"&amp;$B59),$L58)</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="16" t="inlineStr">
+      <c r="A60" s="34" t="inlineStr">
         <is>
           <t>十一·其他</t>
         </is>
       </c>
-      <c r="B60" s="17" t="inlineStr">
+      <c r="B60" s="35" t="inlineStr">
         <is>
           <t>有组织犯罪</t>
         </is>
       </c>
-      <c r="C60" s="19" t="inlineStr">
+      <c r="C60" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D60" s="16" t="n">
+      <c r="D60" s="34" t="n">
         <v>24</v>
       </c>
-      <c r="E60" s="16" t="n">
+      <c r="E60" s="34" t="n">
         <v>10000</v>
       </c>
-      <c r="F60" s="16" t="inlineStr">
+      <c r="F60" s="34" t="inlineStr">
         <is>
           <t>团体以牟利为目的实施违法犯罪(逮捕须先取逮捕令)</t>
         </is>
       </c>
-      <c r="G60" s="16">
+      <c r="G60" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B60)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H60" s="16">
+      <c r="H60" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B60)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I60" s="16">
+      <c r="I60" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B60)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J60" s="16">
+      <c r="J60" s="34">
         <f>IF($G60=1,IF($J59="",$B60,$J59&amp;"、"&amp;$B60),$J59)</f>
         <v/>
       </c>
-      <c r="K60" s="16">
+      <c r="K60" s="34">
         <f>IF($H60=1,IF($K59="",$B60,$K59&amp;"、"&amp;$B60),$K59)</f>
         <v/>
       </c>
-      <c r="L60" s="16">
+      <c r="L60" s="34">
         <f>IF($I60=1,IF($L59="",$B60,$L59&amp;"、"&amp;$B60),$L59)</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="16" t="inlineStr">
+      <c r="A61" s="34" t="inlineStr">
         <is>
           <t>十一·其他</t>
         </is>
       </c>
-      <c r="B61" s="17" t="inlineStr">
+      <c r="B61" s="35" t="inlineStr">
         <is>
           <t>洗钱罪</t>
         </is>
       </c>
-      <c r="C61" s="19" t="inlineStr">
+      <c r="C61" s="37" t="inlineStr">
         <is>
           <t>重罪</t>
         </is>
       </c>
-      <c r="D61" s="16" t="n">
+      <c r="D61" s="34" t="n">
         <v>48</v>
       </c>
-      <c r="E61" s="16" t="n">
+      <c r="E61" s="34" t="n">
         <v>30000</v>
       </c>
-      <c r="F61" s="16" t="inlineStr">
+      <c r="F61" s="34" t="inlineStr">
         <is>
           <t>持有/隐藏/转移违法所得 / 协助洗钱</t>
         </is>
       </c>
-      <c r="G61" s="16">
+      <c r="G61" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B61)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H61" s="16">
+      <c r="H61" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B61)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I61" s="16">
+      <c r="I61" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B61)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J61" s="16">
+      <c r="J61" s="34">
         <f>IF($G61=1,IF($J60="",$B61,$J60&amp;"、"&amp;$B61),$J60)</f>
         <v/>
       </c>
-      <c r="K61" s="16">
+      <c r="K61" s="34">
         <f>IF($H61=1,IF($K60="",$B61,$K60&amp;"、"&amp;$B61),$K60)</f>
         <v/>
       </c>
-      <c r="L61" s="16">
+      <c r="L61" s="34">
         <f>IF($I61=1,IF($L60="",$B61,$L60&amp;"、"&amp;$B61),$L60)</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="16" t="inlineStr">
+      <c r="A62" s="34" t="inlineStr">
         <is>
           <t>十一·其他</t>
         </is>
       </c>
-      <c r="B62" s="17" t="inlineStr">
+      <c r="B62" s="35" t="inlineStr">
         <is>
           <t>身份盗用罪</t>
         </is>
       </c>
-      <c r="C62" s="18" t="inlineStr">
+      <c r="C62" s="36" t="inlineStr">
         <is>
           <t>轻罪</t>
         </is>
       </c>
-      <c r="D62" s="16" t="n">
+      <c r="D62" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="E62" s="16" t="n">
+      <c r="E62" s="34" t="n">
         <v>8000</v>
       </c>
-      <c r="F62" s="16" t="inlineStr">
+      <c r="F62" s="34" t="inlineStr">
         <is>
           <t>未经许可盗取/使用他人个人信息, 另需赔偿</t>
         </is>
       </c>
-      <c r="G62" s="16">
+      <c r="G62" s="34">
         <f>IF(SUMIFS('关键词表'!$C$2:$C$336,'关键词表'!$B$2:$B$336,$B62)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="H62" s="16">
+      <c r="H62" s="34">
         <f>IF(SUMIFS('关键词表'!$D$2:$D$336,'关键词表'!$B$2:$B$336,$B62)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="I62" s="16">
+      <c r="I62" s="34">
         <f>IF(SUMIFS('关键词表'!$E$2:$E$336,'关键词表'!$B$2:$B$336,$B62)&gt;0,1,0)</f>
         <v/>
       </c>
-      <c r="J62" s="16">
+      <c r="J62" s="34">
         <f>IF($G62=1,IF($J61="",$B62,$J61&amp;"、"&amp;$B62),$J61)</f>
         <v/>
       </c>
-      <c r="K62" s="16">
+      <c r="K62" s="34">
         <f>IF($H62=1,IF($K61="",$B62,$K61&amp;"、"&amp;$B62),$K61)</f>
         <v/>
       </c>
-      <c r="L62" s="16">
+      <c r="L62" s="34">
         <f>IF($I62=1,IF($L61="",$B62,$L61&amp;"、"&amp;$B62),$L61)</f>
         <v/>
       </c>
@@ -4255,27 +4479,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="38" t="inlineStr">
         <is>
           <t>对应罪名</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="38" t="inlineStr">
         <is>
           <t>甲出现</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="38" t="inlineStr">
         <is>
           <t>乙出现</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="38" t="inlineStr">
         <is>
           <t>丙出现</t>
         </is>

--- a/fivem_case_analyzer/圣安地列斯州_案件罪名分析器.xlsx
+++ b/fivem_case_analyzer/圣安地列斯州_案件罪名分析器.xlsx
@@ -1285,15 +1285,15 @@
         </is>
       </c>
       <c r="G2" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B2)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B2)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H2" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B2)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B2)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I2" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B2)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B2)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J2" s="34">
@@ -1337,15 +1337,15 @@
         </is>
       </c>
       <c r="G3" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B3)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B3)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H3" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B3)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B3)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I3" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B3)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B3)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J3" s="34">
@@ -1389,15 +1389,15 @@
         </is>
       </c>
       <c r="G4" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B4)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B4)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H4" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B4)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B4)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I4" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B4)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B4)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J4" s="34">
@@ -1441,15 +1441,15 @@
         </is>
       </c>
       <c r="G5" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B5)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B5)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H5" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B5)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B5)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I5" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B5)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B5)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J5" s="34">
@@ -1493,15 +1493,15 @@
         </is>
       </c>
       <c r="G6" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B6)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B6)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H6" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B6)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B6)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I6" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B6)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B6)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J6" s="34">
@@ -1545,15 +1545,15 @@
         </is>
       </c>
       <c r="G7" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B7)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B7)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H7" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B7)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B7)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I7" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B7)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B7)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J7" s="34">
@@ -1597,15 +1597,15 @@
         </is>
       </c>
       <c r="G8" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B8)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B8)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H8" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B8)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B8)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I8" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B8)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B8)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J8" s="34">
@@ -1649,15 +1649,15 @@
         </is>
       </c>
       <c r="G9" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B9)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B9)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H9" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B9)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B9)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I9" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B9)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B9)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J9" s="34">
@@ -1701,15 +1701,15 @@
         </is>
       </c>
       <c r="G10" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B10)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B10)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H10" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B10)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B10)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I10" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B10)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B10)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J10" s="34">
@@ -1753,15 +1753,15 @@
         </is>
       </c>
       <c r="G11" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B11)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B11)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H11" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B11)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B11)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I11" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B11)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B11)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J11" s="34">
@@ -1805,15 +1805,15 @@
         </is>
       </c>
       <c r="G12" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B12)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B12)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H12" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B12)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B12)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I12" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B12)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B12)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J12" s="34">
@@ -1857,15 +1857,15 @@
         </is>
       </c>
       <c r="G13" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B13)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B13)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H13" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B13)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B13)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I13" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B13)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B13)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J13" s="34">
@@ -1909,15 +1909,15 @@
         </is>
       </c>
       <c r="G14" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B14)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B14)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H14" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B14)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B14)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I14" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B14)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B14)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J14" s="34">
@@ -1961,15 +1961,15 @@
         </is>
       </c>
       <c r="G15" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B15)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B15)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H15" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B15)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B15)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I15" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B15)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B15)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J15" s="34">
@@ -2013,15 +2013,15 @@
         </is>
       </c>
       <c r="G16" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B16)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B16)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H16" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B16)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B16)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I16" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B16)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B16)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J16" s="34">
@@ -2065,15 +2065,15 @@
         </is>
       </c>
       <c r="G17" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B17)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B17)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H17" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B17)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B17)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I17" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B17)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B17)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J17" s="34">
@@ -2117,15 +2117,15 @@
         </is>
       </c>
       <c r="G18" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B18)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B18)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H18" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B18)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B18)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I18" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B18)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B18)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J18" s="34">
@@ -2169,15 +2169,15 @@
         </is>
       </c>
       <c r="G19" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B19)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B19)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H19" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B19)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B19)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I19" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B19)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B19)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J19" s="34">
@@ -2221,15 +2221,15 @@
         </is>
       </c>
       <c r="G20" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B20)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B20)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H20" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B20)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B20)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I20" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B20)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B20)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J20" s="34">
@@ -2273,15 +2273,15 @@
         </is>
       </c>
       <c r="G21" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B21)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B21)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H21" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B21)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B21)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I21" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B21)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B21)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J21" s="34">
@@ -2325,15 +2325,15 @@
         </is>
       </c>
       <c r="G22" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B22)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B22)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H22" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B22)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B22)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I22" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B22)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B22)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J22" s="34">
@@ -2377,15 +2377,15 @@
         </is>
       </c>
       <c r="G23" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B23)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B23)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H23" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B23)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B23)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I23" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B23)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B23)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J23" s="34">
@@ -2429,15 +2429,15 @@
         </is>
       </c>
       <c r="G24" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B24)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B24)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H24" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B24)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B24)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I24" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B24)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B24)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J24" s="34">
@@ -2481,15 +2481,15 @@
         </is>
       </c>
       <c r="G25" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B25)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B25)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H25" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B25)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B25)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I25" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B25)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B25)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J25" s="34">
@@ -2533,15 +2533,15 @@
         </is>
       </c>
       <c r="G26" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B26)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B26)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H26" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B26)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B26)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I26" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B26)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B26)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J26" s="34">
@@ -2585,15 +2585,15 @@
         </is>
       </c>
       <c r="G27" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B27)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B27)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H27" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B27)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B27)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I27" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B27)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B27)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J27" s="34">
@@ -2637,15 +2637,15 @@
         </is>
       </c>
       <c r="G28" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B28)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B28)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H28" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B28)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B28)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I28" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B28)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B28)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J28" s="34">
@@ -2689,15 +2689,15 @@
         </is>
       </c>
       <c r="G29" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B29)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B29)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H29" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B29)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B29)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I29" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B29)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B29)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J29" s="34">
@@ -2741,15 +2741,15 @@
         </is>
       </c>
       <c r="G30" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B30)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B30)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H30" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B30)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B30)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I30" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B30)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B30)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J30" s="34">
@@ -2793,15 +2793,15 @@
         </is>
       </c>
       <c r="G31" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B31)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B31)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H31" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B31)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B31)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I31" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B31)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B31)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J31" s="34">
@@ -2845,15 +2845,15 @@
         </is>
       </c>
       <c r="G32" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B32)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B32)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H32" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B32)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B32)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I32" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B32)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B32)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J32" s="34">
@@ -2897,15 +2897,15 @@
         </is>
       </c>
       <c r="G33" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B33)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B33)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H33" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B33)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B33)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I33" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B33)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B33)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J33" s="34">
@@ -2949,15 +2949,15 @@
         </is>
       </c>
       <c r="G34" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B34)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B34)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H34" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B34)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B34)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I34" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B34)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B34)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J34" s="34">
@@ -3001,15 +3001,15 @@
         </is>
       </c>
       <c r="G35" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B35)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B35)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H35" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B35)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B35)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I35" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B35)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B35)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J35" s="34">
@@ -3053,15 +3053,15 @@
         </is>
       </c>
       <c r="G36" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B36)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B36)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H36" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B36)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B36)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I36" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B36)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B36)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J36" s="34">
@@ -3105,15 +3105,15 @@
         </is>
       </c>
       <c r="G37" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B37)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B37)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H37" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B37)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B37)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I37" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B37)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B37)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J37" s="34">
@@ -3157,15 +3157,15 @@
         </is>
       </c>
       <c r="G38" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B38)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B38)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H38" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B38)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B38)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I38" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B38)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B38)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J38" s="34">
@@ -3209,15 +3209,15 @@
         </is>
       </c>
       <c r="G39" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B39)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B39)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H39" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B39)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B39)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I39" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B39)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B39)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J39" s="34">
@@ -3257,19 +3257,19 @@
       </c>
       <c r="F40" s="33" t="inlineStr">
         <is>
-          <t>逮捕时以任何方式拒绝/抗拒/逃避逮捕</t>
+          <t>逮捕/追捕时以任何方式拒绝、抗拒或逃避逮捕（人尚未被捕）</t>
         </is>
       </c>
       <c r="G40" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B40)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B40)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H40" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B40)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B40)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I40" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B40)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B40)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J40" s="34">
@@ -3309,19 +3309,19 @@
       </c>
       <c r="F41" s="33" t="inlineStr">
         <is>
-          <t>被合法扣留/逮捕后逃脱监护</t>
+          <t>★须先被合法扣留/逮捕后，再从监护中逃脱才算（仅在现场逃跑不算，那是拒捕罪）</t>
         </is>
       </c>
       <c r="G41" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B41)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B41)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H41" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B41)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B41)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I41" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B41)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B41)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J41" s="34">
@@ -3365,15 +3365,15 @@
         </is>
       </c>
       <c r="G42" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B42)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B42)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H42" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B42)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B42)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I42" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B42)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B42)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J42" s="34">
@@ -3417,15 +3417,15 @@
         </is>
       </c>
       <c r="G43" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B43)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B43)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H43" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B43)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B43)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I43" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B43)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B43)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J43" s="34">
@@ -3469,15 +3469,15 @@
         </is>
       </c>
       <c r="G44" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B44)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B44)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H44" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B44)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B44)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I44" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B44)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B44)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J44" s="34">
@@ -3521,15 +3521,15 @@
         </is>
       </c>
       <c r="G45" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B45)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B45)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H45" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B45)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B45)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I45" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B45)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B45)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J45" s="34">
@@ -3573,15 +3573,15 @@
         </is>
       </c>
       <c r="G46" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B46)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B46)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H46" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B46)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B46)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I46" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B46)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B46)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J46" s="34">
@@ -3625,15 +3625,15 @@
         </is>
       </c>
       <c r="G47" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B47)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B47)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H47" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B47)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B47)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I47" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B47)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B47)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J47" s="34">
@@ -3677,15 +3677,15 @@
         </is>
       </c>
       <c r="G48" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B48)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B48)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H48" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B48)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B48)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I48" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B48)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B48)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J48" s="34">
@@ -3729,15 +3729,15 @@
         </is>
       </c>
       <c r="G49" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B49)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B49)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H49" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B49)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B49)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I49" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B49)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B49)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J49" s="34">
@@ -3781,15 +3781,15 @@
         </is>
       </c>
       <c r="G50" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B50)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B50)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H50" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B50)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B50)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I50" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B50)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B50)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J50" s="34">
@@ -3833,15 +3833,15 @@
         </is>
       </c>
       <c r="G51" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B51)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B51)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H51" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B51)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B51)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I51" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B51)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B51)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J51" s="34">
@@ -3885,15 +3885,15 @@
         </is>
       </c>
       <c r="G52" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B52)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B52)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H52" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B52)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B52)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I52" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B52)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B52)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J52" s="34">
@@ -3937,15 +3937,15 @@
         </is>
       </c>
       <c r="G53" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B53)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B53)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H53" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B53)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B53)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I53" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B53)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B53)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J53" s="34">
@@ -3989,15 +3989,15 @@
         </is>
       </c>
       <c r="G54" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B54)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B54)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H54" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B54)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B54)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I54" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B54)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B54)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J54" s="34">
@@ -4041,15 +4041,15 @@
         </is>
       </c>
       <c r="G55" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B55)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B55)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H55" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B55)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B55)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I55" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B55)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B55)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J55" s="34">
@@ -4093,15 +4093,15 @@
         </is>
       </c>
       <c r="G56" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B56)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B56)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H56" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B56)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B56)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I56" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B56)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B56)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J56" s="34">
@@ -4145,15 +4145,15 @@
         </is>
       </c>
       <c r="G57" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B57)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B57)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H57" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B57)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B57)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I57" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B57)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B57)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J57" s="34">
@@ -4197,15 +4197,15 @@
         </is>
       </c>
       <c r="G58" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B58)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B58)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H58" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B58)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B58)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I58" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B58)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B58)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J58" s="34">
@@ -4249,15 +4249,15 @@
         </is>
       </c>
       <c r="G59" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B59)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B59)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H59" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B59)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B59)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I59" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B59)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B59)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J59" s="34">
@@ -4301,15 +4301,15 @@
         </is>
       </c>
       <c r="G60" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B60)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B60)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H60" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B60)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B60)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I60" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B60)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B60)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J60" s="34">
@@ -4353,15 +4353,15 @@
         </is>
       </c>
       <c r="G61" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B61)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B61)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H61" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B61)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B61)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I61" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B61)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B61)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J61" s="34">
@@ -4405,15 +4405,15 @@
         </is>
       </c>
       <c r="G62" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$486,'关键词库'!$B$2:$B$486,$B62)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B62)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H62" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$486,'关键词库'!$B$2:$B$486,$B62)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B62)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I62" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$486,'关键词库'!$B$2:$B$486,$B62)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B62)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J62" s="34">
@@ -4445,7 +4445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E487"/>
+  <dimension ref="A1:E504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4832,7 +4832,7 @@
     <row r="17">
       <c r="A17" s="34" t="inlineStr">
         <is>
-          <t>拿刀</t>
+          <t>用刀割</t>
         </is>
       </c>
       <c r="B17" s="34" t="inlineStr">
@@ -4856,7 +4856,7 @@
     <row r="18">
       <c r="A18" s="34" t="inlineStr">
         <is>
-          <t>持刀</t>
+          <t>拿刀</t>
         </is>
       </c>
       <c r="B18" s="34" t="inlineStr">
@@ -4880,7 +4880,7 @@
     <row r="19">
       <c r="A19" s="34" t="inlineStr">
         <is>
-          <t>致命武器</t>
+          <t>持刀</t>
         </is>
       </c>
       <c r="B19" s="34" t="inlineStr">
@@ -4904,7 +4904,7 @@
     <row r="20">
       <c r="A20" s="34" t="inlineStr">
         <is>
-          <t>用武器打</t>
+          <t>致命武器</t>
         </is>
       </c>
       <c r="B20" s="34" t="inlineStr">
@@ -4928,7 +4928,7 @@
     <row r="21">
       <c r="A21" s="34" t="inlineStr">
         <is>
-          <t>拿棍子打</t>
+          <t>用武器打</t>
         </is>
       </c>
       <c r="B21" s="34" t="inlineStr">
@@ -4952,7 +4952,7 @@
     <row r="22">
       <c r="A22" s="34" t="inlineStr">
         <is>
-          <t>持棍</t>
+          <t>拿棍子打</t>
         </is>
       </c>
       <c r="B22" s="34" t="inlineStr">
@@ -4976,7 +4976,7 @@
     <row r="23">
       <c r="A23" s="34" t="inlineStr">
         <is>
-          <t>用球棒</t>
+          <t>持棍</t>
         </is>
       </c>
       <c r="B23" s="34" t="inlineStr">
@@ -5000,7 +5000,7 @@
     <row r="24">
       <c r="A24" s="34" t="inlineStr">
         <is>
-          <t>抄家伙</t>
+          <t>用球棒</t>
         </is>
       </c>
       <c r="B24" s="34" t="inlineStr">
@@ -5024,7 +5024,7 @@
     <row r="25">
       <c r="A25" s="34" t="inlineStr">
         <is>
-          <t>拿管子打</t>
+          <t>抄家伙</t>
         </is>
       </c>
       <c r="B25" s="34" t="inlineStr">
@@ -5048,12 +5048,12 @@
     <row r="26">
       <c r="A26" s="34" t="inlineStr">
         <is>
-          <t>一级谋杀</t>
+          <t>拿管子打</t>
         </is>
       </c>
       <c r="B26" s="34" t="inlineStr">
         <is>
-          <t>一级谋杀罪</t>
+          <t>持有危险武器人身攻击罪</t>
         </is>
       </c>
       <c r="C26" s="34">
@@ -5072,12 +5072,12 @@
     <row r="27">
       <c r="A27" s="34" t="inlineStr">
         <is>
-          <t>预谋杀人</t>
+          <t>割伤</t>
         </is>
       </c>
       <c r="B27" s="34" t="inlineStr">
         <is>
-          <t>一级谋杀罪</t>
+          <t>持有危险武器人身攻击罪</t>
         </is>
       </c>
       <c r="C27" s="34">
@@ -5096,12 +5096,12 @@
     <row r="28">
       <c r="A28" s="34" t="inlineStr">
         <is>
-          <t>蓄意杀人</t>
+          <t>砍伤</t>
         </is>
       </c>
       <c r="B28" s="34" t="inlineStr">
         <is>
-          <t>一级谋杀罪</t>
+          <t>持有危险武器人身攻击罪</t>
         </is>
       </c>
       <c r="C28" s="34">
@@ -5120,12 +5120,12 @@
     <row r="29">
       <c r="A29" s="34" t="inlineStr">
         <is>
-          <t>有预谋</t>
+          <t>捅伤</t>
         </is>
       </c>
       <c r="B29" s="34" t="inlineStr">
         <is>
-          <t>一级谋杀罪</t>
+          <t>持有危险武器人身攻击罪</t>
         </is>
       </c>
       <c r="C29" s="34">
@@ -5144,12 +5144,12 @@
     <row r="30">
       <c r="A30" s="34" t="inlineStr">
         <is>
-          <t>谋划杀</t>
+          <t>刺伤</t>
         </is>
       </c>
       <c r="B30" s="34" t="inlineStr">
         <is>
-          <t>一级谋杀罪</t>
+          <t>持有危险武器人身攻击罪</t>
         </is>
       </c>
       <c r="C30" s="34">
@@ -5168,12 +5168,12 @@
     <row r="31">
       <c r="A31" s="34" t="inlineStr">
         <is>
-          <t>策划杀人</t>
+          <t>划伤</t>
         </is>
       </c>
       <c r="B31" s="34" t="inlineStr">
         <is>
-          <t>一级谋杀罪</t>
+          <t>持有危险武器人身攻击罪</t>
         </is>
       </c>
       <c r="C31" s="34">
@@ -5192,12 +5192,12 @@
     <row r="32">
       <c r="A32" s="34" t="inlineStr">
         <is>
-          <t>二级谋杀</t>
+          <t>刀伤</t>
         </is>
       </c>
       <c r="B32" s="34" t="inlineStr">
         <is>
-          <t>二级谋杀罪</t>
+          <t>持有危险武器人身攻击罪</t>
         </is>
       </c>
       <c r="C32" s="34">
@@ -5216,12 +5216,12 @@
     <row r="33">
       <c r="A33" s="34" t="inlineStr">
         <is>
-          <t>故意杀人</t>
+          <t>一级谋杀</t>
         </is>
       </c>
       <c r="B33" s="34" t="inlineStr">
         <is>
-          <t>二级谋杀罪</t>
+          <t>一级谋杀罪</t>
         </is>
       </c>
       <c r="C33" s="34">
@@ -5240,12 +5240,12 @@
     <row r="34">
       <c r="A34" s="34" t="inlineStr">
         <is>
-          <t>杀人</t>
+          <t>预谋杀人</t>
         </is>
       </c>
       <c r="B34" s="34" t="inlineStr">
         <is>
-          <t>二级谋杀罪</t>
+          <t>一级谋杀罪</t>
         </is>
       </c>
       <c r="C34" s="34">
@@ -5264,12 +5264,12 @@
     <row r="35">
       <c r="A35" s="34" t="inlineStr">
         <is>
-          <t>打死</t>
+          <t>蓄意杀人</t>
         </is>
       </c>
       <c r="B35" s="34" t="inlineStr">
         <is>
-          <t>二级谋杀罪</t>
+          <t>一级谋杀罪</t>
         </is>
       </c>
       <c r="C35" s="34">
@@ -5288,12 +5288,12 @@
     <row r="36">
       <c r="A36" s="34" t="inlineStr">
         <is>
-          <t>枪杀</t>
+          <t>有预谋</t>
         </is>
       </c>
       <c r="B36" s="34" t="inlineStr">
         <is>
-          <t>二级谋杀罪</t>
+          <t>一级谋杀罪</t>
         </is>
       </c>
       <c r="C36" s="34">
@@ -5312,12 +5312,12 @@
     <row r="37">
       <c r="A37" s="34" t="inlineStr">
         <is>
-          <t>致人死亡</t>
+          <t>谋划杀</t>
         </is>
       </c>
       <c r="B37" s="34" t="inlineStr">
         <is>
-          <t>二级谋杀罪</t>
+          <t>一级谋杀罪</t>
         </is>
       </c>
       <c r="C37" s="34">
@@ -5336,12 +5336,12 @@
     <row r="38">
       <c r="A38" s="34" t="inlineStr">
         <is>
-          <t>杀死</t>
+          <t>策划杀人</t>
         </is>
       </c>
       <c r="B38" s="34" t="inlineStr">
         <is>
-          <t>二级谋杀罪</t>
+          <t>一级谋杀罪</t>
         </is>
       </c>
       <c r="C38" s="34">
@@ -5360,7 +5360,7 @@
     <row r="39">
       <c r="A39" s="34" t="inlineStr">
         <is>
-          <t>弄死</t>
+          <t>二级谋杀</t>
         </is>
       </c>
       <c r="B39" s="34" t="inlineStr">
@@ -5384,7 +5384,7 @@
     <row r="40">
       <c r="A40" s="34" t="inlineStr">
         <is>
-          <t>捅死</t>
+          <t>故意杀人</t>
         </is>
       </c>
       <c r="B40" s="34" t="inlineStr">
@@ -5408,7 +5408,7 @@
     <row r="41">
       <c r="A41" s="34" t="inlineStr">
         <is>
-          <t>砍死</t>
+          <t>杀人</t>
         </is>
       </c>
       <c r="B41" s="34" t="inlineStr">
@@ -5432,7 +5432,7 @@
     <row r="42">
       <c r="A42" s="34" t="inlineStr">
         <is>
-          <t>杀了</t>
+          <t>打死</t>
         </is>
       </c>
       <c r="B42" s="34" t="inlineStr">
@@ -5456,12 +5456,12 @@
     <row r="43">
       <c r="A43" s="34" t="inlineStr">
         <is>
-          <t>三级谋杀</t>
+          <t>枪杀</t>
         </is>
       </c>
       <c r="B43" s="34" t="inlineStr">
         <is>
-          <t>三级谋杀罪</t>
+          <t>二级谋杀罪</t>
         </is>
       </c>
       <c r="C43" s="34">
@@ -5480,12 +5480,12 @@
     <row r="44">
       <c r="A44" s="34" t="inlineStr">
         <is>
-          <t>过失致死</t>
+          <t>致人死亡</t>
         </is>
       </c>
       <c r="B44" s="34" t="inlineStr">
         <is>
-          <t>三级谋杀罪</t>
+          <t>二级谋杀罪</t>
         </is>
       </c>
       <c r="C44" s="34">
@@ -5504,12 +5504,12 @@
     <row r="45">
       <c r="A45" s="34" t="inlineStr">
         <is>
-          <t>意外致死</t>
+          <t>杀死</t>
         </is>
       </c>
       <c r="B45" s="34" t="inlineStr">
         <is>
-          <t>三级谋杀罪</t>
+          <t>二级谋杀罪</t>
         </is>
       </c>
       <c r="C45" s="34">
@@ -5528,12 +5528,12 @@
     <row r="46">
       <c r="A46" s="34" t="inlineStr">
         <is>
-          <t>误杀</t>
+          <t>弄死</t>
         </is>
       </c>
       <c r="B46" s="34" t="inlineStr">
         <is>
-          <t>三级谋杀罪</t>
+          <t>二级谋杀罪</t>
         </is>
       </c>
       <c r="C46" s="34">
@@ -5552,12 +5552,12 @@
     <row r="47">
       <c r="A47" s="34" t="inlineStr">
         <is>
-          <t>失手打死</t>
+          <t>捅死</t>
         </is>
       </c>
       <c r="B47" s="34" t="inlineStr">
         <is>
-          <t>三级谋杀罪</t>
+          <t>二级谋杀罪</t>
         </is>
       </c>
       <c r="C47" s="34">
@@ -5576,12 +5576,12 @@
     <row r="48">
       <c r="A48" s="34" t="inlineStr">
         <is>
-          <t>冲突致死</t>
+          <t>砍死</t>
         </is>
       </c>
       <c r="B48" s="34" t="inlineStr">
         <is>
-          <t>三级谋杀罪</t>
+          <t>二级谋杀罪</t>
         </is>
       </c>
       <c r="C48" s="34">
@@ -5600,12 +5600,12 @@
     <row r="49">
       <c r="A49" s="34" t="inlineStr">
         <is>
-          <t>非法拘禁</t>
+          <t>杀了</t>
         </is>
       </c>
       <c r="B49" s="34" t="inlineStr">
         <is>
-          <t>非法拘禁罪</t>
+          <t>二级谋杀罪</t>
         </is>
       </c>
       <c r="C49" s="34">
@@ -5624,12 +5624,12 @@
     <row r="50">
       <c r="A50" s="34" t="inlineStr">
         <is>
-          <t>拘禁</t>
+          <t>三级谋杀</t>
         </is>
       </c>
       <c r="B50" s="34" t="inlineStr">
         <is>
-          <t>非法拘禁罪</t>
+          <t>三级谋杀罪</t>
         </is>
       </c>
       <c r="C50" s="34">
@@ -5648,12 +5648,12 @@
     <row r="51">
       <c r="A51" s="34" t="inlineStr">
         <is>
-          <t>扣押他人</t>
+          <t>过失致死</t>
         </is>
       </c>
       <c r="B51" s="34" t="inlineStr">
         <is>
-          <t>非法拘禁罪</t>
+          <t>三级谋杀罪</t>
         </is>
       </c>
       <c r="C51" s="34">
@@ -5672,12 +5672,12 @@
     <row r="52">
       <c r="A52" s="34" t="inlineStr">
         <is>
-          <t>限制人身自由</t>
+          <t>意外致死</t>
         </is>
       </c>
       <c r="B52" s="34" t="inlineStr">
         <is>
-          <t>非法拘禁罪</t>
+          <t>三级谋杀罪</t>
         </is>
       </c>
       <c r="C52" s="34">
@@ -5696,12 +5696,12 @@
     <row r="53">
       <c r="A53" s="34" t="inlineStr">
         <is>
-          <t>强行关押</t>
+          <t>误杀</t>
         </is>
       </c>
       <c r="B53" s="34" t="inlineStr">
         <is>
-          <t>非法拘禁罪</t>
+          <t>三级谋杀罪</t>
         </is>
       </c>
       <c r="C53" s="34">
@@ -5720,12 +5720,12 @@
     <row r="54">
       <c r="A54" s="34" t="inlineStr">
         <is>
-          <t>私自关押</t>
+          <t>失手打死</t>
         </is>
       </c>
       <c r="B54" s="34" t="inlineStr">
         <is>
-          <t>非法拘禁罪</t>
+          <t>三级谋杀罪</t>
         </is>
       </c>
       <c r="C54" s="34">
@@ -5744,12 +5744,12 @@
     <row r="55">
       <c r="A55" s="34" t="inlineStr">
         <is>
-          <t>关起来</t>
+          <t>冲突致死</t>
         </is>
       </c>
       <c r="B55" s="34" t="inlineStr">
         <is>
-          <t>非法拘禁罪</t>
+          <t>三级谋杀罪</t>
         </is>
       </c>
       <c r="C55" s="34">
@@ -5768,7 +5768,7 @@
     <row r="56">
       <c r="A56" s="34" t="inlineStr">
         <is>
-          <t>囚禁</t>
+          <t>非法拘禁</t>
         </is>
       </c>
       <c r="B56" s="34" t="inlineStr">
@@ -5792,7 +5792,7 @@
     <row r="57">
       <c r="A57" s="34" t="inlineStr">
         <is>
-          <t>绑在</t>
+          <t>拘禁</t>
         </is>
       </c>
       <c r="B57" s="34" t="inlineStr">
@@ -5816,12 +5816,12 @@
     <row r="58">
       <c r="A58" s="34" t="inlineStr">
         <is>
-          <t>故意袭击</t>
+          <t>扣押他人</t>
         </is>
       </c>
       <c r="B58" s="34" t="inlineStr">
         <is>
-          <t>故意袭击罪</t>
+          <t>非法拘禁罪</t>
         </is>
       </c>
       <c r="C58" s="34">
@@ -5840,12 +5840,12 @@
     <row r="59">
       <c r="A59" s="34" t="inlineStr">
         <is>
-          <t>袭击</t>
+          <t>限制人身自由</t>
         </is>
       </c>
       <c r="B59" s="34" t="inlineStr">
         <is>
-          <t>故意袭击罪</t>
+          <t>非法拘禁罪</t>
         </is>
       </c>
       <c r="C59" s="34">
@@ -5864,12 +5864,12 @@
     <row r="60">
       <c r="A60" s="34" t="inlineStr">
         <is>
-          <t>殴打</t>
+          <t>强行关押</t>
         </is>
       </c>
       <c r="B60" s="34" t="inlineStr">
         <is>
-          <t>故意袭击罪</t>
+          <t>非法拘禁罪</t>
         </is>
       </c>
       <c r="C60" s="34">
@@ -5888,12 +5888,12 @@
     <row r="61">
       <c r="A61" s="34" t="inlineStr">
         <is>
-          <t>打人</t>
+          <t>私自关押</t>
         </is>
       </c>
       <c r="B61" s="34" t="inlineStr">
         <is>
-          <t>故意袭击罪</t>
+          <t>非法拘禁罪</t>
         </is>
       </c>
       <c r="C61" s="34">
@@ -5912,12 +5912,12 @@
     <row r="62">
       <c r="A62" s="34" t="inlineStr">
         <is>
-          <t>动手打</t>
+          <t>关起来</t>
         </is>
       </c>
       <c r="B62" s="34" t="inlineStr">
         <is>
-          <t>故意袭击罪</t>
+          <t>非法拘禁罪</t>
         </is>
       </c>
       <c r="C62" s="34">
@@ -5936,12 +5936,12 @@
     <row r="63">
       <c r="A63" s="34" t="inlineStr">
         <is>
-          <t>拳打脚踢</t>
+          <t>囚禁</t>
         </is>
       </c>
       <c r="B63" s="34" t="inlineStr">
         <is>
-          <t>故意袭击罪</t>
+          <t>非法拘禁罪</t>
         </is>
       </c>
       <c r="C63" s="34">
@@ -5960,12 +5960,12 @@
     <row r="64">
       <c r="A64" s="34" t="inlineStr">
         <is>
-          <t>暴力伤人</t>
+          <t>绑在</t>
         </is>
       </c>
       <c r="B64" s="34" t="inlineStr">
         <is>
-          <t>故意袭击罪</t>
+          <t>非法拘禁罪</t>
         </is>
       </c>
       <c r="C64" s="34">
@@ -5984,7 +5984,7 @@
     <row r="65">
       <c r="A65" s="34" t="inlineStr">
         <is>
-          <t>揍</t>
+          <t>故意袭击</t>
         </is>
       </c>
       <c r="B65" s="34" t="inlineStr">
@@ -6008,7 +6008,7 @@
     <row r="66">
       <c r="A66" s="34" t="inlineStr">
         <is>
-          <t>打伤</t>
+          <t>袭击</t>
         </is>
       </c>
       <c r="B66" s="34" t="inlineStr">
@@ -6032,7 +6032,7 @@
     <row r="67">
       <c r="A67" s="34" t="inlineStr">
         <is>
-          <t>打了一顿</t>
+          <t>殴打</t>
         </is>
       </c>
       <c r="B67" s="34" t="inlineStr">
@@ -6056,7 +6056,7 @@
     <row r="68">
       <c r="A68" s="34" t="inlineStr">
         <is>
-          <t>围殴</t>
+          <t>打人</t>
         </is>
       </c>
       <c r="B68" s="34" t="inlineStr">
@@ -6080,7 +6080,7 @@
     <row r="69">
       <c r="A69" s="34" t="inlineStr">
         <is>
-          <t>动手</t>
+          <t>动手打</t>
         </is>
       </c>
       <c r="B69" s="34" t="inlineStr">
@@ -6104,7 +6104,7 @@
     <row r="70">
       <c r="A70" s="34" t="inlineStr">
         <is>
-          <t>打架</t>
+          <t>拳打脚踢</t>
         </is>
       </c>
       <c r="B70" s="34" t="inlineStr">
@@ -6128,12 +6128,12 @@
     <row r="71">
       <c r="A71" s="34" t="inlineStr">
         <is>
-          <t>绑架</t>
+          <t>暴力伤人</t>
         </is>
       </c>
       <c r="B71" s="34" t="inlineStr">
         <is>
-          <t>绑架罪</t>
+          <t>故意袭击罪</t>
         </is>
       </c>
       <c r="C71" s="34">
@@ -6152,12 +6152,12 @@
     <row r="72">
       <c r="A72" s="34" t="inlineStr">
         <is>
-          <t>劫持</t>
+          <t>揍</t>
         </is>
       </c>
       <c r="B72" s="34" t="inlineStr">
         <is>
-          <t>绑架罪</t>
+          <t>故意袭击罪</t>
         </is>
       </c>
       <c r="C72" s="34">
@@ -6176,12 +6176,12 @@
     <row r="73">
       <c r="A73" s="34" t="inlineStr">
         <is>
-          <t>挟持</t>
+          <t>打伤</t>
         </is>
       </c>
       <c r="B73" s="34" t="inlineStr">
         <is>
-          <t>绑架罪</t>
+          <t>故意袭击罪</t>
         </is>
       </c>
       <c r="C73" s="34">
@@ -6200,12 +6200,12 @@
     <row r="74">
       <c r="A74" s="34" t="inlineStr">
         <is>
-          <t>绑票</t>
+          <t>打了一顿</t>
         </is>
       </c>
       <c r="B74" s="34" t="inlineStr">
         <is>
-          <t>绑架罪</t>
+          <t>故意袭击罪</t>
         </is>
       </c>
       <c r="C74" s="34">
@@ -6224,12 +6224,12 @@
     <row r="75">
       <c r="A75" s="34" t="inlineStr">
         <is>
-          <t>控制人质</t>
+          <t>围殴</t>
         </is>
       </c>
       <c r="B75" s="34" t="inlineStr">
         <is>
-          <t>绑架罪</t>
+          <t>故意袭击罪</t>
         </is>
       </c>
       <c r="C75" s="34">
@@ -6248,12 +6248,12 @@
     <row r="76">
       <c r="A76" s="34" t="inlineStr">
         <is>
-          <t>掳走</t>
+          <t>动手</t>
         </is>
       </c>
       <c r="B76" s="34" t="inlineStr">
         <is>
-          <t>绑架罪</t>
+          <t>故意袭击罪</t>
         </is>
       </c>
       <c r="C76" s="34">
@@ -6272,12 +6272,12 @@
     <row r="77">
       <c r="A77" s="34" t="inlineStr">
         <is>
-          <t>抓走人质</t>
+          <t>打架</t>
         </is>
       </c>
       <c r="B77" s="34" t="inlineStr">
         <is>
-          <t>绑架罪</t>
+          <t>故意袭击罪</t>
         </is>
       </c>
       <c r="C77" s="34">
@@ -6296,7 +6296,7 @@
     <row r="78">
       <c r="A78" s="34" t="inlineStr">
         <is>
-          <t>抓人质</t>
+          <t>绑架</t>
         </is>
       </c>
       <c r="B78" s="34" t="inlineStr">
@@ -6320,12 +6320,12 @@
     <row r="79">
       <c r="A79" s="34" t="inlineStr">
         <is>
-          <t>亵渎尸体</t>
+          <t>劫持</t>
         </is>
       </c>
       <c r="B79" s="34" t="inlineStr">
         <is>
-          <t>亵渎尸体罪</t>
+          <t>绑架罪</t>
         </is>
       </c>
       <c r="C79" s="34">
@@ -6344,12 +6344,12 @@
     <row r="80">
       <c r="A80" s="34" t="inlineStr">
         <is>
-          <t>毁尸</t>
+          <t>挟持</t>
         </is>
       </c>
       <c r="B80" s="34" t="inlineStr">
         <is>
-          <t>亵渎尸体罪</t>
+          <t>绑架罪</t>
         </is>
       </c>
       <c r="C80" s="34">
@@ -6368,12 +6368,12 @@
     <row r="81">
       <c r="A81" s="34" t="inlineStr">
         <is>
-          <t>处置尸体</t>
+          <t>绑票</t>
         </is>
       </c>
       <c r="B81" s="34" t="inlineStr">
         <is>
-          <t>亵渎尸体罪</t>
+          <t>绑架罪</t>
         </is>
       </c>
       <c r="C81" s="34">
@@ -6392,12 +6392,12 @@
     <row r="82">
       <c r="A82" s="34" t="inlineStr">
         <is>
-          <t>销毁尸体</t>
+          <t>控制人质</t>
         </is>
       </c>
       <c r="B82" s="34" t="inlineStr">
         <is>
-          <t>亵渎尸体罪</t>
+          <t>绑架罪</t>
         </is>
       </c>
       <c r="C82" s="34">
@@ -6416,12 +6416,12 @@
     <row r="83">
       <c r="A83" s="34" t="inlineStr">
         <is>
-          <t>藏尸</t>
+          <t>掳走</t>
         </is>
       </c>
       <c r="B83" s="34" t="inlineStr">
         <is>
-          <t>亵渎尸体罪</t>
+          <t>绑架罪</t>
         </is>
       </c>
       <c r="C83" s="34">
@@ -6440,12 +6440,12 @@
     <row r="84">
       <c r="A84" s="34" t="inlineStr">
         <is>
-          <t>焚尸</t>
+          <t>抓走人质</t>
         </is>
       </c>
       <c r="B84" s="34" t="inlineStr">
         <is>
-          <t>亵渎尸体罪</t>
+          <t>绑架罪</t>
         </is>
       </c>
       <c r="C84" s="34">
@@ -6464,12 +6464,12 @@
     <row r="85">
       <c r="A85" s="34" t="inlineStr">
         <is>
-          <t>碎尸</t>
+          <t>抓人质</t>
         </is>
       </c>
       <c r="B85" s="34" t="inlineStr">
         <is>
-          <t>亵渎尸体罪</t>
+          <t>绑架罪</t>
         </is>
       </c>
       <c r="C85" s="34">
@@ -6488,12 +6488,12 @@
     <row r="86">
       <c r="A86" s="34" t="inlineStr">
         <is>
-          <t>诈骗</t>
+          <t>亵渎尸体</t>
         </is>
       </c>
       <c r="B86" s="34" t="inlineStr">
         <is>
-          <t>诈骗罪</t>
+          <t>亵渎尸体罪</t>
         </is>
       </c>
       <c r="C86" s="34">
@@ -6512,12 +6512,12 @@
     <row r="87">
       <c r="A87" s="34" t="inlineStr">
         <is>
-          <t>欺诈</t>
+          <t>毁尸</t>
         </is>
       </c>
       <c r="B87" s="34" t="inlineStr">
         <is>
-          <t>诈骗罪</t>
+          <t>亵渎尸体罪</t>
         </is>
       </c>
       <c r="C87" s="34">
@@ -6536,12 +6536,12 @@
     <row r="88">
       <c r="A88" s="34" t="inlineStr">
         <is>
-          <t>骗钱</t>
+          <t>处置尸体</t>
         </is>
       </c>
       <c r="B88" s="34" t="inlineStr">
         <is>
-          <t>诈骗罪</t>
+          <t>亵渎尸体罪</t>
         </is>
       </c>
       <c r="C88" s="34">
@@ -6560,12 +6560,12 @@
     <row r="89">
       <c r="A89" s="34" t="inlineStr">
         <is>
-          <t>行骗</t>
+          <t>销毁尸体</t>
         </is>
       </c>
       <c r="B89" s="34" t="inlineStr">
         <is>
-          <t>诈骗罪</t>
+          <t>亵渎尸体罪</t>
         </is>
       </c>
       <c r="C89" s="34">
@@ -6584,12 +6584,12 @@
     <row r="90">
       <c r="A90" s="34" t="inlineStr">
         <is>
-          <t>诈骗钱财</t>
+          <t>藏尸</t>
         </is>
       </c>
       <c r="B90" s="34" t="inlineStr">
         <is>
-          <t>诈骗罪</t>
+          <t>亵渎尸体罪</t>
         </is>
       </c>
       <c r="C90" s="34">
@@ -6608,12 +6608,12 @@
     <row r="91">
       <c r="A91" s="34" t="inlineStr">
         <is>
-          <t>骗取</t>
+          <t>焚尸</t>
         </is>
       </c>
       <c r="B91" s="34" t="inlineStr">
         <is>
-          <t>诈骗罪</t>
+          <t>亵渎尸体罪</t>
         </is>
       </c>
       <c r="C91" s="34">
@@ -6632,12 +6632,12 @@
     <row r="92">
       <c r="A92" s="34" t="inlineStr">
         <is>
-          <t>坑钱</t>
+          <t>碎尸</t>
         </is>
       </c>
       <c r="B92" s="34" t="inlineStr">
         <is>
-          <t>诈骗罪</t>
+          <t>亵渎尸体罪</t>
         </is>
       </c>
       <c r="C92" s="34">
@@ -6656,7 +6656,7 @@
     <row r="93">
       <c r="A93" s="34" t="inlineStr">
         <is>
-          <t>设局骗</t>
+          <t>诈骗</t>
         </is>
       </c>
       <c r="B93" s="34" t="inlineStr">
@@ -6680,7 +6680,7 @@
     <row r="94">
       <c r="A94" s="34" t="inlineStr">
         <is>
-          <t>骗了</t>
+          <t>欺诈</t>
         </is>
       </c>
       <c r="B94" s="34" t="inlineStr">
@@ -6704,12 +6704,12 @@
     <row r="95">
       <c r="A95" s="34" t="inlineStr">
         <is>
-          <t>非法入侵</t>
+          <t>骗钱</t>
         </is>
       </c>
       <c r="B95" s="34" t="inlineStr">
         <is>
-          <t>非法入侵罪</t>
+          <t>诈骗罪</t>
         </is>
       </c>
       <c r="C95" s="34">
@@ -6728,12 +6728,12 @@
     <row r="96">
       <c r="A96" s="34" t="inlineStr">
         <is>
-          <t>拒绝离开</t>
+          <t>行骗</t>
         </is>
       </c>
       <c r="B96" s="34" t="inlineStr">
         <is>
-          <t>非法入侵罪</t>
+          <t>诈骗罪</t>
         </is>
       </c>
       <c r="C96" s="34">
@@ -6752,12 +6752,12 @@
     <row r="97">
       <c r="A97" s="34" t="inlineStr">
         <is>
-          <t>私闯</t>
+          <t>诈骗钱财</t>
         </is>
       </c>
       <c r="B97" s="34" t="inlineStr">
         <is>
-          <t>非法入侵罪</t>
+          <t>诈骗罪</t>
         </is>
       </c>
       <c r="C97" s="34">
@@ -6776,12 +6776,12 @@
     <row r="98">
       <c r="A98" s="34" t="inlineStr">
         <is>
-          <t>擅自闯入</t>
+          <t>骗取</t>
         </is>
       </c>
       <c r="B98" s="34" t="inlineStr">
         <is>
-          <t>非法入侵罪</t>
+          <t>诈骗罪</t>
         </is>
       </c>
       <c r="C98" s="34">
@@ -6800,12 +6800,12 @@
     <row r="99">
       <c r="A99" s="34" t="inlineStr">
         <is>
-          <t>赖着不走</t>
+          <t>坑钱</t>
         </is>
       </c>
       <c r="B99" s="34" t="inlineStr">
         <is>
-          <t>非法入侵罪</t>
+          <t>诈骗罪</t>
         </is>
       </c>
       <c r="C99" s="34">
@@ -6824,12 +6824,12 @@
     <row r="100">
       <c r="A100" s="34" t="inlineStr">
         <is>
-          <t>不肯走</t>
+          <t>设局骗</t>
         </is>
       </c>
       <c r="B100" s="34" t="inlineStr">
         <is>
-          <t>非法入侵罪</t>
+          <t>诈骗罪</t>
         </is>
       </c>
       <c r="C100" s="34">
@@ -6848,12 +6848,12 @@
     <row r="101">
       <c r="A101" s="34" t="inlineStr">
         <is>
-          <t>闯进别人</t>
+          <t>骗了</t>
         </is>
       </c>
       <c r="B101" s="34" t="inlineStr">
         <is>
-          <t>非法入侵罪</t>
+          <t>诈骗罪</t>
         </is>
       </c>
       <c r="C101" s="34">
@@ -6872,7 +6872,7 @@
     <row r="102">
       <c r="A102" s="34" t="inlineStr">
         <is>
-          <t>闯入民宅</t>
+          <t>非法入侵</t>
         </is>
       </c>
       <c r="B102" s="34" t="inlineStr">
@@ -6896,12 +6896,12 @@
     <row r="103">
       <c r="A103" s="34" t="inlineStr">
         <is>
-          <t>非法入侵禁区</t>
+          <t>拒绝离开</t>
         </is>
       </c>
       <c r="B103" s="34" t="inlineStr">
         <is>
-          <t>非法入侵禁区罪</t>
+          <t>非法入侵罪</t>
         </is>
       </c>
       <c r="C103" s="34">
@@ -6920,12 +6920,12 @@
     <row r="104">
       <c r="A104" s="34" t="inlineStr">
         <is>
-          <t>闯入禁区</t>
+          <t>私闯</t>
         </is>
       </c>
       <c r="B104" s="34" t="inlineStr">
         <is>
-          <t>非法入侵禁区罪</t>
+          <t>非法入侵罪</t>
         </is>
       </c>
       <c r="C104" s="34">
@@ -6944,12 +6944,12 @@
     <row r="105">
       <c r="A105" s="34" t="inlineStr">
         <is>
-          <t>擅闯警局</t>
+          <t>擅自闯入</t>
         </is>
       </c>
       <c r="B105" s="34" t="inlineStr">
         <is>
-          <t>非法入侵禁区罪</t>
+          <t>非法入侵罪</t>
         </is>
       </c>
       <c r="C105" s="34">
@@ -6968,12 +6968,12 @@
     <row r="106">
       <c r="A106" s="34" t="inlineStr">
         <is>
-          <t>擅闯机场</t>
+          <t>赖着不走</t>
         </is>
       </c>
       <c r="B106" s="34" t="inlineStr">
         <is>
-          <t>非法入侵禁区罪</t>
+          <t>非法入侵罪</t>
         </is>
       </c>
       <c r="C106" s="34">
@@ -6992,12 +6992,12 @@
     <row r="107">
       <c r="A107" s="34" t="inlineStr">
         <is>
-          <t>擅闯军事基地</t>
+          <t>不肯走</t>
         </is>
       </c>
       <c r="B107" s="34" t="inlineStr">
         <is>
-          <t>非法入侵禁区罪</t>
+          <t>非法入侵罪</t>
         </is>
       </c>
       <c r="C107" s="34">
@@ -7016,12 +7016,12 @@
     <row r="108">
       <c r="A108" s="34" t="inlineStr">
         <is>
-          <t>限制区域</t>
+          <t>闯进别人</t>
         </is>
       </c>
       <c r="B108" s="34" t="inlineStr">
         <is>
-          <t>非法入侵禁区罪</t>
+          <t>非法入侵罪</t>
         </is>
       </c>
       <c r="C108" s="34">
@@ -7040,12 +7040,12 @@
     <row r="109">
       <c r="A109" s="34" t="inlineStr">
         <is>
-          <t>闯入监狱</t>
+          <t>闯入民宅</t>
         </is>
       </c>
       <c r="B109" s="34" t="inlineStr">
         <is>
-          <t>非法入侵禁区罪</t>
+          <t>非法入侵罪</t>
         </is>
       </c>
       <c r="C109" s="34">
@@ -7064,7 +7064,7 @@
     <row r="110">
       <c r="A110" s="34" t="inlineStr">
         <is>
-          <t>翻进警局</t>
+          <t>非法入侵禁区</t>
         </is>
       </c>
       <c r="B110" s="34" t="inlineStr">
@@ -7088,12 +7088,12 @@
     <row r="111">
       <c r="A111" s="34" t="inlineStr">
         <is>
-          <t>入室盗窃</t>
+          <t>闯入禁区</t>
         </is>
       </c>
       <c r="B111" s="34" t="inlineStr">
         <is>
-          <t>入室盗窃罪</t>
+          <t>非法入侵禁区罪</t>
         </is>
       </c>
       <c r="C111" s="34">
@@ -7112,12 +7112,12 @@
     <row r="112">
       <c r="A112" s="34" t="inlineStr">
         <is>
-          <t>入室</t>
+          <t>擅闯警局</t>
         </is>
       </c>
       <c r="B112" s="34" t="inlineStr">
         <is>
-          <t>入室盗窃罪</t>
+          <t>非法入侵禁区罪</t>
         </is>
       </c>
       <c r="C112" s="34">
@@ -7136,12 +7136,12 @@
     <row r="113">
       <c r="A113" s="34" t="inlineStr">
         <is>
-          <t>撬门盗窃</t>
+          <t>擅闯机场</t>
         </is>
       </c>
       <c r="B113" s="34" t="inlineStr">
         <is>
-          <t>入室盗窃罪</t>
+          <t>非法入侵禁区罪</t>
         </is>
       </c>
       <c r="C113" s="34">
@@ -7160,12 +7160,12 @@
     <row r="114">
       <c r="A114" s="34" t="inlineStr">
         <is>
-          <t>闯入盗窃</t>
+          <t>擅闯军事基地</t>
         </is>
       </c>
       <c r="B114" s="34" t="inlineStr">
         <is>
-          <t>入室盗窃罪</t>
+          <t>非法入侵禁区罪</t>
         </is>
       </c>
       <c r="C114" s="34">
@@ -7184,12 +7184,12 @@
     <row r="115">
       <c r="A115" s="34" t="inlineStr">
         <is>
-          <t>破门盗窃</t>
+          <t>限制区域</t>
         </is>
       </c>
       <c r="B115" s="34" t="inlineStr">
         <is>
-          <t>入室盗窃罪</t>
+          <t>非法入侵禁区罪</t>
         </is>
       </c>
       <c r="C115" s="34">
@@ -7208,12 +7208,12 @@
     <row r="116">
       <c r="A116" s="34" t="inlineStr">
         <is>
-          <t>翻窗偷</t>
+          <t>闯入监狱</t>
         </is>
       </c>
       <c r="B116" s="34" t="inlineStr">
         <is>
-          <t>入室盗窃罪</t>
+          <t>非法入侵禁区罪</t>
         </is>
       </c>
       <c r="C116" s="34">
@@ -7232,12 +7232,12 @@
     <row r="117">
       <c r="A117" s="34" t="inlineStr">
         <is>
-          <t>撬锁进</t>
+          <t>翻进警局</t>
         </is>
       </c>
       <c r="B117" s="34" t="inlineStr">
         <is>
-          <t>入室盗窃罪</t>
+          <t>非法入侵禁区罪</t>
         </is>
       </c>
       <c r="C117" s="34">
@@ -7256,7 +7256,7 @@
     <row r="118">
       <c r="A118" s="34" t="inlineStr">
         <is>
-          <t>入室行窃</t>
+          <t>入室盗窃</t>
         </is>
       </c>
       <c r="B118" s="34" t="inlineStr">
@@ -7280,12 +7280,12 @@
     <row r="119">
       <c r="A119" s="34" t="inlineStr">
         <is>
-          <t>抢劫</t>
+          <t>入室</t>
         </is>
       </c>
       <c r="B119" s="34" t="inlineStr">
         <is>
-          <t>抢劫罪</t>
+          <t>入室盗窃罪</t>
         </is>
       </c>
       <c r="C119" s="34">
@@ -7304,12 +7304,12 @@
     <row r="120">
       <c r="A120" s="34" t="inlineStr">
         <is>
-          <t>持械抢劫</t>
+          <t>撬门盗窃</t>
         </is>
       </c>
       <c r="B120" s="34" t="inlineStr">
         <is>
-          <t>抢劫罪</t>
+          <t>入室盗窃罪</t>
         </is>
       </c>
       <c r="C120" s="34">
@@ -7328,12 +7328,12 @@
     <row r="121">
       <c r="A121" s="34" t="inlineStr">
         <is>
-          <t>持枪抢劫</t>
+          <t>闯入盗窃</t>
         </is>
       </c>
       <c r="B121" s="34" t="inlineStr">
         <is>
-          <t>抢劫罪</t>
+          <t>入室盗窃罪</t>
         </is>
       </c>
       <c r="C121" s="34">
@@ -7352,12 +7352,12 @@
     <row r="122">
       <c r="A122" s="34" t="inlineStr">
         <is>
-          <t>抢夺财物</t>
+          <t>破门盗窃</t>
         </is>
       </c>
       <c r="B122" s="34" t="inlineStr">
         <is>
-          <t>抢劫罪</t>
+          <t>入室盗窃罪</t>
         </is>
       </c>
       <c r="C122" s="34">
@@ -7376,12 +7376,12 @@
     <row r="123">
       <c r="A123" s="34" t="inlineStr">
         <is>
-          <t>武力抢</t>
+          <t>翻窗偷</t>
         </is>
       </c>
       <c r="B123" s="34" t="inlineStr">
         <is>
-          <t>抢劫罪</t>
+          <t>入室盗窃罪</t>
         </is>
       </c>
       <c r="C123" s="34">
@@ -7400,12 +7400,12 @@
     <row r="124">
       <c r="A124" s="34" t="inlineStr">
         <is>
-          <t>威胁抢</t>
+          <t>撬锁进</t>
         </is>
       </c>
       <c r="B124" s="34" t="inlineStr">
         <is>
-          <t>抢劫罪</t>
+          <t>入室盗窃罪</t>
         </is>
       </c>
       <c r="C124" s="34">
@@ -7424,12 +7424,12 @@
     <row r="125">
       <c r="A125" s="34" t="inlineStr">
         <is>
-          <t>打劫</t>
+          <t>入室行窃</t>
         </is>
       </c>
       <c r="B125" s="34" t="inlineStr">
         <is>
-          <t>抢劫罪</t>
+          <t>入室盗窃罪</t>
         </is>
       </c>
       <c r="C125" s="34">
@@ -7448,7 +7448,7 @@
     <row r="126">
       <c r="A126" s="34" t="inlineStr">
         <is>
-          <t>抢东西</t>
+          <t>抢劫</t>
         </is>
       </c>
       <c r="B126" s="34" t="inlineStr">
@@ -7472,7 +7472,7 @@
     <row r="127">
       <c r="A127" s="34" t="inlineStr">
         <is>
-          <t>抢钱</t>
+          <t>持械抢劫</t>
         </is>
       </c>
       <c r="B127" s="34" t="inlineStr">
@@ -7496,7 +7496,7 @@
     <row r="128">
       <c r="A128" s="34" t="inlineStr">
         <is>
-          <t>洗劫</t>
+          <t>持枪抢劫</t>
         </is>
       </c>
       <c r="B128" s="34" t="inlineStr">
@@ -7520,7 +7520,7 @@
     <row r="129">
       <c r="A129" s="34" t="inlineStr">
         <is>
-          <t>抢了</t>
+          <t>抢夺财物</t>
         </is>
       </c>
       <c r="B129" s="34" t="inlineStr">
@@ -7544,12 +7544,12 @@
     <row r="130">
       <c r="A130" s="34" t="inlineStr">
         <is>
-          <t>盗窃</t>
+          <t>武力抢</t>
         </is>
       </c>
       <c r="B130" s="34" t="inlineStr">
         <is>
-          <t>盗窃罪</t>
+          <t>抢劫罪</t>
         </is>
       </c>
       <c r="C130" s="34">
@@ -7568,12 +7568,12 @@
     <row r="131">
       <c r="A131" s="34" t="inlineStr">
         <is>
-          <t>偷窃</t>
+          <t>威胁抢</t>
         </is>
       </c>
       <c r="B131" s="34" t="inlineStr">
         <is>
-          <t>盗窃罪</t>
+          <t>抢劫罪</t>
         </is>
       </c>
       <c r="C131" s="34">
@@ -7592,12 +7592,12 @@
     <row r="132">
       <c r="A132" s="34" t="inlineStr">
         <is>
-          <t>偷东西</t>
+          <t>打劫</t>
         </is>
       </c>
       <c r="B132" s="34" t="inlineStr">
         <is>
-          <t>盗窃罪</t>
+          <t>抢劫罪</t>
         </is>
       </c>
       <c r="C132" s="34">
@@ -7616,12 +7616,12 @@
     <row r="133">
       <c r="A133" s="34" t="inlineStr">
         <is>
-          <t>顺走</t>
+          <t>抢东西</t>
         </is>
       </c>
       <c r="B133" s="34" t="inlineStr">
         <is>
-          <t>盗窃罪</t>
+          <t>抢劫罪</t>
         </is>
       </c>
       <c r="C133" s="34">
@@ -7640,12 +7640,12 @@
     <row r="134">
       <c r="A134" s="34" t="inlineStr">
         <is>
-          <t>擅自使用他人财物</t>
+          <t>抢钱</t>
         </is>
       </c>
       <c r="B134" s="34" t="inlineStr">
         <is>
-          <t>盗窃罪</t>
+          <t>抢劫罪</t>
         </is>
       </c>
       <c r="C134" s="34">
@@ -7664,12 +7664,12 @@
     <row r="135">
       <c r="A135" s="34" t="inlineStr">
         <is>
-          <t>偷走</t>
+          <t>洗劫</t>
         </is>
       </c>
       <c r="B135" s="34" t="inlineStr">
         <is>
-          <t>盗窃罪</t>
+          <t>抢劫罪</t>
         </is>
       </c>
       <c r="C135" s="34">
@@ -7688,12 +7688,12 @@
     <row r="136">
       <c r="A136" s="34" t="inlineStr">
         <is>
-          <t>小偷</t>
+          <t>抢了</t>
         </is>
       </c>
       <c r="B136" s="34" t="inlineStr">
         <is>
-          <t>盗窃罪</t>
+          <t>抢劫罪</t>
         </is>
       </c>
       <c r="C136" s="34">
@@ -7712,7 +7712,7 @@
     <row r="137">
       <c r="A137" s="34" t="inlineStr">
         <is>
-          <t>扒窃</t>
+          <t>盗窃</t>
         </is>
       </c>
       <c r="B137" s="34" t="inlineStr">
@@ -7736,7 +7736,7 @@
     <row r="138">
       <c r="A138" s="34" t="inlineStr">
         <is>
-          <t>顺手牵羊</t>
+          <t>偷窃</t>
         </is>
       </c>
       <c r="B138" s="34" t="inlineStr">
@@ -7760,7 +7760,7 @@
     <row r="139">
       <c r="A139" s="34" t="inlineStr">
         <is>
-          <t>偷拿</t>
+          <t>偷东西</t>
         </is>
       </c>
       <c r="B139" s="34" t="inlineStr">
@@ -7784,7 +7784,7 @@
     <row r="140">
       <c r="A140" s="34" t="inlineStr">
         <is>
-          <t>偷了</t>
+          <t>顺走</t>
         </is>
       </c>
       <c r="B140" s="34" t="inlineStr">
@@ -7808,12 +7808,12 @@
     <row r="141">
       <c r="A141" s="34" t="inlineStr">
         <is>
-          <t>盗窃车辆</t>
+          <t>擅自使用他人财物</t>
         </is>
       </c>
       <c r="B141" s="34" t="inlineStr">
         <is>
-          <t>盗窃车辆罪</t>
+          <t>盗窃罪</t>
         </is>
       </c>
       <c r="C141" s="34">
@@ -7832,12 +7832,12 @@
     <row r="142">
       <c r="A142" s="34" t="inlineStr">
         <is>
-          <t>偷车</t>
+          <t>偷走</t>
         </is>
       </c>
       <c r="B142" s="34" t="inlineStr">
         <is>
-          <t>盗窃车辆罪</t>
+          <t>盗窃罪</t>
         </is>
       </c>
       <c r="C142" s="34">
@@ -7856,12 +7856,12 @@
     <row r="143">
       <c r="A143" s="34" t="inlineStr">
         <is>
-          <t>偷公务车</t>
+          <t>小偷</t>
         </is>
       </c>
       <c r="B143" s="34" t="inlineStr">
         <is>
-          <t>盗窃车辆罪</t>
+          <t>盗窃罪</t>
         </is>
       </c>
       <c r="C143" s="34">
@@ -7880,12 +7880,12 @@
     <row r="144">
       <c r="A144" s="34" t="inlineStr">
         <is>
-          <t>开走他人车</t>
+          <t>扒窃</t>
         </is>
       </c>
       <c r="B144" s="34" t="inlineStr">
         <is>
-          <t>盗窃车辆罪</t>
+          <t>盗窃罪</t>
         </is>
       </c>
       <c r="C144" s="34">
@@ -7904,12 +7904,12 @@
     <row r="145">
       <c r="A145" s="34" t="inlineStr">
         <is>
-          <t>擅自开走</t>
+          <t>顺手牵羊</t>
         </is>
       </c>
       <c r="B145" s="34" t="inlineStr">
         <is>
-          <t>盗窃车辆罪</t>
+          <t>盗窃罪</t>
         </is>
       </c>
       <c r="C145" s="34">
@@ -7928,12 +7928,12 @@
     <row r="146">
       <c r="A146" s="34" t="inlineStr">
         <is>
-          <t>顺走车</t>
+          <t>偷拿</t>
         </is>
       </c>
       <c r="B146" s="34" t="inlineStr">
         <is>
-          <t>盗窃车辆罪</t>
+          <t>盗窃罪</t>
         </is>
       </c>
       <c r="C146" s="34">
@@ -7952,12 +7952,12 @@
     <row r="147">
       <c r="A147" s="34" t="inlineStr">
         <is>
-          <t>撬车</t>
+          <t>偷了</t>
         </is>
       </c>
       <c r="B147" s="34" t="inlineStr">
         <is>
-          <t>盗窃车辆罪</t>
+          <t>盗窃罪</t>
         </is>
       </c>
       <c r="C147" s="34">
@@ -7976,7 +7976,7 @@
     <row r="148">
       <c r="A148" s="34" t="inlineStr">
         <is>
-          <t>把车开走</t>
+          <t>盗窃车辆</t>
         </is>
       </c>
       <c r="B148" s="34" t="inlineStr">
@@ -8000,7 +8000,7 @@
     <row r="149">
       <c r="A149" s="34" t="inlineStr">
         <is>
-          <t>偷了车</t>
+          <t>偷车</t>
         </is>
       </c>
       <c r="B149" s="34" t="inlineStr">
@@ -8024,12 +8024,12 @@
     <row r="150">
       <c r="A150" s="34" t="inlineStr">
         <is>
-          <t>收受赃物</t>
+          <t>偷公务车</t>
         </is>
       </c>
       <c r="B150" s="34" t="inlineStr">
         <is>
-          <t>收受赃物罪</t>
+          <t>盗窃车辆罪</t>
         </is>
       </c>
       <c r="C150" s="34">
@@ -8048,12 +8048,12 @@
     <row r="151">
       <c r="A151" s="34" t="inlineStr">
         <is>
-          <t>销赃</t>
+          <t>开走他人车</t>
         </is>
       </c>
       <c r="B151" s="34" t="inlineStr">
         <is>
-          <t>收受赃物罪</t>
+          <t>盗窃车辆罪</t>
         </is>
       </c>
       <c r="C151" s="34">
@@ -8072,12 +8072,12 @@
     <row r="152">
       <c r="A152" s="34" t="inlineStr">
         <is>
-          <t>买赃物</t>
+          <t>擅自开走</t>
         </is>
       </c>
       <c r="B152" s="34" t="inlineStr">
         <is>
-          <t>收受赃物罪</t>
+          <t>盗窃车辆罪</t>
         </is>
       </c>
       <c r="C152" s="34">
@@ -8096,12 +8096,12 @@
     <row r="153">
       <c r="A153" s="34" t="inlineStr">
         <is>
-          <t>藏赃</t>
+          <t>顺走车</t>
         </is>
       </c>
       <c r="B153" s="34" t="inlineStr">
         <is>
-          <t>收受赃物罪</t>
+          <t>盗窃车辆罪</t>
         </is>
       </c>
       <c r="C153" s="34">
@@ -8120,12 +8120,12 @@
     <row r="154">
       <c r="A154" s="34" t="inlineStr">
         <is>
-          <t>收赃</t>
+          <t>撬车</t>
         </is>
       </c>
       <c r="B154" s="34" t="inlineStr">
         <is>
-          <t>收受赃物罪</t>
+          <t>盗窃车辆罪</t>
         </is>
       </c>
       <c r="C154" s="34">
@@ -8144,12 +8144,12 @@
     <row r="155">
       <c r="A155" s="34" t="inlineStr">
         <is>
-          <t>收黑货</t>
+          <t>把车开走</t>
         </is>
       </c>
       <c r="B155" s="34" t="inlineStr">
         <is>
-          <t>收受赃物罪</t>
+          <t>盗窃车辆罪</t>
         </is>
       </c>
       <c r="C155" s="34">
@@ -8168,12 +8168,12 @@
     <row r="156">
       <c r="A156" s="34" t="inlineStr">
         <is>
-          <t>买黑车</t>
+          <t>偷了车</t>
         </is>
       </c>
       <c r="B156" s="34" t="inlineStr">
         <is>
-          <t>收受赃物罪</t>
+          <t>盗窃车辆罪</t>
         </is>
       </c>
       <c r="C156" s="34">
@@ -8192,12 +8192,12 @@
     <row r="157">
       <c r="A157" s="34" t="inlineStr">
         <is>
-          <t>敲诈</t>
+          <t>收受赃物</t>
         </is>
       </c>
       <c r="B157" s="34" t="inlineStr">
         <is>
-          <t>敲诈勒索罪</t>
+          <t>收受赃物罪</t>
         </is>
       </c>
       <c r="C157" s="34">
@@ -8216,12 +8216,12 @@
     <row r="158">
       <c r="A158" s="34" t="inlineStr">
         <is>
-          <t>勒索</t>
+          <t>销赃</t>
         </is>
       </c>
       <c r="B158" s="34" t="inlineStr">
         <is>
-          <t>敲诈勒索罪</t>
+          <t>收受赃物罪</t>
         </is>
       </c>
       <c r="C158" s="34">
@@ -8240,12 +8240,12 @@
     <row r="159">
       <c r="A159" s="34" t="inlineStr">
         <is>
-          <t>敲诈勒索</t>
+          <t>买赃物</t>
         </is>
       </c>
       <c r="B159" s="34" t="inlineStr">
         <is>
-          <t>敲诈勒索罪</t>
+          <t>收受赃物罪</t>
         </is>
       </c>
       <c r="C159" s="34">
@@ -8264,12 +8264,12 @@
     <row r="160">
       <c r="A160" s="34" t="inlineStr">
         <is>
-          <t>威胁索财</t>
+          <t>藏赃</t>
         </is>
       </c>
       <c r="B160" s="34" t="inlineStr">
         <is>
-          <t>敲诈勒索罪</t>
+          <t>收受赃物罪</t>
         </is>
       </c>
       <c r="C160" s="34">
@@ -8288,12 +8288,12 @@
     <row r="161">
       <c r="A161" s="34" t="inlineStr">
         <is>
-          <t>强迫交钱</t>
+          <t>收赃</t>
         </is>
       </c>
       <c r="B161" s="34" t="inlineStr">
         <is>
-          <t>敲诈勒索罪</t>
+          <t>收受赃物罪</t>
         </is>
       </c>
       <c r="C161" s="34">
@@ -8312,12 +8312,12 @@
     <row r="162">
       <c r="A162" s="34" t="inlineStr">
         <is>
-          <t>收保护费</t>
+          <t>收黑货</t>
         </is>
       </c>
       <c r="B162" s="34" t="inlineStr">
         <is>
-          <t>敲诈勒索罪</t>
+          <t>收受赃物罪</t>
         </is>
       </c>
       <c r="C162" s="34">
@@ -8336,12 +8336,12 @@
     <row r="163">
       <c r="A163" s="34" t="inlineStr">
         <is>
-          <t>逼着给钱</t>
+          <t>买黑车</t>
         </is>
       </c>
       <c r="B163" s="34" t="inlineStr">
         <is>
-          <t>敲诈勒索罪</t>
+          <t>收受赃物罪</t>
         </is>
       </c>
       <c r="C163" s="34">
@@ -8360,7 +8360,7 @@
     <row r="164">
       <c r="A164" s="34" t="inlineStr">
         <is>
-          <t>逼钱</t>
+          <t>敲诈</t>
         </is>
       </c>
       <c r="B164" s="34" t="inlineStr">
@@ -8384,12 +8384,12 @@
     <row r="165">
       <c r="A165" s="34" t="inlineStr">
         <is>
-          <t>蓄意破坏</t>
+          <t>勒索</t>
         </is>
       </c>
       <c r="B165" s="34" t="inlineStr">
         <is>
-          <t>蓄意破坏罪</t>
+          <t>敲诈勒索罪</t>
         </is>
       </c>
       <c r="C165" s="34">
@@ -8408,12 +8408,12 @@
     <row r="166">
       <c r="A166" s="34" t="inlineStr">
         <is>
-          <t>破坏财物</t>
+          <t>敲诈勒索</t>
         </is>
       </c>
       <c r="B166" s="34" t="inlineStr">
         <is>
-          <t>蓄意破坏罪</t>
+          <t>敲诈勒索罪</t>
         </is>
       </c>
       <c r="C166" s="34">
@@ -8432,12 +8432,12 @@
     <row r="167">
       <c r="A167" s="34" t="inlineStr">
         <is>
-          <t>毁损</t>
+          <t>威胁索财</t>
         </is>
       </c>
       <c r="B167" s="34" t="inlineStr">
         <is>
-          <t>蓄意破坏罪</t>
+          <t>敲诈勒索罪</t>
         </is>
       </c>
       <c r="C167" s="34">
@@ -8456,12 +8456,12 @@
     <row r="168">
       <c r="A168" s="34" t="inlineStr">
         <is>
-          <t>砸车</t>
+          <t>强迫交钱</t>
         </is>
       </c>
       <c r="B168" s="34" t="inlineStr">
         <is>
-          <t>蓄意破坏罪</t>
+          <t>敲诈勒索罪</t>
         </is>
       </c>
       <c r="C168" s="34">
@@ -8480,12 +8480,12 @@
     <row r="169">
       <c r="A169" s="34" t="inlineStr">
         <is>
-          <t>打砸</t>
+          <t>收保护费</t>
         </is>
       </c>
       <c r="B169" s="34" t="inlineStr">
         <is>
-          <t>蓄意破坏罪</t>
+          <t>敲诈勒索罪</t>
         </is>
       </c>
       <c r="C169" s="34">
@@ -8504,12 +8504,12 @@
     <row r="170">
       <c r="A170" s="34" t="inlineStr">
         <is>
-          <t>损毁车辆</t>
+          <t>逼着给钱</t>
         </is>
       </c>
       <c r="B170" s="34" t="inlineStr">
         <is>
-          <t>蓄意破坏罪</t>
+          <t>敲诈勒索罪</t>
         </is>
       </c>
       <c r="C170" s="34">
@@ -8528,12 +8528,12 @@
     <row r="171">
       <c r="A171" s="34" t="inlineStr">
         <is>
-          <t>故意损坏</t>
+          <t>逼钱</t>
         </is>
       </c>
       <c r="B171" s="34" t="inlineStr">
         <is>
-          <t>蓄意破坏罪</t>
+          <t>敲诈勒索罪</t>
         </is>
       </c>
       <c r="C171" s="34">
@@ -8552,7 +8552,7 @@
     <row r="172">
       <c r="A172" s="34" t="inlineStr">
         <is>
-          <t>砸东西</t>
+          <t>蓄意破坏</t>
         </is>
       </c>
       <c r="B172" s="34" t="inlineStr">
@@ -8576,7 +8576,7 @@
     <row r="173">
       <c r="A173" s="34" t="inlineStr">
         <is>
-          <t>砸玻璃</t>
+          <t>破坏财物</t>
         </is>
       </c>
       <c r="B173" s="34" t="inlineStr">
@@ -8600,7 +8600,7 @@
     <row r="174">
       <c r="A174" s="34" t="inlineStr">
         <is>
-          <t>破坏设施</t>
+          <t>毁损</t>
         </is>
       </c>
       <c r="B174" s="34" t="inlineStr">
@@ -8624,7 +8624,7 @@
     <row r="175">
       <c r="A175" s="34" t="inlineStr">
         <is>
-          <t>划车</t>
+          <t>砸车</t>
         </is>
       </c>
       <c r="B175" s="34" t="inlineStr">
@@ -8648,7 +8648,7 @@
     <row r="176">
       <c r="A176" s="34" t="inlineStr">
         <is>
-          <t>撞坏</t>
+          <t>打砸</t>
         </is>
       </c>
       <c r="B176" s="34" t="inlineStr">
@@ -8672,7 +8672,7 @@
     <row r="177">
       <c r="A177" s="34" t="inlineStr">
         <is>
-          <t>砸店</t>
+          <t>损毁车辆</t>
         </is>
       </c>
       <c r="B177" s="34" t="inlineStr">
@@ -8696,12 +8696,12 @@
     <row r="178">
       <c r="A178" s="34" t="inlineStr">
         <is>
-          <t>挪用公款</t>
+          <t>故意损坏</t>
         </is>
       </c>
       <c r="B178" s="34" t="inlineStr">
         <is>
-          <t>挪用公款公物罪</t>
+          <t>蓄意破坏罪</t>
         </is>
       </c>
       <c r="C178" s="34">
@@ -8720,12 +8720,12 @@
     <row r="179">
       <c r="A179" s="34" t="inlineStr">
         <is>
-          <t>挪用公物</t>
+          <t>砸东西</t>
         </is>
       </c>
       <c r="B179" s="34" t="inlineStr">
         <is>
-          <t>挪用公款公物罪</t>
+          <t>蓄意破坏罪</t>
         </is>
       </c>
       <c r="C179" s="34">
@@ -8744,12 +8744,12 @@
     <row r="180">
       <c r="A180" s="34" t="inlineStr">
         <is>
-          <t>侵占公款</t>
+          <t>砸玻璃</t>
         </is>
       </c>
       <c r="B180" s="34" t="inlineStr">
         <is>
-          <t>挪用公款公物罪</t>
+          <t>蓄意破坏罪</t>
         </is>
       </c>
       <c r="C180" s="34">
@@ -8768,12 +8768,12 @@
     <row r="181">
       <c r="A181" s="34" t="inlineStr">
         <is>
-          <t>职务侵占</t>
+          <t>破坏设施</t>
         </is>
       </c>
       <c r="B181" s="34" t="inlineStr">
         <is>
-          <t>挪用公款公物罪</t>
+          <t>蓄意破坏罪</t>
         </is>
       </c>
       <c r="C181" s="34">
@@ -8792,12 +8792,12 @@
     <row r="182">
       <c r="A182" s="34" t="inlineStr">
         <is>
-          <t>挪用公家</t>
+          <t>划车</t>
         </is>
       </c>
       <c r="B182" s="34" t="inlineStr">
         <is>
-          <t>挪用公款公物罪</t>
+          <t>蓄意破坏罪</t>
         </is>
       </c>
       <c r="C182" s="34">
@@ -8816,12 +8816,12 @@
     <row r="183">
       <c r="A183" s="34" t="inlineStr">
         <is>
-          <t>持有失窃物品</t>
+          <t>撞坏</t>
         </is>
       </c>
       <c r="B183" s="34" t="inlineStr">
         <is>
-          <t>持有失窃物品罪</t>
+          <t>蓄意破坏罪</t>
         </is>
       </c>
       <c r="C183" s="34">
@@ -8840,12 +8840,12 @@
     <row r="184">
       <c r="A184" s="34" t="inlineStr">
         <is>
-          <t>持有失窃</t>
+          <t>砸店</t>
         </is>
       </c>
       <c r="B184" s="34" t="inlineStr">
         <is>
-          <t>持有失窃物品罪</t>
+          <t>蓄意破坏罪</t>
         </is>
       </c>
       <c r="C184" s="34">
@@ -8864,12 +8864,12 @@
     <row r="185">
       <c r="A185" s="34" t="inlineStr">
         <is>
-          <t>捡到不还</t>
+          <t>挪用公款</t>
         </is>
       </c>
       <c r="B185" s="34" t="inlineStr">
         <is>
-          <t>持有失窃物品罪</t>
+          <t>挪用公款公物罪</t>
         </is>
       </c>
       <c r="C185" s="34">
@@ -8888,12 +8888,12 @@
     <row r="186">
       <c r="A186" s="34" t="inlineStr">
         <is>
-          <t>非法占有遗失物</t>
+          <t>挪用公物</t>
         </is>
       </c>
       <c r="B186" s="34" t="inlineStr">
         <is>
-          <t>持有失窃物品罪</t>
+          <t>挪用公款公物罪</t>
         </is>
       </c>
       <c r="C186" s="34">
@@ -8912,12 +8912,12 @@
     <row r="187">
       <c r="A187" s="34" t="inlineStr">
         <is>
-          <t>藏着别人丢的</t>
+          <t>侵占公款</t>
         </is>
       </c>
       <c r="B187" s="34" t="inlineStr">
         <is>
-          <t>持有失窃物品罪</t>
+          <t>挪用公款公物罪</t>
         </is>
       </c>
       <c r="C187" s="34">
@@ -8936,12 +8936,12 @@
     <row r="188">
       <c r="A188" s="34" t="inlineStr">
         <is>
-          <t>公共场合淫秽</t>
+          <t>职务侵占</t>
         </is>
       </c>
       <c r="B188" s="34" t="inlineStr">
         <is>
-          <t>在公共场合从事淫秽行为罪</t>
+          <t>挪用公款公物罪</t>
         </is>
       </c>
       <c r="C188" s="34">
@@ -8960,12 +8960,12 @@
     <row r="189">
       <c r="A189" s="34" t="inlineStr">
         <is>
-          <t>公然猥亵</t>
+          <t>挪用公家</t>
         </is>
       </c>
       <c r="B189" s="34" t="inlineStr">
         <is>
-          <t>在公共场合从事淫秽行为罪</t>
+          <t>挪用公款公物罪</t>
         </is>
       </c>
       <c r="C189" s="34">
@@ -8984,12 +8984,12 @@
     <row r="190">
       <c r="A190" s="34" t="inlineStr">
         <is>
-          <t>淫秽行为</t>
+          <t>持有失窃物品</t>
         </is>
       </c>
       <c r="B190" s="34" t="inlineStr">
         <is>
-          <t>在公共场合从事淫秽行为罪</t>
+          <t>持有失窃物品罪</t>
         </is>
       </c>
       <c r="C190" s="34">
@@ -9008,12 +9008,12 @@
     <row r="191">
       <c r="A191" s="34" t="inlineStr">
         <is>
-          <t>招嫖</t>
+          <t>持有失窃</t>
         </is>
       </c>
       <c r="B191" s="34" t="inlineStr">
         <is>
-          <t>在公共场合从事淫秽行为罪</t>
+          <t>持有失窃物品罪</t>
         </is>
       </c>
       <c r="C191" s="34">
@@ -9032,12 +9032,12 @@
     <row r="192">
       <c r="A192" s="34" t="inlineStr">
         <is>
-          <t>公开招募性交易</t>
+          <t>捡到不还</t>
         </is>
       </c>
       <c r="B192" s="34" t="inlineStr">
         <is>
-          <t>在公共场合从事淫秽行为罪</t>
+          <t>持有失窃物品罪</t>
         </is>
       </c>
       <c r="C192" s="34">
@@ -9056,12 +9056,12 @@
     <row r="193">
       <c r="A193" s="34" t="inlineStr">
         <is>
-          <t>当街猥亵</t>
+          <t>非法占有遗失物</t>
         </is>
       </c>
       <c r="B193" s="34" t="inlineStr">
         <is>
-          <t>在公共场合从事淫秽行为罪</t>
+          <t>持有失窃物品罪</t>
         </is>
       </c>
       <c r="C193" s="34">
@@ -9080,12 +9080,12 @@
     <row r="194">
       <c r="A194" s="34" t="inlineStr">
         <is>
-          <t>猥亵</t>
+          <t>藏着别人丢的</t>
         </is>
       </c>
       <c r="B194" s="34" t="inlineStr">
         <is>
-          <t>在公共场合从事淫秽行为罪</t>
+          <t>持有失窃物品罪</t>
         </is>
       </c>
       <c r="C194" s="34">
@@ -9104,12 +9104,12 @@
     <row r="195">
       <c r="A195" s="34" t="inlineStr">
         <is>
-          <t>组织卖淫</t>
+          <t>公共场合淫秽</t>
         </is>
       </c>
       <c r="B195" s="34" t="inlineStr">
         <is>
-          <t>组织卖淫罪</t>
+          <t>在公共场合从事淫秽行为罪</t>
         </is>
       </c>
       <c r="C195" s="34">
@@ -9128,12 +9128,12 @@
     <row r="196">
       <c r="A196" s="34" t="inlineStr">
         <is>
-          <t>拉皮条</t>
+          <t>公然猥亵</t>
         </is>
       </c>
       <c r="B196" s="34" t="inlineStr">
         <is>
-          <t>组织卖淫罪</t>
+          <t>在公共场合从事淫秽行为罪</t>
         </is>
       </c>
       <c r="C196" s="34">
@@ -9152,12 +9152,12 @@
     <row r="197">
       <c r="A197" s="34" t="inlineStr">
         <is>
-          <t>强迫卖淫</t>
+          <t>淫秽行为</t>
         </is>
       </c>
       <c r="B197" s="34" t="inlineStr">
         <is>
-          <t>组织卖淫罪</t>
+          <t>在公共场合从事淫秽行为罪</t>
         </is>
       </c>
       <c r="C197" s="34">
@@ -9176,12 +9176,12 @@
     <row r="198">
       <c r="A198" s="34" t="inlineStr">
         <is>
-          <t>介绍卖淫</t>
+          <t>招嫖</t>
         </is>
       </c>
       <c r="B198" s="34" t="inlineStr">
         <is>
-          <t>组织卖淫罪</t>
+          <t>在公共场合从事淫秽行为罪</t>
         </is>
       </c>
       <c r="C198" s="34">
@@ -9200,12 +9200,12 @@
     <row r="199">
       <c r="A199" s="34" t="inlineStr">
         <is>
-          <t>开妓院</t>
+          <t>公开招募性交易</t>
         </is>
       </c>
       <c r="B199" s="34" t="inlineStr">
         <is>
-          <t>组织卖淫罪</t>
+          <t>在公共场合从事淫秽行为罪</t>
         </is>
       </c>
       <c r="C199" s="34">
@@ -9224,12 +9224,12 @@
     <row r="200">
       <c r="A200" s="34" t="inlineStr">
         <is>
-          <t>卖淫</t>
+          <t>当街猥亵</t>
         </is>
       </c>
       <c r="B200" s="34" t="inlineStr">
         <is>
-          <t>卖淫罪</t>
+          <t>在公共场合从事淫秽行为罪</t>
         </is>
       </c>
       <c r="C200" s="34">
@@ -9248,12 +9248,12 @@
     <row r="201">
       <c r="A201" s="34" t="inlineStr">
         <is>
-          <t>性交易</t>
+          <t>猥亵</t>
         </is>
       </c>
       <c r="B201" s="34" t="inlineStr">
         <is>
-          <t>卖淫罪</t>
+          <t>在公共场合从事淫秽行为罪</t>
         </is>
       </c>
       <c r="C201" s="34">
@@ -9272,12 +9272,12 @@
     <row r="202">
       <c r="A202" s="34" t="inlineStr">
         <is>
-          <t>提供性服务</t>
+          <t>组织卖淫</t>
         </is>
       </c>
       <c r="B202" s="34" t="inlineStr">
         <is>
-          <t>卖淫罪</t>
+          <t>组织卖淫罪</t>
         </is>
       </c>
       <c r="C202" s="34">
@@ -9296,12 +9296,12 @@
     <row r="203">
       <c r="A203" s="34" t="inlineStr">
         <is>
-          <t>接客</t>
+          <t>拉皮条</t>
         </is>
       </c>
       <c r="B203" s="34" t="inlineStr">
         <is>
-          <t>卖淫罪</t>
+          <t>组织卖淫罪</t>
         </is>
       </c>
       <c r="C203" s="34">
@@ -9320,12 +9320,12 @@
     <row r="204">
       <c r="A204" s="34" t="inlineStr">
         <is>
-          <t>强奸</t>
+          <t>强迫卖淫</t>
         </is>
       </c>
       <c r="B204" s="34" t="inlineStr">
         <is>
-          <t>强奸罪</t>
+          <t>组织卖淫罪</t>
         </is>
       </c>
       <c r="C204" s="34">
@@ -9344,12 +9344,12 @@
     <row r="205">
       <c r="A205" s="34" t="inlineStr">
         <is>
-          <t>性侵</t>
+          <t>介绍卖淫</t>
         </is>
       </c>
       <c r="B205" s="34" t="inlineStr">
         <is>
-          <t>强奸罪</t>
+          <t>组织卖淫罪</t>
         </is>
       </c>
       <c r="C205" s="34">
@@ -9368,12 +9368,12 @@
     <row r="206">
       <c r="A206" s="34" t="inlineStr">
         <is>
-          <t>强迫性行为</t>
+          <t>开妓院</t>
         </is>
       </c>
       <c r="B206" s="34" t="inlineStr">
         <is>
-          <t>强奸罪</t>
+          <t>组织卖淫罪</t>
         </is>
       </c>
       <c r="C206" s="34">
@@ -9392,12 +9392,12 @@
     <row r="207">
       <c r="A207" s="34" t="inlineStr">
         <is>
-          <t>强迫发生关系</t>
+          <t>卖淫</t>
         </is>
       </c>
       <c r="B207" s="34" t="inlineStr">
         <is>
-          <t>强奸罪</t>
+          <t>卖淫罪</t>
         </is>
       </c>
       <c r="C207" s="34">
@@ -9416,12 +9416,12 @@
     <row r="208">
       <c r="A208" s="34" t="inlineStr">
         <is>
-          <t>迷奸</t>
+          <t>性交易</t>
         </is>
       </c>
       <c r="B208" s="34" t="inlineStr">
         <is>
-          <t>强奸罪</t>
+          <t>卖淫罪</t>
         </is>
       </c>
       <c r="C208" s="34">
@@ -9440,12 +9440,12 @@
     <row r="209">
       <c r="A209" s="34" t="inlineStr">
         <is>
-          <t>传播淫秽</t>
+          <t>提供性服务</t>
         </is>
       </c>
       <c r="B209" s="34" t="inlineStr">
         <is>
-          <t>传播淫秽色情罪</t>
+          <t>卖淫罪</t>
         </is>
       </c>
       <c r="C209" s="34">
@@ -9464,12 +9464,12 @@
     <row r="210">
       <c r="A210" s="34" t="inlineStr">
         <is>
-          <t>传播色情</t>
+          <t>接客</t>
         </is>
       </c>
       <c r="B210" s="34" t="inlineStr">
         <is>
-          <t>传播淫秽色情罪</t>
+          <t>卖淫罪</t>
         </is>
       </c>
       <c r="C210" s="34">
@@ -9488,12 +9488,12 @@
     <row r="211">
       <c r="A211" s="34" t="inlineStr">
         <is>
-          <t>淫秽内容</t>
+          <t>强奸</t>
         </is>
       </c>
       <c r="B211" s="34" t="inlineStr">
         <is>
-          <t>传播淫秽色情罪</t>
+          <t>强奸罪</t>
         </is>
       </c>
       <c r="C211" s="34">
@@ -9512,12 +9512,12 @@
     <row r="212">
       <c r="A212" s="34" t="inlineStr">
         <is>
-          <t>色情视频</t>
+          <t>性侵</t>
         </is>
       </c>
       <c r="B212" s="34" t="inlineStr">
         <is>
-          <t>传播淫秽色情罪</t>
+          <t>强奸罪</t>
         </is>
       </c>
       <c r="C212" s="34">
@@ -9536,12 +9536,12 @@
     <row r="213">
       <c r="A213" s="34" t="inlineStr">
         <is>
-          <t>贩卖色情</t>
+          <t>强迫性行为</t>
         </is>
       </c>
       <c r="B213" s="34" t="inlineStr">
         <is>
-          <t>传播淫秽色情罪</t>
+          <t>强奸罪</t>
         </is>
       </c>
       <c r="C213" s="34">
@@ -9560,12 +9560,12 @@
     <row r="214">
       <c r="A214" s="34" t="inlineStr">
         <is>
-          <t>发黄图</t>
+          <t>强迫发生关系</t>
         </is>
       </c>
       <c r="B214" s="34" t="inlineStr">
         <is>
-          <t>传播淫秽色情罪</t>
+          <t>强奸罪</t>
         </is>
       </c>
       <c r="C214" s="34">
@@ -9584,12 +9584,12 @@
     <row r="215">
       <c r="A215" s="34" t="inlineStr">
         <is>
-          <t>传黄片</t>
+          <t>迷奸</t>
         </is>
       </c>
       <c r="B215" s="34" t="inlineStr">
         <is>
-          <t>传播淫秽色情罪</t>
+          <t>强奸罪</t>
         </is>
       </c>
       <c r="C215" s="34">
@@ -9608,12 +9608,12 @@
     <row r="216">
       <c r="A216" s="34" t="inlineStr">
         <is>
-          <t>歧视</t>
+          <t>传播淫秽</t>
         </is>
       </c>
       <c r="B216" s="34" t="inlineStr">
         <is>
-          <t>歧视罪</t>
+          <t>传播淫秽色情罪</t>
         </is>
       </c>
       <c r="C216" s="34">
@@ -9632,12 +9632,12 @@
     <row r="217">
       <c r="A217" s="34" t="inlineStr">
         <is>
-          <t>种族歧视</t>
+          <t>传播色情</t>
         </is>
       </c>
       <c r="B217" s="34" t="inlineStr">
         <is>
-          <t>歧视罪</t>
+          <t>传播淫秽色情罪</t>
         </is>
       </c>
       <c r="C217" s="34">
@@ -9656,12 +9656,12 @@
     <row r="218">
       <c r="A218" s="34" t="inlineStr">
         <is>
-          <t>辱骂</t>
+          <t>淫秽内容</t>
         </is>
       </c>
       <c r="B218" s="34" t="inlineStr">
         <is>
-          <t>歧视罪</t>
+          <t>传播淫秽色情罪</t>
         </is>
       </c>
       <c r="C218" s="34">
@@ -9680,12 +9680,12 @@
     <row r="219">
       <c r="A219" s="34" t="inlineStr">
         <is>
-          <t>侮辱</t>
+          <t>色情视频</t>
         </is>
       </c>
       <c r="B219" s="34" t="inlineStr">
         <is>
-          <t>歧视罪</t>
+          <t>传播淫秽色情罪</t>
         </is>
       </c>
       <c r="C219" s="34">
@@ -9704,12 +9704,12 @@
     <row r="220">
       <c r="A220" s="34" t="inlineStr">
         <is>
-          <t>贬低</t>
+          <t>贩卖色情</t>
         </is>
       </c>
       <c r="B220" s="34" t="inlineStr">
         <is>
-          <t>歧视罪</t>
+          <t>传播淫秽色情罪</t>
         </is>
       </c>
       <c r="C220" s="34">
@@ -9728,12 +9728,12 @@
     <row r="221">
       <c r="A221" s="34" t="inlineStr">
         <is>
-          <t>地图炮</t>
+          <t>发黄图</t>
         </is>
       </c>
       <c r="B221" s="34" t="inlineStr">
         <is>
-          <t>歧视罪</t>
+          <t>传播淫秽色情罪</t>
         </is>
       </c>
       <c r="C221" s="34">
@@ -9752,12 +9752,12 @@
     <row r="222">
       <c r="A222" s="34" t="inlineStr">
         <is>
-          <t>诽谤</t>
+          <t>传黄片</t>
         </is>
       </c>
       <c r="B222" s="34" t="inlineStr">
         <is>
-          <t>诽谤罪</t>
+          <t>传播淫秽色情罪</t>
         </is>
       </c>
       <c r="C222" s="34">
@@ -9776,12 +9776,12 @@
     <row r="223">
       <c r="A223" s="34" t="inlineStr">
         <is>
-          <t>造谣</t>
+          <t>歧视</t>
         </is>
       </c>
       <c r="B223" s="34" t="inlineStr">
         <is>
-          <t>诽谤罪</t>
+          <t>歧视罪</t>
         </is>
       </c>
       <c r="C223" s="34">
@@ -9800,12 +9800,12 @@
     <row r="224">
       <c r="A224" s="34" t="inlineStr">
         <is>
-          <t>污蔑</t>
+          <t>种族歧视</t>
         </is>
       </c>
       <c r="B224" s="34" t="inlineStr">
         <is>
-          <t>诽谤罪</t>
+          <t>歧视罪</t>
         </is>
       </c>
       <c r="C224" s="34">
@@ -9824,12 +9824,12 @@
     <row r="225">
       <c r="A225" s="34" t="inlineStr">
         <is>
-          <t>捏造</t>
+          <t>辱骂</t>
         </is>
       </c>
       <c r="B225" s="34" t="inlineStr">
         <is>
-          <t>诽谤罪</t>
+          <t>歧视罪</t>
         </is>
       </c>
       <c r="C225" s="34">
@@ -9848,12 +9848,12 @@
     <row r="226">
       <c r="A226" s="34" t="inlineStr">
         <is>
-          <t>损害名誉</t>
+          <t>侮辱</t>
         </is>
       </c>
       <c r="B226" s="34" t="inlineStr">
         <is>
-          <t>诽谤罪</t>
+          <t>歧视罪</t>
         </is>
       </c>
       <c r="C226" s="34">
@@ -9872,12 +9872,12 @@
     <row r="227">
       <c r="A227" s="34" t="inlineStr">
         <is>
-          <t>传播虚假信息</t>
+          <t>贬低</t>
         </is>
       </c>
       <c r="B227" s="34" t="inlineStr">
         <is>
-          <t>诽谤罪</t>
+          <t>歧视罪</t>
         </is>
       </c>
       <c r="C227" s="34">
@@ -9896,12 +9896,12 @@
     <row r="228">
       <c r="A228" s="34" t="inlineStr">
         <is>
-          <t>抹黑</t>
+          <t>地图炮</t>
         </is>
       </c>
       <c r="B228" s="34" t="inlineStr">
         <is>
-          <t>诽谤罪</t>
+          <t>歧视罪</t>
         </is>
       </c>
       <c r="C228" s="34">
@@ -9920,7 +9920,7 @@
     <row r="229">
       <c r="A229" s="34" t="inlineStr">
         <is>
-          <t>造黄谣</t>
+          <t>诽谤</t>
         </is>
       </c>
       <c r="B229" s="34" t="inlineStr">
@@ -9944,12 +9944,12 @@
     <row r="230">
       <c r="A230" s="34" t="inlineStr">
         <is>
-          <t>行贿</t>
+          <t>造谣</t>
         </is>
       </c>
       <c r="B230" s="34" t="inlineStr">
         <is>
-          <t>行贿罪</t>
+          <t>诽谤罪</t>
         </is>
       </c>
       <c r="C230" s="34">
@@ -9968,12 +9968,12 @@
     <row r="231">
       <c r="A231" s="34" t="inlineStr">
         <is>
-          <t>贿赂</t>
+          <t>污蔑</t>
         </is>
       </c>
       <c r="B231" s="34" t="inlineStr">
         <is>
-          <t>行贿罪</t>
+          <t>诽谤罪</t>
         </is>
       </c>
       <c r="C231" s="34">
@@ -9992,12 +9992,12 @@
     <row r="232">
       <c r="A232" s="34" t="inlineStr">
         <is>
-          <t>送钱给</t>
+          <t>捏造</t>
         </is>
       </c>
       <c r="B232" s="34" t="inlineStr">
         <is>
-          <t>行贿罪</t>
+          <t>诽谤罪</t>
         </is>
       </c>
       <c r="C232" s="34">
@@ -10016,12 +10016,12 @@
     <row r="233">
       <c r="A233" s="34" t="inlineStr">
         <is>
-          <t>塞钱</t>
+          <t>损害名誉</t>
         </is>
       </c>
       <c r="B233" s="34" t="inlineStr">
         <is>
-          <t>行贿罪</t>
+          <t>诽谤罪</t>
         </is>
       </c>
       <c r="C233" s="34">
@@ -10040,12 +10040,12 @@
     <row r="234">
       <c r="A234" s="34" t="inlineStr">
         <is>
-          <t>贿赂政府</t>
+          <t>传播虚假信息</t>
         </is>
       </c>
       <c r="B234" s="34" t="inlineStr">
         <is>
-          <t>行贿罪</t>
+          <t>诽谤罪</t>
         </is>
       </c>
       <c r="C234" s="34">
@@ -10064,12 +10064,12 @@
     <row r="235">
       <c r="A235" s="34" t="inlineStr">
         <is>
-          <t>给警察塞钱</t>
+          <t>抹黑</t>
         </is>
       </c>
       <c r="B235" s="34" t="inlineStr">
         <is>
-          <t>行贿罪</t>
+          <t>诽谤罪</t>
         </is>
       </c>
       <c r="C235" s="34">
@@ -10088,12 +10088,12 @@
     <row r="236">
       <c r="A236" s="34" t="inlineStr">
         <is>
-          <t>买通</t>
+          <t>造黄谣</t>
         </is>
       </c>
       <c r="B236" s="34" t="inlineStr">
         <is>
-          <t>行贿罪</t>
+          <t>诽谤罪</t>
         </is>
       </c>
       <c r="C236" s="34">
@@ -10112,7 +10112,7 @@
     <row r="237">
       <c r="A237" s="34" t="inlineStr">
         <is>
-          <t>塞红包</t>
+          <t>行贿</t>
         </is>
       </c>
       <c r="B237" s="34" t="inlineStr">
@@ -10136,12 +10136,12 @@
     <row r="238">
       <c r="A238" s="34" t="inlineStr">
         <is>
-          <t>妨碍司法</t>
+          <t>贿赂</t>
         </is>
       </c>
       <c r="B238" s="34" t="inlineStr">
         <is>
-          <t>妨碍司法罪</t>
+          <t>行贿罪</t>
         </is>
       </c>
       <c r="C238" s="34">
@@ -10160,12 +10160,12 @@
     <row r="239">
       <c r="A239" s="34" t="inlineStr">
         <is>
-          <t>阻碍司法</t>
+          <t>送钱给</t>
         </is>
       </c>
       <c r="B239" s="34" t="inlineStr">
         <is>
-          <t>妨碍司法罪</t>
+          <t>行贿罪</t>
         </is>
       </c>
       <c r="C239" s="34">
@@ -10184,12 +10184,12 @@
     <row r="240">
       <c r="A240" s="34" t="inlineStr">
         <is>
-          <t>阻碍法律文书</t>
+          <t>塞钱</t>
         </is>
       </c>
       <c r="B240" s="34" t="inlineStr">
         <is>
-          <t>妨碍司法罪</t>
+          <t>行贿罪</t>
         </is>
       </c>
       <c r="C240" s="34">
@@ -10208,12 +10208,12 @@
     <row r="241">
       <c r="A241" s="34" t="inlineStr">
         <is>
-          <t>拒绝命令</t>
+          <t>贿赂政府</t>
         </is>
       </c>
       <c r="B241" s="34" t="inlineStr">
         <is>
-          <t>拒绝听从执法人员命令与检查罪</t>
+          <t>行贿罪</t>
         </is>
       </c>
       <c r="C241" s="34">
@@ -10232,12 +10232,12 @@
     <row r="242">
       <c r="A242" s="34" t="inlineStr">
         <is>
-          <t>不服从命令</t>
+          <t>给警察塞钱</t>
         </is>
       </c>
       <c r="B242" s="34" t="inlineStr">
         <is>
-          <t>拒绝听从执法人员命令与检查罪</t>
+          <t>行贿罪</t>
         </is>
       </c>
       <c r="C242" s="34">
@@ -10256,12 +10256,12 @@
     <row r="243">
       <c r="A243" s="34" t="inlineStr">
         <is>
-          <t>拒绝检查</t>
+          <t>买通</t>
         </is>
       </c>
       <c r="B243" s="34" t="inlineStr">
         <is>
-          <t>拒绝听从执法人员命令与检查罪</t>
+          <t>行贿罪</t>
         </is>
       </c>
       <c r="C243" s="34">
@@ -10280,12 +10280,12 @@
     <row r="244">
       <c r="A244" s="34" t="inlineStr">
         <is>
-          <t>不配合检查</t>
+          <t>塞红包</t>
         </is>
       </c>
       <c r="B244" s="34" t="inlineStr">
         <is>
-          <t>拒绝听从执法人员命令与检查罪</t>
+          <t>行贿罪</t>
         </is>
       </c>
       <c r="C244" s="34">
@@ -10304,12 +10304,12 @@
     <row r="245">
       <c r="A245" s="34" t="inlineStr">
         <is>
-          <t>拒绝指示</t>
+          <t>妨碍司法</t>
         </is>
       </c>
       <c r="B245" s="34" t="inlineStr">
         <is>
-          <t>拒绝听从执法人员命令与检查罪</t>
+          <t>妨碍司法罪</t>
         </is>
       </c>
       <c r="C245" s="34">
@@ -10328,12 +10328,12 @@
     <row r="246">
       <c r="A246" s="34" t="inlineStr">
         <is>
-          <t>不听指挥</t>
+          <t>阻碍司法</t>
         </is>
       </c>
       <c r="B246" s="34" t="inlineStr">
         <is>
-          <t>拒绝听从执法人员命令与检查罪</t>
+          <t>妨碍司法罪</t>
         </is>
       </c>
       <c r="C246" s="34">
@@ -10352,12 +10352,12 @@
     <row r="247">
       <c r="A247" s="34" t="inlineStr">
         <is>
-          <t>不配合</t>
+          <t>阻碍法律文书</t>
         </is>
       </c>
       <c r="B247" s="34" t="inlineStr">
         <is>
-          <t>拒绝听从执法人员命令与检查罪</t>
+          <t>妨碍司法罪</t>
         </is>
       </c>
       <c r="C247" s="34">
@@ -10376,7 +10376,7 @@
     <row r="248">
       <c r="A248" s="34" t="inlineStr">
         <is>
-          <t>无视警察命令</t>
+          <t>拒绝命令</t>
         </is>
       </c>
       <c r="B248" s="34" t="inlineStr">
@@ -10400,7 +10400,7 @@
     <row r="249">
       <c r="A249" s="34" t="inlineStr">
         <is>
-          <t>不靠边</t>
+          <t>不服从命令</t>
         </is>
       </c>
       <c r="B249" s="34" t="inlineStr">
@@ -10424,12 +10424,12 @@
     <row r="250">
       <c r="A250" s="34" t="inlineStr">
         <is>
-          <t>拒绝提供身份</t>
+          <t>拒绝检查</t>
         </is>
       </c>
       <c r="B250" s="34" t="inlineStr">
         <is>
-          <t>拒绝提供身份罪</t>
+          <t>拒绝听从执法人员命令与检查罪</t>
         </is>
       </c>
       <c r="C250" s="34">
@@ -10448,12 +10448,12 @@
     <row r="251">
       <c r="A251" s="34" t="inlineStr">
         <is>
-          <t>拒报身份</t>
+          <t>不配合检查</t>
         </is>
       </c>
       <c r="B251" s="34" t="inlineStr">
         <is>
-          <t>拒绝提供身份罪</t>
+          <t>拒绝听从执法人员命令与检查罪</t>
         </is>
       </c>
       <c r="C251" s="34">
@@ -10472,12 +10472,12 @@
     <row r="252">
       <c r="A252" s="34" t="inlineStr">
         <is>
-          <t>不提供身份</t>
+          <t>拒绝指示</t>
         </is>
       </c>
       <c r="B252" s="34" t="inlineStr">
         <is>
-          <t>拒绝提供身份罪</t>
+          <t>拒绝听从执法人员命令与检查罪</t>
         </is>
       </c>
       <c r="C252" s="34">
@@ -10496,12 +10496,12 @@
     <row r="253">
       <c r="A253" s="34" t="inlineStr">
         <is>
-          <t>拒绝出示证件</t>
+          <t>不听指挥</t>
         </is>
       </c>
       <c r="B253" s="34" t="inlineStr">
         <is>
-          <t>拒绝提供身份罪</t>
+          <t>拒绝听从执法人员命令与检查罪</t>
         </is>
       </c>
       <c r="C253" s="34">
@@ -10520,12 +10520,12 @@
     <row r="254">
       <c r="A254" s="34" t="inlineStr">
         <is>
-          <t>不报姓名</t>
+          <t>不配合</t>
         </is>
       </c>
       <c r="B254" s="34" t="inlineStr">
         <is>
-          <t>拒绝提供身份罪</t>
+          <t>拒绝听从执法人员命令与检查罪</t>
         </is>
       </c>
       <c r="C254" s="34">
@@ -10544,12 +10544,12 @@
     <row r="255">
       <c r="A255" s="34" t="inlineStr">
         <is>
-          <t>不给看证件</t>
+          <t>无视警察命令</t>
         </is>
       </c>
       <c r="B255" s="34" t="inlineStr">
         <is>
-          <t>拒绝提供身份罪</t>
+          <t>拒绝听从执法人员命令与检查罪</t>
         </is>
       </c>
       <c r="C255" s="34">
@@ -10568,12 +10568,12 @@
     <row r="256">
       <c r="A256" s="34" t="inlineStr">
         <is>
-          <t>拒绝报名字</t>
+          <t>不靠边</t>
         </is>
       </c>
       <c r="B256" s="34" t="inlineStr">
         <is>
-          <t>拒绝提供身份罪</t>
+          <t>拒绝听从执法人员命令与检查罪</t>
         </is>
       </c>
       <c r="C256" s="34">
@@ -10592,12 +10592,12 @@
     <row r="257">
       <c r="A257" s="34" t="inlineStr">
         <is>
-          <t>破坏证据</t>
+          <t>拒绝提供身份</t>
         </is>
       </c>
       <c r="B257" s="34" t="inlineStr">
         <is>
-          <t>破坏证据罪</t>
+          <t>拒绝提供身份罪</t>
         </is>
       </c>
       <c r="C257" s="34">
@@ -10616,12 +10616,12 @@
     <row r="258">
       <c r="A258" s="34" t="inlineStr">
         <is>
-          <t>销毁证据</t>
+          <t>拒报身份</t>
         </is>
       </c>
       <c r="B258" s="34" t="inlineStr">
         <is>
-          <t>破坏证据罪</t>
+          <t>拒绝提供身份罪</t>
         </is>
       </c>
       <c r="C258" s="34">
@@ -10640,12 +10640,12 @@
     <row r="259">
       <c r="A259" s="34" t="inlineStr">
         <is>
-          <t>毁灭证据</t>
+          <t>不提供身份</t>
         </is>
       </c>
       <c r="B259" s="34" t="inlineStr">
         <is>
-          <t>破坏证据罪</t>
+          <t>拒绝提供身份罪</t>
         </is>
       </c>
       <c r="C259" s="34">
@@ -10664,12 +10664,12 @@
     <row r="260">
       <c r="A260" s="34" t="inlineStr">
         <is>
-          <t>篡改证据</t>
+          <t>拒绝出示证件</t>
         </is>
       </c>
       <c r="B260" s="34" t="inlineStr">
         <is>
-          <t>破坏证据罪</t>
+          <t>拒绝提供身份罪</t>
         </is>
       </c>
       <c r="C260" s="34">
@@ -10688,12 +10688,12 @@
     <row r="261">
       <c r="A261" s="34" t="inlineStr">
         <is>
-          <t>伪造证据</t>
+          <t>不报姓名</t>
         </is>
       </c>
       <c r="B261" s="34" t="inlineStr">
         <is>
-          <t>破坏证据罪</t>
+          <t>拒绝提供身份罪</t>
         </is>
       </c>
       <c r="C261" s="34">
@@ -10712,12 +10712,12 @@
     <row r="262">
       <c r="A262" s="34" t="inlineStr">
         <is>
-          <t>藏匿证据</t>
+          <t>不给看证件</t>
         </is>
       </c>
       <c r="B262" s="34" t="inlineStr">
         <is>
-          <t>破坏证据罪</t>
+          <t>拒绝提供身份罪</t>
         </is>
       </c>
       <c r="C262" s="34">
@@ -10736,12 +10736,12 @@
     <row r="263">
       <c r="A263" s="34" t="inlineStr">
         <is>
-          <t>丢掉证据</t>
+          <t>拒绝报名字</t>
         </is>
       </c>
       <c r="B263" s="34" t="inlineStr">
         <is>
-          <t>破坏证据罪</t>
+          <t>拒绝提供身份罪</t>
         </is>
       </c>
       <c r="C263" s="34">
@@ -10760,7 +10760,7 @@
     <row r="264">
       <c r="A264" s="34" t="inlineStr">
         <is>
-          <t>扔掉毒品</t>
+          <t>破坏证据</t>
         </is>
       </c>
       <c r="B264" s="34" t="inlineStr">
@@ -10784,12 +10784,12 @@
     <row r="265">
       <c r="A265" s="34" t="inlineStr">
         <is>
-          <t>冒充政府</t>
+          <t>销毁证据</t>
         </is>
       </c>
       <c r="B265" s="34" t="inlineStr">
         <is>
-          <t>冒充政府雇员罪</t>
+          <t>破坏证据罪</t>
         </is>
       </c>
       <c r="C265" s="34">
@@ -10808,12 +10808,12 @@
     <row r="266">
       <c r="A266" s="34" t="inlineStr">
         <is>
-          <t>冒充警察</t>
+          <t>毁灭证据</t>
         </is>
       </c>
       <c r="B266" s="34" t="inlineStr">
         <is>
-          <t>冒充政府雇员罪</t>
+          <t>破坏证据罪</t>
         </is>
       </c>
       <c r="C266" s="34">
@@ -10832,12 +10832,12 @@
     <row r="267">
       <c r="A267" s="34" t="inlineStr">
         <is>
-          <t>假冒警察</t>
+          <t>篡改证据</t>
         </is>
       </c>
       <c r="B267" s="34" t="inlineStr">
         <is>
-          <t>冒充政府雇员罪</t>
+          <t>破坏证据罪</t>
         </is>
       </c>
       <c r="C267" s="34">
@@ -10856,12 +10856,12 @@
     <row r="268">
       <c r="A268" s="34" t="inlineStr">
         <is>
-          <t>冒充公职</t>
+          <t>伪造证据</t>
         </is>
       </c>
       <c r="B268" s="34" t="inlineStr">
         <is>
-          <t>冒充政府雇员罪</t>
+          <t>破坏证据罪</t>
         </is>
       </c>
       <c r="C268" s="34">
@@ -10880,12 +10880,12 @@
     <row r="269">
       <c r="A269" s="34" t="inlineStr">
         <is>
-          <t>假扮警察</t>
+          <t>藏匿证据</t>
         </is>
       </c>
       <c r="B269" s="34" t="inlineStr">
         <is>
-          <t>冒充政府雇员罪</t>
+          <t>破坏证据罪</t>
         </is>
       </c>
       <c r="C269" s="34">
@@ -10904,12 +10904,12 @@
     <row r="270">
       <c r="A270" s="34" t="inlineStr">
         <is>
-          <t>假冒执法</t>
+          <t>丢掉证据</t>
         </is>
       </c>
       <c r="B270" s="34" t="inlineStr">
         <is>
-          <t>冒充政府雇员罪</t>
+          <t>破坏证据罪</t>
         </is>
       </c>
       <c r="C270" s="34">
@@ -10928,12 +10928,12 @@
     <row r="271">
       <c r="A271" s="34" t="inlineStr">
         <is>
-          <t>冒充公务员</t>
+          <t>扔掉毒品</t>
         </is>
       </c>
       <c r="B271" s="34" t="inlineStr">
         <is>
-          <t>冒充政府雇员罪</t>
+          <t>破坏证据罪</t>
         </is>
       </c>
       <c r="C271" s="34">
@@ -10952,7 +10952,7 @@
     <row r="272">
       <c r="A272" s="34" t="inlineStr">
         <is>
-          <t>假警察</t>
+          <t>冒充政府</t>
         </is>
       </c>
       <c r="B272" s="34" t="inlineStr">
@@ -10976,12 +10976,12 @@
     <row r="273">
       <c r="A273" s="34" t="inlineStr">
         <is>
-          <t>虚假逮捕</t>
+          <t>冒充警察</t>
         </is>
       </c>
       <c r="B273" s="34" t="inlineStr">
         <is>
-          <t>虚假逮捕罪</t>
+          <t>冒充政府雇员罪</t>
         </is>
       </c>
       <c r="C273" s="34">
@@ -11000,12 +11000,12 @@
     <row r="274">
       <c r="A274" s="34" t="inlineStr">
         <is>
-          <t>非法逮捕</t>
+          <t>假冒警察</t>
         </is>
       </c>
       <c r="B274" s="34" t="inlineStr">
         <is>
-          <t>虚假逮捕罪</t>
+          <t>冒充政府雇员罪</t>
         </is>
       </c>
       <c r="C274" s="34">
@@ -11024,12 +11024,12 @@
     <row r="275">
       <c r="A275" s="34" t="inlineStr">
         <is>
-          <t>非法扣押</t>
+          <t>冒充公职</t>
         </is>
       </c>
       <c r="B275" s="34" t="inlineStr">
         <is>
-          <t>虚假逮捕罪</t>
+          <t>冒充政府雇员罪</t>
         </is>
       </c>
       <c r="C275" s="34">
@@ -11048,12 +11048,12 @@
     <row r="276">
       <c r="A276" s="34" t="inlineStr">
         <is>
-          <t>无依据逮捕</t>
+          <t>假扮警察</t>
         </is>
       </c>
       <c r="B276" s="34" t="inlineStr">
         <is>
-          <t>虚假逮捕罪</t>
+          <t>冒充政府雇员罪</t>
         </is>
       </c>
       <c r="C276" s="34">
@@ -11072,12 +11072,12 @@
     <row r="277">
       <c r="A277" s="34" t="inlineStr">
         <is>
-          <t>乱抓人</t>
+          <t>假冒执法</t>
         </is>
       </c>
       <c r="B277" s="34" t="inlineStr">
         <is>
-          <t>虚假逮捕罪</t>
+          <t>冒充政府雇员罪</t>
         </is>
       </c>
       <c r="C277" s="34">
@@ -11096,12 +11096,12 @@
     <row r="278">
       <c r="A278" s="34" t="inlineStr">
         <is>
-          <t>伪证</t>
+          <t>冒充公务员</t>
         </is>
       </c>
       <c r="B278" s="34" t="inlineStr">
         <is>
-          <t>伪证罪</t>
+          <t>冒充政府雇员罪</t>
         </is>
       </c>
       <c r="C278" s="34">
@@ -11120,12 +11120,12 @@
     <row r="279">
       <c r="A279" s="34" t="inlineStr">
         <is>
-          <t>作伪证</t>
+          <t>假警察</t>
         </is>
       </c>
       <c r="B279" s="34" t="inlineStr">
         <is>
-          <t>伪证罪</t>
+          <t>冒充政府雇员罪</t>
         </is>
       </c>
       <c r="C279" s="34">
@@ -11144,12 +11144,12 @@
     <row r="280">
       <c r="A280" s="34" t="inlineStr">
         <is>
-          <t>虚假证言</t>
+          <t>虚假逮捕</t>
         </is>
       </c>
       <c r="B280" s="34" t="inlineStr">
         <is>
-          <t>伪证罪</t>
+          <t>虚假逮捕罪</t>
         </is>
       </c>
       <c r="C280" s="34">
@@ -11168,12 +11168,12 @@
     <row r="281">
       <c r="A281" s="34" t="inlineStr">
         <is>
-          <t>假证供</t>
+          <t>非法逮捕</t>
         </is>
       </c>
       <c r="B281" s="34" t="inlineStr">
         <is>
-          <t>伪证罪</t>
+          <t>虚假逮捕罪</t>
         </is>
       </c>
       <c r="C281" s="34">
@@ -11192,12 +11192,12 @@
     <row r="282">
       <c r="A282" s="34" t="inlineStr">
         <is>
-          <t>提供假证</t>
+          <t>非法扣押</t>
         </is>
       </c>
       <c r="B282" s="34" t="inlineStr">
         <is>
-          <t>伪证罪</t>
+          <t>虚假逮捕罪</t>
         </is>
       </c>
       <c r="C282" s="34">
@@ -11216,12 +11216,12 @@
     <row r="283">
       <c r="A283" s="34" t="inlineStr">
         <is>
-          <t>撒谎作证</t>
+          <t>无依据逮捕</t>
         </is>
       </c>
       <c r="B283" s="34" t="inlineStr">
         <is>
-          <t>伪证罪</t>
+          <t>虚假逮捕罪</t>
         </is>
       </c>
       <c r="C283" s="34">
@@ -11240,12 +11240,12 @@
     <row r="284">
       <c r="A284" s="34" t="inlineStr">
         <is>
-          <t>冒充律师</t>
+          <t>乱抓人</t>
         </is>
       </c>
       <c r="B284" s="34" t="inlineStr">
         <is>
-          <t>冒充律师罪</t>
+          <t>虚假逮捕罪</t>
         </is>
       </c>
       <c r="C284" s="34">
@@ -11264,12 +11264,12 @@
     <row r="285">
       <c r="A285" s="34" t="inlineStr">
         <is>
-          <t>假冒律师</t>
+          <t>伪证</t>
         </is>
       </c>
       <c r="B285" s="34" t="inlineStr">
         <is>
-          <t>冒充律师罪</t>
+          <t>伪证罪</t>
         </is>
       </c>
       <c r="C285" s="34">
@@ -11288,12 +11288,12 @@
     <row r="286">
       <c r="A286" s="34" t="inlineStr">
         <is>
-          <t>假扮律师</t>
+          <t>作伪证</t>
         </is>
       </c>
       <c r="B286" s="34" t="inlineStr">
         <is>
-          <t>冒充律师罪</t>
+          <t>伪证罪</t>
         </is>
       </c>
       <c r="C286" s="34">
@@ -11312,12 +11312,12 @@
     <row r="287">
       <c r="A287" s="34" t="inlineStr">
         <is>
-          <t>妨碍公务</t>
+          <t>虚假证言</t>
         </is>
       </c>
       <c r="B287" s="34" t="inlineStr">
         <is>
-          <t>妨碍政府雇员执行公务罪</t>
+          <t>伪证罪</t>
         </is>
       </c>
       <c r="C287" s="34">
@@ -11336,12 +11336,12 @@
     <row r="288">
       <c r="A288" s="34" t="inlineStr">
         <is>
-          <t>阻碍执法</t>
+          <t>假证供</t>
         </is>
       </c>
       <c r="B288" s="34" t="inlineStr">
         <is>
-          <t>妨碍政府雇员执行公务罪</t>
+          <t>伪证罪</t>
         </is>
       </c>
       <c r="C288" s="34">
@@ -11360,12 +11360,12 @@
     <row r="289">
       <c r="A289" s="34" t="inlineStr">
         <is>
-          <t>妨碍执法</t>
+          <t>提供假证</t>
         </is>
       </c>
       <c r="B289" s="34" t="inlineStr">
         <is>
-          <t>妨碍政府雇员执行公务罪</t>
+          <t>伪证罪</t>
         </is>
       </c>
       <c r="C289" s="34">
@@ -11384,12 +11384,12 @@
     <row r="290">
       <c r="A290" s="34" t="inlineStr">
         <is>
-          <t>阻挠执法</t>
+          <t>撒谎作证</t>
         </is>
       </c>
       <c r="B290" s="34" t="inlineStr">
         <is>
-          <t>妨碍政府雇员执行公务罪</t>
+          <t>伪证罪</t>
         </is>
       </c>
       <c r="C290" s="34">
@@ -11408,12 +11408,12 @@
     <row r="291">
       <c r="A291" s="34" t="inlineStr">
         <is>
-          <t>妨碍政府雇员</t>
+          <t>冒充律师</t>
         </is>
       </c>
       <c r="B291" s="34" t="inlineStr">
         <is>
-          <t>妨碍政府雇员执行公务罪</t>
+          <t>冒充律师罪</t>
         </is>
       </c>
       <c r="C291" s="34">
@@ -11432,12 +11432,12 @@
     <row r="292">
       <c r="A292" s="34" t="inlineStr">
         <is>
-          <t>阻碍救援</t>
+          <t>假冒律师</t>
         </is>
       </c>
       <c r="B292" s="34" t="inlineStr">
         <is>
-          <t>妨碍政府雇员执行公务罪</t>
+          <t>冒充律师罪</t>
         </is>
       </c>
       <c r="C292" s="34">
@@ -11456,12 +11456,12 @@
     <row r="293">
       <c r="A293" s="34" t="inlineStr">
         <is>
-          <t>阻碍消防</t>
+          <t>假扮律师</t>
         </is>
       </c>
       <c r="B293" s="34" t="inlineStr">
         <is>
-          <t>妨碍政府雇员执行公务罪</t>
+          <t>冒充律师罪</t>
         </is>
       </c>
       <c r="C293" s="34">
@@ -11480,7 +11480,7 @@
     <row r="294">
       <c r="A294" s="34" t="inlineStr">
         <is>
-          <t>挡着警察</t>
+          <t>妨碍公务</t>
         </is>
       </c>
       <c r="B294" s="34" t="inlineStr">
@@ -11504,7 +11504,7 @@
     <row r="295">
       <c r="A295" s="34" t="inlineStr">
         <is>
-          <t>干扰执法</t>
+          <t>阻碍执法</t>
         </is>
       </c>
       <c r="B295" s="34" t="inlineStr">
@@ -11528,7 +11528,7 @@
     <row r="296">
       <c r="A296" s="34" t="inlineStr">
         <is>
-          <t>阻拦警察</t>
+          <t>妨碍执法</t>
         </is>
       </c>
       <c r="B296" s="34" t="inlineStr">
@@ -11552,7 +11552,7 @@
     <row r="297">
       <c r="A297" s="34" t="inlineStr">
         <is>
-          <t>阻碍医护</t>
+          <t>阻挠执法</t>
         </is>
       </c>
       <c r="B297" s="34" t="inlineStr">
@@ -11576,12 +11576,12 @@
     <row r="298">
       <c r="A298" s="34" t="inlineStr">
         <is>
-          <t>拒捕</t>
+          <t>妨碍政府雇员</t>
         </is>
       </c>
       <c r="B298" s="34" t="inlineStr">
         <is>
-          <t>拒捕罪</t>
+          <t>妨碍政府雇员执行公务罪</t>
         </is>
       </c>
       <c r="C298" s="34">
@@ -11600,12 +11600,12 @@
     <row r="299">
       <c r="A299" s="34" t="inlineStr">
         <is>
-          <t>拒绝逮捕</t>
+          <t>阻碍救援</t>
         </is>
       </c>
       <c r="B299" s="34" t="inlineStr">
         <is>
-          <t>拒捕罪</t>
+          <t>妨碍政府雇员执行公务罪</t>
         </is>
       </c>
       <c r="C299" s="34">
@@ -11624,12 +11624,12 @@
     <row r="300">
       <c r="A300" s="34" t="inlineStr">
         <is>
-          <t>抗拒逮捕</t>
+          <t>阻碍消防</t>
         </is>
       </c>
       <c r="B300" s="34" t="inlineStr">
         <is>
-          <t>拒捕罪</t>
+          <t>妨碍政府雇员执行公务罪</t>
         </is>
       </c>
       <c r="C300" s="34">
@@ -11648,12 +11648,12 @@
     <row r="301">
       <c r="A301" s="34" t="inlineStr">
         <is>
-          <t>拒绝被捕</t>
+          <t>挡着警察</t>
         </is>
       </c>
       <c r="B301" s="34" t="inlineStr">
         <is>
-          <t>拒捕罪</t>
+          <t>妨碍政府雇员执行公务罪</t>
         </is>
       </c>
       <c r="C301" s="34">
@@ -11672,12 +11672,12 @@
     <row r="302">
       <c r="A302" s="34" t="inlineStr">
         <is>
-          <t>反抗逮捕</t>
+          <t>干扰执法</t>
         </is>
       </c>
       <c r="B302" s="34" t="inlineStr">
         <is>
-          <t>拒捕罪</t>
+          <t>妨碍政府雇员执行公务罪</t>
         </is>
       </c>
       <c r="C302" s="34">
@@ -11696,12 +11696,12 @@
     <row r="303">
       <c r="A303" s="34" t="inlineStr">
         <is>
-          <t>不让铐</t>
+          <t>阻拦警察</t>
         </is>
       </c>
       <c r="B303" s="34" t="inlineStr">
         <is>
-          <t>拒捕罪</t>
+          <t>妨碍政府雇员执行公务罪</t>
         </is>
       </c>
       <c r="C303" s="34">
@@ -11720,12 +11720,12 @@
     <row r="304">
       <c r="A304" s="34" t="inlineStr">
         <is>
-          <t>挣脱</t>
+          <t>阻碍医护</t>
         </is>
       </c>
       <c r="B304" s="34" t="inlineStr">
         <is>
-          <t>拒捕罪</t>
+          <t>妨碍政府雇员执行公务罪</t>
         </is>
       </c>
       <c r="C304" s="34">
@@ -11744,7 +11744,7 @@
     <row r="305">
       <c r="A305" s="34" t="inlineStr">
         <is>
-          <t>反抗抓捕</t>
+          <t>拒捕</t>
         </is>
       </c>
       <c r="B305" s="34" t="inlineStr">
@@ -11768,12 +11768,12 @@
     <row r="306">
       <c r="A306" s="34" t="inlineStr">
         <is>
-          <t>逃避羁押</t>
+          <t>拒绝逮捕</t>
         </is>
       </c>
       <c r="B306" s="34" t="inlineStr">
         <is>
-          <t>逃避羁押罪</t>
+          <t>拒捕罪</t>
         </is>
       </c>
       <c r="C306" s="34">
@@ -11792,12 +11792,12 @@
     <row r="307">
       <c r="A307" s="34" t="inlineStr">
         <is>
-          <t>逃脱</t>
+          <t>抗拒逮捕</t>
         </is>
       </c>
       <c r="B307" s="34" t="inlineStr">
         <is>
-          <t>逃避羁押罪</t>
+          <t>拒捕罪</t>
         </is>
       </c>
       <c r="C307" s="34">
@@ -11816,12 +11816,12 @@
     <row r="308">
       <c r="A308" s="34" t="inlineStr">
         <is>
-          <t>越狱</t>
+          <t>拒绝被捕</t>
         </is>
       </c>
       <c r="B308" s="34" t="inlineStr">
         <is>
-          <t>逃避羁押罪</t>
+          <t>拒捕罪</t>
         </is>
       </c>
       <c r="C308" s="34">
@@ -11840,12 +11840,12 @@
     <row r="309">
       <c r="A309" s="34" t="inlineStr">
         <is>
-          <t>逃跑</t>
+          <t>反抗逮捕</t>
         </is>
       </c>
       <c r="B309" s="34" t="inlineStr">
         <is>
-          <t>逃避羁押罪</t>
+          <t>拒捕罪</t>
         </is>
       </c>
       <c r="C309" s="34">
@@ -11864,12 +11864,12 @@
     <row r="310">
       <c r="A310" s="34" t="inlineStr">
         <is>
-          <t>脱逃</t>
+          <t>不让铐</t>
         </is>
       </c>
       <c r="B310" s="34" t="inlineStr">
         <is>
-          <t>逃避羁押罪</t>
+          <t>拒捕罪</t>
         </is>
       </c>
       <c r="C310" s="34">
@@ -11888,12 +11888,12 @@
     <row r="311">
       <c r="A311" s="34" t="inlineStr">
         <is>
-          <t>逃离监管</t>
+          <t>挣脱</t>
         </is>
       </c>
       <c r="B311" s="34" t="inlineStr">
         <is>
-          <t>逃避羁押罪</t>
+          <t>拒捕罪</t>
         </is>
       </c>
       <c r="C311" s="34">
@@ -11912,12 +11912,12 @@
     <row r="312">
       <c r="A312" s="34" t="inlineStr">
         <is>
-          <t>趁机逃走</t>
+          <t>反抗抓捕</t>
         </is>
       </c>
       <c r="B312" s="34" t="inlineStr">
         <is>
-          <t>逃避羁押罪</t>
+          <t>拒捕罪</t>
         </is>
       </c>
       <c r="C312" s="34">
@@ -11936,12 +11936,12 @@
     <row r="313">
       <c r="A313" s="34" t="inlineStr">
         <is>
-          <t>跑了</t>
+          <t>逃避逮捕</t>
         </is>
       </c>
       <c r="B313" s="34" t="inlineStr">
         <is>
-          <t>逃避羁押罪</t>
+          <t>拒捕罪</t>
         </is>
       </c>
       <c r="C313" s="34">
@@ -11960,12 +11960,12 @@
     <row r="314">
       <c r="A314" s="34" t="inlineStr">
         <is>
-          <t>驾车逃跑</t>
+          <t>逃避追捕</t>
         </is>
       </c>
       <c r="B314" s="34" t="inlineStr">
         <is>
-          <t>逃避羁押罪</t>
+          <t>拒捕罪</t>
         </is>
       </c>
       <c r="C314" s="34">
@@ -11984,12 +11984,12 @@
     <row r="315">
       <c r="A315" s="34" t="inlineStr">
         <is>
-          <t>开车逃</t>
+          <t>逃避抓捕</t>
         </is>
       </c>
       <c r="B315" s="34" t="inlineStr">
         <is>
-          <t>逃避羁押罪</t>
+          <t>拒捕罪</t>
         </is>
       </c>
       <c r="C315" s="34">
@@ -12008,12 +12008,12 @@
     <row r="316">
       <c r="A316" s="34" t="inlineStr">
         <is>
-          <t>逃窜</t>
+          <t>拒不就范</t>
         </is>
       </c>
       <c r="B316" s="34" t="inlineStr">
         <is>
-          <t>逃避羁押罪</t>
+          <t>拒捕罪</t>
         </is>
       </c>
       <c r="C316" s="34">
@@ -12032,7 +12032,7 @@
     <row r="317">
       <c r="A317" s="34" t="inlineStr">
         <is>
-          <t>逃逸</t>
+          <t>逃避羁押</t>
         </is>
       </c>
       <c r="B317" s="34" t="inlineStr">
@@ -12056,7 +12056,7 @@
     <row r="318">
       <c r="A318" s="34" t="inlineStr">
         <is>
-          <t>驾车逃逸</t>
+          <t>越狱</t>
         </is>
       </c>
       <c r="B318" s="34" t="inlineStr">
@@ -12080,7 +12080,7 @@
     <row r="319">
       <c r="A319" s="34" t="inlineStr">
         <is>
-          <t>弃车逃</t>
+          <t>脱逃</t>
         </is>
       </c>
       <c r="B319" s="34" t="inlineStr">
@@ -12104,12 +12104,12 @@
     <row r="320">
       <c r="A320" s="34" t="inlineStr">
         <is>
-          <t>藐视法庭</t>
+          <t>逃离监管</t>
         </is>
       </c>
       <c r="B320" s="34" t="inlineStr">
         <is>
-          <t>藐视法庭罪</t>
+          <t>逃避羁押罪</t>
         </is>
       </c>
       <c r="C320" s="34">
@@ -12128,12 +12128,12 @@
     <row r="321">
       <c r="A321" s="34" t="inlineStr">
         <is>
-          <t>扰乱法庭</t>
+          <t>逃脱羁押</t>
         </is>
       </c>
       <c r="B321" s="34" t="inlineStr">
         <is>
-          <t>藐视法庭罪</t>
+          <t>逃避羁押罪</t>
         </is>
       </c>
       <c r="C321" s="34">
@@ -12152,12 +12152,12 @@
     <row r="322">
       <c r="A322" s="34" t="inlineStr">
         <is>
-          <t>无视法庭命令</t>
+          <t>从拘留中逃</t>
         </is>
       </c>
       <c r="B322" s="34" t="inlineStr">
         <is>
-          <t>藐视法庭罪</t>
+          <t>逃避羁押罪</t>
         </is>
       </c>
       <c r="C322" s="34">
@@ -12176,12 +12176,12 @@
     <row r="323">
       <c r="A323" s="34" t="inlineStr">
         <is>
-          <t>不尊重法庭</t>
+          <t>从警车上逃</t>
         </is>
       </c>
       <c r="B323" s="34" t="inlineStr">
         <is>
-          <t>藐视法庭罪</t>
+          <t>逃避羁押罪</t>
         </is>
       </c>
       <c r="C323" s="34">
@@ -12200,12 +12200,12 @@
     <row r="324">
       <c r="A324" s="34" t="inlineStr">
         <is>
-          <t>在法庭上闹</t>
+          <t>逃出监管</t>
         </is>
       </c>
       <c r="B324" s="34" t="inlineStr">
         <is>
-          <t>藐视法庭罪</t>
+          <t>逃避羁押罪</t>
         </is>
       </c>
       <c r="C324" s="34">
@@ -12224,12 +12224,12 @@
     <row r="325">
       <c r="A325" s="34" t="inlineStr">
         <is>
-          <t>恶意占用公共资源</t>
+          <t>保释期间潜逃</t>
         </is>
       </c>
       <c r="B325" s="34" t="inlineStr">
         <is>
-          <t>恶意占用公共资源罪</t>
+          <t>逃避羁押罪</t>
         </is>
       </c>
       <c r="C325" s="34">
@@ -12248,12 +12248,12 @@
     <row r="326">
       <c r="A326" s="34" t="inlineStr">
         <is>
-          <t>骚扰报警电话</t>
+          <t>押解途中逃</t>
         </is>
       </c>
       <c r="B326" s="34" t="inlineStr">
         <is>
-          <t>恶意占用公共资源罪</t>
+          <t>逃避羁押罪</t>
         </is>
       </c>
       <c r="C326" s="34">
@@ -12272,12 +12272,12 @@
     <row r="327">
       <c r="A327" s="34" t="inlineStr">
         <is>
-          <t>恶意报警</t>
+          <t>藐视法庭</t>
         </is>
       </c>
       <c r="B327" s="34" t="inlineStr">
         <is>
-          <t>恶意占用公共资源罪</t>
+          <t>藐视法庭罪</t>
         </is>
       </c>
       <c r="C327" s="34">
@@ -12296,12 +12296,12 @@
     <row r="328">
       <c r="A328" s="34" t="inlineStr">
         <is>
-          <t>虚假报警</t>
+          <t>扰乱法庭</t>
         </is>
       </c>
       <c r="B328" s="34" t="inlineStr">
         <is>
-          <t>恶意占用公共资源罪</t>
+          <t>藐视法庭罪</t>
         </is>
       </c>
       <c r="C328" s="34">
@@ -12320,12 +12320,12 @@
     <row r="329">
       <c r="A329" s="34" t="inlineStr">
         <is>
-          <t>乱打报警</t>
+          <t>无视法庭命令</t>
         </is>
       </c>
       <c r="B329" s="34" t="inlineStr">
         <is>
-          <t>恶意占用公共资源罪</t>
+          <t>藐视法庭罪</t>
         </is>
       </c>
       <c r="C329" s="34">
@@ -12344,12 +12344,12 @@
     <row r="330">
       <c r="A330" s="34" t="inlineStr">
         <is>
-          <t>谎报警情</t>
+          <t>不尊重法庭</t>
         </is>
       </c>
       <c r="B330" s="34" t="inlineStr">
         <is>
-          <t>恶意占用公共资源罪</t>
+          <t>藐视法庭罪</t>
         </is>
       </c>
       <c r="C330" s="34">
@@ -12368,12 +12368,12 @@
     <row r="331">
       <c r="A331" s="34" t="inlineStr">
         <is>
-          <t>谎报</t>
+          <t>在法庭上闹</t>
         </is>
       </c>
       <c r="B331" s="34" t="inlineStr">
         <is>
-          <t>恶意占用公共资源罪</t>
+          <t>藐视法庭罪</t>
         </is>
       </c>
       <c r="C331" s="34">
@@ -12392,12 +12392,12 @@
     <row r="332">
       <c r="A332" s="34" t="inlineStr">
         <is>
-          <t>进入封闭区域</t>
+          <t>恶意占用公共资源</t>
         </is>
       </c>
       <c r="B332" s="34" t="inlineStr">
         <is>
-          <t>未经许可进入封闭紧急区域罪</t>
+          <t>恶意占用公共资源罪</t>
         </is>
       </c>
       <c r="C332" s="34">
@@ -12416,12 +12416,12 @@
     <row r="333">
       <c r="A333" s="34" t="inlineStr">
         <is>
-          <t>闯入警戒线</t>
+          <t>骚扰报警电话</t>
         </is>
       </c>
       <c r="B333" s="34" t="inlineStr">
         <is>
-          <t>未经许可进入封闭紧急区域罪</t>
+          <t>恶意占用公共资源罪</t>
         </is>
       </c>
       <c r="C333" s="34">
@@ -12440,12 +12440,12 @@
     <row r="334">
       <c r="A334" s="34" t="inlineStr">
         <is>
-          <t>擅闯封锁区</t>
+          <t>恶意报警</t>
         </is>
       </c>
       <c r="B334" s="34" t="inlineStr">
         <is>
-          <t>未经许可进入封闭紧急区域罪</t>
+          <t>恶意占用公共资源罪</t>
         </is>
       </c>
       <c r="C334" s="34">
@@ -12464,12 +12464,12 @@
     <row r="335">
       <c r="A335" s="34" t="inlineStr">
         <is>
-          <t>越过警戒线</t>
+          <t>虚假报警</t>
         </is>
       </c>
       <c r="B335" s="34" t="inlineStr">
         <is>
-          <t>未经许可进入封闭紧急区域罪</t>
+          <t>恶意占用公共资源罪</t>
         </is>
       </c>
       <c r="C335" s="34">
@@ -12488,12 +12488,12 @@
     <row r="336">
       <c r="A336" s="34" t="inlineStr">
         <is>
-          <t>闯入事故现场</t>
+          <t>乱打报警</t>
         </is>
       </c>
       <c r="B336" s="34" t="inlineStr">
         <is>
-          <t>未经许可进入封闭紧急区域罪</t>
+          <t>恶意占用公共资源罪</t>
         </is>
       </c>
       <c r="C336" s="34">
@@ -12512,12 +12512,12 @@
     <row r="337">
       <c r="A337" s="34" t="inlineStr">
         <is>
-          <t>跨过警戒带</t>
+          <t>谎报警情</t>
         </is>
       </c>
       <c r="B337" s="34" t="inlineStr">
         <is>
-          <t>未经许可进入封闭紧急区域罪</t>
+          <t>恶意占用公共资源罪</t>
         </is>
       </c>
       <c r="C337" s="34">
@@ -12536,12 +12536,12 @@
     <row r="338">
       <c r="A338" s="34" t="inlineStr">
         <is>
-          <t>袭警</t>
+          <t>谎报</t>
         </is>
       </c>
       <c r="B338" s="34" t="inlineStr">
         <is>
-          <t>袭警罪</t>
+          <t>恶意占用公共资源罪</t>
         </is>
       </c>
       <c r="C338" s="34">
@@ -12560,12 +12560,12 @@
     <row r="339">
       <c r="A339" s="34" t="inlineStr">
         <is>
-          <t>袭击警察</t>
+          <t>进入封闭区域</t>
         </is>
       </c>
       <c r="B339" s="34" t="inlineStr">
         <is>
-          <t>袭警罪</t>
+          <t>未经许可进入封闭紧急区域罪</t>
         </is>
       </c>
       <c r="C339" s="34">
@@ -12584,12 +12584,12 @@
     <row r="340">
       <c r="A340" s="34" t="inlineStr">
         <is>
-          <t>打警察</t>
+          <t>闯入警戒线</t>
         </is>
       </c>
       <c r="B340" s="34" t="inlineStr">
         <is>
-          <t>袭警罪</t>
+          <t>未经许可进入封闭紧急区域罪</t>
         </is>
       </c>
       <c r="C340" s="34">
@@ -12608,12 +12608,12 @@
     <row r="341">
       <c r="A341" s="34" t="inlineStr">
         <is>
-          <t>攻击警察</t>
+          <t>擅闯封锁区</t>
         </is>
       </c>
       <c r="B341" s="34" t="inlineStr">
         <is>
-          <t>袭警罪</t>
+          <t>未经许可进入封闭紧急区域罪</t>
         </is>
       </c>
       <c r="C341" s="34">
@@ -12632,12 +12632,12 @@
     <row r="342">
       <c r="A342" s="34" t="inlineStr">
         <is>
-          <t>伤害警察</t>
+          <t>越过警戒线</t>
         </is>
       </c>
       <c r="B342" s="34" t="inlineStr">
         <is>
-          <t>袭警罪</t>
+          <t>未经许可进入封闭紧急区域罪</t>
         </is>
       </c>
       <c r="C342" s="34">
@@ -12656,12 +12656,12 @@
     <row r="343">
       <c r="A343" s="34" t="inlineStr">
         <is>
-          <t>攻击警车</t>
+          <t>闯入事故现场</t>
         </is>
       </c>
       <c r="B343" s="34" t="inlineStr">
         <is>
-          <t>袭警罪</t>
+          <t>未经许可进入封闭紧急区域罪</t>
         </is>
       </c>
       <c r="C343" s="34">
@@ -12680,12 +12680,12 @@
     <row r="344">
       <c r="A344" s="34" t="inlineStr">
         <is>
-          <t>攻击警犬</t>
+          <t>跨过警戒带</t>
         </is>
       </c>
       <c r="B344" s="34" t="inlineStr">
         <is>
-          <t>袭警罪</t>
+          <t>未经许可进入封闭紧急区域罪</t>
         </is>
       </c>
       <c r="C344" s="34">
@@ -12704,7 +12704,7 @@
     <row r="345">
       <c r="A345" s="34" t="inlineStr">
         <is>
-          <t>殴打警察</t>
+          <t>袭警</t>
         </is>
       </c>
       <c r="B345" s="34" t="inlineStr">
@@ -12728,7 +12728,7 @@
     <row r="346">
       <c r="A346" s="34" t="inlineStr">
         <is>
-          <t>动手打警察</t>
+          <t>袭击警察</t>
         </is>
       </c>
       <c r="B346" s="34" t="inlineStr">
@@ -12752,7 +12752,7 @@
     <row r="347">
       <c r="A347" s="34" t="inlineStr">
         <is>
-          <t>撞警车</t>
+          <t>打警察</t>
         </is>
       </c>
       <c r="B347" s="34" t="inlineStr">
@@ -12776,7 +12776,7 @@
     <row r="348">
       <c r="A348" s="34" t="inlineStr">
         <is>
-          <t>枪击警察</t>
+          <t>攻击警察</t>
         </is>
       </c>
       <c r="B348" s="34" t="inlineStr">
@@ -12800,7 +12800,7 @@
     <row r="349">
       <c r="A349" s="34" t="inlineStr">
         <is>
-          <t>打了警察</t>
+          <t>伤害警察</t>
         </is>
       </c>
       <c r="B349" s="34" t="inlineStr">
@@ -12824,12 +12824,12 @@
     <row r="350">
       <c r="A350" s="34" t="inlineStr">
         <is>
-          <t>扰乱治安</t>
+          <t>攻击警车</t>
         </is>
       </c>
       <c r="B350" s="34" t="inlineStr">
         <is>
-          <t>扰乱治安罪</t>
+          <t>袭警罪</t>
         </is>
       </c>
       <c r="C350" s="34">
@@ -12848,12 +12848,12 @@
     <row r="351">
       <c r="A351" s="34" t="inlineStr">
         <is>
-          <t>挑衅</t>
+          <t>攻击警犬</t>
         </is>
       </c>
       <c r="B351" s="34" t="inlineStr">
         <is>
-          <t>扰乱治安罪</t>
+          <t>袭警罪</t>
         </is>
       </c>
       <c r="C351" s="34">
@@ -12872,12 +12872,12 @@
     <row r="352">
       <c r="A352" s="34" t="inlineStr">
         <is>
-          <t>寻衅</t>
+          <t>殴打警察</t>
         </is>
       </c>
       <c r="B352" s="34" t="inlineStr">
         <is>
-          <t>扰乱治安罪</t>
+          <t>袭警罪</t>
         </is>
       </c>
       <c r="C352" s="34">
@@ -12896,12 +12896,12 @@
     <row r="353">
       <c r="A353" s="34" t="inlineStr">
         <is>
-          <t>扰民</t>
+          <t>动手打警察</t>
         </is>
       </c>
       <c r="B353" s="34" t="inlineStr">
         <is>
-          <t>扰乱治安罪</t>
+          <t>袭警罪</t>
         </is>
       </c>
       <c r="C353" s="34">
@@ -12920,12 +12920,12 @@
     <row r="354">
       <c r="A354" s="34" t="inlineStr">
         <is>
-          <t>冒犯性语言</t>
+          <t>撞警车</t>
         </is>
       </c>
       <c r="B354" s="34" t="inlineStr">
         <is>
-          <t>扰乱治安罪</t>
+          <t>袭警罪</t>
         </is>
       </c>
       <c r="C354" s="34">
@@ -12944,12 +12944,12 @@
     <row r="355">
       <c r="A355" s="34" t="inlineStr">
         <is>
-          <t>引起恐慌</t>
+          <t>枪击警察</t>
         </is>
       </c>
       <c r="B355" s="34" t="inlineStr">
         <is>
-          <t>扰乱治安罪</t>
+          <t>袭警罪</t>
         </is>
       </c>
       <c r="C355" s="34">
@@ -12968,12 +12968,12 @@
     <row r="356">
       <c r="A356" s="34" t="inlineStr">
         <is>
-          <t>公共场所吵闹</t>
+          <t>打了警察</t>
         </is>
       </c>
       <c r="B356" s="34" t="inlineStr">
         <is>
-          <t>扰乱治安罪</t>
+          <t>袭警罪</t>
         </is>
       </c>
       <c r="C356" s="34">
@@ -12992,12 +12992,12 @@
     <row r="357">
       <c r="A357" s="34" t="inlineStr">
         <is>
-          <t>闹事</t>
+          <t>朝警察开枪</t>
         </is>
       </c>
       <c r="B357" s="34" t="inlineStr">
         <is>
-          <t>扰乱治安罪</t>
+          <t>袭警罪</t>
         </is>
       </c>
       <c r="C357" s="34">
@@ -13016,12 +13016,12 @@
     <row r="358">
       <c r="A358" s="34" t="inlineStr">
         <is>
-          <t>大吵大闹</t>
+          <t>朝警察射击</t>
         </is>
       </c>
       <c r="B358" s="34" t="inlineStr">
         <is>
-          <t>扰乱治安罪</t>
+          <t>袭警罪</t>
         </is>
       </c>
       <c r="C358" s="34">
@@ -13040,12 +13040,12 @@
     <row r="359">
       <c r="A359" s="34" t="inlineStr">
         <is>
-          <t>挑事</t>
+          <t>向警察开枪</t>
         </is>
       </c>
       <c r="B359" s="34" t="inlineStr">
         <is>
-          <t>扰乱治安罪</t>
+          <t>袭警罪</t>
         </is>
       </c>
       <c r="C359" s="34">
@@ -13064,12 +13064,12 @@
     <row r="360">
       <c r="A360" s="34" t="inlineStr">
         <is>
-          <t>起哄</t>
+          <t>向警察射击</t>
         </is>
       </c>
       <c r="B360" s="34" t="inlineStr">
         <is>
-          <t>扰乱治安罪</t>
+          <t>袭警罪</t>
         </is>
       </c>
       <c r="C360" s="34">
@@ -13088,12 +13088,12 @@
     <row r="361">
       <c r="A361" s="34" t="inlineStr">
         <is>
-          <t>非法集会</t>
+          <t>射击警察</t>
         </is>
       </c>
       <c r="B361" s="34" t="inlineStr">
         <is>
-          <t>非法集会罪</t>
+          <t>袭警罪</t>
         </is>
       </c>
       <c r="C361" s="34">
@@ -13112,12 +13112,12 @@
     <row r="362">
       <c r="A362" s="34" t="inlineStr">
         <is>
-          <t>聚众</t>
+          <t>打伤警察</t>
         </is>
       </c>
       <c r="B362" s="34" t="inlineStr">
         <is>
-          <t>非法集会罪</t>
+          <t>袭警罪</t>
         </is>
       </c>
       <c r="C362" s="34">
@@ -13136,12 +13136,12 @@
     <row r="363">
       <c r="A363" s="34" t="inlineStr">
         <is>
-          <t>聚集骚乱</t>
+          <t>击伤警察</t>
         </is>
       </c>
       <c r="B363" s="34" t="inlineStr">
         <is>
-          <t>非法集会罪</t>
+          <t>袭警罪</t>
         </is>
       </c>
       <c r="C363" s="34">
@@ -13160,12 +13160,12 @@
     <row r="364">
       <c r="A364" s="34" t="inlineStr">
         <is>
-          <t>非法聚集</t>
+          <t>警察重伤</t>
         </is>
       </c>
       <c r="B364" s="34" t="inlineStr">
         <is>
-          <t>非法集会罪</t>
+          <t>袭警罪</t>
         </is>
       </c>
       <c r="C364" s="34">
@@ -13184,12 +13184,12 @@
     <row r="365">
       <c r="A365" s="34" t="inlineStr">
         <is>
-          <t>聚众闹事</t>
+          <t>警察受伤</t>
         </is>
       </c>
       <c r="B365" s="34" t="inlineStr">
         <is>
-          <t>非法集会罪</t>
+          <t>袭警罪</t>
         </is>
       </c>
       <c r="C365" s="34">
@@ -13208,12 +13208,12 @@
     <row r="366">
       <c r="A366" s="34" t="inlineStr">
         <is>
-          <t>聚集斗殴</t>
+          <t>枪伤警察</t>
         </is>
       </c>
       <c r="B366" s="34" t="inlineStr">
         <is>
-          <t>非法集会罪</t>
+          <t>袭警罪</t>
         </is>
       </c>
       <c r="C366" s="34">
@@ -13232,12 +13232,12 @@
     <row r="367">
       <c r="A367" s="34" t="inlineStr">
         <is>
-          <t>聚众斗殴</t>
+          <t>扰乱治安</t>
         </is>
       </c>
       <c r="B367" s="34" t="inlineStr">
         <is>
-          <t>非法集会罪</t>
+          <t>扰乱治安罪</t>
         </is>
       </c>
       <c r="C367" s="34">
@@ -13256,12 +13256,12 @@
     <row r="368">
       <c r="A368" s="34" t="inlineStr">
         <is>
-          <t>煽动暴乱</t>
+          <t>挑衅</t>
         </is>
       </c>
       <c r="B368" s="34" t="inlineStr">
         <is>
-          <t>煽动暴乱罪</t>
+          <t>扰乱治安罪</t>
         </is>
       </c>
       <c r="C368" s="34">
@@ -13280,12 +13280,12 @@
     <row r="369">
       <c r="A369" s="34" t="inlineStr">
         <is>
-          <t>煽动暴力</t>
+          <t>寻衅</t>
         </is>
       </c>
       <c r="B369" s="34" t="inlineStr">
         <is>
-          <t>煽动暴乱罪</t>
+          <t>扰乱治安罪</t>
         </is>
       </c>
       <c r="C369" s="34">
@@ -13304,12 +13304,12 @@
     <row r="370">
       <c r="A370" s="34" t="inlineStr">
         <is>
-          <t>鼓动暴乱</t>
+          <t>扰民</t>
         </is>
       </c>
       <c r="B370" s="34" t="inlineStr">
         <is>
-          <t>煽动暴乱罪</t>
+          <t>扰乱治安罪</t>
         </is>
       </c>
       <c r="C370" s="34">
@@ -13328,12 +13328,12 @@
     <row r="371">
       <c r="A371" s="34" t="inlineStr">
         <is>
-          <t>鼓动暴力</t>
+          <t>冒犯性语言</t>
         </is>
       </c>
       <c r="B371" s="34" t="inlineStr">
         <is>
-          <t>煽动暴乱罪</t>
+          <t>扰乱治安罪</t>
         </is>
       </c>
       <c r="C371" s="34">
@@ -13352,12 +13352,12 @@
     <row r="372">
       <c r="A372" s="34" t="inlineStr">
         <is>
-          <t>带头闹事</t>
+          <t>引起恐慌</t>
         </is>
       </c>
       <c r="B372" s="34" t="inlineStr">
         <is>
-          <t>煽动暴乱罪</t>
+          <t>扰乱治安罪</t>
         </is>
       </c>
       <c r="C372" s="34">
@@ -13376,12 +13376,12 @@
     <row r="373">
       <c r="A373" s="34" t="inlineStr">
         <is>
-          <t>煽动</t>
+          <t>公共场所吵闹</t>
         </is>
       </c>
       <c r="B373" s="34" t="inlineStr">
         <is>
-          <t>煽动暴乱罪</t>
+          <t>扰乱治安罪</t>
         </is>
       </c>
       <c r="C373" s="34">
@@ -13400,12 +13400,12 @@
     <row r="374">
       <c r="A374" s="34" t="inlineStr">
         <is>
-          <t>遮挡面部</t>
+          <t>闹事</t>
         </is>
       </c>
       <c r="B374" s="34" t="inlineStr">
         <is>
-          <t>遮挡面部罪</t>
+          <t>扰乱治安罪</t>
         </is>
       </c>
       <c r="C374" s="34">
@@ -13424,12 +13424,12 @@
     <row r="375">
       <c r="A375" s="34" t="inlineStr">
         <is>
-          <t>蒙面</t>
+          <t>大吵大闹</t>
         </is>
       </c>
       <c r="B375" s="34" t="inlineStr">
         <is>
-          <t>遮挡面部罪</t>
+          <t>扰乱治安罪</t>
         </is>
       </c>
       <c r="C375" s="34">
@@ -13448,12 +13448,12 @@
     <row r="376">
       <c r="A376" s="34" t="inlineStr">
         <is>
-          <t>戴面具</t>
+          <t>挑事</t>
         </is>
       </c>
       <c r="B376" s="34" t="inlineStr">
         <is>
-          <t>遮挡面部罪</t>
+          <t>扰乱治安罪</t>
         </is>
       </c>
       <c r="C376" s="34">
@@ -13472,12 +13472,12 @@
     <row r="377">
       <c r="A377" s="34" t="inlineStr">
         <is>
-          <t>兜帽遮脸</t>
+          <t>起哄</t>
         </is>
       </c>
       <c r="B377" s="34" t="inlineStr">
         <is>
-          <t>遮挡面部罪</t>
+          <t>扰乱治安罪</t>
         </is>
       </c>
       <c r="C377" s="34">
@@ -13496,12 +13496,12 @@
     <row r="378">
       <c r="A378" s="34" t="inlineStr">
         <is>
-          <t>拒绝揭开面罩</t>
+          <t>非法集会</t>
         </is>
       </c>
       <c r="B378" s="34" t="inlineStr">
         <is>
-          <t>遮挡面部罪</t>
+          <t>非法集会罪</t>
         </is>
       </c>
       <c r="C378" s="34">
@@ -13520,12 +13520,12 @@
     <row r="379">
       <c r="A379" s="34" t="inlineStr">
         <is>
-          <t>蒙着脸</t>
+          <t>聚众</t>
         </is>
       </c>
       <c r="B379" s="34" t="inlineStr">
         <is>
-          <t>遮挡面部罪</t>
+          <t>非法集会罪</t>
         </is>
       </c>
       <c r="C379" s="34">
@@ -13544,12 +13544,12 @@
     <row r="380">
       <c r="A380" s="34" t="inlineStr">
         <is>
-          <t>戴头套</t>
+          <t>聚集骚乱</t>
         </is>
       </c>
       <c r="B380" s="34" t="inlineStr">
         <is>
-          <t>遮挡面部罪</t>
+          <t>非法集会罪</t>
         </is>
       </c>
       <c r="C380" s="34">
@@ -13568,12 +13568,12 @@
     <row r="381">
       <c r="A381" s="34" t="inlineStr">
         <is>
-          <t>非法持有热武器</t>
+          <t>非法聚集</t>
         </is>
       </c>
       <c r="B381" s="34" t="inlineStr">
         <is>
-          <t>非法持有热武器罪</t>
+          <t>非法集会罪</t>
         </is>
       </c>
       <c r="C381" s="34">
@@ -13592,12 +13592,12 @@
     <row r="382">
       <c r="A382" s="34" t="inlineStr">
         <is>
-          <t>无证持枪</t>
+          <t>聚众闹事</t>
         </is>
       </c>
       <c r="B382" s="34" t="inlineStr">
         <is>
-          <t>非法持有热武器罪</t>
+          <t>非法集会罪</t>
         </is>
       </c>
       <c r="C382" s="34">
@@ -13616,12 +13616,12 @@
     <row r="383">
       <c r="A383" s="34" t="inlineStr">
         <is>
-          <t>非法持枪</t>
+          <t>聚集斗殴</t>
         </is>
       </c>
       <c r="B383" s="34" t="inlineStr">
         <is>
-          <t>非法持有热武器罪</t>
+          <t>非法集会罪</t>
         </is>
       </c>
       <c r="C383" s="34">
@@ -13640,12 +13640,12 @@
     <row r="384">
       <c r="A384" s="34" t="inlineStr">
         <is>
-          <t>持有非法武器</t>
+          <t>聚众斗殴</t>
         </is>
       </c>
       <c r="B384" s="34" t="inlineStr">
         <is>
-          <t>非法持有热武器罪</t>
+          <t>非法集会罪</t>
         </is>
       </c>
       <c r="C384" s="34">
@@ -13664,12 +13664,12 @@
     <row r="385">
       <c r="A385" s="34" t="inlineStr">
         <is>
-          <t>无序列号枪支</t>
+          <t>煽动暴乱</t>
         </is>
       </c>
       <c r="B385" s="34" t="inlineStr">
         <is>
-          <t>非法持有热武器罪</t>
+          <t>煽动暴乱罪</t>
         </is>
       </c>
       <c r="C385" s="34">
@@ -13688,12 +13688,12 @@
     <row r="386">
       <c r="A386" s="34" t="inlineStr">
         <is>
-          <t>全自动枪支</t>
+          <t>煽动暴力</t>
         </is>
       </c>
       <c r="B386" s="34" t="inlineStr">
         <is>
-          <t>非法持有热武器罪</t>
+          <t>煽动暴乱罪</t>
         </is>
       </c>
       <c r="C386" s="34">
@@ -13712,12 +13712,12 @@
     <row r="387">
       <c r="A387" s="34" t="inlineStr">
         <is>
-          <t>私藏枪支</t>
+          <t>鼓动暴乱</t>
         </is>
       </c>
       <c r="B387" s="34" t="inlineStr">
         <is>
-          <t>非法持有热武器罪</t>
+          <t>煽动暴乱罪</t>
         </is>
       </c>
       <c r="C387" s="34">
@@ -13736,12 +13736,12 @@
     <row r="388">
       <c r="A388" s="34" t="inlineStr">
         <is>
-          <t>持有爆炸物</t>
+          <t>鼓动暴力</t>
         </is>
       </c>
       <c r="B388" s="34" t="inlineStr">
         <is>
-          <t>非法持有热武器罪</t>
+          <t>煽动暴乱罪</t>
         </is>
       </c>
       <c r="C388" s="34">
@@ -13760,12 +13760,12 @@
     <row r="389">
       <c r="A389" s="34" t="inlineStr">
         <is>
-          <t>身上有枪</t>
+          <t>带头闹事</t>
         </is>
       </c>
       <c r="B389" s="34" t="inlineStr">
         <is>
-          <t>非法持有热武器罪</t>
+          <t>煽动暴乱罪</t>
         </is>
       </c>
       <c r="C389" s="34">
@@ -13784,12 +13784,12 @@
     <row r="390">
       <c r="A390" s="34" t="inlineStr">
         <is>
-          <t>携带枪支</t>
+          <t>煽动</t>
         </is>
       </c>
       <c r="B390" s="34" t="inlineStr">
         <is>
-          <t>非法持有热武器罪</t>
+          <t>煽动暴乱罪</t>
         </is>
       </c>
       <c r="C390" s="34">
@@ -13808,12 +13808,12 @@
     <row r="391">
       <c r="A391" s="34" t="inlineStr">
         <is>
-          <t>藏枪</t>
+          <t>遮挡面部</t>
         </is>
       </c>
       <c r="B391" s="34" t="inlineStr">
         <is>
-          <t>非法持有热武器罪</t>
+          <t>遮挡面部罪</t>
         </is>
       </c>
       <c r="C391" s="34">
@@ -13832,12 +13832,12 @@
     <row r="392">
       <c r="A392" s="34" t="inlineStr">
         <is>
-          <t>非法展示热武器</t>
+          <t>蒙面</t>
         </is>
       </c>
       <c r="B392" s="34" t="inlineStr">
         <is>
-          <t>非法展示热武器罪</t>
+          <t>遮挡面部罪</t>
         </is>
       </c>
       <c r="C392" s="34">
@@ -13856,12 +13856,12 @@
     <row r="393">
       <c r="A393" s="34" t="inlineStr">
         <is>
-          <t>公开持枪</t>
+          <t>戴面具</t>
         </is>
       </c>
       <c r="B393" s="34" t="inlineStr">
         <is>
-          <t>非法展示热武器罪</t>
+          <t>遮挡面部罪</t>
         </is>
       </c>
       <c r="C393" s="34">
@@ -13880,12 +13880,12 @@
     <row r="394">
       <c r="A394" s="34" t="inlineStr">
         <is>
-          <t>挥舞武器</t>
+          <t>兜帽遮脸</t>
         </is>
       </c>
       <c r="B394" s="34" t="inlineStr">
         <is>
-          <t>非法展示热武器罪</t>
+          <t>遮挡面部罪</t>
         </is>
       </c>
       <c r="C394" s="34">
@@ -13904,12 +13904,12 @@
     <row r="395">
       <c r="A395" s="34" t="inlineStr">
         <is>
-          <t>亮枪</t>
+          <t>拒绝揭开面罩</t>
         </is>
       </c>
       <c r="B395" s="34" t="inlineStr">
         <is>
-          <t>非法展示热武器罪</t>
+          <t>遮挡面部罪</t>
         </is>
       </c>
       <c r="C395" s="34">
@@ -13928,12 +13928,12 @@
     <row r="396">
       <c r="A396" s="34" t="inlineStr">
         <is>
-          <t>展示武器</t>
+          <t>蒙着脸</t>
         </is>
       </c>
       <c r="B396" s="34" t="inlineStr">
         <is>
-          <t>非法展示热武器罪</t>
+          <t>遮挡面部罪</t>
         </is>
       </c>
       <c r="C396" s="34">
@@ -13952,12 +13952,12 @@
     <row r="397">
       <c r="A397" s="34" t="inlineStr">
         <is>
-          <t>公开携带枪支</t>
+          <t>戴头套</t>
         </is>
       </c>
       <c r="B397" s="34" t="inlineStr">
         <is>
-          <t>非法展示热武器罪</t>
+          <t>遮挡面部罪</t>
         </is>
       </c>
       <c r="C397" s="34">
@@ -13976,12 +13976,12 @@
     <row r="398">
       <c r="A398" s="34" t="inlineStr">
         <is>
-          <t>掏枪威胁</t>
+          <t>非法持有热武器</t>
         </is>
       </c>
       <c r="B398" s="34" t="inlineStr">
         <is>
-          <t>非法展示热武器罪</t>
+          <t>非法持有热武器罪</t>
         </is>
       </c>
       <c r="C398" s="34">
@@ -14000,12 +14000,12 @@
     <row r="399">
       <c r="A399" s="34" t="inlineStr">
         <is>
-          <t>拔枪</t>
+          <t>无证持枪</t>
         </is>
       </c>
       <c r="B399" s="34" t="inlineStr">
         <is>
-          <t>非法展示热武器罪</t>
+          <t>非法持有热武器罪</t>
         </is>
       </c>
       <c r="C399" s="34">
@@ -14024,12 +14024,12 @@
     <row r="400">
       <c r="A400" s="34" t="inlineStr">
         <is>
-          <t>亮出枪</t>
+          <t>非法持枪</t>
         </is>
       </c>
       <c r="B400" s="34" t="inlineStr">
         <is>
-          <t>非法展示热武器罪</t>
+          <t>非法持有热武器罪</t>
         </is>
       </c>
       <c r="C400" s="34">
@@ -14048,12 +14048,12 @@
     <row r="401">
       <c r="A401" s="34" t="inlineStr">
         <is>
-          <t>举枪</t>
+          <t>持有非法武器</t>
         </is>
       </c>
       <c r="B401" s="34" t="inlineStr">
         <is>
-          <t>非法展示热武器罪</t>
+          <t>非法持有热武器罪</t>
         </is>
       </c>
       <c r="C401" s="34">
@@ -14072,12 +14072,12 @@
     <row r="402">
       <c r="A402" s="34" t="inlineStr">
         <is>
-          <t>非法使用热武器</t>
+          <t>无序列号枪支</t>
         </is>
       </c>
       <c r="B402" s="34" t="inlineStr">
         <is>
-          <t>非法使用热武器罪</t>
+          <t>非法持有热武器罪</t>
         </is>
       </c>
       <c r="C402" s="34">
@@ -14096,12 +14096,12 @@
     <row r="403">
       <c r="A403" s="34" t="inlineStr">
         <is>
-          <t>鲁莽开枪</t>
+          <t>全自动枪支</t>
         </is>
       </c>
       <c r="B403" s="34" t="inlineStr">
         <is>
-          <t>非法使用热武器罪</t>
+          <t>非法持有热武器罪</t>
         </is>
       </c>
       <c r="C403" s="34">
@@ -14120,12 +14120,12 @@
     <row r="404">
       <c r="A404" s="34" t="inlineStr">
         <is>
-          <t>乱开枪</t>
+          <t>私藏枪支</t>
         </is>
       </c>
       <c r="B404" s="34" t="inlineStr">
         <is>
-          <t>非法使用热武器罪</t>
+          <t>非法持有热武器罪</t>
         </is>
       </c>
       <c r="C404" s="34">
@@ -14144,12 +14144,12 @@
     <row r="405">
       <c r="A405" s="34" t="inlineStr">
         <is>
-          <t>违规射击</t>
+          <t>持有爆炸物</t>
         </is>
       </c>
       <c r="B405" s="34" t="inlineStr">
         <is>
-          <t>非法使用热武器罪</t>
+          <t>非法持有热武器罪</t>
         </is>
       </c>
       <c r="C405" s="34">
@@ -14168,12 +14168,12 @@
     <row r="406">
       <c r="A406" s="34" t="inlineStr">
         <is>
-          <t>开枪</t>
+          <t>身上有枪</t>
         </is>
       </c>
       <c r="B406" s="34" t="inlineStr">
         <is>
-          <t>非法使用热武器罪</t>
+          <t>非法持有热武器罪</t>
         </is>
       </c>
       <c r="C406" s="34">
@@ -14192,12 +14192,12 @@
     <row r="407">
       <c r="A407" s="34" t="inlineStr">
         <is>
-          <t>朝天开枪</t>
+          <t>携带枪支</t>
         </is>
       </c>
       <c r="B407" s="34" t="inlineStr">
         <is>
-          <t>非法使用热武器罪</t>
+          <t>非法持有热武器罪</t>
         </is>
       </c>
       <c r="C407" s="34">
@@ -14216,12 +14216,12 @@
     <row r="408">
       <c r="A408" s="34" t="inlineStr">
         <is>
-          <t>随意射击</t>
+          <t>藏枪</t>
         </is>
       </c>
       <c r="B408" s="34" t="inlineStr">
         <is>
-          <t>非法使用热武器罪</t>
+          <t>非法持有热武器罪</t>
         </is>
       </c>
       <c r="C408" s="34">
@@ -14240,12 +14240,12 @@
     <row r="409">
       <c r="A409" s="34" t="inlineStr">
         <is>
-          <t>开了一枪</t>
+          <t>非法展示热武器</t>
         </is>
       </c>
       <c r="B409" s="34" t="inlineStr">
         <is>
-          <t>非法使用热武器罪</t>
+          <t>非法展示热武器罪</t>
         </is>
       </c>
       <c r="C409" s="34">
@@ -14264,12 +14264,12 @@
     <row r="410">
       <c r="A410" s="34" t="inlineStr">
         <is>
-          <t>射击</t>
+          <t>公开持枪</t>
         </is>
       </c>
       <c r="B410" s="34" t="inlineStr">
         <is>
-          <t>非法使用热武器罪</t>
+          <t>非法展示热武器罪</t>
         </is>
       </c>
       <c r="C410" s="34">
@@ -14288,12 +14288,12 @@
     <row r="411">
       <c r="A411" s="34" t="inlineStr">
         <is>
-          <t>扫射</t>
+          <t>挥舞武器</t>
         </is>
       </c>
       <c r="B411" s="34" t="inlineStr">
         <is>
-          <t>非法使用热武器罪</t>
+          <t>非法展示热武器罪</t>
         </is>
       </c>
       <c r="C411" s="34">
@@ -14312,12 +14312,12 @@
     <row r="412">
       <c r="A412" s="34" t="inlineStr">
         <is>
-          <t>鸣枪</t>
+          <t>亮枪</t>
         </is>
       </c>
       <c r="B412" s="34" t="inlineStr">
         <is>
-          <t>非法使用热武器罪</t>
+          <t>非法展示热武器罪</t>
         </is>
       </c>
       <c r="C412" s="34">
@@ -14336,12 +14336,12 @@
     <row r="413">
       <c r="A413" s="34" t="inlineStr">
         <is>
-          <t>对空鸣枪</t>
+          <t>展示武器</t>
         </is>
       </c>
       <c r="B413" s="34" t="inlineStr">
         <is>
-          <t>非法使用热武器罪</t>
+          <t>非法展示热武器罪</t>
         </is>
       </c>
       <c r="C413" s="34">
@@ -14360,12 +14360,12 @@
     <row r="414">
       <c r="A414" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖武器</t>
+          <t>公开携带枪支</t>
         </is>
       </c>
       <c r="B414" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖武器罪</t>
+          <t>非法展示热武器罪</t>
         </is>
       </c>
       <c r="C414" s="34">
@@ -14384,12 +14384,12 @@
     <row r="415">
       <c r="A415" s="34" t="inlineStr">
         <is>
-          <t>卖枪</t>
+          <t>掏枪威胁</t>
         </is>
       </c>
       <c r="B415" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖武器罪</t>
+          <t>非法展示热武器罪</t>
         </is>
       </c>
       <c r="C415" s="34">
@@ -14408,12 +14408,12 @@
     <row r="416">
       <c r="A416" s="34" t="inlineStr">
         <is>
-          <t>贩卖武器</t>
+          <t>拔枪</t>
         </is>
       </c>
       <c r="B416" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖武器罪</t>
+          <t>非法展示热武器罪</t>
         </is>
       </c>
       <c r="C416" s="34">
@@ -14432,12 +14432,12 @@
     <row r="417">
       <c r="A417" s="34" t="inlineStr">
         <is>
-          <t>出售武器</t>
+          <t>亮出枪</t>
         </is>
       </c>
       <c r="B417" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖武器罪</t>
+          <t>非法展示热武器罪</t>
         </is>
       </c>
       <c r="C417" s="34">
@@ -14456,12 +14456,12 @@
     <row r="418">
       <c r="A418" s="34" t="inlineStr">
         <is>
-          <t>转让武器</t>
+          <t>举枪</t>
         </is>
       </c>
       <c r="B418" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖武器罪</t>
+          <t>非法展示热武器罪</t>
         </is>
       </c>
       <c r="C418" s="34">
@@ -14480,12 +14480,12 @@
     <row r="419">
       <c r="A419" s="34" t="inlineStr">
         <is>
-          <t>倒卖枪支</t>
+          <t>非法使用热武器</t>
         </is>
       </c>
       <c r="B419" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖武器罪</t>
+          <t>非法使用热武器罪</t>
         </is>
       </c>
       <c r="C419" s="34">
@@ -14504,12 +14504,12 @@
     <row r="420">
       <c r="A420" s="34" t="inlineStr">
         <is>
-          <t>军火买卖</t>
+          <t>鲁莽开枪</t>
         </is>
       </c>
       <c r="B420" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖武器罪</t>
+          <t>非法使用热武器罪</t>
         </is>
       </c>
       <c r="C420" s="34">
@@ -14528,12 +14528,12 @@
     <row r="421">
       <c r="A421" s="34" t="inlineStr">
         <is>
-          <t>走私</t>
+          <t>乱开枪</t>
         </is>
       </c>
       <c r="B421" s="34" t="inlineStr">
         <is>
-          <t>走私罪</t>
+          <t>非法使用热武器罪</t>
         </is>
       </c>
       <c r="C421" s="34">
@@ -14552,12 +14552,12 @@
     <row r="422">
       <c r="A422" s="34" t="inlineStr">
         <is>
-          <t>军火走私</t>
+          <t>违规射击</t>
         </is>
       </c>
       <c r="B422" s="34" t="inlineStr">
         <is>
-          <t>走私罪</t>
+          <t>非法使用热武器罪</t>
         </is>
       </c>
       <c r="C422" s="34">
@@ -14576,12 +14576,12 @@
     <row r="423">
       <c r="A423" s="34" t="inlineStr">
         <is>
-          <t>走私武器</t>
+          <t>开枪</t>
         </is>
       </c>
       <c r="B423" s="34" t="inlineStr">
         <is>
-          <t>走私罪</t>
+          <t>非法使用热武器罪</t>
         </is>
       </c>
       <c r="C423" s="34">
@@ -14600,12 +14600,12 @@
     <row r="424">
       <c r="A424" s="34" t="inlineStr">
         <is>
-          <t>走私爆炸物</t>
+          <t>朝天开枪</t>
         </is>
       </c>
       <c r="B424" s="34" t="inlineStr">
         <is>
-          <t>走私罪</t>
+          <t>非法使用热武器罪</t>
         </is>
       </c>
       <c r="C424" s="34">
@@ -14624,12 +14624,12 @@
     <row r="425">
       <c r="A425" s="34" t="inlineStr">
         <is>
-          <t>走私军火</t>
+          <t>随意射击</t>
         </is>
       </c>
       <c r="B425" s="34" t="inlineStr">
         <is>
-          <t>走私罪</t>
+          <t>非法使用热武器罪</t>
         </is>
       </c>
       <c r="C425" s="34">
@@ -14648,12 +14648,12 @@
     <row r="426">
       <c r="A426" s="34" t="inlineStr">
         <is>
-          <t>偷运军火</t>
+          <t>开了一枪</t>
         </is>
       </c>
       <c r="B426" s="34" t="inlineStr">
         <is>
-          <t>走私罪</t>
+          <t>非法使用热武器罪</t>
         </is>
       </c>
       <c r="C426" s="34">
@@ -14672,12 +14672,12 @@
     <row r="427">
       <c r="A427" s="34" t="inlineStr">
         <is>
-          <t>非法持有管制物品</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="B427" s="34" t="inlineStr">
         <is>
-          <t>非法持有管制物品罪</t>
+          <t>非法使用热武器罪</t>
         </is>
       </c>
       <c r="C427" s="34">
@@ -14696,12 +14696,12 @@
     <row r="428">
       <c r="A428" s="34" t="inlineStr">
         <is>
-          <t>持有毒品</t>
+          <t>扫射</t>
         </is>
       </c>
       <c r="B428" s="34" t="inlineStr">
         <is>
-          <t>非法持有管制物品罪</t>
+          <t>非法使用热武器罪</t>
         </is>
       </c>
       <c r="C428" s="34">
@@ -14720,12 +14720,12 @@
     <row r="429">
       <c r="A429" s="34" t="inlineStr">
         <is>
-          <t>持有大麻</t>
+          <t>鸣枪</t>
         </is>
       </c>
       <c r="B429" s="34" t="inlineStr">
         <is>
-          <t>非法持有管制物品罪</t>
+          <t>非法使用热武器罪</t>
         </is>
       </c>
       <c r="C429" s="34">
@@ -14744,12 +14744,12 @@
     <row r="430">
       <c r="A430" s="34" t="inlineStr">
         <is>
-          <t>持有可卡因</t>
+          <t>对空鸣枪</t>
         </is>
       </c>
       <c r="B430" s="34" t="inlineStr">
         <is>
-          <t>非法持有管制物品罪</t>
+          <t>非法使用热武器罪</t>
         </is>
       </c>
       <c r="C430" s="34">
@@ -14768,12 +14768,12 @@
     <row r="431">
       <c r="A431" s="34" t="inlineStr">
         <is>
-          <t>持有海洛因</t>
+          <t>非法贩卖武器</t>
         </is>
       </c>
       <c r="B431" s="34" t="inlineStr">
         <is>
-          <t>非法持有管制物品罪</t>
+          <t>非法贩卖武器罪</t>
         </is>
       </c>
       <c r="C431" s="34">
@@ -14792,12 +14792,12 @@
     <row r="432">
       <c r="A432" s="34" t="inlineStr">
         <is>
-          <t>持有冰毒</t>
+          <t>卖枪</t>
         </is>
       </c>
       <c r="B432" s="34" t="inlineStr">
         <is>
-          <t>非法持有管制物品罪</t>
+          <t>非法贩卖武器罪</t>
         </is>
       </c>
       <c r="C432" s="34">
@@ -14816,12 +14816,12 @@
     <row r="433">
       <c r="A433" s="34" t="inlineStr">
         <is>
-          <t>持有管制刀具</t>
+          <t>贩卖武器</t>
         </is>
       </c>
       <c r="B433" s="34" t="inlineStr">
         <is>
-          <t>非法持有管制物品罪</t>
+          <t>非法贩卖武器罪</t>
         </is>
       </c>
       <c r="C433" s="34">
@@ -14840,12 +14840,12 @@
     <row r="434">
       <c r="A434" s="34" t="inlineStr">
         <is>
-          <t>管制器具</t>
+          <t>出售武器</t>
         </is>
       </c>
       <c r="B434" s="34" t="inlineStr">
         <is>
-          <t>非法持有管制物品罪</t>
+          <t>非法贩卖武器罪</t>
         </is>
       </c>
       <c r="C434" s="34">
@@ -14864,12 +14864,12 @@
     <row r="435">
       <c r="A435" s="34" t="inlineStr">
         <is>
-          <t>指虎</t>
+          <t>转让武器</t>
         </is>
       </c>
       <c r="B435" s="34" t="inlineStr">
         <is>
-          <t>非法持有管制物品罪</t>
+          <t>非法贩卖武器罪</t>
         </is>
       </c>
       <c r="C435" s="34">
@@ -14888,12 +14888,12 @@
     <row r="436">
       <c r="A436" s="34" t="inlineStr">
         <is>
-          <t>弹簧刀</t>
+          <t>倒卖枪支</t>
         </is>
       </c>
       <c r="B436" s="34" t="inlineStr">
         <is>
-          <t>非法持有管制物品罪</t>
+          <t>非法贩卖武器罪</t>
         </is>
       </c>
       <c r="C436" s="34">
@@ -14912,12 +14912,12 @@
     <row r="437">
       <c r="A437" s="34" t="inlineStr">
         <is>
-          <t>开锁器</t>
+          <t>军火买卖</t>
         </is>
       </c>
       <c r="B437" s="34" t="inlineStr">
         <is>
-          <t>非法持有管制物品罪</t>
+          <t>非法贩卖武器罪</t>
         </is>
       </c>
       <c r="C437" s="34">
@@ -14936,12 +14936,12 @@
     <row r="438">
       <c r="A438" s="34" t="inlineStr">
         <is>
-          <t>黑客电脑</t>
+          <t>走私</t>
         </is>
       </c>
       <c r="B438" s="34" t="inlineStr">
         <is>
-          <t>非法持有管制物品罪</t>
+          <t>走私罪</t>
         </is>
       </c>
       <c r="C438" s="34">
@@ -14960,12 +14960,12 @@
     <row r="439">
       <c r="A439" s="34" t="inlineStr">
         <is>
-          <t>身上有毒品</t>
+          <t>军火走私</t>
         </is>
       </c>
       <c r="B439" s="34" t="inlineStr">
         <is>
-          <t>非法持有管制物品罪</t>
+          <t>走私罪</t>
         </is>
       </c>
       <c r="C439" s="34">
@@ -14984,12 +14984,12 @@
     <row r="440">
       <c r="A440" s="34" t="inlineStr">
         <is>
-          <t>带着毒品</t>
+          <t>走私武器</t>
         </is>
       </c>
       <c r="B440" s="34" t="inlineStr">
         <is>
-          <t>非法持有管制物品罪</t>
+          <t>走私罪</t>
         </is>
       </c>
       <c r="C440" s="34">
@@ -15008,12 +15008,12 @@
     <row r="441">
       <c r="A441" s="34" t="inlineStr">
         <is>
-          <t>藏毒</t>
+          <t>走私爆炸物</t>
         </is>
       </c>
       <c r="B441" s="34" t="inlineStr">
         <is>
-          <t>非法持有管制物品罪</t>
+          <t>走私罪</t>
         </is>
       </c>
       <c r="C441" s="34">
@@ -15032,12 +15032,12 @@
     <row r="442">
       <c r="A442" s="34" t="inlineStr">
         <is>
-          <t>大量管制物品</t>
+          <t>走私军火</t>
         </is>
       </c>
       <c r="B442" s="34" t="inlineStr">
         <is>
-          <t>非法持有大量管制物品罪</t>
+          <t>走私罪</t>
         </is>
       </c>
       <c r="C442" s="34">
@@ -15056,12 +15056,12 @@
     <row r="443">
       <c r="A443" s="34" t="inlineStr">
         <is>
-          <t>大量毒品</t>
+          <t>偷运军火</t>
         </is>
       </c>
       <c r="B443" s="34" t="inlineStr">
         <is>
-          <t>非法持有大量管制物品罪</t>
+          <t>走私罪</t>
         </is>
       </c>
       <c r="C443" s="34">
@@ -15080,12 +15080,12 @@
     <row r="444">
       <c r="A444" s="34" t="inlineStr">
         <is>
-          <t>分装毒品</t>
+          <t>非法持有管制物品</t>
         </is>
       </c>
       <c r="B444" s="34" t="inlineStr">
         <is>
-          <t>非法持有大量管制物品罪</t>
+          <t>非法持有管制物品罪</t>
         </is>
       </c>
       <c r="C444" s="34">
@@ -15104,12 +15104,12 @@
     <row r="445">
       <c r="A445" s="34" t="inlineStr">
         <is>
-          <t>成批毒品</t>
+          <t>持有毒品</t>
         </is>
       </c>
       <c r="B445" s="34" t="inlineStr">
         <is>
-          <t>非法持有大量管制物品罪</t>
+          <t>非法持有管制物品罪</t>
         </is>
       </c>
       <c r="C445" s="34">
@@ -15128,12 +15128,12 @@
     <row r="446">
       <c r="A446" s="34" t="inlineStr">
         <is>
-          <t>整箱毒品</t>
+          <t>持有大麻</t>
         </is>
       </c>
       <c r="B446" s="34" t="inlineStr">
         <is>
-          <t>非法持有大量管制物品罪</t>
+          <t>非法持有管制物品罪</t>
         </is>
       </c>
       <c r="C446" s="34">
@@ -15152,12 +15152,12 @@
     <row r="447">
       <c r="A447" s="34" t="inlineStr">
         <is>
-          <t>一堆毒品</t>
+          <t>持有可卡因</t>
         </is>
       </c>
       <c r="B447" s="34" t="inlineStr">
         <is>
-          <t>非法持有大量管制物品罪</t>
+          <t>非法持有管制物品罪</t>
         </is>
       </c>
       <c r="C447" s="34">
@@ -15176,12 +15176,12 @@
     <row r="448">
       <c r="A448" s="34" t="inlineStr">
         <is>
-          <t>大批毒品</t>
+          <t>持有海洛因</t>
         </is>
       </c>
       <c r="B448" s="34" t="inlineStr">
         <is>
-          <t>非法持有大量管制物品罪</t>
+          <t>非法持有管制物品罪</t>
         </is>
       </c>
       <c r="C448" s="34">
@@ -15200,12 +15200,12 @@
     <row r="449">
       <c r="A449" s="34" t="inlineStr">
         <is>
-          <t>经营管制物品</t>
+          <t>持有冰毒</t>
         </is>
       </c>
       <c r="B449" s="34" t="inlineStr">
         <is>
-          <t>非法经营和分发管制物品罪</t>
+          <t>非法持有管制物品罪</t>
         </is>
       </c>
       <c r="C449" s="34">
@@ -15224,12 +15224,12 @@
     <row r="450">
       <c r="A450" s="34" t="inlineStr">
         <is>
-          <t>分发毒品</t>
+          <t>持有管制刀具</t>
         </is>
       </c>
       <c r="B450" s="34" t="inlineStr">
         <is>
-          <t>非法经营和分发管制物品罪</t>
+          <t>非法持有管制物品罪</t>
         </is>
       </c>
       <c r="C450" s="34">
@@ -15248,12 +15248,12 @@
     <row r="451">
       <c r="A451" s="34" t="inlineStr">
         <is>
-          <t>贩毒据点</t>
+          <t>管制器具</t>
         </is>
       </c>
       <c r="B451" s="34" t="inlineStr">
         <is>
-          <t>非法经营和分发管制物品罪</t>
+          <t>非法持有管制物品罪</t>
         </is>
       </c>
       <c r="C451" s="34">
@@ -15272,12 +15272,12 @@
     <row r="452">
       <c r="A452" s="34" t="inlineStr">
         <is>
-          <t>毒品窝点</t>
+          <t>指虎</t>
         </is>
       </c>
       <c r="B452" s="34" t="inlineStr">
         <is>
-          <t>非法经营和分发管制物品罪</t>
+          <t>非法持有管制物品罪</t>
         </is>
       </c>
       <c r="C452" s="34">
@@ -15296,12 +15296,12 @@
     <row r="453">
       <c r="A453" s="34" t="inlineStr">
         <is>
-          <t>开设毒品区域</t>
+          <t>弹簧刀</t>
         </is>
       </c>
       <c r="B453" s="34" t="inlineStr">
         <is>
-          <t>非法经营和分发管制物品罪</t>
+          <t>非法持有管制物品罪</t>
         </is>
       </c>
       <c r="C453" s="34">
@@ -15320,12 +15320,12 @@
     <row r="454">
       <c r="A454" s="34" t="inlineStr">
         <is>
-          <t>卖毒品的店</t>
+          <t>开锁器</t>
         </is>
       </c>
       <c r="B454" s="34" t="inlineStr">
         <is>
-          <t>非法经营和分发管制物品罪</t>
+          <t>非法持有管制物品罪</t>
         </is>
       </c>
       <c r="C454" s="34">
@@ -15344,12 +15344,12 @@
     <row r="455">
       <c r="A455" s="34" t="inlineStr">
         <is>
-          <t>制造管制物品</t>
+          <t>黑客电脑</t>
         </is>
       </c>
       <c r="B455" s="34" t="inlineStr">
         <is>
-          <t>非法制造管制物品罪</t>
+          <t>非法持有管制物品罪</t>
         </is>
       </c>
       <c r="C455" s="34">
@@ -15368,12 +15368,12 @@
     <row r="456">
       <c r="A456" s="34" t="inlineStr">
         <is>
-          <t>制毒</t>
+          <t>身上有毒品</t>
         </is>
       </c>
       <c r="B456" s="34" t="inlineStr">
         <is>
-          <t>非法制造管制物品罪</t>
+          <t>非法持有管制物品罪</t>
         </is>
       </c>
       <c r="C456" s="34">
@@ -15392,12 +15392,12 @@
     <row r="457">
       <c r="A457" s="34" t="inlineStr">
         <is>
-          <t>生产毒品</t>
+          <t>带着毒品</t>
         </is>
       </c>
       <c r="B457" s="34" t="inlineStr">
         <is>
-          <t>非法制造管制物品罪</t>
+          <t>非法持有管制物品罪</t>
         </is>
       </c>
       <c r="C457" s="34">
@@ -15416,12 +15416,12 @@
     <row r="458">
       <c r="A458" s="34" t="inlineStr">
         <is>
-          <t>种植大麻</t>
+          <t>藏毒</t>
         </is>
       </c>
       <c r="B458" s="34" t="inlineStr">
         <is>
-          <t>非法制造管制物品罪</t>
+          <t>非法持有管制物品罪</t>
         </is>
       </c>
       <c r="C458" s="34">
@@ -15440,12 +15440,12 @@
     <row r="459">
       <c r="A459" s="34" t="inlineStr">
         <is>
-          <t>制造毒品</t>
+          <t>大量管制物品</t>
         </is>
       </c>
       <c r="B459" s="34" t="inlineStr">
         <is>
-          <t>非法制造管制物品罪</t>
+          <t>非法持有大量管制物品罪</t>
         </is>
       </c>
       <c r="C459" s="34">
@@ -15464,12 +15464,12 @@
     <row r="460">
       <c r="A460" s="34" t="inlineStr">
         <is>
-          <t>种大麻</t>
+          <t>大量毒品</t>
         </is>
       </c>
       <c r="B460" s="34" t="inlineStr">
         <is>
-          <t>非法制造管制物品罪</t>
+          <t>非法持有大量管制物品罪</t>
         </is>
       </c>
       <c r="C460" s="34">
@@ -15488,12 +15488,12 @@
     <row r="461">
       <c r="A461" s="34" t="inlineStr">
         <is>
-          <t>煮毒</t>
+          <t>分装毒品</t>
         </is>
       </c>
       <c r="B461" s="34" t="inlineStr">
         <is>
-          <t>非法制造管制物品罪</t>
+          <t>非法持有大量管制物品罪</t>
         </is>
       </c>
       <c r="C461" s="34">
@@ -15512,12 +15512,12 @@
     <row r="462">
       <c r="A462" s="34" t="inlineStr">
         <is>
-          <t>贩卖管制物品</t>
+          <t>成批毒品</t>
         </is>
       </c>
       <c r="B462" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖管制物品罪</t>
+          <t>非法持有大量管制物品罪</t>
         </is>
       </c>
       <c r="C462" s="34">
@@ -15536,12 +15536,12 @@
     <row r="463">
       <c r="A463" s="34" t="inlineStr">
         <is>
-          <t>贩毒</t>
+          <t>整箱毒品</t>
         </is>
       </c>
       <c r="B463" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖管制物品罪</t>
+          <t>非法持有大量管制物品罪</t>
         </is>
       </c>
       <c r="C463" s="34">
@@ -15560,12 +15560,12 @@
     <row r="464">
       <c r="A464" s="34" t="inlineStr">
         <is>
-          <t>卖毒品</t>
+          <t>一堆毒品</t>
         </is>
       </c>
       <c r="B464" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖管制物品罪</t>
+          <t>非法持有大量管制物品罪</t>
         </is>
       </c>
       <c r="C464" s="34">
@@ -15584,12 +15584,12 @@
     <row r="465">
       <c r="A465" s="34" t="inlineStr">
         <is>
-          <t>运输毒品</t>
+          <t>大批毒品</t>
         </is>
       </c>
       <c r="B465" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖管制物品罪</t>
+          <t>非法持有大量管制物品罪</t>
         </is>
       </c>
       <c r="C465" s="34">
@@ -15608,12 +15608,12 @@
     <row r="466">
       <c r="A466" s="34" t="inlineStr">
         <is>
-          <t>贩卖毒品</t>
+          <t>经营管制物品</t>
         </is>
       </c>
       <c r="B466" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖管制物品罪</t>
+          <t>非法经营和分发管制物品罪</t>
         </is>
       </c>
       <c r="C466" s="34">
@@ -15632,12 +15632,12 @@
     <row r="467">
       <c r="A467" s="34" t="inlineStr">
         <is>
-          <t>运毒</t>
+          <t>分发毒品</t>
         </is>
       </c>
       <c r="B467" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖管制物品罪</t>
+          <t>非法经营和分发管制物品罪</t>
         </is>
       </c>
       <c r="C467" s="34">
@@ -15656,12 +15656,12 @@
     <row r="468">
       <c r="A468" s="34" t="inlineStr">
         <is>
-          <t>送毒品</t>
+          <t>贩毒据点</t>
         </is>
       </c>
       <c r="B468" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖管制物品罪</t>
+          <t>非法经营和分发管制物品罪</t>
         </is>
       </c>
       <c r="C468" s="34">
@@ -15680,12 +15680,12 @@
     <row r="469">
       <c r="A469" s="34" t="inlineStr">
         <is>
-          <t>倒卖毒品</t>
+          <t>毒品窝点</t>
         </is>
       </c>
       <c r="B469" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖管制物品罪</t>
+          <t>非法经营和分发管制物品罪</t>
         </is>
       </c>
       <c r="C469" s="34">
@@ -15704,12 +15704,12 @@
     <row r="470">
       <c r="A470" s="34" t="inlineStr">
         <is>
-          <t>有组织犯罪</t>
+          <t>开设毒品区域</t>
         </is>
       </c>
       <c r="B470" s="34" t="inlineStr">
         <is>
-          <t>有组织犯罪</t>
+          <t>非法经营和分发管制物品罪</t>
         </is>
       </c>
       <c r="C470" s="34">
@@ -15728,12 +15728,12 @@
     <row r="471">
       <c r="A471" s="34" t="inlineStr">
         <is>
-          <t>团伙犯罪</t>
+          <t>卖毒品的店</t>
         </is>
       </c>
       <c r="B471" s="34" t="inlineStr">
         <is>
-          <t>有组织犯罪</t>
+          <t>非法经营和分发管制物品罪</t>
         </is>
       </c>
       <c r="C471" s="34">
@@ -15752,12 +15752,12 @@
     <row r="472">
       <c r="A472" s="34" t="inlineStr">
         <is>
-          <t>黑帮犯罪</t>
+          <t>制造管制物品</t>
         </is>
       </c>
       <c r="B472" s="34" t="inlineStr">
         <is>
-          <t>有组织犯罪</t>
+          <t>非法制造管制物品罪</t>
         </is>
       </c>
       <c r="C472" s="34">
@@ -15776,12 +15776,12 @@
     <row r="473">
       <c r="A473" s="34" t="inlineStr">
         <is>
-          <t>犯罪集团</t>
+          <t>制毒</t>
         </is>
       </c>
       <c r="B473" s="34" t="inlineStr">
         <is>
-          <t>有组织犯罪</t>
+          <t>非法制造管制物品罪</t>
         </is>
       </c>
       <c r="C473" s="34">
@@ -15800,12 +15800,12 @@
     <row r="474">
       <c r="A474" s="34" t="inlineStr">
         <is>
-          <t>帮派作案</t>
+          <t>生产毒品</t>
         </is>
       </c>
       <c r="B474" s="34" t="inlineStr">
         <is>
-          <t>有组织犯罪</t>
+          <t>非法制造管制物品罪</t>
         </is>
       </c>
       <c r="C474" s="34">
@@ -15824,12 +15824,12 @@
     <row r="475">
       <c r="A475" s="34" t="inlineStr">
         <is>
-          <t>团伙作案</t>
+          <t>种植大麻</t>
         </is>
       </c>
       <c r="B475" s="34" t="inlineStr">
         <is>
-          <t>有组织犯罪</t>
+          <t>非法制造管制物品罪</t>
         </is>
       </c>
       <c r="C475" s="34">
@@ -15848,12 +15848,12 @@
     <row r="476">
       <c r="A476" s="34" t="inlineStr">
         <is>
-          <t>洗钱</t>
+          <t>制造毒品</t>
         </is>
       </c>
       <c r="B476" s="34" t="inlineStr">
         <is>
-          <t>洗钱罪</t>
+          <t>非法制造管制物品罪</t>
         </is>
       </c>
       <c r="C476" s="34">
@@ -15872,12 +15872,12 @@
     <row r="477">
       <c r="A477" s="34" t="inlineStr">
         <is>
-          <t>转移赃款</t>
+          <t>种大麻</t>
         </is>
       </c>
       <c r="B477" s="34" t="inlineStr">
         <is>
-          <t>洗钱罪</t>
+          <t>非法制造管制物品罪</t>
         </is>
       </c>
       <c r="C477" s="34">
@@ -15896,12 +15896,12 @@
     <row r="478">
       <c r="A478" s="34" t="inlineStr">
         <is>
-          <t>清洗黑钱</t>
+          <t>煮毒</t>
         </is>
       </c>
       <c r="B478" s="34" t="inlineStr">
         <is>
-          <t>洗钱罪</t>
+          <t>非法制造管制物品罪</t>
         </is>
       </c>
       <c r="C478" s="34">
@@ -15920,12 +15920,12 @@
     <row r="479">
       <c r="A479" s="34" t="inlineStr">
         <is>
-          <t>标记钞票</t>
+          <t>贩卖管制物品</t>
         </is>
       </c>
       <c r="B479" s="34" t="inlineStr">
         <is>
-          <t>洗钱罪</t>
+          <t>非法贩卖管制物品罪</t>
         </is>
       </c>
       <c r="C479" s="34">
@@ -15944,12 +15944,12 @@
     <row r="480">
       <c r="A480" s="34" t="inlineStr">
         <is>
-          <t>漂白黑钱</t>
+          <t>贩毒</t>
         </is>
       </c>
       <c r="B480" s="34" t="inlineStr">
         <is>
-          <t>洗钱罪</t>
+          <t>非法贩卖管制物品罪</t>
         </is>
       </c>
       <c r="C480" s="34">
@@ -15968,12 +15968,12 @@
     <row r="481">
       <c r="A481" s="34" t="inlineStr">
         <is>
-          <t>洗黑钱</t>
+          <t>卖毒品</t>
         </is>
       </c>
       <c r="B481" s="34" t="inlineStr">
         <is>
-          <t>洗钱罪</t>
+          <t>非法贩卖管制物品罪</t>
         </is>
       </c>
       <c r="C481" s="34">
@@ -15992,12 +15992,12 @@
     <row r="482">
       <c r="A482" s="34" t="inlineStr">
         <is>
-          <t>身份盗用</t>
+          <t>运输毒品</t>
         </is>
       </c>
       <c r="B482" s="34" t="inlineStr">
         <is>
-          <t>身份盗用罪</t>
+          <t>非法贩卖管制物品罪</t>
         </is>
       </c>
       <c r="C482" s="34">
@@ -16016,12 +16016,12 @@
     <row r="483">
       <c r="A483" s="34" t="inlineStr">
         <is>
-          <t>盗用身份</t>
+          <t>贩卖毒品</t>
         </is>
       </c>
       <c r="B483" s="34" t="inlineStr">
         <is>
-          <t>身份盗用罪</t>
+          <t>非法贩卖管制物品罪</t>
         </is>
       </c>
       <c r="C483" s="34">
@@ -16040,12 +16040,12 @@
     <row r="484">
       <c r="A484" s="34" t="inlineStr">
         <is>
-          <t>冒用身份</t>
+          <t>运毒</t>
         </is>
       </c>
       <c r="B484" s="34" t="inlineStr">
         <is>
-          <t>身份盗用罪</t>
+          <t>非法贩卖管制物品罪</t>
         </is>
       </c>
       <c r="C484" s="34">
@@ -16064,12 +16064,12 @@
     <row r="485">
       <c r="A485" s="34" t="inlineStr">
         <is>
-          <t>盗用个人信息</t>
+          <t>送毒品</t>
         </is>
       </c>
       <c r="B485" s="34" t="inlineStr">
         <is>
-          <t>身份盗用罪</t>
+          <t>非法贩卖管制物品罪</t>
         </is>
       </c>
       <c r="C485" s="34">
@@ -16088,12 +16088,12 @@
     <row r="486">
       <c r="A486" s="34" t="inlineStr">
         <is>
-          <t>盗用银行账号</t>
+          <t>倒卖毒品</t>
         </is>
       </c>
       <c r="B486" s="34" t="inlineStr">
         <is>
-          <t>身份盗用罪</t>
+          <t>非法贩卖管制物品罪</t>
         </is>
       </c>
       <c r="C486" s="34">
@@ -16112,12 +16112,12 @@
     <row r="487">
       <c r="A487" s="34" t="inlineStr">
         <is>
-          <t>冒用他人信息</t>
+          <t>有组织犯罪</t>
         </is>
       </c>
       <c r="B487" s="34" t="inlineStr">
         <is>
-          <t>身份盗用罪</t>
+          <t>有组织犯罪</t>
         </is>
       </c>
       <c r="C487" s="34">
@@ -16130,6 +16130,414 @@
       </c>
       <c r="E487" s="34">
         <f>IF(AND($A486&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A486,'算罪台'!$B$6))),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="34" t="inlineStr">
+        <is>
+          <t>团伙犯罪</t>
+        </is>
+      </c>
+      <c r="B488" s="34" t="inlineStr">
+        <is>
+          <t>有组织犯罪</t>
+        </is>
+      </c>
+      <c r="C488" s="34">
+        <f>IF(AND($A487&lt;&gt;"",'算罪台'!$B$4&lt;&gt;"",ISNUMBER(SEARCH($A487,'算罪台'!$B$4))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D488" s="34">
+        <f>IF(AND($A487&lt;&gt;"",'算罪台'!$B$5&lt;&gt;"",ISNUMBER(SEARCH($A487,'算罪台'!$B$5))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E488" s="34">
+        <f>IF(AND($A487&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A487,'算罪台'!$B$6))),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="34" t="inlineStr">
+        <is>
+          <t>黑帮犯罪</t>
+        </is>
+      </c>
+      <c r="B489" s="34" t="inlineStr">
+        <is>
+          <t>有组织犯罪</t>
+        </is>
+      </c>
+      <c r="C489" s="34">
+        <f>IF(AND($A488&lt;&gt;"",'算罪台'!$B$4&lt;&gt;"",ISNUMBER(SEARCH($A488,'算罪台'!$B$4))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D489" s="34">
+        <f>IF(AND($A488&lt;&gt;"",'算罪台'!$B$5&lt;&gt;"",ISNUMBER(SEARCH($A488,'算罪台'!$B$5))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E489" s="34">
+        <f>IF(AND($A488&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A488,'算罪台'!$B$6))),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="34" t="inlineStr">
+        <is>
+          <t>犯罪集团</t>
+        </is>
+      </c>
+      <c r="B490" s="34" t="inlineStr">
+        <is>
+          <t>有组织犯罪</t>
+        </is>
+      </c>
+      <c r="C490" s="34">
+        <f>IF(AND($A489&lt;&gt;"",'算罪台'!$B$4&lt;&gt;"",ISNUMBER(SEARCH($A489,'算罪台'!$B$4))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D490" s="34">
+        <f>IF(AND($A489&lt;&gt;"",'算罪台'!$B$5&lt;&gt;"",ISNUMBER(SEARCH($A489,'算罪台'!$B$5))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E490" s="34">
+        <f>IF(AND($A489&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A489,'算罪台'!$B$6))),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="34" t="inlineStr">
+        <is>
+          <t>帮派作案</t>
+        </is>
+      </c>
+      <c r="B491" s="34" t="inlineStr">
+        <is>
+          <t>有组织犯罪</t>
+        </is>
+      </c>
+      <c r="C491" s="34">
+        <f>IF(AND($A490&lt;&gt;"",'算罪台'!$B$4&lt;&gt;"",ISNUMBER(SEARCH($A490,'算罪台'!$B$4))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D491" s="34">
+        <f>IF(AND($A490&lt;&gt;"",'算罪台'!$B$5&lt;&gt;"",ISNUMBER(SEARCH($A490,'算罪台'!$B$5))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E491" s="34">
+        <f>IF(AND($A490&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A490,'算罪台'!$B$6))),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="34" t="inlineStr">
+        <is>
+          <t>团伙作案</t>
+        </is>
+      </c>
+      <c r="B492" s="34" t="inlineStr">
+        <is>
+          <t>有组织犯罪</t>
+        </is>
+      </c>
+      <c r="C492" s="34">
+        <f>IF(AND($A491&lt;&gt;"",'算罪台'!$B$4&lt;&gt;"",ISNUMBER(SEARCH($A491,'算罪台'!$B$4))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D492" s="34">
+        <f>IF(AND($A491&lt;&gt;"",'算罪台'!$B$5&lt;&gt;"",ISNUMBER(SEARCH($A491,'算罪台'!$B$5))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E492" s="34">
+        <f>IF(AND($A491&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A491,'算罪台'!$B$6))),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="34" t="inlineStr">
+        <is>
+          <t>洗钱</t>
+        </is>
+      </c>
+      <c r="B493" s="34" t="inlineStr">
+        <is>
+          <t>洗钱罪</t>
+        </is>
+      </c>
+      <c r="C493" s="34">
+        <f>IF(AND($A492&lt;&gt;"",'算罪台'!$B$4&lt;&gt;"",ISNUMBER(SEARCH($A492,'算罪台'!$B$4))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D493" s="34">
+        <f>IF(AND($A492&lt;&gt;"",'算罪台'!$B$5&lt;&gt;"",ISNUMBER(SEARCH($A492,'算罪台'!$B$5))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E493" s="34">
+        <f>IF(AND($A492&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A492,'算罪台'!$B$6))),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="34" t="inlineStr">
+        <is>
+          <t>转移赃款</t>
+        </is>
+      </c>
+      <c r="B494" s="34" t="inlineStr">
+        <is>
+          <t>洗钱罪</t>
+        </is>
+      </c>
+      <c r="C494" s="34">
+        <f>IF(AND($A493&lt;&gt;"",'算罪台'!$B$4&lt;&gt;"",ISNUMBER(SEARCH($A493,'算罪台'!$B$4))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D494" s="34">
+        <f>IF(AND($A493&lt;&gt;"",'算罪台'!$B$5&lt;&gt;"",ISNUMBER(SEARCH($A493,'算罪台'!$B$5))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E494" s="34">
+        <f>IF(AND($A493&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A493,'算罪台'!$B$6))),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="34" t="inlineStr">
+        <is>
+          <t>清洗黑钱</t>
+        </is>
+      </c>
+      <c r="B495" s="34" t="inlineStr">
+        <is>
+          <t>洗钱罪</t>
+        </is>
+      </c>
+      <c r="C495" s="34">
+        <f>IF(AND($A494&lt;&gt;"",'算罪台'!$B$4&lt;&gt;"",ISNUMBER(SEARCH($A494,'算罪台'!$B$4))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D495" s="34">
+        <f>IF(AND($A494&lt;&gt;"",'算罪台'!$B$5&lt;&gt;"",ISNUMBER(SEARCH($A494,'算罪台'!$B$5))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E495" s="34">
+        <f>IF(AND($A494&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A494,'算罪台'!$B$6))),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="34" t="inlineStr">
+        <is>
+          <t>标记钞票</t>
+        </is>
+      </c>
+      <c r="B496" s="34" t="inlineStr">
+        <is>
+          <t>洗钱罪</t>
+        </is>
+      </c>
+      <c r="C496" s="34">
+        <f>IF(AND($A495&lt;&gt;"",'算罪台'!$B$4&lt;&gt;"",ISNUMBER(SEARCH($A495,'算罪台'!$B$4))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D496" s="34">
+        <f>IF(AND($A495&lt;&gt;"",'算罪台'!$B$5&lt;&gt;"",ISNUMBER(SEARCH($A495,'算罪台'!$B$5))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E496" s="34">
+        <f>IF(AND($A495&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A495,'算罪台'!$B$6))),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="34" t="inlineStr">
+        <is>
+          <t>漂白黑钱</t>
+        </is>
+      </c>
+      <c r="B497" s="34" t="inlineStr">
+        <is>
+          <t>洗钱罪</t>
+        </is>
+      </c>
+      <c r="C497" s="34">
+        <f>IF(AND($A496&lt;&gt;"",'算罪台'!$B$4&lt;&gt;"",ISNUMBER(SEARCH($A496,'算罪台'!$B$4))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D497" s="34">
+        <f>IF(AND($A496&lt;&gt;"",'算罪台'!$B$5&lt;&gt;"",ISNUMBER(SEARCH($A496,'算罪台'!$B$5))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E497" s="34">
+        <f>IF(AND($A496&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A496,'算罪台'!$B$6))),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="34" t="inlineStr">
+        <is>
+          <t>洗黑钱</t>
+        </is>
+      </c>
+      <c r="B498" s="34" t="inlineStr">
+        <is>
+          <t>洗钱罪</t>
+        </is>
+      </c>
+      <c r="C498" s="34">
+        <f>IF(AND($A497&lt;&gt;"",'算罪台'!$B$4&lt;&gt;"",ISNUMBER(SEARCH($A497,'算罪台'!$B$4))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D498" s="34">
+        <f>IF(AND($A497&lt;&gt;"",'算罪台'!$B$5&lt;&gt;"",ISNUMBER(SEARCH($A497,'算罪台'!$B$5))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E498" s="34">
+        <f>IF(AND($A497&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A497,'算罪台'!$B$6))),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="34" t="inlineStr">
+        <is>
+          <t>身份盗用</t>
+        </is>
+      </c>
+      <c r="B499" s="34" t="inlineStr">
+        <is>
+          <t>身份盗用罪</t>
+        </is>
+      </c>
+      <c r="C499" s="34">
+        <f>IF(AND($A498&lt;&gt;"",'算罪台'!$B$4&lt;&gt;"",ISNUMBER(SEARCH($A498,'算罪台'!$B$4))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D499" s="34">
+        <f>IF(AND($A498&lt;&gt;"",'算罪台'!$B$5&lt;&gt;"",ISNUMBER(SEARCH($A498,'算罪台'!$B$5))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E499" s="34">
+        <f>IF(AND($A498&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A498,'算罪台'!$B$6))),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="34" t="inlineStr">
+        <is>
+          <t>盗用身份</t>
+        </is>
+      </c>
+      <c r="B500" s="34" t="inlineStr">
+        <is>
+          <t>身份盗用罪</t>
+        </is>
+      </c>
+      <c r="C500" s="34">
+        <f>IF(AND($A499&lt;&gt;"",'算罪台'!$B$4&lt;&gt;"",ISNUMBER(SEARCH($A499,'算罪台'!$B$4))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D500" s="34">
+        <f>IF(AND($A499&lt;&gt;"",'算罪台'!$B$5&lt;&gt;"",ISNUMBER(SEARCH($A499,'算罪台'!$B$5))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E500" s="34">
+        <f>IF(AND($A499&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A499,'算罪台'!$B$6))),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="34" t="inlineStr">
+        <is>
+          <t>冒用身份</t>
+        </is>
+      </c>
+      <c r="B501" s="34" t="inlineStr">
+        <is>
+          <t>身份盗用罪</t>
+        </is>
+      </c>
+      <c r="C501" s="34">
+        <f>IF(AND($A500&lt;&gt;"",'算罪台'!$B$4&lt;&gt;"",ISNUMBER(SEARCH($A500,'算罪台'!$B$4))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D501" s="34">
+        <f>IF(AND($A500&lt;&gt;"",'算罪台'!$B$5&lt;&gt;"",ISNUMBER(SEARCH($A500,'算罪台'!$B$5))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E501" s="34">
+        <f>IF(AND($A500&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A500,'算罪台'!$B$6))),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="34" t="inlineStr">
+        <is>
+          <t>盗用个人信息</t>
+        </is>
+      </c>
+      <c r="B502" s="34" t="inlineStr">
+        <is>
+          <t>身份盗用罪</t>
+        </is>
+      </c>
+      <c r="C502" s="34">
+        <f>IF(AND($A501&lt;&gt;"",'算罪台'!$B$4&lt;&gt;"",ISNUMBER(SEARCH($A501,'算罪台'!$B$4))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D502" s="34">
+        <f>IF(AND($A501&lt;&gt;"",'算罪台'!$B$5&lt;&gt;"",ISNUMBER(SEARCH($A501,'算罪台'!$B$5))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E502" s="34">
+        <f>IF(AND($A501&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A501,'算罪台'!$B$6))),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="34" t="inlineStr">
+        <is>
+          <t>盗用银行账号</t>
+        </is>
+      </c>
+      <c r="B503" s="34" t="inlineStr">
+        <is>
+          <t>身份盗用罪</t>
+        </is>
+      </c>
+      <c r="C503" s="34">
+        <f>IF(AND($A502&lt;&gt;"",'算罪台'!$B$4&lt;&gt;"",ISNUMBER(SEARCH($A502,'算罪台'!$B$4))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D503" s="34">
+        <f>IF(AND($A502&lt;&gt;"",'算罪台'!$B$5&lt;&gt;"",ISNUMBER(SEARCH($A502,'算罪台'!$B$5))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E503" s="34">
+        <f>IF(AND($A502&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A502,'算罪台'!$B$6))),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="34" t="inlineStr">
+        <is>
+          <t>冒用他人信息</t>
+        </is>
+      </c>
+      <c r="B504" s="34" t="inlineStr">
+        <is>
+          <t>身份盗用罪</t>
+        </is>
+      </c>
+      <c r="C504" s="34">
+        <f>IF(AND($A503&lt;&gt;"",'算罪台'!$B$4&lt;&gt;"",ISNUMBER(SEARCH($A503,'算罪台'!$B$4))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D504" s="34">
+        <f>IF(AND($A503&lt;&gt;"",'算罪台'!$B$5&lt;&gt;"",ISNUMBER(SEARCH($A503,'算罪台'!$B$5))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E504" s="34">
+        <f>IF(AND($A503&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A503,'算罪台'!$B$6))),1,0)</f>
         <v/>
       </c>
     </row>

--- a/fivem_case_analyzer/圣安地列斯州_案件罪名分析器.xlsx
+++ b/fivem_case_analyzer/圣安地列斯州_案件罪名分析器.xlsx
@@ -1285,15 +1285,15 @@
         </is>
       </c>
       <c r="G2" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B2)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B2)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H2" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B2)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B2)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I2" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B2)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B2)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J2" s="34">
@@ -1337,15 +1337,15 @@
         </is>
       </c>
       <c r="G3" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B3)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B3)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H3" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B3)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B3)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I3" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B3)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B3)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J3" s="34">
@@ -1389,15 +1389,15 @@
         </is>
       </c>
       <c r="G4" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B4)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B4)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H4" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B4)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B4)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I4" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B4)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B4)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J4" s="34">
@@ -1441,15 +1441,15 @@
         </is>
       </c>
       <c r="G5" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B5)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B5)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H5" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B5)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B5)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I5" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B5)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B5)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J5" s="34">
@@ -1493,15 +1493,15 @@
         </is>
       </c>
       <c r="G6" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B6)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B6)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H6" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B6)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B6)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I6" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B6)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B6)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J6" s="34">
@@ -1545,15 +1545,15 @@
         </is>
       </c>
       <c r="G7" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B7)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B7)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H7" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B7)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B7)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I7" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B7)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B7)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J7" s="34">
@@ -1597,15 +1597,15 @@
         </is>
       </c>
       <c r="G8" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B8)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B8)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H8" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B8)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B8)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I8" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B8)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B8)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J8" s="34">
@@ -1649,15 +1649,15 @@
         </is>
       </c>
       <c r="G9" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B9)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B9)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H9" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B9)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B9)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I9" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B9)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B9)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J9" s="34">
@@ -1701,15 +1701,15 @@
         </is>
       </c>
       <c r="G10" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B10)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B10)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H10" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B10)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B10)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I10" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B10)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B10)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J10" s="34">
@@ -1753,15 +1753,15 @@
         </is>
       </c>
       <c r="G11" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B11)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B11)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H11" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B11)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B11)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I11" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B11)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B11)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J11" s="34">
@@ -1805,15 +1805,15 @@
         </is>
       </c>
       <c r="G12" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B12)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B12)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H12" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B12)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B12)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I12" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B12)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B12)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J12" s="34">
@@ -1857,15 +1857,15 @@
         </is>
       </c>
       <c r="G13" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B13)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B13)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H13" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B13)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B13)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I13" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B13)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B13)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J13" s="34">
@@ -1909,15 +1909,15 @@
         </is>
       </c>
       <c r="G14" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B14)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B14)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H14" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B14)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B14)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I14" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B14)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B14)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J14" s="34">
@@ -1961,15 +1961,15 @@
         </is>
       </c>
       <c r="G15" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B15)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B15)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H15" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B15)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B15)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I15" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B15)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B15)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J15" s="34">
@@ -2013,15 +2013,15 @@
         </is>
       </c>
       <c r="G16" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B16)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B16)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H16" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B16)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B16)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I16" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B16)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B16)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J16" s="34">
@@ -2065,15 +2065,15 @@
         </is>
       </c>
       <c r="G17" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B17)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B17)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H17" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B17)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B17)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I17" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B17)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B17)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J17" s="34">
@@ -2117,15 +2117,15 @@
         </is>
       </c>
       <c r="G18" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B18)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B18)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H18" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B18)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B18)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I18" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B18)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B18)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J18" s="34">
@@ -2169,15 +2169,15 @@
         </is>
       </c>
       <c r="G19" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B19)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B19)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H19" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B19)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B19)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I19" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B19)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B19)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J19" s="34">
@@ -2221,15 +2221,15 @@
         </is>
       </c>
       <c r="G20" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B20)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B20)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H20" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B20)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B20)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I20" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B20)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B20)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J20" s="34">
@@ -2273,15 +2273,15 @@
         </is>
       </c>
       <c r="G21" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B21)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B21)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H21" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B21)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B21)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I21" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B21)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B21)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J21" s="34">
@@ -2325,15 +2325,15 @@
         </is>
       </c>
       <c r="G22" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B22)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B22)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H22" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B22)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B22)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I22" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B22)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B22)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J22" s="34">
@@ -2377,15 +2377,15 @@
         </is>
       </c>
       <c r="G23" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B23)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B23)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H23" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B23)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B23)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I23" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B23)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B23)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J23" s="34">
@@ -2429,15 +2429,15 @@
         </is>
       </c>
       <c r="G24" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B24)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B24)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H24" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B24)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B24)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I24" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B24)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B24)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J24" s="34">
@@ -2481,15 +2481,15 @@
         </is>
       </c>
       <c r="G25" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B25)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B25)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H25" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B25)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B25)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I25" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B25)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B25)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J25" s="34">
@@ -2533,15 +2533,15 @@
         </is>
       </c>
       <c r="G26" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B26)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B26)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H26" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B26)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B26)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I26" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B26)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B26)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J26" s="34">
@@ -2585,15 +2585,15 @@
         </is>
       </c>
       <c r="G27" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B27)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B27)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H27" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B27)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B27)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I27" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B27)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B27)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J27" s="34">
@@ -2637,15 +2637,15 @@
         </is>
       </c>
       <c r="G28" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B28)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B28)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H28" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B28)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B28)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I28" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B28)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B28)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J28" s="34">
@@ -2689,15 +2689,15 @@
         </is>
       </c>
       <c r="G29" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B29)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B29)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H29" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B29)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B29)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I29" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B29)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B29)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J29" s="34">
@@ -2741,15 +2741,15 @@
         </is>
       </c>
       <c r="G30" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B30)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B30)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H30" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B30)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B30)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I30" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B30)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B30)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J30" s="34">
@@ -2793,15 +2793,15 @@
         </is>
       </c>
       <c r="G31" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B31)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B31)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H31" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B31)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B31)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I31" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B31)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B31)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J31" s="34">
@@ -2845,15 +2845,15 @@
         </is>
       </c>
       <c r="G32" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B32)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B32)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H32" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B32)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B32)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I32" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B32)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B32)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J32" s="34">
@@ -2897,15 +2897,15 @@
         </is>
       </c>
       <c r="G33" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B33)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B33)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H33" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B33)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B33)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I33" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B33)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B33)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J33" s="34">
@@ -2949,15 +2949,15 @@
         </is>
       </c>
       <c r="G34" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B34)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B34)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H34" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B34)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B34)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I34" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B34)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B34)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J34" s="34">
@@ -3001,15 +3001,15 @@
         </is>
       </c>
       <c r="G35" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B35)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B35)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H35" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B35)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B35)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I35" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B35)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B35)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J35" s="34">
@@ -3053,15 +3053,15 @@
         </is>
       </c>
       <c r="G36" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B36)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B36)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H36" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B36)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B36)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I36" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B36)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B36)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J36" s="34">
@@ -3105,15 +3105,15 @@
         </is>
       </c>
       <c r="G37" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B37)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B37)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H37" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B37)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B37)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I37" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B37)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B37)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J37" s="34">
@@ -3157,15 +3157,15 @@
         </is>
       </c>
       <c r="G38" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B38)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B38)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H38" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B38)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B38)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I38" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B38)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B38)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J38" s="34">
@@ -3209,15 +3209,15 @@
         </is>
       </c>
       <c r="G39" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B39)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B39)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H39" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B39)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B39)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I39" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B39)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B39)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J39" s="34">
@@ -3261,15 +3261,15 @@
         </is>
       </c>
       <c r="G40" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B40)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B40)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H40" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B40)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B40)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I40" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B40)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B40)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J40" s="34">
@@ -3309,19 +3309,19 @@
       </c>
       <c r="F41" s="33" t="inlineStr">
         <is>
-          <t>★须先被合法扣留/逮捕后，再从监护中逃脱才算（仅在现场逃跑不算，那是拒捕罪）</t>
+          <t>★须先被抓到(已逮捕/拘留)后再从监护中逃脱才算；当场逃跑、没抓到不算(那是拒捕罪)</t>
         </is>
       </c>
       <c r="G41" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B41)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B41)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H41" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B41)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B41)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I41" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B41)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B41)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J41" s="34">
@@ -3365,15 +3365,15 @@
         </is>
       </c>
       <c r="G42" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B42)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B42)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H42" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B42)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B42)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I42" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B42)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B42)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J42" s="34">
@@ -3417,15 +3417,15 @@
         </is>
       </c>
       <c r="G43" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B43)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B43)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H43" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B43)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B43)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I43" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B43)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B43)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J43" s="34">
@@ -3469,15 +3469,15 @@
         </is>
       </c>
       <c r="G44" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B44)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B44)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H44" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B44)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B44)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I44" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B44)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B44)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J44" s="34">
@@ -3521,15 +3521,15 @@
         </is>
       </c>
       <c r="G45" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B45)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B45)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H45" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B45)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B45)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I45" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B45)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B45)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J45" s="34">
@@ -3573,15 +3573,15 @@
         </is>
       </c>
       <c r="G46" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B46)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B46)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H46" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B46)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B46)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I46" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B46)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B46)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J46" s="34">
@@ -3625,15 +3625,15 @@
         </is>
       </c>
       <c r="G47" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B47)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B47)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H47" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B47)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B47)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I47" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B47)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B47)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J47" s="34">
@@ -3677,15 +3677,15 @@
         </is>
       </c>
       <c r="G48" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B48)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B48)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H48" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B48)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B48)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I48" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B48)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B48)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J48" s="34">
@@ -3729,15 +3729,15 @@
         </is>
       </c>
       <c r="G49" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B49)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B49)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H49" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B49)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B49)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I49" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B49)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B49)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J49" s="34">
@@ -3781,15 +3781,15 @@
         </is>
       </c>
       <c r="G50" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B50)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B50)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H50" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B50)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B50)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I50" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B50)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B50)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J50" s="34">
@@ -3833,15 +3833,15 @@
         </is>
       </c>
       <c r="G51" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B51)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B51)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H51" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B51)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B51)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I51" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B51)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B51)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J51" s="34">
@@ -3885,15 +3885,15 @@
         </is>
       </c>
       <c r="G52" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B52)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B52)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H52" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B52)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B52)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I52" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B52)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B52)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J52" s="34">
@@ -3937,15 +3937,15 @@
         </is>
       </c>
       <c r="G53" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B53)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B53)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H53" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B53)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B53)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I53" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B53)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B53)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J53" s="34">
@@ -3989,15 +3989,15 @@
         </is>
       </c>
       <c r="G54" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B54)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B54)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H54" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B54)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B54)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I54" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B54)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B54)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J54" s="34">
@@ -4041,15 +4041,15 @@
         </is>
       </c>
       <c r="G55" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B55)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B55)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H55" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B55)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B55)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I55" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B55)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B55)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J55" s="34">
@@ -4093,15 +4093,15 @@
         </is>
       </c>
       <c r="G56" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B56)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B56)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H56" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B56)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B56)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I56" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B56)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B56)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J56" s="34">
@@ -4145,15 +4145,15 @@
         </is>
       </c>
       <c r="G57" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B57)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B57)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H57" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B57)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B57)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I57" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B57)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B57)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J57" s="34">
@@ -4197,15 +4197,15 @@
         </is>
       </c>
       <c r="G58" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B58)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B58)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H58" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B58)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B58)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I58" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B58)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B58)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J58" s="34">
@@ -4249,15 +4249,15 @@
         </is>
       </c>
       <c r="G59" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B59)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B59)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H59" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B59)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B59)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I59" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B59)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B59)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J59" s="34">
@@ -4301,15 +4301,15 @@
         </is>
       </c>
       <c r="G60" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B60)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B60)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H60" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B60)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B60)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I60" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B60)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B60)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J60" s="34">
@@ -4353,15 +4353,15 @@
         </is>
       </c>
       <c r="G61" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B61)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B61)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H61" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B61)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B61)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I61" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B61)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B61)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J61" s="34">
@@ -4405,15 +4405,15 @@
         </is>
       </c>
       <c r="G62" s="34">
-        <f>IF(SUMIFS('关键词库'!$C$2:$C$503,'关键词库'!$B$2:$B$503,$B62)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$C$2:$C$515,'关键词库'!$B$2:$B$515,$B62)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="H62" s="34">
-        <f>IF(SUMIFS('关键词库'!$D$2:$D$503,'关键词库'!$B$2:$B$503,$B62)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$D$2:$D$515,'关键词库'!$B$2:$B$515,$B62)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="I62" s="34">
-        <f>IF(SUMIFS('关键词库'!$E$2:$E$503,'关键词库'!$B$2:$B$503,$B62)&gt;0,1,0)</f>
+        <f>IF(SUMIFS('关键词库'!$E$2:$E$515,'关键词库'!$B$2:$B$515,$B62)&gt;0,1,0)</f>
         <v/>
       </c>
       <c r="J62" s="34">
@@ -4445,7 +4445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E504"/>
+  <dimension ref="A1:E516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12272,12 +12272,12 @@
     <row r="327">
       <c r="A327" s="34" t="inlineStr">
         <is>
-          <t>藐视法庭</t>
+          <t>押送途中逃</t>
         </is>
       </c>
       <c r="B327" s="34" t="inlineStr">
         <is>
-          <t>藐视法庭罪</t>
+          <t>逃避羁押罪</t>
         </is>
       </c>
       <c r="C327" s="34">
@@ -12296,12 +12296,12 @@
     <row r="328">
       <c r="A328" s="34" t="inlineStr">
         <is>
-          <t>扰乱法庭</t>
+          <t>被捕后逃</t>
         </is>
       </c>
       <c r="B328" s="34" t="inlineStr">
         <is>
-          <t>藐视法庭罪</t>
+          <t>逃避羁押罪</t>
         </is>
       </c>
       <c r="C328" s="34">
@@ -12320,12 +12320,12 @@
     <row r="329">
       <c r="A329" s="34" t="inlineStr">
         <is>
-          <t>无视法庭命令</t>
+          <t>逮捕后逃</t>
         </is>
       </c>
       <c r="B329" s="34" t="inlineStr">
         <is>
-          <t>藐视法庭罪</t>
+          <t>逃避羁押罪</t>
         </is>
       </c>
       <c r="C329" s="34">
@@ -12344,12 +12344,12 @@
     <row r="330">
       <c r="A330" s="34" t="inlineStr">
         <is>
-          <t>不尊重法庭</t>
+          <t>被抓后逃</t>
         </is>
       </c>
       <c r="B330" s="34" t="inlineStr">
         <is>
-          <t>藐视法庭罪</t>
+          <t>逃避羁押罪</t>
         </is>
       </c>
       <c r="C330" s="34">
@@ -12368,12 +12368,12 @@
     <row r="331">
       <c r="A331" s="34" t="inlineStr">
         <is>
-          <t>在法庭上闹</t>
+          <t>抓住后逃</t>
         </is>
       </c>
       <c r="B331" s="34" t="inlineStr">
         <is>
-          <t>藐视法庭罪</t>
+          <t>逃避羁押罪</t>
         </is>
       </c>
       <c r="C331" s="34">
@@ -12392,12 +12392,12 @@
     <row r="332">
       <c r="A332" s="34" t="inlineStr">
         <is>
-          <t>恶意占用公共资源</t>
+          <t>抓获后逃</t>
         </is>
       </c>
       <c r="B332" s="34" t="inlineStr">
         <is>
-          <t>恶意占用公共资源罪</t>
+          <t>逃避羁押罪</t>
         </is>
       </c>
       <c r="C332" s="34">
@@ -12416,12 +12416,12 @@
     <row r="333">
       <c r="A333" s="34" t="inlineStr">
         <is>
-          <t>骚扰报警电话</t>
+          <t>铐上后逃</t>
         </is>
       </c>
       <c r="B333" s="34" t="inlineStr">
         <is>
-          <t>恶意占用公共资源罪</t>
+          <t>逃避羁押罪</t>
         </is>
       </c>
       <c r="C333" s="34">
@@ -12440,12 +12440,12 @@
     <row r="334">
       <c r="A334" s="34" t="inlineStr">
         <is>
-          <t>恶意报警</t>
+          <t>铐住后逃</t>
         </is>
       </c>
       <c r="B334" s="34" t="inlineStr">
         <is>
-          <t>恶意占用公共资源罪</t>
+          <t>逃避羁押罪</t>
         </is>
       </c>
       <c r="C334" s="34">
@@ -12464,12 +12464,12 @@
     <row r="335">
       <c r="A335" s="34" t="inlineStr">
         <is>
-          <t>虚假报警</t>
+          <t>收押后逃</t>
         </is>
       </c>
       <c r="B335" s="34" t="inlineStr">
         <is>
-          <t>恶意占用公共资源罪</t>
+          <t>逃避羁押罪</t>
         </is>
       </c>
       <c r="C335" s="34">
@@ -12488,12 +12488,12 @@
     <row r="336">
       <c r="A336" s="34" t="inlineStr">
         <is>
-          <t>乱打报警</t>
+          <t>拘留后逃</t>
         </is>
       </c>
       <c r="B336" s="34" t="inlineStr">
         <is>
-          <t>恶意占用公共资源罪</t>
+          <t>逃避羁押罪</t>
         </is>
       </c>
       <c r="C336" s="34">
@@ -12512,12 +12512,12 @@
     <row r="337">
       <c r="A337" s="34" t="inlineStr">
         <is>
-          <t>谎报警情</t>
+          <t>关进警局后逃</t>
         </is>
       </c>
       <c r="B337" s="34" t="inlineStr">
         <is>
-          <t>恶意占用公共资源罪</t>
+          <t>逃避羁押罪</t>
         </is>
       </c>
       <c r="C337" s="34">
@@ -12536,12 +12536,12 @@
     <row r="338">
       <c r="A338" s="34" t="inlineStr">
         <is>
-          <t>谎报</t>
+          <t>进局子后逃</t>
         </is>
       </c>
       <c r="B338" s="34" t="inlineStr">
         <is>
-          <t>恶意占用公共资源罪</t>
+          <t>逃避羁押罪</t>
         </is>
       </c>
       <c r="C338" s="34">
@@ -12560,12 +12560,12 @@
     <row r="339">
       <c r="A339" s="34" t="inlineStr">
         <is>
-          <t>进入封闭区域</t>
+          <t>藐视法庭</t>
         </is>
       </c>
       <c r="B339" s="34" t="inlineStr">
         <is>
-          <t>未经许可进入封闭紧急区域罪</t>
+          <t>藐视法庭罪</t>
         </is>
       </c>
       <c r="C339" s="34">
@@ -12584,12 +12584,12 @@
     <row r="340">
       <c r="A340" s="34" t="inlineStr">
         <is>
-          <t>闯入警戒线</t>
+          <t>扰乱法庭</t>
         </is>
       </c>
       <c r="B340" s="34" t="inlineStr">
         <is>
-          <t>未经许可进入封闭紧急区域罪</t>
+          <t>藐视法庭罪</t>
         </is>
       </c>
       <c r="C340" s="34">
@@ -12608,12 +12608,12 @@
     <row r="341">
       <c r="A341" s="34" t="inlineStr">
         <is>
-          <t>擅闯封锁区</t>
+          <t>无视法庭命令</t>
         </is>
       </c>
       <c r="B341" s="34" t="inlineStr">
         <is>
-          <t>未经许可进入封闭紧急区域罪</t>
+          <t>藐视法庭罪</t>
         </is>
       </c>
       <c r="C341" s="34">
@@ -12632,12 +12632,12 @@
     <row r="342">
       <c r="A342" s="34" t="inlineStr">
         <is>
-          <t>越过警戒线</t>
+          <t>不尊重法庭</t>
         </is>
       </c>
       <c r="B342" s="34" t="inlineStr">
         <is>
-          <t>未经许可进入封闭紧急区域罪</t>
+          <t>藐视法庭罪</t>
         </is>
       </c>
       <c r="C342" s="34">
@@ -12656,12 +12656,12 @@
     <row r="343">
       <c r="A343" s="34" t="inlineStr">
         <is>
-          <t>闯入事故现场</t>
+          <t>在法庭上闹</t>
         </is>
       </c>
       <c r="B343" s="34" t="inlineStr">
         <is>
-          <t>未经许可进入封闭紧急区域罪</t>
+          <t>藐视法庭罪</t>
         </is>
       </c>
       <c r="C343" s="34">
@@ -12680,12 +12680,12 @@
     <row r="344">
       <c r="A344" s="34" t="inlineStr">
         <is>
-          <t>跨过警戒带</t>
+          <t>恶意占用公共资源</t>
         </is>
       </c>
       <c r="B344" s="34" t="inlineStr">
         <is>
-          <t>未经许可进入封闭紧急区域罪</t>
+          <t>恶意占用公共资源罪</t>
         </is>
       </c>
       <c r="C344" s="34">
@@ -12704,12 +12704,12 @@
     <row r="345">
       <c r="A345" s="34" t="inlineStr">
         <is>
-          <t>袭警</t>
+          <t>骚扰报警电话</t>
         </is>
       </c>
       <c r="B345" s="34" t="inlineStr">
         <is>
-          <t>袭警罪</t>
+          <t>恶意占用公共资源罪</t>
         </is>
       </c>
       <c r="C345" s="34">
@@ -12728,12 +12728,12 @@
     <row r="346">
       <c r="A346" s="34" t="inlineStr">
         <is>
-          <t>袭击警察</t>
+          <t>恶意报警</t>
         </is>
       </c>
       <c r="B346" s="34" t="inlineStr">
         <is>
-          <t>袭警罪</t>
+          <t>恶意占用公共资源罪</t>
         </is>
       </c>
       <c r="C346" s="34">
@@ -12752,12 +12752,12 @@
     <row r="347">
       <c r="A347" s="34" t="inlineStr">
         <is>
-          <t>打警察</t>
+          <t>虚假报警</t>
         </is>
       </c>
       <c r="B347" s="34" t="inlineStr">
         <is>
-          <t>袭警罪</t>
+          <t>恶意占用公共资源罪</t>
         </is>
       </c>
       <c r="C347" s="34">
@@ -12776,12 +12776,12 @@
     <row r="348">
       <c r="A348" s="34" t="inlineStr">
         <is>
-          <t>攻击警察</t>
+          <t>乱打报警</t>
         </is>
       </c>
       <c r="B348" s="34" t="inlineStr">
         <is>
-          <t>袭警罪</t>
+          <t>恶意占用公共资源罪</t>
         </is>
       </c>
       <c r="C348" s="34">
@@ -12800,12 +12800,12 @@
     <row r="349">
       <c r="A349" s="34" t="inlineStr">
         <is>
-          <t>伤害警察</t>
+          <t>谎报警情</t>
         </is>
       </c>
       <c r="B349" s="34" t="inlineStr">
         <is>
-          <t>袭警罪</t>
+          <t>恶意占用公共资源罪</t>
         </is>
       </c>
       <c r="C349" s="34">
@@ -12824,12 +12824,12 @@
     <row r="350">
       <c r="A350" s="34" t="inlineStr">
         <is>
-          <t>攻击警车</t>
+          <t>谎报</t>
         </is>
       </c>
       <c r="B350" s="34" t="inlineStr">
         <is>
-          <t>袭警罪</t>
+          <t>恶意占用公共资源罪</t>
         </is>
       </c>
       <c r="C350" s="34">
@@ -12848,12 +12848,12 @@
     <row r="351">
       <c r="A351" s="34" t="inlineStr">
         <is>
-          <t>攻击警犬</t>
+          <t>进入封闭区域</t>
         </is>
       </c>
       <c r="B351" s="34" t="inlineStr">
         <is>
-          <t>袭警罪</t>
+          <t>未经许可进入封闭紧急区域罪</t>
         </is>
       </c>
       <c r="C351" s="34">
@@ -12872,12 +12872,12 @@
     <row r="352">
       <c r="A352" s="34" t="inlineStr">
         <is>
-          <t>殴打警察</t>
+          <t>闯入警戒线</t>
         </is>
       </c>
       <c r="B352" s="34" t="inlineStr">
         <is>
-          <t>袭警罪</t>
+          <t>未经许可进入封闭紧急区域罪</t>
         </is>
       </c>
       <c r="C352" s="34">
@@ -12896,12 +12896,12 @@
     <row r="353">
       <c r="A353" s="34" t="inlineStr">
         <is>
-          <t>动手打警察</t>
+          <t>擅闯封锁区</t>
         </is>
       </c>
       <c r="B353" s="34" t="inlineStr">
         <is>
-          <t>袭警罪</t>
+          <t>未经许可进入封闭紧急区域罪</t>
         </is>
       </c>
       <c r="C353" s="34">
@@ -12920,12 +12920,12 @@
     <row r="354">
       <c r="A354" s="34" t="inlineStr">
         <is>
-          <t>撞警车</t>
+          <t>越过警戒线</t>
         </is>
       </c>
       <c r="B354" s="34" t="inlineStr">
         <is>
-          <t>袭警罪</t>
+          <t>未经许可进入封闭紧急区域罪</t>
         </is>
       </c>
       <c r="C354" s="34">
@@ -12944,12 +12944,12 @@
     <row r="355">
       <c r="A355" s="34" t="inlineStr">
         <is>
-          <t>枪击警察</t>
+          <t>闯入事故现场</t>
         </is>
       </c>
       <c r="B355" s="34" t="inlineStr">
         <is>
-          <t>袭警罪</t>
+          <t>未经许可进入封闭紧急区域罪</t>
         </is>
       </c>
       <c r="C355" s="34">
@@ -12968,12 +12968,12 @@
     <row r="356">
       <c r="A356" s="34" t="inlineStr">
         <is>
-          <t>打了警察</t>
+          <t>跨过警戒带</t>
         </is>
       </c>
       <c r="B356" s="34" t="inlineStr">
         <is>
-          <t>袭警罪</t>
+          <t>未经许可进入封闭紧急区域罪</t>
         </is>
       </c>
       <c r="C356" s="34">
@@ -12992,7 +12992,7 @@
     <row r="357">
       <c r="A357" s="34" t="inlineStr">
         <is>
-          <t>朝警察开枪</t>
+          <t>袭警</t>
         </is>
       </c>
       <c r="B357" s="34" t="inlineStr">
@@ -13016,7 +13016,7 @@
     <row r="358">
       <c r="A358" s="34" t="inlineStr">
         <is>
-          <t>朝警察射击</t>
+          <t>袭击警察</t>
         </is>
       </c>
       <c r="B358" s="34" t="inlineStr">
@@ -13040,7 +13040,7 @@
     <row r="359">
       <c r="A359" s="34" t="inlineStr">
         <is>
-          <t>向警察开枪</t>
+          <t>打警察</t>
         </is>
       </c>
       <c r="B359" s="34" t="inlineStr">
@@ -13064,7 +13064,7 @@
     <row r="360">
       <c r="A360" s="34" t="inlineStr">
         <is>
-          <t>向警察射击</t>
+          <t>攻击警察</t>
         </is>
       </c>
       <c r="B360" s="34" t="inlineStr">
@@ -13088,7 +13088,7 @@
     <row r="361">
       <c r="A361" s="34" t="inlineStr">
         <is>
-          <t>射击警察</t>
+          <t>伤害警察</t>
         </is>
       </c>
       <c r="B361" s="34" t="inlineStr">
@@ -13112,7 +13112,7 @@
     <row r="362">
       <c r="A362" s="34" t="inlineStr">
         <is>
-          <t>打伤警察</t>
+          <t>攻击警车</t>
         </is>
       </c>
       <c r="B362" s="34" t="inlineStr">
@@ -13136,7 +13136,7 @@
     <row r="363">
       <c r="A363" s="34" t="inlineStr">
         <is>
-          <t>击伤警察</t>
+          <t>攻击警犬</t>
         </is>
       </c>
       <c r="B363" s="34" t="inlineStr">
@@ -13160,7 +13160,7 @@
     <row r="364">
       <c r="A364" s="34" t="inlineStr">
         <is>
-          <t>警察重伤</t>
+          <t>殴打警察</t>
         </is>
       </c>
       <c r="B364" s="34" t="inlineStr">
@@ -13184,7 +13184,7 @@
     <row r="365">
       <c r="A365" s="34" t="inlineStr">
         <is>
-          <t>警察受伤</t>
+          <t>动手打警察</t>
         </is>
       </c>
       <c r="B365" s="34" t="inlineStr">
@@ -13208,7 +13208,7 @@
     <row r="366">
       <c r="A366" s="34" t="inlineStr">
         <is>
-          <t>枪伤警察</t>
+          <t>撞警车</t>
         </is>
       </c>
       <c r="B366" s="34" t="inlineStr">
@@ -13232,12 +13232,12 @@
     <row r="367">
       <c r="A367" s="34" t="inlineStr">
         <is>
-          <t>扰乱治安</t>
+          <t>枪击警察</t>
         </is>
       </c>
       <c r="B367" s="34" t="inlineStr">
         <is>
-          <t>扰乱治安罪</t>
+          <t>袭警罪</t>
         </is>
       </c>
       <c r="C367" s="34">
@@ -13256,12 +13256,12 @@
     <row r="368">
       <c r="A368" s="34" t="inlineStr">
         <is>
-          <t>挑衅</t>
+          <t>打了警察</t>
         </is>
       </c>
       <c r="B368" s="34" t="inlineStr">
         <is>
-          <t>扰乱治安罪</t>
+          <t>袭警罪</t>
         </is>
       </c>
       <c r="C368" s="34">
@@ -13280,12 +13280,12 @@
     <row r="369">
       <c r="A369" s="34" t="inlineStr">
         <is>
-          <t>寻衅</t>
+          <t>朝警察开枪</t>
         </is>
       </c>
       <c r="B369" s="34" t="inlineStr">
         <is>
-          <t>扰乱治安罪</t>
+          <t>袭警罪</t>
         </is>
       </c>
       <c r="C369" s="34">
@@ -13304,12 +13304,12 @@
     <row r="370">
       <c r="A370" s="34" t="inlineStr">
         <is>
-          <t>扰民</t>
+          <t>朝警察射击</t>
         </is>
       </c>
       <c r="B370" s="34" t="inlineStr">
         <is>
-          <t>扰乱治安罪</t>
+          <t>袭警罪</t>
         </is>
       </c>
       <c r="C370" s="34">
@@ -13328,12 +13328,12 @@
     <row r="371">
       <c r="A371" s="34" t="inlineStr">
         <is>
-          <t>冒犯性语言</t>
+          <t>向警察开枪</t>
         </is>
       </c>
       <c r="B371" s="34" t="inlineStr">
         <is>
-          <t>扰乱治安罪</t>
+          <t>袭警罪</t>
         </is>
       </c>
       <c r="C371" s="34">
@@ -13352,12 +13352,12 @@
     <row r="372">
       <c r="A372" s="34" t="inlineStr">
         <is>
-          <t>引起恐慌</t>
+          <t>向警察射击</t>
         </is>
       </c>
       <c r="B372" s="34" t="inlineStr">
         <is>
-          <t>扰乱治安罪</t>
+          <t>袭警罪</t>
         </is>
       </c>
       <c r="C372" s="34">
@@ -13376,12 +13376,12 @@
     <row r="373">
       <c r="A373" s="34" t="inlineStr">
         <is>
-          <t>公共场所吵闹</t>
+          <t>射击警察</t>
         </is>
       </c>
       <c r="B373" s="34" t="inlineStr">
         <is>
-          <t>扰乱治安罪</t>
+          <t>袭警罪</t>
         </is>
       </c>
       <c r="C373" s="34">
@@ -13400,12 +13400,12 @@
     <row r="374">
       <c r="A374" s="34" t="inlineStr">
         <is>
-          <t>闹事</t>
+          <t>打伤警察</t>
         </is>
       </c>
       <c r="B374" s="34" t="inlineStr">
         <is>
-          <t>扰乱治安罪</t>
+          <t>袭警罪</t>
         </is>
       </c>
       <c r="C374" s="34">
@@ -13424,12 +13424,12 @@
     <row r="375">
       <c r="A375" s="34" t="inlineStr">
         <is>
-          <t>大吵大闹</t>
+          <t>击伤警察</t>
         </is>
       </c>
       <c r="B375" s="34" t="inlineStr">
         <is>
-          <t>扰乱治安罪</t>
+          <t>袭警罪</t>
         </is>
       </c>
       <c r="C375" s="34">
@@ -13448,12 +13448,12 @@
     <row r="376">
       <c r="A376" s="34" t="inlineStr">
         <is>
-          <t>挑事</t>
+          <t>警察重伤</t>
         </is>
       </c>
       <c r="B376" s="34" t="inlineStr">
         <is>
-          <t>扰乱治安罪</t>
+          <t>袭警罪</t>
         </is>
       </c>
       <c r="C376" s="34">
@@ -13472,12 +13472,12 @@
     <row r="377">
       <c r="A377" s="34" t="inlineStr">
         <is>
-          <t>起哄</t>
+          <t>警察受伤</t>
         </is>
       </c>
       <c r="B377" s="34" t="inlineStr">
         <is>
-          <t>扰乱治安罪</t>
+          <t>袭警罪</t>
         </is>
       </c>
       <c r="C377" s="34">
@@ -13496,12 +13496,12 @@
     <row r="378">
       <c r="A378" s="34" t="inlineStr">
         <is>
-          <t>非法集会</t>
+          <t>枪伤警察</t>
         </is>
       </c>
       <c r="B378" s="34" t="inlineStr">
         <is>
-          <t>非法集会罪</t>
+          <t>袭警罪</t>
         </is>
       </c>
       <c r="C378" s="34">
@@ -13520,12 +13520,12 @@
     <row r="379">
       <c r="A379" s="34" t="inlineStr">
         <is>
-          <t>聚众</t>
+          <t>扰乱治安</t>
         </is>
       </c>
       <c r="B379" s="34" t="inlineStr">
         <is>
-          <t>非法集会罪</t>
+          <t>扰乱治安罪</t>
         </is>
       </c>
       <c r="C379" s="34">
@@ -13544,12 +13544,12 @@
     <row r="380">
       <c r="A380" s="34" t="inlineStr">
         <is>
-          <t>聚集骚乱</t>
+          <t>挑衅</t>
         </is>
       </c>
       <c r="B380" s="34" t="inlineStr">
         <is>
-          <t>非法集会罪</t>
+          <t>扰乱治安罪</t>
         </is>
       </c>
       <c r="C380" s="34">
@@ -13568,12 +13568,12 @@
     <row r="381">
       <c r="A381" s="34" t="inlineStr">
         <is>
-          <t>非法聚集</t>
+          <t>寻衅</t>
         </is>
       </c>
       <c r="B381" s="34" t="inlineStr">
         <is>
-          <t>非法集会罪</t>
+          <t>扰乱治安罪</t>
         </is>
       </c>
       <c r="C381" s="34">
@@ -13592,12 +13592,12 @@
     <row r="382">
       <c r="A382" s="34" t="inlineStr">
         <is>
-          <t>聚众闹事</t>
+          <t>扰民</t>
         </is>
       </c>
       <c r="B382" s="34" t="inlineStr">
         <is>
-          <t>非法集会罪</t>
+          <t>扰乱治安罪</t>
         </is>
       </c>
       <c r="C382" s="34">
@@ -13616,12 +13616,12 @@
     <row r="383">
       <c r="A383" s="34" t="inlineStr">
         <is>
-          <t>聚集斗殴</t>
+          <t>冒犯性语言</t>
         </is>
       </c>
       <c r="B383" s="34" t="inlineStr">
         <is>
-          <t>非法集会罪</t>
+          <t>扰乱治安罪</t>
         </is>
       </c>
       <c r="C383" s="34">
@@ -13640,12 +13640,12 @@
     <row r="384">
       <c r="A384" s="34" t="inlineStr">
         <is>
-          <t>聚众斗殴</t>
+          <t>引起恐慌</t>
         </is>
       </c>
       <c r="B384" s="34" t="inlineStr">
         <is>
-          <t>非法集会罪</t>
+          <t>扰乱治安罪</t>
         </is>
       </c>
       <c r="C384" s="34">
@@ -13664,12 +13664,12 @@
     <row r="385">
       <c r="A385" s="34" t="inlineStr">
         <is>
-          <t>煽动暴乱</t>
+          <t>公共场所吵闹</t>
         </is>
       </c>
       <c r="B385" s="34" t="inlineStr">
         <is>
-          <t>煽动暴乱罪</t>
+          <t>扰乱治安罪</t>
         </is>
       </c>
       <c r="C385" s="34">
@@ -13688,12 +13688,12 @@
     <row r="386">
       <c r="A386" s="34" t="inlineStr">
         <is>
-          <t>煽动暴力</t>
+          <t>闹事</t>
         </is>
       </c>
       <c r="B386" s="34" t="inlineStr">
         <is>
-          <t>煽动暴乱罪</t>
+          <t>扰乱治安罪</t>
         </is>
       </c>
       <c r="C386" s="34">
@@ -13712,12 +13712,12 @@
     <row r="387">
       <c r="A387" s="34" t="inlineStr">
         <is>
-          <t>鼓动暴乱</t>
+          <t>大吵大闹</t>
         </is>
       </c>
       <c r="B387" s="34" t="inlineStr">
         <is>
-          <t>煽动暴乱罪</t>
+          <t>扰乱治安罪</t>
         </is>
       </c>
       <c r="C387" s="34">
@@ -13736,12 +13736,12 @@
     <row r="388">
       <c r="A388" s="34" t="inlineStr">
         <is>
-          <t>鼓动暴力</t>
+          <t>挑事</t>
         </is>
       </c>
       <c r="B388" s="34" t="inlineStr">
         <is>
-          <t>煽动暴乱罪</t>
+          <t>扰乱治安罪</t>
         </is>
       </c>
       <c r="C388" s="34">
@@ -13760,12 +13760,12 @@
     <row r="389">
       <c r="A389" s="34" t="inlineStr">
         <is>
-          <t>带头闹事</t>
+          <t>起哄</t>
         </is>
       </c>
       <c r="B389" s="34" t="inlineStr">
         <is>
-          <t>煽动暴乱罪</t>
+          <t>扰乱治安罪</t>
         </is>
       </c>
       <c r="C389" s="34">
@@ -13784,12 +13784,12 @@
     <row r="390">
       <c r="A390" s="34" t="inlineStr">
         <is>
-          <t>煽动</t>
+          <t>非法集会</t>
         </is>
       </c>
       <c r="B390" s="34" t="inlineStr">
         <is>
-          <t>煽动暴乱罪</t>
+          <t>非法集会罪</t>
         </is>
       </c>
       <c r="C390" s="34">
@@ -13808,12 +13808,12 @@
     <row r="391">
       <c r="A391" s="34" t="inlineStr">
         <is>
-          <t>遮挡面部</t>
+          <t>聚众</t>
         </is>
       </c>
       <c r="B391" s="34" t="inlineStr">
         <is>
-          <t>遮挡面部罪</t>
+          <t>非法集会罪</t>
         </is>
       </c>
       <c r="C391" s="34">
@@ -13832,12 +13832,12 @@
     <row r="392">
       <c r="A392" s="34" t="inlineStr">
         <is>
-          <t>蒙面</t>
+          <t>聚集骚乱</t>
         </is>
       </c>
       <c r="B392" s="34" t="inlineStr">
         <is>
-          <t>遮挡面部罪</t>
+          <t>非法集会罪</t>
         </is>
       </c>
       <c r="C392" s="34">
@@ -13856,12 +13856,12 @@
     <row r="393">
       <c r="A393" s="34" t="inlineStr">
         <is>
-          <t>戴面具</t>
+          <t>非法聚集</t>
         </is>
       </c>
       <c r="B393" s="34" t="inlineStr">
         <is>
-          <t>遮挡面部罪</t>
+          <t>非法集会罪</t>
         </is>
       </c>
       <c r="C393" s="34">
@@ -13880,12 +13880,12 @@
     <row r="394">
       <c r="A394" s="34" t="inlineStr">
         <is>
-          <t>兜帽遮脸</t>
+          <t>聚众闹事</t>
         </is>
       </c>
       <c r="B394" s="34" t="inlineStr">
         <is>
-          <t>遮挡面部罪</t>
+          <t>非法集会罪</t>
         </is>
       </c>
       <c r="C394" s="34">
@@ -13904,12 +13904,12 @@
     <row r="395">
       <c r="A395" s="34" t="inlineStr">
         <is>
-          <t>拒绝揭开面罩</t>
+          <t>聚集斗殴</t>
         </is>
       </c>
       <c r="B395" s="34" t="inlineStr">
         <is>
-          <t>遮挡面部罪</t>
+          <t>非法集会罪</t>
         </is>
       </c>
       <c r="C395" s="34">
@@ -13928,12 +13928,12 @@
     <row r="396">
       <c r="A396" s="34" t="inlineStr">
         <is>
-          <t>蒙着脸</t>
+          <t>聚众斗殴</t>
         </is>
       </c>
       <c r="B396" s="34" t="inlineStr">
         <is>
-          <t>遮挡面部罪</t>
+          <t>非法集会罪</t>
         </is>
       </c>
       <c r="C396" s="34">
@@ -13952,12 +13952,12 @@
     <row r="397">
       <c r="A397" s="34" t="inlineStr">
         <is>
-          <t>戴头套</t>
+          <t>煽动暴乱</t>
         </is>
       </c>
       <c r="B397" s="34" t="inlineStr">
         <is>
-          <t>遮挡面部罪</t>
+          <t>煽动暴乱罪</t>
         </is>
       </c>
       <c r="C397" s="34">
@@ -13976,12 +13976,12 @@
     <row r="398">
       <c r="A398" s="34" t="inlineStr">
         <is>
-          <t>非法持有热武器</t>
+          <t>煽动暴力</t>
         </is>
       </c>
       <c r="B398" s="34" t="inlineStr">
         <is>
-          <t>非法持有热武器罪</t>
+          <t>煽动暴乱罪</t>
         </is>
       </c>
       <c r="C398" s="34">
@@ -14000,12 +14000,12 @@
     <row r="399">
       <c r="A399" s="34" t="inlineStr">
         <is>
-          <t>无证持枪</t>
+          <t>鼓动暴乱</t>
         </is>
       </c>
       <c r="B399" s="34" t="inlineStr">
         <is>
-          <t>非法持有热武器罪</t>
+          <t>煽动暴乱罪</t>
         </is>
       </c>
       <c r="C399" s="34">
@@ -14024,12 +14024,12 @@
     <row r="400">
       <c r="A400" s="34" t="inlineStr">
         <is>
-          <t>非法持枪</t>
+          <t>鼓动暴力</t>
         </is>
       </c>
       <c r="B400" s="34" t="inlineStr">
         <is>
-          <t>非法持有热武器罪</t>
+          <t>煽动暴乱罪</t>
         </is>
       </c>
       <c r="C400" s="34">
@@ -14048,12 +14048,12 @@
     <row r="401">
       <c r="A401" s="34" t="inlineStr">
         <is>
-          <t>持有非法武器</t>
+          <t>带头闹事</t>
         </is>
       </c>
       <c r="B401" s="34" t="inlineStr">
         <is>
-          <t>非法持有热武器罪</t>
+          <t>煽动暴乱罪</t>
         </is>
       </c>
       <c r="C401" s="34">
@@ -14072,12 +14072,12 @@
     <row r="402">
       <c r="A402" s="34" t="inlineStr">
         <is>
-          <t>无序列号枪支</t>
+          <t>煽动</t>
         </is>
       </c>
       <c r="B402" s="34" t="inlineStr">
         <is>
-          <t>非法持有热武器罪</t>
+          <t>煽动暴乱罪</t>
         </is>
       </c>
       <c r="C402" s="34">
@@ -14096,12 +14096,12 @@
     <row r="403">
       <c r="A403" s="34" t="inlineStr">
         <is>
-          <t>全自动枪支</t>
+          <t>遮挡面部</t>
         </is>
       </c>
       <c r="B403" s="34" t="inlineStr">
         <is>
-          <t>非法持有热武器罪</t>
+          <t>遮挡面部罪</t>
         </is>
       </c>
       <c r="C403" s="34">
@@ -14120,12 +14120,12 @@
     <row r="404">
       <c r="A404" s="34" t="inlineStr">
         <is>
-          <t>私藏枪支</t>
+          <t>蒙面</t>
         </is>
       </c>
       <c r="B404" s="34" t="inlineStr">
         <is>
-          <t>非法持有热武器罪</t>
+          <t>遮挡面部罪</t>
         </is>
       </c>
       <c r="C404" s="34">
@@ -14144,12 +14144,12 @@
     <row r="405">
       <c r="A405" s="34" t="inlineStr">
         <is>
-          <t>持有爆炸物</t>
+          <t>戴面具</t>
         </is>
       </c>
       <c r="B405" s="34" t="inlineStr">
         <is>
-          <t>非法持有热武器罪</t>
+          <t>遮挡面部罪</t>
         </is>
       </c>
       <c r="C405" s="34">
@@ -14168,12 +14168,12 @@
     <row r="406">
       <c r="A406" s="34" t="inlineStr">
         <is>
-          <t>身上有枪</t>
+          <t>兜帽遮脸</t>
         </is>
       </c>
       <c r="B406" s="34" t="inlineStr">
         <is>
-          <t>非法持有热武器罪</t>
+          <t>遮挡面部罪</t>
         </is>
       </c>
       <c r="C406" s="34">
@@ -14192,12 +14192,12 @@
     <row r="407">
       <c r="A407" s="34" t="inlineStr">
         <is>
-          <t>携带枪支</t>
+          <t>拒绝揭开面罩</t>
         </is>
       </c>
       <c r="B407" s="34" t="inlineStr">
         <is>
-          <t>非法持有热武器罪</t>
+          <t>遮挡面部罪</t>
         </is>
       </c>
       <c r="C407" s="34">
@@ -14216,12 +14216,12 @@
     <row r="408">
       <c r="A408" s="34" t="inlineStr">
         <is>
-          <t>藏枪</t>
+          <t>蒙着脸</t>
         </is>
       </c>
       <c r="B408" s="34" t="inlineStr">
         <is>
-          <t>非法持有热武器罪</t>
+          <t>遮挡面部罪</t>
         </is>
       </c>
       <c r="C408" s="34">
@@ -14240,12 +14240,12 @@
     <row r="409">
       <c r="A409" s="34" t="inlineStr">
         <is>
-          <t>非法展示热武器</t>
+          <t>戴头套</t>
         </is>
       </c>
       <c r="B409" s="34" t="inlineStr">
         <is>
-          <t>非法展示热武器罪</t>
+          <t>遮挡面部罪</t>
         </is>
       </c>
       <c r="C409" s="34">
@@ -14264,12 +14264,12 @@
     <row r="410">
       <c r="A410" s="34" t="inlineStr">
         <is>
-          <t>公开持枪</t>
+          <t>非法持有热武器</t>
         </is>
       </c>
       <c r="B410" s="34" t="inlineStr">
         <is>
-          <t>非法展示热武器罪</t>
+          <t>非法持有热武器罪</t>
         </is>
       </c>
       <c r="C410" s="34">
@@ -14288,12 +14288,12 @@
     <row r="411">
       <c r="A411" s="34" t="inlineStr">
         <is>
-          <t>挥舞武器</t>
+          <t>无证持枪</t>
         </is>
       </c>
       <c r="B411" s="34" t="inlineStr">
         <is>
-          <t>非法展示热武器罪</t>
+          <t>非法持有热武器罪</t>
         </is>
       </c>
       <c r="C411" s="34">
@@ -14312,12 +14312,12 @@
     <row r="412">
       <c r="A412" s="34" t="inlineStr">
         <is>
-          <t>亮枪</t>
+          <t>非法持枪</t>
         </is>
       </c>
       <c r="B412" s="34" t="inlineStr">
         <is>
-          <t>非法展示热武器罪</t>
+          <t>非法持有热武器罪</t>
         </is>
       </c>
       <c r="C412" s="34">
@@ -14336,12 +14336,12 @@
     <row r="413">
       <c r="A413" s="34" t="inlineStr">
         <is>
-          <t>展示武器</t>
+          <t>持有非法武器</t>
         </is>
       </c>
       <c r="B413" s="34" t="inlineStr">
         <is>
-          <t>非法展示热武器罪</t>
+          <t>非法持有热武器罪</t>
         </is>
       </c>
       <c r="C413" s="34">
@@ -14360,12 +14360,12 @@
     <row r="414">
       <c r="A414" s="34" t="inlineStr">
         <is>
-          <t>公开携带枪支</t>
+          <t>无序列号枪支</t>
         </is>
       </c>
       <c r="B414" s="34" t="inlineStr">
         <is>
-          <t>非法展示热武器罪</t>
+          <t>非法持有热武器罪</t>
         </is>
       </c>
       <c r="C414" s="34">
@@ -14384,12 +14384,12 @@
     <row r="415">
       <c r="A415" s="34" t="inlineStr">
         <is>
-          <t>掏枪威胁</t>
+          <t>全自动枪支</t>
         </is>
       </c>
       <c r="B415" s="34" t="inlineStr">
         <is>
-          <t>非法展示热武器罪</t>
+          <t>非法持有热武器罪</t>
         </is>
       </c>
       <c r="C415" s="34">
@@ -14408,12 +14408,12 @@
     <row r="416">
       <c r="A416" s="34" t="inlineStr">
         <is>
-          <t>拔枪</t>
+          <t>私藏枪支</t>
         </is>
       </c>
       <c r="B416" s="34" t="inlineStr">
         <is>
-          <t>非法展示热武器罪</t>
+          <t>非法持有热武器罪</t>
         </is>
       </c>
       <c r="C416" s="34">
@@ -14432,12 +14432,12 @@
     <row r="417">
       <c r="A417" s="34" t="inlineStr">
         <is>
-          <t>亮出枪</t>
+          <t>持有爆炸物</t>
         </is>
       </c>
       <c r="B417" s="34" t="inlineStr">
         <is>
-          <t>非法展示热武器罪</t>
+          <t>非法持有热武器罪</t>
         </is>
       </c>
       <c r="C417" s="34">
@@ -14456,12 +14456,12 @@
     <row r="418">
       <c r="A418" s="34" t="inlineStr">
         <is>
-          <t>举枪</t>
+          <t>身上有枪</t>
         </is>
       </c>
       <c r="B418" s="34" t="inlineStr">
         <is>
-          <t>非法展示热武器罪</t>
+          <t>非法持有热武器罪</t>
         </is>
       </c>
       <c r="C418" s="34">
@@ -14480,12 +14480,12 @@
     <row r="419">
       <c r="A419" s="34" t="inlineStr">
         <is>
-          <t>非法使用热武器</t>
+          <t>携带枪支</t>
         </is>
       </c>
       <c r="B419" s="34" t="inlineStr">
         <is>
-          <t>非法使用热武器罪</t>
+          <t>非法持有热武器罪</t>
         </is>
       </c>
       <c r="C419" s="34">
@@ -14504,12 +14504,12 @@
     <row r="420">
       <c r="A420" s="34" t="inlineStr">
         <is>
-          <t>鲁莽开枪</t>
+          <t>藏枪</t>
         </is>
       </c>
       <c r="B420" s="34" t="inlineStr">
         <is>
-          <t>非法使用热武器罪</t>
+          <t>非法持有热武器罪</t>
         </is>
       </c>
       <c r="C420" s="34">
@@ -14528,12 +14528,12 @@
     <row r="421">
       <c r="A421" s="34" t="inlineStr">
         <is>
-          <t>乱开枪</t>
+          <t>非法展示热武器</t>
         </is>
       </c>
       <c r="B421" s="34" t="inlineStr">
         <is>
-          <t>非法使用热武器罪</t>
+          <t>非法展示热武器罪</t>
         </is>
       </c>
       <c r="C421" s="34">
@@ -14552,12 +14552,12 @@
     <row r="422">
       <c r="A422" s="34" t="inlineStr">
         <is>
-          <t>违规射击</t>
+          <t>公开持枪</t>
         </is>
       </c>
       <c r="B422" s="34" t="inlineStr">
         <is>
-          <t>非法使用热武器罪</t>
+          <t>非法展示热武器罪</t>
         </is>
       </c>
       <c r="C422" s="34">
@@ -14576,12 +14576,12 @@
     <row r="423">
       <c r="A423" s="34" t="inlineStr">
         <is>
-          <t>开枪</t>
+          <t>挥舞武器</t>
         </is>
       </c>
       <c r="B423" s="34" t="inlineStr">
         <is>
-          <t>非法使用热武器罪</t>
+          <t>非法展示热武器罪</t>
         </is>
       </c>
       <c r="C423" s="34">
@@ -14600,12 +14600,12 @@
     <row r="424">
       <c r="A424" s="34" t="inlineStr">
         <is>
-          <t>朝天开枪</t>
+          <t>亮枪</t>
         </is>
       </c>
       <c r="B424" s="34" t="inlineStr">
         <is>
-          <t>非法使用热武器罪</t>
+          <t>非法展示热武器罪</t>
         </is>
       </c>
       <c r="C424" s="34">
@@ -14624,12 +14624,12 @@
     <row r="425">
       <c r="A425" s="34" t="inlineStr">
         <is>
-          <t>随意射击</t>
+          <t>展示武器</t>
         </is>
       </c>
       <c r="B425" s="34" t="inlineStr">
         <is>
-          <t>非法使用热武器罪</t>
+          <t>非法展示热武器罪</t>
         </is>
       </c>
       <c r="C425" s="34">
@@ -14648,12 +14648,12 @@
     <row r="426">
       <c r="A426" s="34" t="inlineStr">
         <is>
-          <t>开了一枪</t>
+          <t>公开携带枪支</t>
         </is>
       </c>
       <c r="B426" s="34" t="inlineStr">
         <is>
-          <t>非法使用热武器罪</t>
+          <t>非法展示热武器罪</t>
         </is>
       </c>
       <c r="C426" s="34">
@@ -14672,12 +14672,12 @@
     <row r="427">
       <c r="A427" s="34" t="inlineStr">
         <is>
-          <t>射击</t>
+          <t>掏枪威胁</t>
         </is>
       </c>
       <c r="B427" s="34" t="inlineStr">
         <is>
-          <t>非法使用热武器罪</t>
+          <t>非法展示热武器罪</t>
         </is>
       </c>
       <c r="C427" s="34">
@@ -14696,12 +14696,12 @@
     <row r="428">
       <c r="A428" s="34" t="inlineStr">
         <is>
-          <t>扫射</t>
+          <t>拔枪</t>
         </is>
       </c>
       <c r="B428" s="34" t="inlineStr">
         <is>
-          <t>非法使用热武器罪</t>
+          <t>非法展示热武器罪</t>
         </is>
       </c>
       <c r="C428" s="34">
@@ -14720,12 +14720,12 @@
     <row r="429">
       <c r="A429" s="34" t="inlineStr">
         <is>
-          <t>鸣枪</t>
+          <t>亮出枪</t>
         </is>
       </c>
       <c r="B429" s="34" t="inlineStr">
         <is>
-          <t>非法使用热武器罪</t>
+          <t>非法展示热武器罪</t>
         </is>
       </c>
       <c r="C429" s="34">
@@ -14744,12 +14744,12 @@
     <row r="430">
       <c r="A430" s="34" t="inlineStr">
         <is>
-          <t>对空鸣枪</t>
+          <t>举枪</t>
         </is>
       </c>
       <c r="B430" s="34" t="inlineStr">
         <is>
-          <t>非法使用热武器罪</t>
+          <t>非法展示热武器罪</t>
         </is>
       </c>
       <c r="C430" s="34">
@@ -14768,12 +14768,12 @@
     <row r="431">
       <c r="A431" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖武器</t>
+          <t>非法使用热武器</t>
         </is>
       </c>
       <c r="B431" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖武器罪</t>
+          <t>非法使用热武器罪</t>
         </is>
       </c>
       <c r="C431" s="34">
@@ -14792,12 +14792,12 @@
     <row r="432">
       <c r="A432" s="34" t="inlineStr">
         <is>
-          <t>卖枪</t>
+          <t>鲁莽开枪</t>
         </is>
       </c>
       <c r="B432" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖武器罪</t>
+          <t>非法使用热武器罪</t>
         </is>
       </c>
       <c r="C432" s="34">
@@ -14816,12 +14816,12 @@
     <row r="433">
       <c r="A433" s="34" t="inlineStr">
         <is>
-          <t>贩卖武器</t>
+          <t>乱开枪</t>
         </is>
       </c>
       <c r="B433" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖武器罪</t>
+          <t>非法使用热武器罪</t>
         </is>
       </c>
       <c r="C433" s="34">
@@ -14840,12 +14840,12 @@
     <row r="434">
       <c r="A434" s="34" t="inlineStr">
         <is>
-          <t>出售武器</t>
+          <t>违规射击</t>
         </is>
       </c>
       <c r="B434" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖武器罪</t>
+          <t>非法使用热武器罪</t>
         </is>
       </c>
       <c r="C434" s="34">
@@ -14864,12 +14864,12 @@
     <row r="435">
       <c r="A435" s="34" t="inlineStr">
         <is>
-          <t>转让武器</t>
+          <t>开枪</t>
         </is>
       </c>
       <c r="B435" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖武器罪</t>
+          <t>非法使用热武器罪</t>
         </is>
       </c>
       <c r="C435" s="34">
@@ -14888,12 +14888,12 @@
     <row r="436">
       <c r="A436" s="34" t="inlineStr">
         <is>
-          <t>倒卖枪支</t>
+          <t>朝天开枪</t>
         </is>
       </c>
       <c r="B436" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖武器罪</t>
+          <t>非法使用热武器罪</t>
         </is>
       </c>
       <c r="C436" s="34">
@@ -14912,12 +14912,12 @@
     <row r="437">
       <c r="A437" s="34" t="inlineStr">
         <is>
-          <t>军火买卖</t>
+          <t>随意射击</t>
         </is>
       </c>
       <c r="B437" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖武器罪</t>
+          <t>非法使用热武器罪</t>
         </is>
       </c>
       <c r="C437" s="34">
@@ -14936,12 +14936,12 @@
     <row r="438">
       <c r="A438" s="34" t="inlineStr">
         <is>
-          <t>走私</t>
+          <t>开了一枪</t>
         </is>
       </c>
       <c r="B438" s="34" t="inlineStr">
         <is>
-          <t>走私罪</t>
+          <t>非法使用热武器罪</t>
         </is>
       </c>
       <c r="C438" s="34">
@@ -14960,12 +14960,12 @@
     <row r="439">
       <c r="A439" s="34" t="inlineStr">
         <is>
-          <t>军火走私</t>
+          <t>射击</t>
         </is>
       </c>
       <c r="B439" s="34" t="inlineStr">
         <is>
-          <t>走私罪</t>
+          <t>非法使用热武器罪</t>
         </is>
       </c>
       <c r="C439" s="34">
@@ -14984,12 +14984,12 @@
     <row r="440">
       <c r="A440" s="34" t="inlineStr">
         <is>
-          <t>走私武器</t>
+          <t>扫射</t>
         </is>
       </c>
       <c r="B440" s="34" t="inlineStr">
         <is>
-          <t>走私罪</t>
+          <t>非法使用热武器罪</t>
         </is>
       </c>
       <c r="C440" s="34">
@@ -15008,12 +15008,12 @@
     <row r="441">
       <c r="A441" s="34" t="inlineStr">
         <is>
-          <t>走私爆炸物</t>
+          <t>鸣枪</t>
         </is>
       </c>
       <c r="B441" s="34" t="inlineStr">
         <is>
-          <t>走私罪</t>
+          <t>非法使用热武器罪</t>
         </is>
       </c>
       <c r="C441" s="34">
@@ -15032,12 +15032,12 @@
     <row r="442">
       <c r="A442" s="34" t="inlineStr">
         <is>
-          <t>走私军火</t>
+          <t>对空鸣枪</t>
         </is>
       </c>
       <c r="B442" s="34" t="inlineStr">
         <is>
-          <t>走私罪</t>
+          <t>非法使用热武器罪</t>
         </is>
       </c>
       <c r="C442" s="34">
@@ -15056,12 +15056,12 @@
     <row r="443">
       <c r="A443" s="34" t="inlineStr">
         <is>
-          <t>偷运军火</t>
+          <t>非法贩卖武器</t>
         </is>
       </c>
       <c r="B443" s="34" t="inlineStr">
         <is>
-          <t>走私罪</t>
+          <t>非法贩卖武器罪</t>
         </is>
       </c>
       <c r="C443" s="34">
@@ -15080,12 +15080,12 @@
     <row r="444">
       <c r="A444" s="34" t="inlineStr">
         <is>
-          <t>非法持有管制物品</t>
+          <t>卖枪</t>
         </is>
       </c>
       <c r="B444" s="34" t="inlineStr">
         <is>
-          <t>非法持有管制物品罪</t>
+          <t>非法贩卖武器罪</t>
         </is>
       </c>
       <c r="C444" s="34">
@@ -15104,12 +15104,12 @@
     <row r="445">
       <c r="A445" s="34" t="inlineStr">
         <is>
-          <t>持有毒品</t>
+          <t>贩卖武器</t>
         </is>
       </c>
       <c r="B445" s="34" t="inlineStr">
         <is>
-          <t>非法持有管制物品罪</t>
+          <t>非法贩卖武器罪</t>
         </is>
       </c>
       <c r="C445" s="34">
@@ -15128,12 +15128,12 @@
     <row r="446">
       <c r="A446" s="34" t="inlineStr">
         <is>
-          <t>持有大麻</t>
+          <t>出售武器</t>
         </is>
       </c>
       <c r="B446" s="34" t="inlineStr">
         <is>
-          <t>非法持有管制物品罪</t>
+          <t>非法贩卖武器罪</t>
         </is>
       </c>
       <c r="C446" s="34">
@@ -15152,12 +15152,12 @@
     <row r="447">
       <c r="A447" s="34" t="inlineStr">
         <is>
-          <t>持有可卡因</t>
+          <t>转让武器</t>
         </is>
       </c>
       <c r="B447" s="34" t="inlineStr">
         <is>
-          <t>非法持有管制物品罪</t>
+          <t>非法贩卖武器罪</t>
         </is>
       </c>
       <c r="C447" s="34">
@@ -15176,12 +15176,12 @@
     <row r="448">
       <c r="A448" s="34" t="inlineStr">
         <is>
-          <t>持有海洛因</t>
+          <t>倒卖枪支</t>
         </is>
       </c>
       <c r="B448" s="34" t="inlineStr">
         <is>
-          <t>非法持有管制物品罪</t>
+          <t>非法贩卖武器罪</t>
         </is>
       </c>
       <c r="C448" s="34">
@@ -15200,12 +15200,12 @@
     <row r="449">
       <c r="A449" s="34" t="inlineStr">
         <is>
-          <t>持有冰毒</t>
+          <t>军火买卖</t>
         </is>
       </c>
       <c r="B449" s="34" t="inlineStr">
         <is>
-          <t>非法持有管制物品罪</t>
+          <t>非法贩卖武器罪</t>
         </is>
       </c>
       <c r="C449" s="34">
@@ -15224,12 +15224,12 @@
     <row r="450">
       <c r="A450" s="34" t="inlineStr">
         <is>
-          <t>持有管制刀具</t>
+          <t>走私</t>
         </is>
       </c>
       <c r="B450" s="34" t="inlineStr">
         <is>
-          <t>非法持有管制物品罪</t>
+          <t>走私罪</t>
         </is>
       </c>
       <c r="C450" s="34">
@@ -15248,12 +15248,12 @@
     <row r="451">
       <c r="A451" s="34" t="inlineStr">
         <is>
-          <t>管制器具</t>
+          <t>军火走私</t>
         </is>
       </c>
       <c r="B451" s="34" t="inlineStr">
         <is>
-          <t>非法持有管制物品罪</t>
+          <t>走私罪</t>
         </is>
       </c>
       <c r="C451" s="34">
@@ -15272,12 +15272,12 @@
     <row r="452">
       <c r="A452" s="34" t="inlineStr">
         <is>
-          <t>指虎</t>
+          <t>走私武器</t>
         </is>
       </c>
       <c r="B452" s="34" t="inlineStr">
         <is>
-          <t>非法持有管制物品罪</t>
+          <t>走私罪</t>
         </is>
       </c>
       <c r="C452" s="34">
@@ -15296,12 +15296,12 @@
     <row r="453">
       <c r="A453" s="34" t="inlineStr">
         <is>
-          <t>弹簧刀</t>
+          <t>走私爆炸物</t>
         </is>
       </c>
       <c r="B453" s="34" t="inlineStr">
         <is>
-          <t>非法持有管制物品罪</t>
+          <t>走私罪</t>
         </is>
       </c>
       <c r="C453" s="34">
@@ -15320,12 +15320,12 @@
     <row r="454">
       <c r="A454" s="34" t="inlineStr">
         <is>
-          <t>开锁器</t>
+          <t>走私军火</t>
         </is>
       </c>
       <c r="B454" s="34" t="inlineStr">
         <is>
-          <t>非法持有管制物品罪</t>
+          <t>走私罪</t>
         </is>
       </c>
       <c r="C454" s="34">
@@ -15344,12 +15344,12 @@
     <row r="455">
       <c r="A455" s="34" t="inlineStr">
         <is>
-          <t>黑客电脑</t>
+          <t>偷运军火</t>
         </is>
       </c>
       <c r="B455" s="34" t="inlineStr">
         <is>
-          <t>非法持有管制物品罪</t>
+          <t>走私罪</t>
         </is>
       </c>
       <c r="C455" s="34">
@@ -15368,7 +15368,7 @@
     <row r="456">
       <c r="A456" s="34" t="inlineStr">
         <is>
-          <t>身上有毒品</t>
+          <t>非法持有管制物品</t>
         </is>
       </c>
       <c r="B456" s="34" t="inlineStr">
@@ -15392,7 +15392,7 @@
     <row r="457">
       <c r="A457" s="34" t="inlineStr">
         <is>
-          <t>带着毒品</t>
+          <t>持有毒品</t>
         </is>
       </c>
       <c r="B457" s="34" t="inlineStr">
@@ -15416,7 +15416,7 @@
     <row r="458">
       <c r="A458" s="34" t="inlineStr">
         <is>
-          <t>藏毒</t>
+          <t>持有大麻</t>
         </is>
       </c>
       <c r="B458" s="34" t="inlineStr">
@@ -15440,12 +15440,12 @@
     <row r="459">
       <c r="A459" s="34" t="inlineStr">
         <is>
-          <t>大量管制物品</t>
+          <t>持有可卡因</t>
         </is>
       </c>
       <c r="B459" s="34" t="inlineStr">
         <is>
-          <t>非法持有大量管制物品罪</t>
+          <t>非法持有管制物品罪</t>
         </is>
       </c>
       <c r="C459" s="34">
@@ -15464,12 +15464,12 @@
     <row r="460">
       <c r="A460" s="34" t="inlineStr">
         <is>
-          <t>大量毒品</t>
+          <t>持有海洛因</t>
         </is>
       </c>
       <c r="B460" s="34" t="inlineStr">
         <is>
-          <t>非法持有大量管制物品罪</t>
+          <t>非法持有管制物品罪</t>
         </is>
       </c>
       <c r="C460" s="34">
@@ -15488,12 +15488,12 @@
     <row r="461">
       <c r="A461" s="34" t="inlineStr">
         <is>
-          <t>分装毒品</t>
+          <t>持有冰毒</t>
         </is>
       </c>
       <c r="B461" s="34" t="inlineStr">
         <is>
-          <t>非法持有大量管制物品罪</t>
+          <t>非法持有管制物品罪</t>
         </is>
       </c>
       <c r="C461" s="34">
@@ -15512,12 +15512,12 @@
     <row r="462">
       <c r="A462" s="34" t="inlineStr">
         <is>
-          <t>成批毒品</t>
+          <t>持有管制刀具</t>
         </is>
       </c>
       <c r="B462" s="34" t="inlineStr">
         <is>
-          <t>非法持有大量管制物品罪</t>
+          <t>非法持有管制物品罪</t>
         </is>
       </c>
       <c r="C462" s="34">
@@ -15536,12 +15536,12 @@
     <row r="463">
       <c r="A463" s="34" t="inlineStr">
         <is>
-          <t>整箱毒品</t>
+          <t>管制器具</t>
         </is>
       </c>
       <c r="B463" s="34" t="inlineStr">
         <is>
-          <t>非法持有大量管制物品罪</t>
+          <t>非法持有管制物品罪</t>
         </is>
       </c>
       <c r="C463" s="34">
@@ -15560,12 +15560,12 @@
     <row r="464">
       <c r="A464" s="34" t="inlineStr">
         <is>
-          <t>一堆毒品</t>
+          <t>指虎</t>
         </is>
       </c>
       <c r="B464" s="34" t="inlineStr">
         <is>
-          <t>非法持有大量管制物品罪</t>
+          <t>非法持有管制物品罪</t>
         </is>
       </c>
       <c r="C464" s="34">
@@ -15584,12 +15584,12 @@
     <row r="465">
       <c r="A465" s="34" t="inlineStr">
         <is>
-          <t>大批毒品</t>
+          <t>弹簧刀</t>
         </is>
       </c>
       <c r="B465" s="34" t="inlineStr">
         <is>
-          <t>非法持有大量管制物品罪</t>
+          <t>非法持有管制物品罪</t>
         </is>
       </c>
       <c r="C465" s="34">
@@ -15608,12 +15608,12 @@
     <row r="466">
       <c r="A466" s="34" t="inlineStr">
         <is>
-          <t>经营管制物品</t>
+          <t>开锁器</t>
         </is>
       </c>
       <c r="B466" s="34" t="inlineStr">
         <is>
-          <t>非法经营和分发管制物品罪</t>
+          <t>非法持有管制物品罪</t>
         </is>
       </c>
       <c r="C466" s="34">
@@ -15632,12 +15632,12 @@
     <row r="467">
       <c r="A467" s="34" t="inlineStr">
         <is>
-          <t>分发毒品</t>
+          <t>黑客电脑</t>
         </is>
       </c>
       <c r="B467" s="34" t="inlineStr">
         <is>
-          <t>非法经营和分发管制物品罪</t>
+          <t>非法持有管制物品罪</t>
         </is>
       </c>
       <c r="C467" s="34">
@@ -15656,12 +15656,12 @@
     <row r="468">
       <c r="A468" s="34" t="inlineStr">
         <is>
-          <t>贩毒据点</t>
+          <t>身上有毒品</t>
         </is>
       </c>
       <c r="B468" s="34" t="inlineStr">
         <is>
-          <t>非法经营和分发管制物品罪</t>
+          <t>非法持有管制物品罪</t>
         </is>
       </c>
       <c r="C468" s="34">
@@ -15680,12 +15680,12 @@
     <row r="469">
       <c r="A469" s="34" t="inlineStr">
         <is>
-          <t>毒品窝点</t>
+          <t>带着毒品</t>
         </is>
       </c>
       <c r="B469" s="34" t="inlineStr">
         <is>
-          <t>非法经营和分发管制物品罪</t>
+          <t>非法持有管制物品罪</t>
         </is>
       </c>
       <c r="C469" s="34">
@@ -15704,12 +15704,12 @@
     <row r="470">
       <c r="A470" s="34" t="inlineStr">
         <is>
-          <t>开设毒品区域</t>
+          <t>藏毒</t>
         </is>
       </c>
       <c r="B470" s="34" t="inlineStr">
         <is>
-          <t>非法经营和分发管制物品罪</t>
+          <t>非法持有管制物品罪</t>
         </is>
       </c>
       <c r="C470" s="34">
@@ -15728,12 +15728,12 @@
     <row r="471">
       <c r="A471" s="34" t="inlineStr">
         <is>
-          <t>卖毒品的店</t>
+          <t>大量管制物品</t>
         </is>
       </c>
       <c r="B471" s="34" t="inlineStr">
         <is>
-          <t>非法经营和分发管制物品罪</t>
+          <t>非法持有大量管制物品罪</t>
         </is>
       </c>
       <c r="C471" s="34">
@@ -15752,12 +15752,12 @@
     <row r="472">
       <c r="A472" s="34" t="inlineStr">
         <is>
-          <t>制造管制物品</t>
+          <t>大量毒品</t>
         </is>
       </c>
       <c r="B472" s="34" t="inlineStr">
         <is>
-          <t>非法制造管制物品罪</t>
+          <t>非法持有大量管制物品罪</t>
         </is>
       </c>
       <c r="C472" s="34">
@@ -15776,12 +15776,12 @@
     <row r="473">
       <c r="A473" s="34" t="inlineStr">
         <is>
-          <t>制毒</t>
+          <t>分装毒品</t>
         </is>
       </c>
       <c r="B473" s="34" t="inlineStr">
         <is>
-          <t>非法制造管制物品罪</t>
+          <t>非法持有大量管制物品罪</t>
         </is>
       </c>
       <c r="C473" s="34">
@@ -15800,12 +15800,12 @@
     <row r="474">
       <c r="A474" s="34" t="inlineStr">
         <is>
-          <t>生产毒品</t>
+          <t>成批毒品</t>
         </is>
       </c>
       <c r="B474" s="34" t="inlineStr">
         <is>
-          <t>非法制造管制物品罪</t>
+          <t>非法持有大量管制物品罪</t>
         </is>
       </c>
       <c r="C474" s="34">
@@ -15824,12 +15824,12 @@
     <row r="475">
       <c r="A475" s="34" t="inlineStr">
         <is>
-          <t>种植大麻</t>
+          <t>整箱毒品</t>
         </is>
       </c>
       <c r="B475" s="34" t="inlineStr">
         <is>
-          <t>非法制造管制物品罪</t>
+          <t>非法持有大量管制物品罪</t>
         </is>
       </c>
       <c r="C475" s="34">
@@ -15848,12 +15848,12 @@
     <row r="476">
       <c r="A476" s="34" t="inlineStr">
         <is>
-          <t>制造毒品</t>
+          <t>一堆毒品</t>
         </is>
       </c>
       <c r="B476" s="34" t="inlineStr">
         <is>
-          <t>非法制造管制物品罪</t>
+          <t>非法持有大量管制物品罪</t>
         </is>
       </c>
       <c r="C476" s="34">
@@ -15872,12 +15872,12 @@
     <row r="477">
       <c r="A477" s="34" t="inlineStr">
         <is>
-          <t>种大麻</t>
+          <t>大批毒品</t>
         </is>
       </c>
       <c r="B477" s="34" t="inlineStr">
         <is>
-          <t>非法制造管制物品罪</t>
+          <t>非法持有大量管制物品罪</t>
         </is>
       </c>
       <c r="C477" s="34">
@@ -15896,12 +15896,12 @@
     <row r="478">
       <c r="A478" s="34" t="inlineStr">
         <is>
-          <t>煮毒</t>
+          <t>经营管制物品</t>
         </is>
       </c>
       <c r="B478" s="34" t="inlineStr">
         <is>
-          <t>非法制造管制物品罪</t>
+          <t>非法经营和分发管制物品罪</t>
         </is>
       </c>
       <c r="C478" s="34">
@@ -15920,12 +15920,12 @@
     <row r="479">
       <c r="A479" s="34" t="inlineStr">
         <is>
-          <t>贩卖管制物品</t>
+          <t>分发毒品</t>
         </is>
       </c>
       <c r="B479" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖管制物品罪</t>
+          <t>非法经营和分发管制物品罪</t>
         </is>
       </c>
       <c r="C479" s="34">
@@ -15944,12 +15944,12 @@
     <row r="480">
       <c r="A480" s="34" t="inlineStr">
         <is>
-          <t>贩毒</t>
+          <t>贩毒据点</t>
         </is>
       </c>
       <c r="B480" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖管制物品罪</t>
+          <t>非法经营和分发管制物品罪</t>
         </is>
       </c>
       <c r="C480" s="34">
@@ -15968,12 +15968,12 @@
     <row r="481">
       <c r="A481" s="34" t="inlineStr">
         <is>
-          <t>卖毒品</t>
+          <t>毒品窝点</t>
         </is>
       </c>
       <c r="B481" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖管制物品罪</t>
+          <t>非法经营和分发管制物品罪</t>
         </is>
       </c>
       <c r="C481" s="34">
@@ -15992,12 +15992,12 @@
     <row r="482">
       <c r="A482" s="34" t="inlineStr">
         <is>
-          <t>运输毒品</t>
+          <t>开设毒品区域</t>
         </is>
       </c>
       <c r="B482" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖管制物品罪</t>
+          <t>非法经营和分发管制物品罪</t>
         </is>
       </c>
       <c r="C482" s="34">
@@ -16016,12 +16016,12 @@
     <row r="483">
       <c r="A483" s="34" t="inlineStr">
         <is>
-          <t>贩卖毒品</t>
+          <t>卖毒品的店</t>
         </is>
       </c>
       <c r="B483" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖管制物品罪</t>
+          <t>非法经营和分发管制物品罪</t>
         </is>
       </c>
       <c r="C483" s="34">
@@ -16040,12 +16040,12 @@
     <row r="484">
       <c r="A484" s="34" t="inlineStr">
         <is>
-          <t>运毒</t>
+          <t>制造管制物品</t>
         </is>
       </c>
       <c r="B484" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖管制物品罪</t>
+          <t>非法制造管制物品罪</t>
         </is>
       </c>
       <c r="C484" s="34">
@@ -16064,12 +16064,12 @@
     <row r="485">
       <c r="A485" s="34" t="inlineStr">
         <is>
-          <t>送毒品</t>
+          <t>制毒</t>
         </is>
       </c>
       <c r="B485" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖管制物品罪</t>
+          <t>非法制造管制物品罪</t>
         </is>
       </c>
       <c r="C485" s="34">
@@ -16088,12 +16088,12 @@
     <row r="486">
       <c r="A486" s="34" t="inlineStr">
         <is>
-          <t>倒卖毒品</t>
+          <t>生产毒品</t>
         </is>
       </c>
       <c r="B486" s="34" t="inlineStr">
         <is>
-          <t>非法贩卖管制物品罪</t>
+          <t>非法制造管制物品罪</t>
         </is>
       </c>
       <c r="C486" s="34">
@@ -16112,12 +16112,12 @@
     <row r="487">
       <c r="A487" s="34" t="inlineStr">
         <is>
-          <t>有组织犯罪</t>
+          <t>种植大麻</t>
         </is>
       </c>
       <c r="B487" s="34" t="inlineStr">
         <is>
-          <t>有组织犯罪</t>
+          <t>非法制造管制物品罪</t>
         </is>
       </c>
       <c r="C487" s="34">
@@ -16136,12 +16136,12 @@
     <row r="488">
       <c r="A488" s="34" t="inlineStr">
         <is>
-          <t>团伙犯罪</t>
+          <t>制造毒品</t>
         </is>
       </c>
       <c r="B488" s="34" t="inlineStr">
         <is>
-          <t>有组织犯罪</t>
+          <t>非法制造管制物品罪</t>
         </is>
       </c>
       <c r="C488" s="34">
@@ -16160,12 +16160,12 @@
     <row r="489">
       <c r="A489" s="34" t="inlineStr">
         <is>
-          <t>黑帮犯罪</t>
+          <t>种大麻</t>
         </is>
       </c>
       <c r="B489" s="34" t="inlineStr">
         <is>
-          <t>有组织犯罪</t>
+          <t>非法制造管制物品罪</t>
         </is>
       </c>
       <c r="C489" s="34">
@@ -16184,12 +16184,12 @@
     <row r="490">
       <c r="A490" s="34" t="inlineStr">
         <is>
-          <t>犯罪集团</t>
+          <t>煮毒</t>
         </is>
       </c>
       <c r="B490" s="34" t="inlineStr">
         <is>
-          <t>有组织犯罪</t>
+          <t>非法制造管制物品罪</t>
         </is>
       </c>
       <c r="C490" s="34">
@@ -16208,12 +16208,12 @@
     <row r="491">
       <c r="A491" s="34" t="inlineStr">
         <is>
-          <t>帮派作案</t>
+          <t>贩卖管制物品</t>
         </is>
       </c>
       <c r="B491" s="34" t="inlineStr">
         <is>
-          <t>有组织犯罪</t>
+          <t>非法贩卖管制物品罪</t>
         </is>
       </c>
       <c r="C491" s="34">
@@ -16232,12 +16232,12 @@
     <row r="492">
       <c r="A492" s="34" t="inlineStr">
         <is>
-          <t>团伙作案</t>
+          <t>贩毒</t>
         </is>
       </c>
       <c r="B492" s="34" t="inlineStr">
         <is>
-          <t>有组织犯罪</t>
+          <t>非法贩卖管制物品罪</t>
         </is>
       </c>
       <c r="C492" s="34">
@@ -16256,12 +16256,12 @@
     <row r="493">
       <c r="A493" s="34" t="inlineStr">
         <is>
-          <t>洗钱</t>
+          <t>卖毒品</t>
         </is>
       </c>
       <c r="B493" s="34" t="inlineStr">
         <is>
-          <t>洗钱罪</t>
+          <t>非法贩卖管制物品罪</t>
         </is>
       </c>
       <c r="C493" s="34">
@@ -16280,12 +16280,12 @@
     <row r="494">
       <c r="A494" s="34" t="inlineStr">
         <is>
-          <t>转移赃款</t>
+          <t>运输毒品</t>
         </is>
       </c>
       <c r="B494" s="34" t="inlineStr">
         <is>
-          <t>洗钱罪</t>
+          <t>非法贩卖管制物品罪</t>
         </is>
       </c>
       <c r="C494" s="34">
@@ -16304,12 +16304,12 @@
     <row r="495">
       <c r="A495" s="34" t="inlineStr">
         <is>
-          <t>清洗黑钱</t>
+          <t>贩卖毒品</t>
         </is>
       </c>
       <c r="B495" s="34" t="inlineStr">
         <is>
-          <t>洗钱罪</t>
+          <t>非法贩卖管制物品罪</t>
         </is>
       </c>
       <c r="C495" s="34">
@@ -16328,12 +16328,12 @@
     <row r="496">
       <c r="A496" s="34" t="inlineStr">
         <is>
-          <t>标记钞票</t>
+          <t>运毒</t>
         </is>
       </c>
       <c r="B496" s="34" t="inlineStr">
         <is>
-          <t>洗钱罪</t>
+          <t>非法贩卖管制物品罪</t>
         </is>
       </c>
       <c r="C496" s="34">
@@ -16352,12 +16352,12 @@
     <row r="497">
       <c r="A497" s="34" t="inlineStr">
         <is>
-          <t>漂白黑钱</t>
+          <t>送毒品</t>
         </is>
       </c>
       <c r="B497" s="34" t="inlineStr">
         <is>
-          <t>洗钱罪</t>
+          <t>非法贩卖管制物品罪</t>
         </is>
       </c>
       <c r="C497" s="34">
@@ -16376,12 +16376,12 @@
     <row r="498">
       <c r="A498" s="34" t="inlineStr">
         <is>
-          <t>洗黑钱</t>
+          <t>倒卖毒品</t>
         </is>
       </c>
       <c r="B498" s="34" t="inlineStr">
         <is>
-          <t>洗钱罪</t>
+          <t>非法贩卖管制物品罪</t>
         </is>
       </c>
       <c r="C498" s="34">
@@ -16400,12 +16400,12 @@
     <row r="499">
       <c r="A499" s="34" t="inlineStr">
         <is>
-          <t>身份盗用</t>
+          <t>有组织犯罪</t>
         </is>
       </c>
       <c r="B499" s="34" t="inlineStr">
         <is>
-          <t>身份盗用罪</t>
+          <t>有组织犯罪</t>
         </is>
       </c>
       <c r="C499" s="34">
@@ -16424,12 +16424,12 @@
     <row r="500">
       <c r="A500" s="34" t="inlineStr">
         <is>
-          <t>盗用身份</t>
+          <t>团伙犯罪</t>
         </is>
       </c>
       <c r="B500" s="34" t="inlineStr">
         <is>
-          <t>身份盗用罪</t>
+          <t>有组织犯罪</t>
         </is>
       </c>
       <c r="C500" s="34">
@@ -16448,12 +16448,12 @@
     <row r="501">
       <c r="A501" s="34" t="inlineStr">
         <is>
-          <t>冒用身份</t>
+          <t>黑帮犯罪</t>
         </is>
       </c>
       <c r="B501" s="34" t="inlineStr">
         <is>
-          <t>身份盗用罪</t>
+          <t>有组织犯罪</t>
         </is>
       </c>
       <c r="C501" s="34">
@@ -16472,12 +16472,12 @@
     <row r="502">
       <c r="A502" s="34" t="inlineStr">
         <is>
-          <t>盗用个人信息</t>
+          <t>犯罪集团</t>
         </is>
       </c>
       <c r="B502" s="34" t="inlineStr">
         <is>
-          <t>身份盗用罪</t>
+          <t>有组织犯罪</t>
         </is>
       </c>
       <c r="C502" s="34">
@@ -16496,12 +16496,12 @@
     <row r="503">
       <c r="A503" s="34" t="inlineStr">
         <is>
-          <t>盗用银行账号</t>
+          <t>帮派作案</t>
         </is>
       </c>
       <c r="B503" s="34" t="inlineStr">
         <is>
-          <t>身份盗用罪</t>
+          <t>有组织犯罪</t>
         </is>
       </c>
       <c r="C503" s="34">
@@ -16520,12 +16520,12 @@
     <row r="504">
       <c r="A504" s="34" t="inlineStr">
         <is>
-          <t>冒用他人信息</t>
+          <t>团伙作案</t>
         </is>
       </c>
       <c r="B504" s="34" t="inlineStr">
         <is>
-          <t>身份盗用罪</t>
+          <t>有组织犯罪</t>
         </is>
       </c>
       <c r="C504" s="34">
@@ -16538,6 +16538,294 @@
       </c>
       <c r="E504" s="34">
         <f>IF(AND($A503&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A503,'算罪台'!$B$6))),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="34" t="inlineStr">
+        <is>
+          <t>洗钱</t>
+        </is>
+      </c>
+      <c r="B505" s="34" t="inlineStr">
+        <is>
+          <t>洗钱罪</t>
+        </is>
+      </c>
+      <c r="C505" s="34">
+        <f>IF(AND($A504&lt;&gt;"",'算罪台'!$B$4&lt;&gt;"",ISNUMBER(SEARCH($A504,'算罪台'!$B$4))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D505" s="34">
+        <f>IF(AND($A504&lt;&gt;"",'算罪台'!$B$5&lt;&gt;"",ISNUMBER(SEARCH($A504,'算罪台'!$B$5))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E505" s="34">
+        <f>IF(AND($A504&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A504,'算罪台'!$B$6))),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="34" t="inlineStr">
+        <is>
+          <t>转移赃款</t>
+        </is>
+      </c>
+      <c r="B506" s="34" t="inlineStr">
+        <is>
+          <t>洗钱罪</t>
+        </is>
+      </c>
+      <c r="C506" s="34">
+        <f>IF(AND($A505&lt;&gt;"",'算罪台'!$B$4&lt;&gt;"",ISNUMBER(SEARCH($A505,'算罪台'!$B$4))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D506" s="34">
+        <f>IF(AND($A505&lt;&gt;"",'算罪台'!$B$5&lt;&gt;"",ISNUMBER(SEARCH($A505,'算罪台'!$B$5))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E506" s="34">
+        <f>IF(AND($A505&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A505,'算罪台'!$B$6))),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="34" t="inlineStr">
+        <is>
+          <t>清洗黑钱</t>
+        </is>
+      </c>
+      <c r="B507" s="34" t="inlineStr">
+        <is>
+          <t>洗钱罪</t>
+        </is>
+      </c>
+      <c r="C507" s="34">
+        <f>IF(AND($A506&lt;&gt;"",'算罪台'!$B$4&lt;&gt;"",ISNUMBER(SEARCH($A506,'算罪台'!$B$4))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D507" s="34">
+        <f>IF(AND($A506&lt;&gt;"",'算罪台'!$B$5&lt;&gt;"",ISNUMBER(SEARCH($A506,'算罪台'!$B$5))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E507" s="34">
+        <f>IF(AND($A506&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A506,'算罪台'!$B$6))),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="34" t="inlineStr">
+        <is>
+          <t>标记钞票</t>
+        </is>
+      </c>
+      <c r="B508" s="34" t="inlineStr">
+        <is>
+          <t>洗钱罪</t>
+        </is>
+      </c>
+      <c r="C508" s="34">
+        <f>IF(AND($A507&lt;&gt;"",'算罪台'!$B$4&lt;&gt;"",ISNUMBER(SEARCH($A507,'算罪台'!$B$4))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D508" s="34">
+        <f>IF(AND($A507&lt;&gt;"",'算罪台'!$B$5&lt;&gt;"",ISNUMBER(SEARCH($A507,'算罪台'!$B$5))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E508" s="34">
+        <f>IF(AND($A507&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A507,'算罪台'!$B$6))),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="34" t="inlineStr">
+        <is>
+          <t>漂白黑钱</t>
+        </is>
+      </c>
+      <c r="B509" s="34" t="inlineStr">
+        <is>
+          <t>洗钱罪</t>
+        </is>
+      </c>
+      <c r="C509" s="34">
+        <f>IF(AND($A508&lt;&gt;"",'算罪台'!$B$4&lt;&gt;"",ISNUMBER(SEARCH($A508,'算罪台'!$B$4))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D509" s="34">
+        <f>IF(AND($A508&lt;&gt;"",'算罪台'!$B$5&lt;&gt;"",ISNUMBER(SEARCH($A508,'算罪台'!$B$5))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E509" s="34">
+        <f>IF(AND($A508&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A508,'算罪台'!$B$6))),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="34" t="inlineStr">
+        <is>
+          <t>洗黑钱</t>
+        </is>
+      </c>
+      <c r="B510" s="34" t="inlineStr">
+        <is>
+          <t>洗钱罪</t>
+        </is>
+      </c>
+      <c r="C510" s="34">
+        <f>IF(AND($A509&lt;&gt;"",'算罪台'!$B$4&lt;&gt;"",ISNUMBER(SEARCH($A509,'算罪台'!$B$4))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D510" s="34">
+        <f>IF(AND($A509&lt;&gt;"",'算罪台'!$B$5&lt;&gt;"",ISNUMBER(SEARCH($A509,'算罪台'!$B$5))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E510" s="34">
+        <f>IF(AND($A509&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A509,'算罪台'!$B$6))),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="34" t="inlineStr">
+        <is>
+          <t>身份盗用</t>
+        </is>
+      </c>
+      <c r="B511" s="34" t="inlineStr">
+        <is>
+          <t>身份盗用罪</t>
+        </is>
+      </c>
+      <c r="C511" s="34">
+        <f>IF(AND($A510&lt;&gt;"",'算罪台'!$B$4&lt;&gt;"",ISNUMBER(SEARCH($A510,'算罪台'!$B$4))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D511" s="34">
+        <f>IF(AND($A510&lt;&gt;"",'算罪台'!$B$5&lt;&gt;"",ISNUMBER(SEARCH($A510,'算罪台'!$B$5))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E511" s="34">
+        <f>IF(AND($A510&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A510,'算罪台'!$B$6))),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="34" t="inlineStr">
+        <is>
+          <t>盗用身份</t>
+        </is>
+      </c>
+      <c r="B512" s="34" t="inlineStr">
+        <is>
+          <t>身份盗用罪</t>
+        </is>
+      </c>
+      <c r="C512" s="34">
+        <f>IF(AND($A511&lt;&gt;"",'算罪台'!$B$4&lt;&gt;"",ISNUMBER(SEARCH($A511,'算罪台'!$B$4))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D512" s="34">
+        <f>IF(AND($A511&lt;&gt;"",'算罪台'!$B$5&lt;&gt;"",ISNUMBER(SEARCH($A511,'算罪台'!$B$5))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E512" s="34">
+        <f>IF(AND($A511&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A511,'算罪台'!$B$6))),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="34" t="inlineStr">
+        <is>
+          <t>冒用身份</t>
+        </is>
+      </c>
+      <c r="B513" s="34" t="inlineStr">
+        <is>
+          <t>身份盗用罪</t>
+        </is>
+      </c>
+      <c r="C513" s="34">
+        <f>IF(AND($A512&lt;&gt;"",'算罪台'!$B$4&lt;&gt;"",ISNUMBER(SEARCH($A512,'算罪台'!$B$4))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D513" s="34">
+        <f>IF(AND($A512&lt;&gt;"",'算罪台'!$B$5&lt;&gt;"",ISNUMBER(SEARCH($A512,'算罪台'!$B$5))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E513" s="34">
+        <f>IF(AND($A512&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A512,'算罪台'!$B$6))),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="34" t="inlineStr">
+        <is>
+          <t>盗用个人信息</t>
+        </is>
+      </c>
+      <c r="B514" s="34" t="inlineStr">
+        <is>
+          <t>身份盗用罪</t>
+        </is>
+      </c>
+      <c r="C514" s="34">
+        <f>IF(AND($A513&lt;&gt;"",'算罪台'!$B$4&lt;&gt;"",ISNUMBER(SEARCH($A513,'算罪台'!$B$4))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D514" s="34">
+        <f>IF(AND($A513&lt;&gt;"",'算罪台'!$B$5&lt;&gt;"",ISNUMBER(SEARCH($A513,'算罪台'!$B$5))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E514" s="34">
+        <f>IF(AND($A513&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A513,'算罪台'!$B$6))),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="34" t="inlineStr">
+        <is>
+          <t>盗用银行账号</t>
+        </is>
+      </c>
+      <c r="B515" s="34" t="inlineStr">
+        <is>
+          <t>身份盗用罪</t>
+        </is>
+      </c>
+      <c r="C515" s="34">
+        <f>IF(AND($A514&lt;&gt;"",'算罪台'!$B$4&lt;&gt;"",ISNUMBER(SEARCH($A514,'算罪台'!$B$4))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D515" s="34">
+        <f>IF(AND($A514&lt;&gt;"",'算罪台'!$B$5&lt;&gt;"",ISNUMBER(SEARCH($A514,'算罪台'!$B$5))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E515" s="34">
+        <f>IF(AND($A514&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A514,'算罪台'!$B$6))),1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="34" t="inlineStr">
+        <is>
+          <t>冒用他人信息</t>
+        </is>
+      </c>
+      <c r="B516" s="34" t="inlineStr">
+        <is>
+          <t>身份盗用罪</t>
+        </is>
+      </c>
+      <c r="C516" s="34">
+        <f>IF(AND($A515&lt;&gt;"",'算罪台'!$B$4&lt;&gt;"",ISNUMBER(SEARCH($A515,'算罪台'!$B$4))),1,0)</f>
+        <v/>
+      </c>
+      <c r="D516" s="34">
+        <f>IF(AND($A515&lt;&gt;"",'算罪台'!$B$5&lt;&gt;"",ISNUMBER(SEARCH($A515,'算罪台'!$B$5))),1,0)</f>
+        <v/>
+      </c>
+      <c r="E516" s="34">
+        <f>IF(AND($A515&lt;&gt;"",'算罪台'!$B$6&lt;&gt;"",ISNUMBER(SEARCH($A515,'算罪台'!$B$6))),1,0)</f>
         <v/>
       </c>
     </row>

--- a/fivem_case_analyzer/圣安地列斯州_案件罪名分析器.xlsx
+++ b/fivem_case_analyzer/圣安地列斯州_案件罪名分析器.xlsx
@@ -11,6 +11,8 @@
     <sheet name="算罪台" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="罪名表" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="关键词库" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="医疗费用计算器" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="规章速查" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -87,6 +89,38 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002C4A7C"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C0392B"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <color rgb="008A6D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3A5F"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="15"/>
     </font>
     <font>
@@ -95,7 +129,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -162,6 +196,21 @@
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C9A227"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F5FA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -207,13 +256,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -298,6 +347,40 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="17" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -35219,4 +35302,1000 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="37" t="inlineStr">
+        <is>
+          <t>🚑 医疗费用计算器</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="n"/>
+      <c r="C1" s="6" t="n"/>
+      <c r="D1" s="6" t="n"/>
+      <c r="E1" s="6" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>在「数量」列填数字 → 自动算总价（来源：小首尔国际医疗中心 价格表）</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="38" t="inlineStr">
+        <is>
+          <t>💴 本次合计 ($)</t>
+        </is>
+      </c>
+      <c r="B3" s="39" t="n"/>
+      <c r="C3" s="40" t="n"/>
+      <c r="D3" s="41">
+        <f>SUM(D5:D30)</f>
+        <v/>
+      </c>
+      <c r="E3" s="42" t="inlineStr">
+        <is>
+          <t>↙ 在下面各项填数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>单价($)</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>小计($)</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>▍ 物品</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="44" t="inlineStr">
+        <is>
+          <t>民用医疗包</t>
+        </is>
+      </c>
+      <c r="B6" s="45" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C6" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="45">
+        <f>B6*C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="47" t="inlineStr">
+        <is>
+          <t>对外出售</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="44" t="inlineStr">
+        <is>
+          <t>感冒药</t>
+        </is>
+      </c>
+      <c r="B7" s="45" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="45">
+        <f>B7*C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="47" t="inlineStr">
+        <is>
+          <t>病人感冒使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="44" t="inlineStr">
+        <is>
+          <t>退烧药</t>
+        </is>
+      </c>
+      <c r="B8" s="45" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C8" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="45">
+        <f>B8*C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="47" t="inlineStr">
+        <is>
+          <t>感冒药</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="44" t="inlineStr">
+        <is>
+          <t>肺炎特效药</t>
+        </is>
+      </c>
+      <c r="B9" s="45" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="45">
+        <f>B9*C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="47" t="inlineStr">
+        <is>
+          <t>病人肺炎使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="44" t="inlineStr">
+        <is>
+          <t>口罩</t>
+        </is>
+      </c>
+      <c r="B10" s="45" t="n">
+        <v>600</v>
+      </c>
+      <c r="C10" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="45">
+        <f>B10*C10</f>
+        <v/>
+      </c>
+      <c r="E10" s="47" t="inlineStr">
+        <is>
+          <t>预防病毒</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="44" t="inlineStr">
+        <is>
+          <t>拐杖</t>
+        </is>
+      </c>
+      <c r="B11" s="45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C11" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="45">
+        <f>B11*C11</f>
+        <v/>
+      </c>
+      <c r="E11" s="47" t="inlineStr">
+        <is>
+          <t>单腿骨折 / 断裂式骨折</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="44" t="inlineStr">
+        <is>
+          <t>轮椅</t>
+        </is>
+      </c>
+      <c r="B12" s="45" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C12" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="45">
+        <f>B12*C12</f>
+        <v/>
+      </c>
+      <c r="E12" s="47" t="inlineStr">
+        <is>
+          <t>双腿骨折 / 断裂式骨折</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="44" t="inlineStr">
+        <is>
+          <t>整容</t>
+        </is>
+      </c>
+      <c r="B13" s="45" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C13" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="45">
+        <f>B13*C13</f>
+        <v/>
+      </c>
+      <c r="E13" s="47" t="inlineStr">
+        <is>
+          <t>新市民第一次不收费</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>▍ 手术</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="44" t="inlineStr">
+        <is>
+          <t>轻伤手术</t>
+        </is>
+      </c>
+      <c r="B15" s="45" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C15" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="45">
+        <f>B15*C15</f>
+        <v/>
+      </c>
+      <c r="E15" s="47" t="inlineStr">
+        <is>
+          <t>挫伤 / 轻微刀伤 / 击打伤</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="44" t="inlineStr">
+        <is>
+          <t>中伤手术</t>
+        </is>
+      </c>
+      <c r="B16" s="45" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C16" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="45">
+        <f>B16*C16</f>
+        <v/>
+      </c>
+      <c r="E16" s="47" t="inlineStr">
+        <is>
+          <t>脑震荡 / 昏厥 / 中度刀伤</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="44" t="inlineStr">
+        <is>
+          <t>重伤手术</t>
+        </is>
+      </c>
+      <c r="B17" s="45" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C17" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="45">
+        <f>B17*C17</f>
+        <v/>
+      </c>
+      <c r="E17" s="47" t="inlineStr">
+        <is>
+          <t>骨折 / 枪伤 / 大出血</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="44" t="inlineStr">
+        <is>
+          <t>死亡火化</t>
+        </is>
+      </c>
+      <c r="B18" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="45">
+        <f>B18*C18</f>
+        <v/>
+      </c>
+      <c r="E18" s="47" t="inlineStr">
+        <is>
+          <t>现场验伤</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="43" t="inlineStr">
+        <is>
+          <t>▍ 住院</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="44" t="inlineStr">
+        <is>
+          <t>普通病房</t>
+        </is>
+      </c>
+      <c r="B20" s="45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C20" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="45">
+        <f>B20*C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="47" t="inlineStr">
+        <is>
+          <t>脑震荡 / 轻微刀伤</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="44" t="inlineStr">
+        <is>
+          <t>重症病房</t>
+        </is>
+      </c>
+      <c r="B21" s="45" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C21" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="45">
+        <f>B21*C21</f>
+        <v/>
+      </c>
+      <c r="E21" s="47" t="inlineStr">
+        <is>
+          <t>枪伤 / 骨折 / 大出血</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="44" t="inlineStr">
+        <is>
+          <t>ICU 病房</t>
+        </is>
+      </c>
+      <c r="B22" s="45" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C22" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="45">
+        <f>B22*C22</f>
+        <v/>
+      </c>
+      <c r="E22" s="47" t="inlineStr">
+        <is>
+          <t>重度枪伤 / 刀伤 / 头部重创</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="43" t="inlineStr">
+        <is>
+          <t>▍ 救护车出车</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="44" t="inlineStr">
+        <is>
+          <t>市内出车</t>
+        </is>
+      </c>
+      <c r="B24" s="45" t="n">
+        <v>300</v>
+      </c>
+      <c r="C24" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="45">
+        <f>B24*C24</f>
+        <v/>
+      </c>
+      <c r="E24" s="47" t="inlineStr">
+        <is>
+          <t>大探 / 萨博班 / 道奇战马</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="44" t="inlineStr">
+        <is>
+          <t>中部出车</t>
+        </is>
+      </c>
+      <c r="B25" s="45" t="n">
+        <v>500</v>
+      </c>
+      <c r="C25" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="45">
+        <f>B25*C25</f>
+        <v/>
+      </c>
+      <c r="E25" s="47" t="inlineStr"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="44" t="inlineStr">
+        <is>
+          <t>北部出车</t>
+        </is>
+      </c>
+      <c r="B26" s="45" t="n">
+        <v>700</v>
+      </c>
+      <c r="C26" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="45">
+        <f>B26*C26</f>
+        <v/>
+      </c>
+      <c r="E26" s="47" t="inlineStr">
+        <is>
+          <t>可开越野车</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="43" t="inlineStr">
+        <is>
+          <t>▍ 直升机出车</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="44" t="inlineStr">
+        <is>
+          <t>市内直升机</t>
+        </is>
+      </c>
+      <c r="B28" s="45" t="n">
+        <v>600</v>
+      </c>
+      <c r="C28" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="45">
+        <f>B28*C28</f>
+        <v/>
+      </c>
+      <c r="E28" s="47" t="inlineStr">
+        <is>
+          <t>仅港口区域可用</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="44" t="inlineStr">
+        <is>
+          <t>中部直升机</t>
+        </is>
+      </c>
+      <c r="B29" s="45" t="n">
+        <v>800</v>
+      </c>
+      <c r="C29" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="45">
+        <f>B29*C29</f>
+        <v/>
+      </c>
+      <c r="E29" s="47" t="inlineStr"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="44" t="inlineStr">
+        <is>
+          <t>北部直升机</t>
+        </is>
+      </c>
+      <c r="B30" s="45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C30" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="45">
+        <f>B30*C30</f>
+        <v/>
+      </c>
+      <c r="E30" s="47" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="n"/>
+      <c r="B31" s="15" t="n"/>
+      <c r="C31" s="15" t="n"/>
+      <c r="D31" s="15" t="n"/>
+      <c r="E31" s="15" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　⚠ 开车救援单人最高收 $6,700；直升机救援单人最高 $7,000（出售其他药品另计）。</t>
+        </is>
+      </c>
+      <c r="B32" s="49" t="n"/>
+      <c r="C32" s="49" t="n"/>
+      <c r="D32" s="49" t="n"/>
+      <c r="E32" s="49" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　⚠ 手术费如由医护车辆带回，需额外加收出车费（PD 免出车费）。</t>
+        </is>
+      </c>
+      <c r="B33" s="49" t="n"/>
+      <c r="C33" s="49" t="n"/>
+      <c r="D33" s="49" t="n"/>
+      <c r="E33" s="49" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　⚠ 不得以任何理由拒绝住院；乱收费 / 不开账单 / 收私钱 → 核实降级，多次开除。</t>
+        </is>
+      </c>
+      <c r="B34" s="49" t="n"/>
+      <c r="C34" s="49" t="n"/>
+      <c r="D34" s="49" t="n"/>
+      <c r="E34" s="49" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="n"/>
+      <c r="B35" s="15" t="n"/>
+      <c r="C35" s="15" t="n"/>
+      <c r="D35" s="15" t="n"/>
+      <c r="E35" s="15" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">原创制作：袁尘　</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="n"/>
+      <c r="C36" s="15" t="n"/>
+      <c r="D36" s="15" t="n"/>
+      <c r="E36" s="15" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="15" t="n"/>
+      <c r="B37" s="15" t="n"/>
+      <c r="C37" s="15" t="n"/>
+      <c r="D37" s="15" t="n"/>
+      <c r="E37" s="15" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="n"/>
+      <c r="B38" s="15" t="n"/>
+      <c r="C38" s="15" t="n"/>
+      <c r="D38" s="15" t="n"/>
+      <c r="E38" s="15" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="n"/>
+      <c r="B39" s="15" t="n"/>
+      <c r="C39" s="15" t="n"/>
+      <c r="D39" s="15" t="n"/>
+      <c r="E39" s="15" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="n"/>
+      <c r="B40" s="15" t="n"/>
+      <c r="C40" s="15" t="n"/>
+      <c r="D40" s="15" t="n"/>
+      <c r="E40" s="15" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="E3"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="96" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="37" t="inlineStr">
+        <is>
+          <t>📖 规章速查（警务 / 医护）</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>以下为规章/手册里的关键规则与「内务处分」要点（对警员/医护，非市民算罪）。可按 Ctrl+F 搜索</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　🛡 警务 · 武力等级条例</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="50" t="inlineStr">
+        <is>
+          <t>一级 · 非致命</t>
+        </is>
+      </c>
+      <c r="B4" s="33" t="inlineStr">
+        <is>
+          <t>口头警告（表明身份）、徒手制服（奔跑 G 神经扑倒）。对象对周围个人/财产产生威胁时即可徒手制服。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="50" t="inlineStr">
+        <is>
+          <t>二级 · 低致命</t>
+        </is>
+      </c>
+      <c r="B5" s="33" t="inlineStr">
+        <is>
+          <t>嫌犯持管制刀具、对警员/市民造成生命威胁时：使用警棍、电击枪、豆袋枪（请勿射击头部）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="50" t="inlineStr">
+        <is>
+          <t>三级 · 致命</t>
+        </is>
+      </c>
+      <c r="B6" s="33" t="inlineStr">
+        <is>
+          <t>嫌犯持热武器展示/开火、重大绑架案/抢劫案、帮派案件中可用致命武器：格洛克22、UPR步枪(AR-15)、TSG霰弹枪(M870)。错误使用致命武器将受内务组调查。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　⚖ 警务 · 内务处分阶梯（对警员，由轻到重）</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n"/>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="50" t="inlineStr">
+        <is>
+          <t>处分等级</t>
+        </is>
+      </c>
+      <c r="B8" s="33" t="inlineStr">
+        <is>
+          <t>① 无处分/口头警告 → ② 正式处分 → ③ 停职1天 → ④ 停职2天 → ⑤ 停职3天 → ⑥ 降级/降职 → ⑦ 终止雇佣（开除警籍）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="50" t="inlineStr">
+        <is>
+          <t>调查期间</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>受内务调查期间属行政休假：无执法权、无警械使用权、无警车使用权。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="50" t="inlineStr">
+        <is>
+          <t>警械流出</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>贩卖/赠送警械违反联邦法 → 可能受 FBI 调查，甚至永久驱逐出境。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　📻 警务 · 常用 Code 代码</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n"/>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="50" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>2 常规(非紧急,无警灯笛)｜2-H 优先(紧急,需警灯)｜3 紧急(警灯+警笛)｜4 案件结束/无需增援｜6 离车调查｜6-A 离车调查需支援｜7 用餐休息｜99 紧急情况</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="50" t="inlineStr">
+        <is>
+          <t>10-Code</t>
+        </is>
+      </c>
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>10-41 开始执勤｜10-42 结束执勤(出国)｜10-41 10-8 正常状态(请求调度)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　📢 警务 · 米兰达宣言（逮捕时宣读）</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n"/>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="50" t="inlineStr">
+        <is>
+          <t>宣读词</t>
+        </is>
+      </c>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>“您现在因涉嫌 XX 罪名而被我们逮捕。你有权保持沉默，但你所说的每一句话都将成为呈堂证供。你有权聘请律师，如果没有条件，我们会为你指派一名公派律师。以上权利你是否清楚？”</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="50" t="inlineStr">
+        <is>
+          <t>程序</t>
+        </is>
+      </c>
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>若无正面回应需重读，连续共计 3 次后可停止并继续程序。须全程开启执法记录仪；若未完整宣读或未记录，嫌犯可要求无罪释放。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="50" t="inlineStr">
+        <is>
+          <t>莱伯格条例(高层)</t>
+        </is>
+      </c>
+      <c r="B17" s="33" t="inlineStr">
+        <is>
+          <t>“你没有权力保持沉默，你所说的一切都会成为呈堂证供，拒绝完整回答我的所有问题会导致你立即被解雇，并转交内务调查组起诉，你清楚了吗？”</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　👮 警务 · 警衔（高 → 低）</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n"/>
+    </row>
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="50" t="inlineStr">
+        <is>
+          <t>警衔顺序</t>
+        </is>
+      </c>
+      <c r="B19" s="33" t="inlineStr">
+        <is>
+          <t>局长(总警监) → 助理局长/二级副警司 → 副局长(一级副总警监) → 警长(Commander) → 警监(Captain) → 警督(Lieutenant) → 二级警司 → 一级警司 → 三/二/一级警探 → 高级警员 → 三级警员 → 一/二级警员</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　🚑 医护 · 上班守则要点</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n"/>
+    </row>
+    <row r="21" ht="46" customHeight="1">
+      <c r="A21" s="50" t="inlineStr">
+        <is>
+          <t>守则</t>
+        </is>
+      </c>
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>上班穿工服、开救护车（禁开私家车）、KOOK 打卡与药品报备；救援须开警灯警笛；不介入警匪/玩家/帮派纠纷；遇交战或有人开枪立即撤离保命；到点及返院须锁车；不得拒绝住院。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　⚖ 医护 · 内务处分</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="n"/>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="50" t="inlineStr">
+        <is>
+          <t>私搜患者</t>
+        </is>
+      </c>
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>私自搜查/拿取患者背包、物资、枪械：第一次内务警告，第二次直接开除。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="50" t="inlineStr">
+        <is>
+          <t>乱收费</t>
+        </is>
+      </c>
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>乱收费 / 不开账单 / 收私钱：核查属实降级，多次现象 → 开除。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="50" t="inlineStr">
+        <is>
+          <t>违法乱纪</t>
+        </is>
+      </c>
+      <c r="B25" s="33" t="inlineStr">
+        <is>
+          <t>采集毒品/抢劫/殴打玩家等有损形象行为（无论上下班）：视情节承担，严重者直接开除。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">原创整理：袁尘　</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A22:B22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/fivem_case_analyzer/圣安地列斯州_案件罪名分析器.xlsx
+++ b/fivem_case_analyzer/圣安地列斯州_案件罪名分析器.xlsx
@@ -895,14 +895,14 @@
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>数罪叠加、罚款累计；总刑期最高 5 年(60 个月)，同一罪名不重复并罚。</t>
+          <t>数罪叠加、罚款累计；总刑期最高 5 年，同一罪名不重复并罚。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>建议保释金 = 刑期(月) × 罚款 ÷ 6（法典第九章·保释）。</t>
+          <t>建议保释金 = 刑期(年) × 罚款 ÷ 6（法典第九章·保释）。</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>合计刑期(月)</t>
+          <t>合计刑期(年)</t>
         </is>
       </c>
       <c r="E9" s="16" t="inlineStr">
@@ -1145,7 +1145,7 @@
         <v/>
       </c>
       <c r="D10" s="20">
-        <f>MIN(60,SUMIF('罪名表'!$G$2:$G$109,1,'罪名表'!$D$2:$D$109))</f>
+        <f>MIN(5,SUMIF('罪名表'!$G$2:$G$109,1,'罪名表'!$D$2:$D$109))</f>
         <v/>
       </c>
       <c r="E10" s="21">
@@ -1172,7 +1172,7 @@
         <v/>
       </c>
       <c r="D11" s="20">
-        <f>MIN(60,SUMIF('罪名表'!$H$2:$H$109,1,'罪名表'!$D$2:$D$109))</f>
+        <f>MIN(5,SUMIF('罪名表'!$H$2:$H$109,1,'罪名表'!$D$2:$D$109))</f>
         <v/>
       </c>
       <c r="E11" s="21">
@@ -1199,7 +1199,7 @@
         <v/>
       </c>
       <c r="D12" s="20">
-        <f>MIN(60,SUMIF('罪名表'!$I$2:$I$109,1,'罪名表'!$D$2:$D$109))</f>
+        <f>MIN(5,SUMIF('罪名表'!$I$2:$I$109,1,'罪名表'!$D$2:$D$109))</f>
         <v/>
       </c>
       <c r="E12" s="21">
@@ -1221,7 +1221,7 @@
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="25">
-        <f>IF(MAX(D10,D11,D12)=0,"⚠ 还没识别到罪名：在上面把案情写得更具体些，或去「关键词库」补充说法。","🔨 主要责任方：当事人"&amp;IF(D10=MAX(D10,D11,D12),"甲",IF(D11=MAX(D10,D11,D12),"乙","丙"))&amp;"　|　合计刑期 "&amp;MAX(D10,D11,D12)&amp;" 个月（"&amp;ROUND(MAX(D10,D11,D12)/12,1)&amp;" 年）"&amp;"　|　仅供参考，正当防卫 / 堡垒原则 / 同类不并罚等请人工复核")</f>
+        <f>IF(MAX(D10,D11,D12)=0,"⚠ 还没识别到罪名：在上面把案情写得更具体些，或去「关键词库」补充说法。","🔨 主要责任方：当事人"&amp;IF(D10=MAX(D10,D11,D12),"甲",IF(D11=MAX(D10,D11,D12),"乙","丙"))&amp;"　|　合计刑期 "&amp;MAX(D10,D11,D12)&amp;" 年"&amp;"　|　仅供参考，正当防卫 / 堡垒原则 / 同类不并罚等请人工复核")</f>
         <v/>
       </c>
       <c r="B14" s="26" t="n"/>
@@ -1306,7 +1306,7 @@
     <row r="21" ht="34" customHeight="1">
       <c r="A21" s="31" t="inlineStr">
         <is>
-          <t>提示 · 写得越具体识别越准（如「持枪、拒捕、开枪、撞伤、贩毒」）；保释金 = 刑期(月)×罚款÷6；刑事罪名对所有人一视同仁，职务违规只是额外加一层内务处分；识别不到的说法去「关键词库」加。</t>
+          <t>提示 · 写得越具体识别越准（如「持枪、拒捕、开枪、撞伤、贩毒」）；保释金 = 刑期(年)×罚款÷6；刑事罪名对所有人一视同仁，职务违规只是额外加一层内务处分；识别不到的说法去「关键词库」加。</t>
         </is>
       </c>
       <c r="B21" s="15" t="n"/>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="D1" s="16" t="inlineStr">
         <is>
-          <t>刑期(月)</t>
+          <t>刑期(年)</t>
         </is>
       </c>
       <c r="E1" s="16" t="inlineStr">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="D2" s="33" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E2" s="36" t="n">
         <v>8000</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="D3" s="33" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="E3" s="36" t="n">
         <v>20000</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="D4" s="33" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="E4" s="36" t="n">
         <v>30000</v>
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="D5" s="33" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="E5" s="36" t="n">
         <v>20000</v>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="D6" s="33" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>15000</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="D7" s="33" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>15000</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="D8" s="33" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>15000</v>
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="D9" s="33" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>25000</v>
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="D10" s="33" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>20000</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="D11" s="33" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>5000</v>
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="D12" s="33" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>8000</v>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="D13" s="33" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>10000</v>
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="D14" s="33" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>25000</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>20000</v>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="D16" s="33" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>20000</v>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="D17" s="33" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>5000</v>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="D18" s="33" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>10000</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="D19" s="33" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>20000</v>
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="D20" s="33" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>25000</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="D21" s="33" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>80000</v>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="D22" s="33" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E22" s="36" t="n">
         <v>2000</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="D23" s="33" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E23" s="36" t="n">
         <v>10000</v>
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="D24" s="33" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E24" s="36" t="n">
         <v>15000</v>
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="D25" s="33" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E25" s="36" t="n">
         <v>15000</v>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="D26" s="33" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="E26" s="36" t="n">
         <v>30000</v>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="D27" s="33" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E27" s="36" t="n">
         <v>8000</v>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="D28" s="33" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E28" s="36" t="n">
         <v>30000</v>
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="D29" s="33" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E29" s="36" t="n">
         <v>15000</v>
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="D30" s="33" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E30" s="36" t="n">
         <v>20000</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="D31" s="33" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E31" s="36" t="n">
         <v>15000</v>
@@ -3423,7 +3423,7 @@
         </is>
       </c>
       <c r="D32" s="33" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E32" s="36" t="n">
         <v>15000</v>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="D33" s="33" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E33" s="36" t="n">
         <v>10000</v>
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="D34" s="33" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E34" s="36" t="n">
         <v>20000</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="D35" s="33" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E35" s="36" t="n">
         <v>15000</v>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="D36" s="33" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="E36" s="36" t="n">
         <v>20000</v>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="D37" s="33" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="E37" s="36" t="n">
         <v>25000</v>
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="D38" s="33" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E38" s="36" t="n">
         <v>15000</v>
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="D39" s="33" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E39" s="36" t="n">
         <v>15000</v>
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="D40" s="33" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E40" s="36" t="n">
         <v>15000</v>
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="D41" s="33" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E41" s="36" t="n">
         <v>10000</v>
@@ -4063,7 +4063,7 @@
         </is>
       </c>
       <c r="D42" s="33" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="E42" s="36" t="n">
         <v>25000</v>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="D43" s="33" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E43" s="36" t="n">
         <v>5000</v>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="D44" s="33" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E44" s="36" t="n">
         <v>15000</v>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="D45" s="33" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="E45" s="36" t="n">
         <v>25000</v>
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="D46" s="33" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E46" s="36" t="n">
         <v>3000</v>
@@ -4383,7 +4383,7 @@
         </is>
       </c>
       <c r="D47" s="33" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E47" s="36" t="n">
         <v>5000</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="D48" s="33" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E48" s="36" t="n">
         <v>20000</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="D49" s="33" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="E49" s="36" t="n">
         <v>0</v>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="D50" s="33" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E50" s="36" t="n">
         <v>5000</v>
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="D51" s="33" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E51" s="36" t="n">
         <v>15000</v>
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="D52" s="33" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E52" s="36" t="n">
         <v>8000</v>
@@ -4767,7 +4767,7 @@
         </is>
       </c>
       <c r="D53" s="33" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E53" s="36" t="n">
         <v>15000</v>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="D54" s="33" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="E54" s="36" t="n">
         <v>25000</v>
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="D55" s="33" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="E55" s="36" t="n">
         <v>30000</v>
@@ -4959,7 +4959,7 @@
         </is>
       </c>
       <c r="D56" s="33" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="E56" s="36" t="n">
         <v>30000</v>
@@ -5023,7 +5023,7 @@
         </is>
       </c>
       <c r="D57" s="33" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E57" s="36" t="n">
         <v>6000</v>
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="D58" s="33" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E58" s="36" t="n">
         <v>5000</v>
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="D59" s="33" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E59" s="36" t="n">
         <v>8000</v>
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="D60" s="33" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E60" s="36" t="n">
         <v>10000</v>
@@ -5279,7 +5279,7 @@
         </is>
       </c>
       <c r="D61" s="33" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E61" s="36" t="n">
         <v>10000</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="D62" s="33" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="E62" s="36" t="n">
         <v>30000</v>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="D63" s="33" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E63" s="36" t="n">
         <v>8000</v>
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="D65" s="33" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E65" s="36" t="n">
         <v>4000</v>
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="D67" s="33" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E67" s="36" t="n">
         <v>10000</v>
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="D72" s="33" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E72" s="36" t="n">
         <v>5000</v>
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="D73" s="33" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E73" s="36" t="n">
         <v>5000</v>
@@ -6111,7 +6111,7 @@
         </is>
       </c>
       <c r="D74" s="33" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E74" s="36" t="n">
         <v>8000</v>
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="D75" s="33" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E75" s="36" t="n">
         <v>10000</v>
@@ -54137,7 +54137,7 @@
       </c>
       <c r="B50" s="37" t="inlineStr">
         <is>
-          <t>保释金 = 刑期(月) × 罚款 ÷ 6；赔偿：财产≥$8000、人身/精神 $5000~$80000；警局错误扣留赔偿 $500/分钟。</t>
+          <t>保释金 = 刑期(年) × 罚款 ÷ 6；赔偿：财产≥$8000、人身/精神 $5000~$80000；警局错误扣留赔偿 $500/分钟。</t>
         </is>
       </c>
     </row>
